--- a/Financial Analysis/RTX.xlsx
+++ b/Financial Analysis/RTX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE19F4BD-72A9-4214-9D65-A74F13927B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD18CDC-A799-49FD-891B-9FCAB4610D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4DC2FBA0-6E3D-459B-9C6A-21AC42B1058B}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="65">
   <si>
     <t>RTX</t>
   </si>
@@ -249,6 +249,36 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Maturity</t>
+  </si>
+  <si>
+    <t>Discount rate</t>
+  </si>
+  <si>
+    <t>NPV</t>
+  </si>
+  <si>
+    <t>Net cash</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Per share</t>
+  </si>
+  <si>
+    <t>Current price</t>
+  </si>
+  <si>
+    <t>Variance</t>
+  </si>
+  <si>
+    <t>Consensus</t>
+  </si>
+  <si>
+    <t>Heavily overvalued</t>
   </si>
 </sst>
 </file>
@@ -350,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -371,6 +401,7 @@
     <xf numFmtId="3" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -825,7 +856,7 @@
       </c>
       <c r="F3" s="10">
         <f ca="1">TODAY()</f>
-        <v>45770</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="10">
         <v>45867</v>
@@ -904,12 +935,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37BCCFEA-4609-4B74-A80E-9BDBF53DBD8A}">
-  <dimension ref="B2:AK34"/>
+  <dimension ref="B2:EE34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="19.109375" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="39" width="8.88671875" style="1"/>
+    <col min="40" max="40" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.109375" style="1" customWidth="1"/>
+    <col min="42" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:37" x14ac:dyDescent="0.3">
@@ -1053,6 +1087,50 @@
       <c r="Z3" s="3">
         <v>59612</v>
       </c>
+      <c r="AA3" s="3">
+        <f>Z3*1.07</f>
+        <v>63784.840000000004</v>
+      </c>
+      <c r="AB3" s="3">
+        <f>AA3*1.05</f>
+        <v>66974.082000000009</v>
+      </c>
+      <c r="AC3" s="3">
+        <f>AB3*1.03</f>
+        <v>68983.304460000014</v>
+      </c>
+      <c r="AD3" s="3">
+        <f>AC3*1.02</f>
+        <v>70362.970549200021</v>
+      </c>
+      <c r="AE3" s="3">
+        <f>AD3*1.01</f>
+        <v>71066.600254692021</v>
+      </c>
+      <c r="AF3" s="3">
+        <f t="shared" ref="AF3:AK3" si="0">AE3*1.01</f>
+        <v>71777.266257238938</v>
+      </c>
+      <c r="AG3" s="3">
+        <f t="shared" si="0"/>
+        <v>72495.038919811326</v>
+      </c>
+      <c r="AH3" s="3">
+        <f t="shared" si="0"/>
+        <v>73219.989309009441</v>
+      </c>
+      <c r="AI3" s="3">
+        <f t="shared" si="0"/>
+        <v>73952.189202099529</v>
+      </c>
+      <c r="AJ3" s="3">
+        <f t="shared" si="0"/>
+        <v>74691.711094120532</v>
+      </c>
+      <c r="AK3" s="3">
+        <f t="shared" si="0"/>
+        <v>75438.628205061745</v>
+      </c>
     </row>
     <row r="4" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -1094,6 +1172,50 @@
       <c r="Z4" s="3">
         <v>21126</v>
       </c>
+      <c r="AA4" s="3">
+        <f>Z4*1.08</f>
+        <v>22816.080000000002</v>
+      </c>
+      <c r="AB4" s="3">
+        <f>AA4*1.05</f>
+        <v>23956.884000000002</v>
+      </c>
+      <c r="AC4" s="3">
+        <f>AB4*1.04</f>
+        <v>24915.159360000001</v>
+      </c>
+      <c r="AD4" s="3">
+        <f>AC4*1.03</f>
+        <v>25662.614140800004</v>
+      </c>
+      <c r="AE4" s="3">
+        <f t="shared" ref="AE4:AK4" si="1">AD4*1.03</f>
+        <v>26432.492565024004</v>
+      </c>
+      <c r="AF4" s="3">
+        <f t="shared" si="1"/>
+        <v>27225.467341974723</v>
+      </c>
+      <c r="AG4" s="3">
+        <f t="shared" si="1"/>
+        <v>28042.231362233964</v>
+      </c>
+      <c r="AH4" s="3">
+        <f t="shared" si="1"/>
+        <v>28883.498303100983</v>
+      </c>
+      <c r="AI4" s="3">
+        <f t="shared" si="1"/>
+        <v>29750.003252194012</v>
+      </c>
+      <c r="AJ4" s="3">
+        <f t="shared" si="1"/>
+        <v>30642.503349759834</v>
+      </c>
+      <c r="AK4" s="3">
+        <f t="shared" si="1"/>
+        <v>31561.77845025263</v>
+      </c>
     </row>
     <row r="5" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
@@ -1124,28 +1246,72 @@
         <v>20306</v>
       </c>
       <c r="U5" s="5">
-        <f t="shared" ref="U5:Z5" si="0">U3+U4</f>
+        <f t="shared" ref="U5:AK5" si="2">U3+U4</f>
         <v>45349</v>
       </c>
       <c r="V5" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>56587</v>
       </c>
       <c r="W5" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>64388</v>
       </c>
       <c r="X5" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>67074</v>
       </c>
       <c r="Y5" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>68920</v>
       </c>
       <c r="Z5" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>80738</v>
+      </c>
+      <c r="AA5" s="5">
+        <f t="shared" si="2"/>
+        <v>86600.920000000013</v>
+      </c>
+      <c r="AB5" s="5">
+        <f t="shared" si="2"/>
+        <v>90930.966000000015</v>
+      </c>
+      <c r="AC5" s="5">
+        <f t="shared" si="2"/>
+        <v>93898.463820000019</v>
+      </c>
+      <c r="AD5" s="5">
+        <f t="shared" si="2"/>
+        <v>96025.584690000018</v>
+      </c>
+      <c r="AE5" s="5">
+        <f t="shared" si="2"/>
+        <v>97499.092819716025</v>
+      </c>
+      <c r="AF5" s="5">
+        <f t="shared" si="2"/>
+        <v>99002.733599213665</v>
+      </c>
+      <c r="AG5" s="5">
+        <f t="shared" si="2"/>
+        <v>100537.2702820453</v>
+      </c>
+      <c r="AH5" s="5">
+        <f t="shared" si="2"/>
+        <v>102103.48761211042</v>
+      </c>
+      <c r="AI5" s="5">
+        <f t="shared" si="2"/>
+        <v>103702.19245429354</v>
+      </c>
+      <c r="AJ5" s="5">
+        <f t="shared" si="2"/>
+        <v>105334.21444388037</v>
+      </c>
+      <c r="AK5" s="5">
+        <f t="shared" si="2"/>
+        <v>107000.40665531438</v>
       </c>
     </row>
     <row r="6" spans="2:37" x14ac:dyDescent="0.3">
@@ -1188,6 +1354,50 @@
       <c r="Z6" s="3">
         <v>50768</v>
       </c>
+      <c r="AA6" s="3">
+        <f>AA3*0.85</f>
+        <v>54217.114000000001</v>
+      </c>
+      <c r="AB6" s="3">
+        <f t="shared" ref="AB6:AK6" si="3">AB3*0.85</f>
+        <v>56927.969700000009</v>
+      </c>
+      <c r="AC6" s="3">
+        <f t="shared" si="3"/>
+        <v>58635.80879100001</v>
+      </c>
+      <c r="AD6" s="3">
+        <f t="shared" si="3"/>
+        <v>59808.524966820019</v>
+      </c>
+      <c r="AE6" s="3">
+        <f t="shared" si="3"/>
+        <v>60406.610216488218</v>
+      </c>
+      <c r="AF6" s="3">
+        <f t="shared" si="3"/>
+        <v>61010.676318653095</v>
+      </c>
+      <c r="AG6" s="3">
+        <f t="shared" si="3"/>
+        <v>61620.783081839625</v>
+      </c>
+      <c r="AH6" s="3">
+        <f t="shared" si="3"/>
+        <v>62236.990912658024</v>
+      </c>
+      <c r="AI6" s="3">
+        <f t="shared" si="3"/>
+        <v>62859.360821784598</v>
+      </c>
+      <c r="AJ6" s="3">
+        <f t="shared" si="3"/>
+        <v>63487.95443000245</v>
+      </c>
+      <c r="AK6" s="3">
+        <f t="shared" si="3"/>
+        <v>64122.833974302484</v>
+      </c>
     </row>
     <row r="7" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -1229,6 +1439,50 @@
       <c r="Z7" s="3">
         <v>14560</v>
       </c>
+      <c r="AA7" s="3">
+        <f>AA4*0.69</f>
+        <v>15743.0952</v>
+      </c>
+      <c r="AB7" s="3">
+        <f t="shared" ref="AB7:AK7" si="4">AB4*0.69</f>
+        <v>16530.249960000001</v>
+      </c>
+      <c r="AC7" s="3">
+        <f t="shared" si="4"/>
+        <v>17191.459958399999</v>
+      </c>
+      <c r="AD7" s="3">
+        <f t="shared" si="4"/>
+        <v>17707.203757152001</v>
+      </c>
+      <c r="AE7" s="3">
+        <f t="shared" si="4"/>
+        <v>18238.41986986656</v>
+      </c>
+      <c r="AF7" s="3">
+        <f t="shared" si="4"/>
+        <v>18785.572465962559</v>
+      </c>
+      <c r="AG7" s="3">
+        <f t="shared" si="4"/>
+        <v>19349.139639941433</v>
+      </c>
+      <c r="AH7" s="3">
+        <f t="shared" si="4"/>
+        <v>19929.613829139678</v>
+      </c>
+      <c r="AI7" s="3">
+        <f t="shared" si="4"/>
+        <v>20527.502244013867</v>
+      </c>
+      <c r="AJ7" s="3">
+        <f t="shared" si="4"/>
+        <v>21143.327311334284</v>
+      </c>
+      <c r="AK7" s="3">
+        <f t="shared" si="4"/>
+        <v>21777.627130674315</v>
+      </c>
     </row>
     <row r="8" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
@@ -1259,28 +1513,72 @@
         <v>16190</v>
       </c>
       <c r="U8" s="3">
-        <f t="shared" ref="U8:Z8" si="1">U6+U7</f>
+        <f t="shared" ref="U8:Z8" si="5">U6+U7</f>
         <v>34598</v>
       </c>
       <c r="V8" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>48056</v>
       </c>
       <c r="W8" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>51897</v>
       </c>
       <c r="X8" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>53406</v>
       </c>
       <c r="Y8" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>56831</v>
       </c>
       <c r="Z8" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>65328</v>
+      </c>
+      <c r="AA8" s="3">
+        <f t="shared" ref="AA8:AK8" si="6">AA6+AA7</f>
+        <v>69960.209199999998</v>
+      </c>
+      <c r="AB8" s="3">
+        <f t="shared" si="6"/>
+        <v>73458.219660000002</v>
+      </c>
+      <c r="AC8" s="3">
+        <f t="shared" si="6"/>
+        <v>75827.268749400013</v>
+      </c>
+      <c r="AD8" s="3">
+        <f t="shared" si="6"/>
+        <v>77515.728723972017</v>
+      </c>
+      <c r="AE8" s="3">
+        <f t="shared" si="6"/>
+        <v>78645.030086354775</v>
+      </c>
+      <c r="AF8" s="3">
+        <f t="shared" si="6"/>
+        <v>79796.248784615658</v>
+      </c>
+      <c r="AG8" s="3">
+        <f t="shared" si="6"/>
+        <v>80969.922721781055</v>
+      </c>
+      <c r="AH8" s="3">
+        <f t="shared" si="6"/>
+        <v>82166.604741797695</v>
+      </c>
+      <c r="AI8" s="3">
+        <f t="shared" si="6"/>
+        <v>83386.863065798461</v>
+      </c>
+      <c r="AJ8" s="3">
+        <f t="shared" si="6"/>
+        <v>84631.28174133673</v>
+      </c>
+      <c r="AK8" s="3">
+        <f t="shared" si="6"/>
+        <v>85900.461104976799</v>
       </c>
     </row>
     <row r="9" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1312,28 +1610,72 @@
         <v>4116</v>
       </c>
       <c r="U9" s="5">
-        <f t="shared" ref="U9:Z9" si="2">U5-U8</f>
+        <f t="shared" ref="U9:Z9" si="7">U5-U8</f>
         <v>10751</v>
       </c>
       <c r="V9" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>8531</v>
       </c>
       <c r="W9" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>12491</v>
       </c>
       <c r="X9" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>13668</v>
       </c>
       <c r="Y9" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>12089</v>
       </c>
       <c r="Z9" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>15410</v>
+      </c>
+      <c r="AA9" s="5">
+        <f t="shared" ref="AA9:AK9" si="8">AA5-AA8</f>
+        <v>16640.710800000015</v>
+      </c>
+      <c r="AB9" s="5">
+        <f t="shared" si="8"/>
+        <v>17472.746340000012</v>
+      </c>
+      <c r="AC9" s="5">
+        <f t="shared" si="8"/>
+        <v>18071.195070600006</v>
+      </c>
+      <c r="AD9" s="5">
+        <f t="shared" si="8"/>
+        <v>18509.855966028001</v>
+      </c>
+      <c r="AE9" s="5">
+        <f t="shared" si="8"/>
+        <v>18854.06273336125</v>
+      </c>
+      <c r="AF9" s="5">
+        <f t="shared" si="8"/>
+        <v>19206.484814598007</v>
+      </c>
+      <c r="AG9" s="5">
+        <f t="shared" si="8"/>
+        <v>19567.347560264243</v>
+      </c>
+      <c r="AH9" s="5">
+        <f t="shared" si="8"/>
+        <v>19936.882870312722</v>
+      </c>
+      <c r="AI9" s="5">
+        <f t="shared" si="8"/>
+        <v>20315.329388495084</v>
+      </c>
+      <c r="AJ9" s="5">
+        <f t="shared" si="8"/>
+        <v>20702.932702543636</v>
+      </c>
+      <c r="AK9" s="5">
+        <f t="shared" si="8"/>
+        <v>21099.945550337579</v>
       </c>
     </row>
     <row r="10" spans="2:37" x14ac:dyDescent="0.3">
@@ -1376,6 +1718,50 @@
       <c r="Z10" s="3">
         <v>2934</v>
       </c>
+      <c r="AA10" s="3">
+        <f>Z10*1.02</f>
+        <v>2992.68</v>
+      </c>
+      <c r="AB10" s="3">
+        <f t="shared" ref="AB10:AK10" si="9">AA10*1.02</f>
+        <v>3052.5335999999998</v>
+      </c>
+      <c r="AC10" s="3">
+        <f t="shared" si="9"/>
+        <v>3113.5842719999996</v>
+      </c>
+      <c r="AD10" s="3">
+        <f t="shared" si="9"/>
+        <v>3175.8559574399997</v>
+      </c>
+      <c r="AE10" s="3">
+        <f t="shared" si="9"/>
+        <v>3239.3730765887999</v>
+      </c>
+      <c r="AF10" s="3">
+        <f>AE10*1.01</f>
+        <v>3271.7668073546879</v>
+      </c>
+      <c r="AG10" s="3">
+        <f t="shared" ref="AG10:AK10" si="10">AF10*1.01</f>
+        <v>3304.4844754282349</v>
+      </c>
+      <c r="AH10" s="3">
+        <f t="shared" si="10"/>
+        <v>3337.529320182517</v>
+      </c>
+      <c r="AI10" s="3">
+        <f t="shared" si="10"/>
+        <v>3370.9046133843422</v>
+      </c>
+      <c r="AJ10" s="3">
+        <f t="shared" si="10"/>
+        <v>3404.6136595181856</v>
+      </c>
+      <c r="AK10" s="3">
+        <f t="shared" si="10"/>
+        <v>3438.6597961133675</v>
+      </c>
     </row>
     <row r="11" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
@@ -1417,6 +1803,50 @@
       <c r="Z11" s="3">
         <v>5806</v>
       </c>
+      <c r="AA11" s="3">
+        <f>AA5*0.07</f>
+        <v>6062.0644000000011</v>
+      </c>
+      <c r="AB11" s="3">
+        <f t="shared" ref="AB11:AK11" si="11">AB5*0.07</f>
+        <v>6365.167620000002</v>
+      </c>
+      <c r="AC11" s="3">
+        <f t="shared" si="11"/>
+        <v>6572.8924674000018</v>
+      </c>
+      <c r="AD11" s="3">
+        <f t="shared" si="11"/>
+        <v>6721.7909283000017</v>
+      </c>
+      <c r="AE11" s="3">
+        <f t="shared" si="11"/>
+        <v>6824.9364973801221</v>
+      </c>
+      <c r="AF11" s="3">
+        <f t="shared" si="11"/>
+        <v>6930.1913519449572</v>
+      </c>
+      <c r="AG11" s="3">
+        <f t="shared" si="11"/>
+        <v>7037.6089197431711</v>
+      </c>
+      <c r="AH11" s="3">
+        <f t="shared" si="11"/>
+        <v>7147.2441328477298</v>
+      </c>
+      <c r="AI11" s="3">
+        <f t="shared" si="11"/>
+        <v>7259.1534718005487</v>
+      </c>
+      <c r="AJ11" s="3">
+        <f t="shared" si="11"/>
+        <v>7373.395011071626</v>
+      </c>
+      <c r="AK11" s="3">
+        <f t="shared" si="11"/>
+        <v>7490.0284658720075</v>
+      </c>
     </row>
     <row r="12" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
@@ -1447,28 +1877,72 @@
         <v>2031</v>
       </c>
       <c r="U12" s="5">
-        <f t="shared" ref="U12:Z12" si="3">U9-U10-U11</f>
+        <f t="shared" ref="U12:AA12" si="12">U9-U10-U11</f>
         <v>4588</v>
       </c>
       <c r="V12" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>409</v>
       </c>
       <c r="W12" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>4535</v>
       </c>
       <c r="X12" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>5384</v>
       </c>
       <c r="Y12" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>3475</v>
       </c>
       <c r="Z12" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>6670</v>
+      </c>
+      <c r="AA12" s="5">
+        <f t="shared" si="12"/>
+        <v>7585.9664000000139</v>
+      </c>
+      <c r="AB12" s="5">
+        <f t="shared" ref="AB12:AK12" si="13">AB9-AB10-AB11</f>
+        <v>8055.0451200000116</v>
+      </c>
+      <c r="AC12" s="5">
+        <f t="shared" si="13"/>
+        <v>8384.7183312000052</v>
+      </c>
+      <c r="AD12" s="5">
+        <f t="shared" si="13"/>
+        <v>8612.2090802880011</v>
+      </c>
+      <c r="AE12" s="5">
+        <f t="shared" si="13"/>
+        <v>8789.7531593923286</v>
+      </c>
+      <c r="AF12" s="5">
+        <f t="shared" si="13"/>
+        <v>9004.5266552983612</v>
+      </c>
+      <c r="AG12" s="5">
+        <f t="shared" si="13"/>
+        <v>9225.254165092836</v>
+      </c>
+      <c r="AH12" s="5">
+        <f t="shared" si="13"/>
+        <v>9452.1094172824742</v>
+      </c>
+      <c r="AI12" s="5">
+        <f t="shared" si="13"/>
+        <v>9685.27130331019</v>
+      </c>
+      <c r="AJ12" s="5">
+        <f t="shared" si="13"/>
+        <v>9924.9240319538258</v>
+      </c>
+      <c r="AK12" s="5">
+        <f t="shared" si="13"/>
+        <v>10171.257288352204</v>
       </c>
     </row>
     <row r="13" spans="2:37" x14ac:dyDescent="0.3">
@@ -1512,6 +1986,39 @@
       <c r="Z13" s="3">
         <v>132</v>
       </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
@@ -1553,6 +2060,50 @@
       <c r="Z14" s="3">
         <v>-1518</v>
       </c>
+      <c r="AA14" s="3">
+        <f>Z14*1.01</f>
+        <v>-1533.18</v>
+      </c>
+      <c r="AB14" s="3">
+        <f t="shared" ref="AB14:AK14" si="14">AA14*1.01</f>
+        <v>-1548.5118</v>
+      </c>
+      <c r="AC14" s="3">
+        <f t="shared" si="14"/>
+        <v>-1563.9969180000001</v>
+      </c>
+      <c r="AD14" s="3">
+        <f t="shared" si="14"/>
+        <v>-1579.63688718</v>
+      </c>
+      <c r="AE14" s="3">
+        <f t="shared" si="14"/>
+        <v>-1595.4332560518001</v>
+      </c>
+      <c r="AF14" s="3">
+        <f t="shared" si="14"/>
+        <v>-1611.387588612318</v>
+      </c>
+      <c r="AG14" s="3">
+        <f t="shared" si="14"/>
+        <v>-1627.5014644984412</v>
+      </c>
+      <c r="AH14" s="3">
+        <f t="shared" si="14"/>
+        <v>-1643.7764791434256</v>
+      </c>
+      <c r="AI14" s="3">
+        <f t="shared" si="14"/>
+        <v>-1660.21424393486</v>
+      </c>
+      <c r="AJ14" s="3">
+        <f t="shared" si="14"/>
+        <v>-1676.8163863742086</v>
+      </c>
+      <c r="AK14" s="3">
+        <f t="shared" si="14"/>
+        <v>-1693.5845502379507</v>
+      </c>
     </row>
     <row r="15" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
@@ -1595,6 +2146,50 @@
       <c r="Z15" s="3">
         <v>1862</v>
       </c>
+      <c r="AA15" s="3">
+        <f>Z15*1.01</f>
+        <v>1880.6200000000001</v>
+      </c>
+      <c r="AB15" s="3">
+        <f t="shared" ref="AB15:AK15" si="15">AA15*1.01</f>
+        <v>1899.4262000000001</v>
+      </c>
+      <c r="AC15" s="3">
+        <f t="shared" si="15"/>
+        <v>1918.420462</v>
+      </c>
+      <c r="AD15" s="3">
+        <f t="shared" si="15"/>
+        <v>1937.60466662</v>
+      </c>
+      <c r="AE15" s="3">
+        <f t="shared" si="15"/>
+        <v>1956.9807132861999</v>
+      </c>
+      <c r="AF15" s="3">
+        <f t="shared" si="15"/>
+        <v>1976.550520419062</v>
+      </c>
+      <c r="AG15" s="3">
+        <f t="shared" si="15"/>
+        <v>1996.3160256232527</v>
+      </c>
+      <c r="AH15" s="3">
+        <f t="shared" si="15"/>
+        <v>2016.2791858794853</v>
+      </c>
+      <c r="AI15" s="3">
+        <f t="shared" si="15"/>
+        <v>2036.4419777382802</v>
+      </c>
+      <c r="AJ15" s="3">
+        <f t="shared" si="15"/>
+        <v>2056.8063975156629</v>
+      </c>
+      <c r="AK15" s="3">
+        <f t="shared" si="15"/>
+        <v>2077.3744614908196</v>
+      </c>
     </row>
     <row r="16" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
@@ -1625,31 +2220,75 @@
         <v>1958</v>
       </c>
       <c r="U16" s="5">
-        <f t="shared" ref="U16:Z16" si="4">U12-U13-U14-U15</f>
+        <f t="shared" ref="U16:AA16" si="16">U12-U13-U14-U15</f>
         <v>4152</v>
       </c>
       <c r="V16" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>-2353</v>
       </c>
       <c r="W16" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>4931</v>
       </c>
       <c r="X16" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>6117</v>
       </c>
       <c r="Y16" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>3836</v>
       </c>
       <c r="Z16" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>6194</v>
       </c>
+      <c r="AA16" s="5">
+        <f t="shared" si="16"/>
+        <v>7238.5264000000143</v>
+      </c>
+      <c r="AB16" s="5">
+        <f t="shared" ref="AB16:AK16" si="17">AB12-AB13-AB14-AB15</f>
+        <v>7704.1307200000119</v>
+      </c>
+      <c r="AC16" s="5">
+        <f t="shared" si="17"/>
+        <v>8030.2947872000059</v>
+      </c>
+      <c r="AD16" s="5">
+        <f t="shared" si="17"/>
+        <v>8254.2413008480016</v>
+      </c>
+      <c r="AE16" s="5">
+        <f t="shared" si="17"/>
+        <v>8428.2057021579276</v>
+      </c>
+      <c r="AF16" s="5">
+        <f t="shared" si="17"/>
+        <v>8639.3637234916187</v>
+      </c>
+      <c r="AG16" s="5">
+        <f t="shared" si="17"/>
+        <v>8856.4396039680232</v>
+      </c>
+      <c r="AH16" s="5">
+        <f t="shared" si="17"/>
+        <v>9079.6067105464135</v>
+      </c>
+      <c r="AI16" s="5">
+        <f t="shared" si="17"/>
+        <v>9309.0435695067699</v>
+      </c>
+      <c r="AJ16" s="5">
+        <f t="shared" si="17"/>
+        <v>9544.9340208123722</v>
+      </c>
+      <c r="AK16" s="5">
+        <f t="shared" si="17"/>
+        <v>9787.4673770993359</v>
+      </c>
     </row>
-    <row r="17" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>37</v>
       </c>
@@ -1689,8 +2328,52 @@
       <c r="Z17" s="3">
         <v>1181</v>
       </c>
+      <c r="AA17" s="3">
+        <f>AA16*0.15</f>
+        <v>1085.7789600000021</v>
+      </c>
+      <c r="AB17" s="3">
+        <f t="shared" ref="AB17:AK17" si="18">AB16*0.15</f>
+        <v>1155.6196080000018</v>
+      </c>
+      <c r="AC17" s="3">
+        <f t="shared" si="18"/>
+        <v>1204.5442180800007</v>
+      </c>
+      <c r="AD17" s="3">
+        <f t="shared" si="18"/>
+        <v>1238.1361951272002</v>
+      </c>
+      <c r="AE17" s="3">
+        <f t="shared" si="18"/>
+        <v>1264.2308553236892</v>
+      </c>
+      <c r="AF17" s="3">
+        <f t="shared" si="18"/>
+        <v>1295.9045585237427</v>
+      </c>
+      <c r="AG17" s="3">
+        <f t="shared" si="18"/>
+        <v>1328.4659405952034</v>
+      </c>
+      <c r="AH17" s="3">
+        <f t="shared" si="18"/>
+        <v>1361.941006581962</v>
+      </c>
+      <c r="AI17" s="3">
+        <f t="shared" si="18"/>
+        <v>1396.3565354260154</v>
+      </c>
+      <c r="AJ17" s="3">
+        <f t="shared" si="18"/>
+        <v>1431.7401031218558</v>
+      </c>
+      <c r="AK17" s="3">
+        <f t="shared" si="18"/>
+        <v>1468.1201065649004</v>
+      </c>
     </row>
-    <row r="18" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
@@ -1730,8 +2413,52 @@
       <c r="Z18" s="3">
         <v>239</v>
       </c>
+      <c r="AA18" s="3">
+        <f>AA16*0.03</f>
+        <v>217.15579200000042</v>
+      </c>
+      <c r="AB18" s="3">
+        <f t="shared" ref="AB18:AK18" si="19">AB16*0.03</f>
+        <v>231.12392160000036</v>
+      </c>
+      <c r="AC18" s="3">
+        <f t="shared" si="19"/>
+        <v>240.90884361600015</v>
+      </c>
+      <c r="AD18" s="3">
+        <f t="shared" si="19"/>
+        <v>247.62723902544005</v>
+      </c>
+      <c r="AE18" s="3">
+        <f t="shared" si="19"/>
+        <v>252.84617106473783</v>
+      </c>
+      <c r="AF18" s="3">
+        <f t="shared" si="19"/>
+        <v>259.18091170474855</v>
+      </c>
+      <c r="AG18" s="3">
+        <f t="shared" si="19"/>
+        <v>265.69318811904071</v>
+      </c>
+      <c r="AH18" s="3">
+        <f t="shared" si="19"/>
+        <v>272.38820131639238</v>
+      </c>
+      <c r="AI18" s="3">
+        <f t="shared" si="19"/>
+        <v>279.27130708520309</v>
+      </c>
+      <c r="AJ18" s="3">
+        <f t="shared" si="19"/>
+        <v>286.34802062437115</v>
+      </c>
+      <c r="AK18" s="3">
+        <f t="shared" si="19"/>
+        <v>293.62402131298006</v>
+      </c>
     </row>
-    <row r="19" spans="2:26" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:135" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>39</v>
       </c>
@@ -1760,31 +2487,467 @@
         <v>1535</v>
       </c>
       <c r="U19" s="5">
-        <f t="shared" ref="U19:Z19" si="5">U16-U17-U18</f>
+        <f t="shared" ref="U19:Z19" si="20">U16-U17-U18</f>
         <v>3510</v>
       </c>
       <c r="V19" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="20"/>
         <v>-3109</v>
       </c>
       <c r="W19" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="20"/>
         <v>3897</v>
       </c>
       <c r="X19" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="20"/>
         <v>5216</v>
       </c>
       <c r="Y19" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="20"/>
         <v>3195</v>
       </c>
       <c r="Z19" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="20"/>
         <v>4774</v>
       </c>
+      <c r="AA19" s="5">
+        <f t="shared" ref="AA19:AK19" si="21">AA16-AA17-AA18</f>
+        <v>5935.5916480000114</v>
+      </c>
+      <c r="AB19" s="5">
+        <f t="shared" si="21"/>
+        <v>6317.3871904000098</v>
+      </c>
+      <c r="AC19" s="5">
+        <f t="shared" si="21"/>
+        <v>6584.8417255040049</v>
+      </c>
+      <c r="AD19" s="5">
+        <f t="shared" si="21"/>
+        <v>6768.4778666953616</v>
+      </c>
+      <c r="AE19" s="5">
+        <f t="shared" si="21"/>
+        <v>6911.1286757695007</v>
+      </c>
+      <c r="AF19" s="5">
+        <f t="shared" si="21"/>
+        <v>7084.2782532631272</v>
+      </c>
+      <c r="AG19" s="5">
+        <f t="shared" si="21"/>
+        <v>7262.2804752537795</v>
+      </c>
+      <c r="AH19" s="5">
+        <f t="shared" si="21"/>
+        <v>7445.2775026480595</v>
+      </c>
+      <c r="AI19" s="5">
+        <f t="shared" si="21"/>
+        <v>7633.4157269955513</v>
+      </c>
+      <c r="AJ19" s="5">
+        <f t="shared" si="21"/>
+        <v>7826.845897066145</v>
+      </c>
+      <c r="AK19" s="5">
+        <f t="shared" si="21"/>
+        <v>8025.7232492214553</v>
+      </c>
+      <c r="AL19" s="4">
+        <f>AK19*(1+$AO$25)</f>
+        <v>7945.4660167292404</v>
+      </c>
+      <c r="AM19" s="4">
+        <f t="shared" ref="AM19:CX19" si="22">AL19*(1+$AO$25)</f>
+        <v>7866.0113565619477</v>
+      </c>
+      <c r="AN19" s="4">
+        <f t="shared" si="22"/>
+        <v>7787.3512429963284</v>
+      </c>
+      <c r="AO19" s="4">
+        <f t="shared" si="22"/>
+        <v>7709.4777305663647</v>
+      </c>
+      <c r="AP19" s="4">
+        <f t="shared" si="22"/>
+        <v>7632.3829532607006</v>
+      </c>
+      <c r="AQ19" s="4">
+        <f t="shared" si="22"/>
+        <v>7556.0591237280933</v>
+      </c>
+      <c r="AR19" s="4">
+        <f t="shared" si="22"/>
+        <v>7480.4985324908121</v>
+      </c>
+      <c r="AS19" s="4">
+        <f t="shared" si="22"/>
+        <v>7405.6935471659035</v>
+      </c>
+      <c r="AT19" s="4">
+        <f t="shared" si="22"/>
+        <v>7331.6366116942445</v>
+      </c>
+      <c r="AU19" s="4">
+        <f t="shared" si="22"/>
+        <v>7258.3202455773016</v>
+      </c>
+      <c r="AV19" s="4">
+        <f t="shared" si="22"/>
+        <v>7185.7370431215286</v>
+      </c>
+      <c r="AW19" s="4">
+        <f t="shared" si="22"/>
+        <v>7113.8796726903129</v>
+      </c>
+      <c r="AX19" s="4">
+        <f t="shared" si="22"/>
+        <v>7042.74087596341</v>
+      </c>
+      <c r="AY19" s="4">
+        <f t="shared" si="22"/>
+        <v>6972.3134672037759</v>
+      </c>
+      <c r="AZ19" s="4">
+        <f t="shared" si="22"/>
+        <v>6902.5903325317377</v>
+      </c>
+      <c r="BA19" s="4">
+        <f t="shared" si="22"/>
+        <v>6833.5644292064198</v>
+      </c>
+      <c r="BB19" s="4">
+        <f t="shared" si="22"/>
+        <v>6765.2287849143559</v>
+      </c>
+      <c r="BC19" s="4">
+        <f t="shared" si="22"/>
+        <v>6697.5764970652126</v>
+      </c>
+      <c r="BD19" s="4">
+        <f t="shared" si="22"/>
+        <v>6630.60073209456</v>
+      </c>
+      <c r="BE19" s="4">
+        <f t="shared" si="22"/>
+        <v>6564.2947247736147</v>
+      </c>
+      <c r="BF19" s="4">
+        <f t="shared" si="22"/>
+        <v>6498.6517775258781</v>
+      </c>
+      <c r="BG19" s="4">
+        <f t="shared" si="22"/>
+        <v>6433.665259750619</v>
+      </c>
+      <c r="BH19" s="4">
+        <f t="shared" si="22"/>
+        <v>6369.3286071531129</v>
+      </c>
+      <c r="BI19" s="4">
+        <f t="shared" si="22"/>
+        <v>6305.6353210815814</v>
+      </c>
+      <c r="BJ19" s="4">
+        <f t="shared" si="22"/>
+        <v>6242.5789678707652</v>
+      </c>
+      <c r="BK19" s="4">
+        <f t="shared" si="22"/>
+        <v>6180.1531781920576</v>
+      </c>
+      <c r="BL19" s="4">
+        <f t="shared" si="22"/>
+        <v>6118.3516464101367</v>
+      </c>
+      <c r="BM19" s="4">
+        <f t="shared" si="22"/>
+        <v>6057.1681299460352</v>
+      </c>
+      <c r="BN19" s="4">
+        <f t="shared" si="22"/>
+        <v>5996.5964486465746</v>
+      </c>
+      <c r="BO19" s="4">
+        <f t="shared" si="22"/>
+        <v>5936.6304841601086</v>
+      </c>
+      <c r="BP19" s="4">
+        <f t="shared" si="22"/>
+        <v>5877.2641793185076</v>
+      </c>
+      <c r="BQ19" s="4">
+        <f t="shared" si="22"/>
+        <v>5818.4915375253222</v>
+      </c>
+      <c r="BR19" s="4">
+        <f t="shared" si="22"/>
+        <v>5760.3066221500685</v>
+      </c>
+      <c r="BS19" s="4">
+        <f t="shared" si="22"/>
+        <v>5702.7035559285678</v>
+      </c>
+      <c r="BT19" s="4">
+        <f t="shared" si="22"/>
+        <v>5645.6765203692821</v>
+      </c>
+      <c r="BU19" s="4">
+        <f t="shared" si="22"/>
+        <v>5589.219755165589</v>
+      </c>
+      <c r="BV19" s="4">
+        <f t="shared" si="22"/>
+        <v>5533.3275576139331</v>
+      </c>
+      <c r="BW19" s="4">
+        <f t="shared" si="22"/>
+        <v>5477.9942820377937</v>
+      </c>
+      <c r="BX19" s="4">
+        <f t="shared" si="22"/>
+        <v>5423.2143392174157</v>
+      </c>
+      <c r="BY19" s="4">
+        <f t="shared" si="22"/>
+        <v>5368.9821958252414</v>
+      </c>
+      <c r="BZ19" s="4">
+        <f t="shared" si="22"/>
+        <v>5315.2923738669888</v>
+      </c>
+      <c r="CA19" s="4">
+        <f t="shared" si="22"/>
+        <v>5262.1394501283185</v>
+      </c>
+      <c r="CB19" s="4">
+        <f t="shared" si="22"/>
+        <v>5209.5180556270352</v>
+      </c>
+      <c r="CC19" s="4">
+        <f t="shared" si="22"/>
+        <v>5157.4228750707653</v>
+      </c>
+      <c r="CD19" s="4">
+        <f t="shared" si="22"/>
+        <v>5105.8486463200579</v>
+      </c>
+      <c r="CE19" s="4">
+        <f t="shared" si="22"/>
+        <v>5054.7901598568569</v>
+      </c>
+      <c r="CF19" s="4">
+        <f t="shared" si="22"/>
+        <v>5004.2422582582885</v>
+      </c>
+      <c r="CG19" s="4">
+        <f t="shared" si="22"/>
+        <v>4954.1998356757058</v>
+      </c>
+      <c r="CH19" s="4">
+        <f t="shared" si="22"/>
+        <v>4904.6578373189486</v>
+      </c>
+      <c r="CI19" s="4">
+        <f t="shared" si="22"/>
+        <v>4855.6112589457589</v>
+      </c>
+      <c r="CJ19" s="4">
+        <f t="shared" si="22"/>
+        <v>4807.0551463563015</v>
+      </c>
+      <c r="CK19" s="4">
+        <f t="shared" si="22"/>
+        <v>4758.9845948927386</v>
+      </c>
+      <c r="CL19" s="4">
+        <f t="shared" si="22"/>
+        <v>4711.3947489438115</v>
+      </c>
+      <c r="CM19" s="4">
+        <f t="shared" si="22"/>
+        <v>4664.2808014543734</v>
+      </c>
+      <c r="CN19" s="4">
+        <f t="shared" si="22"/>
+        <v>4617.6379934398301</v>
+      </c>
+      <c r="CO19" s="4">
+        <f t="shared" si="22"/>
+        <v>4571.4616135054321</v>
+      </c>
+      <c r="CP19" s="4">
+        <f t="shared" si="22"/>
+        <v>4525.7469973703774</v>
+      </c>
+      <c r="CQ19" s="4">
+        <f t="shared" si="22"/>
+        <v>4480.4895273966731</v>
+      </c>
+      <c r="CR19" s="4">
+        <f t="shared" si="22"/>
+        <v>4435.6846321227067</v>
+      </c>
+      <c r="CS19" s="4">
+        <f t="shared" si="22"/>
+        <v>4391.3277858014799</v>
+      </c>
+      <c r="CT19" s="4">
+        <f t="shared" si="22"/>
+        <v>4347.4145079434647</v>
+      </c>
+      <c r="CU19" s="4">
+        <f t="shared" si="22"/>
+        <v>4303.9403628640302</v>
+      </c>
+      <c r="CV19" s="4">
+        <f t="shared" si="22"/>
+        <v>4260.9009592353896</v>
+      </c>
+      <c r="CW19" s="4">
+        <f t="shared" si="22"/>
+        <v>4218.2919496430359</v>
+      </c>
+      <c r="CX19" s="4">
+        <f t="shared" si="22"/>
+        <v>4176.1090301466056</v>
+      </c>
+      <c r="CY19" s="4">
+        <f t="shared" ref="CY19:EE19" si="23">CX19*(1+$AO$25)</f>
+        <v>4134.3479398451391</v>
+      </c>
+      <c r="CZ19" s="4">
+        <f t="shared" si="23"/>
+        <v>4093.0044604466875</v>
+      </c>
+      <c r="DA19" s="4">
+        <f t="shared" si="23"/>
+        <v>4052.0744158422208</v>
+      </c>
+      <c r="DB19" s="4">
+        <f t="shared" si="23"/>
+        <v>4011.5536716837987</v>
+      </c>
+      <c r="DC19" s="4">
+        <f t="shared" si="23"/>
+        <v>3971.4381349669607</v>
+      </c>
+      <c r="DD19" s="4">
+        <f t="shared" si="23"/>
+        <v>3931.7237536172911</v>
+      </c>
+      <c r="DE19" s="4">
+        <f t="shared" si="23"/>
+        <v>3892.4065160811183</v>
+      </c>
+      <c r="DF19" s="4">
+        <f t="shared" si="23"/>
+        <v>3853.4824509203072</v>
+      </c>
+      <c r="DG19" s="4">
+        <f t="shared" si="23"/>
+        <v>3814.947626411104</v>
+      </c>
+      <c r="DH19" s="4">
+        <f t="shared" si="23"/>
+        <v>3776.7981501469931</v>
+      </c>
+      <c r="DI19" s="4">
+        <f t="shared" si="23"/>
+        <v>3739.0301686455232</v>
+      </c>
+      <c r="DJ19" s="4">
+        <f t="shared" si="23"/>
+        <v>3701.6398669590681</v>
+      </c>
+      <c r="DK19" s="4">
+        <f t="shared" si="23"/>
+        <v>3664.6234682894774</v>
+      </c>
+      <c r="DL19" s="4">
+        <f t="shared" si="23"/>
+        <v>3627.9772336065826</v>
+      </c>
+      <c r="DM19" s="4">
+        <f t="shared" si="23"/>
+        <v>3591.6974612705167</v>
+      </c>
+      <c r="DN19" s="4">
+        <f t="shared" si="23"/>
+        <v>3555.7804866578113</v>
+      </c>
+      <c r="DO19" s="4">
+        <f t="shared" si="23"/>
+        <v>3520.2226817912333</v>
+      </c>
+      <c r="DP19" s="4">
+        <f t="shared" si="23"/>
+        <v>3485.0204549733207</v>
+      </c>
+      <c r="DQ19" s="4">
+        <f t="shared" si="23"/>
+        <v>3450.1702504235873</v>
+      </c>
+      <c r="DR19" s="4">
+        <f t="shared" si="23"/>
+        <v>3415.6685479193516</v>
+      </c>
+      <c r="DS19" s="4">
+        <f t="shared" si="23"/>
+        <v>3381.511862440158</v>
+      </c>
+      <c r="DT19" s="4">
+        <f t="shared" si="23"/>
+        <v>3347.6967438157562</v>
+      </c>
+      <c r="DU19" s="4">
+        <f t="shared" si="23"/>
+        <v>3314.2197763775985</v>
+      </c>
+      <c r="DV19" s="4">
+        <f t="shared" si="23"/>
+        <v>3281.0775786138224</v>
+      </c>
+      <c r="DW19" s="4">
+        <f t="shared" si="23"/>
+        <v>3248.2668028276844</v>
+      </c>
+      <c r="DX19" s="4">
+        <f t="shared" si="23"/>
+        <v>3215.7841347994076</v>
+      </c>
+      <c r="DY19" s="4">
+        <f t="shared" si="23"/>
+        <v>3183.6262934514134</v>
+      </c>
+      <c r="DZ19" s="4">
+        <f t="shared" si="23"/>
+        <v>3151.7900305168992</v>
+      </c>
+      <c r="EA19" s="4">
+        <f t="shared" si="23"/>
+        <v>3120.2721302117302</v>
+      </c>
+      <c r="EB19" s="4">
+        <f t="shared" si="23"/>
+        <v>3089.0694089096128</v>
+      </c>
+      <c r="EC19" s="4">
+        <f t="shared" si="23"/>
+        <v>3058.1787148205167</v>
+      </c>
+      <c r="ED19" s="4">
+        <f t="shared" si="23"/>
+        <v>3027.5969276723117</v>
+      </c>
+      <c r="EE19" s="4">
+        <f t="shared" si="23"/>
+        <v>2997.3209583955886</v>
+      </c>
     </row>
-    <row r="20" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>2</v>
       </c>
@@ -1807,31 +2970,75 @@
         <v>1330</v>
       </c>
       <c r="U20" s="3">
-        <f t="shared" ref="U20:Z20" si="6">1332.1</f>
+        <f t="shared" ref="U20:AK20" si="24">1332.1</f>
         <v>1332.1</v>
       </c>
       <c r="V20" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="24"/>
         <v>1332.1</v>
       </c>
       <c r="W20" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="24"/>
         <v>1332.1</v>
       </c>
       <c r="X20" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="24"/>
         <v>1332.1</v>
       </c>
       <c r="Y20" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="24"/>
         <v>1332.1</v>
       </c>
       <c r="Z20" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="24"/>
         <v>1332.1</v>
       </c>
+      <c r="AA20" s="3">
+        <f t="shared" si="24"/>
+        <v>1332.1</v>
+      </c>
+      <c r="AB20" s="3">
+        <f t="shared" si="24"/>
+        <v>1332.1</v>
+      </c>
+      <c r="AC20" s="3">
+        <f t="shared" si="24"/>
+        <v>1332.1</v>
+      </c>
+      <c r="AD20" s="3">
+        <f t="shared" si="24"/>
+        <v>1332.1</v>
+      </c>
+      <c r="AE20" s="3">
+        <f t="shared" si="24"/>
+        <v>1332.1</v>
+      </c>
+      <c r="AF20" s="3">
+        <f t="shared" si="24"/>
+        <v>1332.1</v>
+      </c>
+      <c r="AG20" s="3">
+        <f t="shared" si="24"/>
+        <v>1332.1</v>
+      </c>
+      <c r="AH20" s="3">
+        <f t="shared" si="24"/>
+        <v>1332.1</v>
+      </c>
+      <c r="AI20" s="3">
+        <f t="shared" si="24"/>
+        <v>1332.1</v>
+      </c>
+      <c r="AJ20" s="3">
+        <f t="shared" si="24"/>
+        <v>1332.1</v>
+      </c>
+      <c r="AK20" s="3">
+        <f t="shared" si="24"/>
+        <v>1332.1</v>
+      </c>
     </row>
-    <row r="21" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>40</v>
       </c>
@@ -1860,31 +3067,75 @@
         <v>1.1541353383458646</v>
       </c>
       <c r="U21" s="6">
-        <f t="shared" ref="U21:Z21" si="7">U19/U20</f>
+        <f t="shared" ref="U21:Z21" si="25">U19/U20</f>
         <v>2.6349373170182422</v>
       </c>
       <c r="V21" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="25"/>
         <v>-2.3339088657007734</v>
       </c>
       <c r="W21" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="25"/>
         <v>2.9254560468433302</v>
       </c>
       <c r="X21" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="25"/>
         <v>3.9156219503040317</v>
       </c>
       <c r="Y21" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="25"/>
         <v>2.3984685834396817</v>
       </c>
       <c r="Z21" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="25"/>
         <v>3.5838150289017343</v>
       </c>
+      <c r="AA21" s="6">
+        <f t="shared" ref="AA21:AK21" si="26">AA19/AA20</f>
+        <v>4.4558153652128309</v>
+      </c>
+      <c r="AB21" s="6">
+        <f t="shared" si="26"/>
+        <v>4.7424271379025678</v>
+      </c>
+      <c r="AC21" s="6">
+        <f t="shared" si="26"/>
+        <v>4.9432037576037873</v>
+      </c>
+      <c r="AD21" s="6">
+        <f t="shared" si="26"/>
+        <v>5.0810583790221173</v>
+      </c>
+      <c r="AE21" s="6">
+        <f t="shared" si="26"/>
+        <v>5.18814554145297</v>
+      </c>
+      <c r="AF21" s="6">
+        <f t="shared" si="26"/>
+        <v>5.3181279583087813</v>
+      </c>
+      <c r="AG21" s="6">
+        <f t="shared" si="26"/>
+        <v>5.4517532281763978</v>
+      </c>
+      <c r="AH21" s="6">
+        <f t="shared" si="26"/>
+        <v>5.5891280704512125</v>
+      </c>
+      <c r="AI21" s="6">
+        <f t="shared" si="26"/>
+        <v>5.7303623804485788</v>
+      </c>
+      <c r="AJ21" s="6">
+        <f t="shared" si="26"/>
+        <v>5.8755693244247018</v>
+      </c>
+      <c r="AK21" s="6">
+        <f t="shared" si="26"/>
+        <v>6.0248654374457296</v>
+      </c>
     </row>
-    <row r="23" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>42</v>
       </c>
@@ -1894,19 +3145,19 @@
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7" t="e">
-        <f t="shared" ref="H23:K23" si="8">H9/D9-1</f>
+        <f t="shared" ref="H23:K23" si="27">H9/D9-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I23" s="7" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J23" s="7" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K23" s="7" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L23" s="7">
@@ -1919,23 +3170,67 @@
         <v>0.31277653191102495</v>
       </c>
       <c r="W23" s="7">
-        <f t="shared" ref="W23:Z23" si="9">W3/V3-1</f>
+        <f t="shared" ref="W23:Z23" si="28">W3/V3-1</f>
         <v>0.13737620905376402</v>
       </c>
       <c r="X23" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="28"/>
         <v>3.0505378526486604E-2</v>
       </c>
       <c r="Y23" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="28"/>
         <v>-2.3673999960609038E-2</v>
       </c>
       <c r="Z23" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="28"/>
         <v>0.20255794718686326</v>
       </c>
+      <c r="AA23" s="7">
+        <f t="shared" ref="AA23:AA25" si="29">AA3/Z3-1</f>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AB23" s="7">
+        <f t="shared" ref="AB23:AB25" si="30">AB3/AA3-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AC23" s="7">
+        <f t="shared" ref="AC23:AC25" si="31">AC3/AB3-1</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AD23" s="7">
+        <f t="shared" ref="AD23:AD25" si="32">AD3/AC3-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AE23" s="7">
+        <f t="shared" ref="AE23:AE25" si="33">AE3/AD3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AF23" s="7">
+        <f t="shared" ref="AF23:AF25" si="34">AF3/AE3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AG23" s="7">
+        <f t="shared" ref="AG23:AG25" si="35">AG3/AF3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AH23" s="7">
+        <f t="shared" ref="AH23:AH25" si="36">AH3/AG3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AI23" s="7">
+        <f t="shared" ref="AI23:AI25" si="37">AI3/AH3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AJ23" s="7">
+        <f t="shared" ref="AJ23:AJ25" si="38">AJ3/AI3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AK23" s="7">
+        <f t="shared" ref="AK23:AK25" si="39">AK3/AJ3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
     </row>
-    <row r="24" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>43</v>
       </c>
@@ -1945,48 +3240,92 @@
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
       <c r="H24" s="7" t="e">
-        <f t="shared" ref="H24:K24" si="10">H10/#REF!-1</f>
+        <f t="shared" ref="H24:K24" si="40">H10/#REF!-1</f>
         <v>#REF!</v>
       </c>
       <c r="I24" s="7" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>#REF!</v>
       </c>
       <c r="J24" s="7" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>#REF!</v>
       </c>
       <c r="K24" s="7" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>#REF!</v>
       </c>
       <c r="L24" s="7">
-        <f t="shared" ref="L24:L25" si="11">L4/H4-1</f>
+        <f t="shared" ref="L24:L25" si="41">L4/H4-1</f>
         <v>5.1998368678629614E-2</v>
       </c>
       <c r="U24" s="7"/>
       <c r="V24" s="7">
-        <f t="shared" ref="V24:Z25" si="12">V4/U4-1</f>
+        <f t="shared" ref="V24:Z25" si="42">V4/U4-1</f>
         <v>7.4245000404825623E-2</v>
       </c>
       <c r="W24" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="42"/>
         <v>0.13943322279167925</v>
       </c>
       <c r="X24" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="42"/>
         <v>7.8251091414208274E-2</v>
       </c>
       <c r="Y24" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="42"/>
         <v>0.18698239371817671</v>
       </c>
       <c r="Z24" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="42"/>
         <v>9.1839371543749104E-2</v>
       </c>
+      <c r="AA24" s="7">
+        <f t="shared" si="29"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="AB24" s="7">
+        <f t="shared" si="30"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AC24" s="7">
+        <f t="shared" si="31"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AD24" s="7">
+        <f t="shared" si="32"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AE24" s="7">
+        <f t="shared" si="33"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AF24" s="7">
+        <f t="shared" si="34"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AG24" s="7">
+        <f t="shared" si="35"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AH24" s="7">
+        <f t="shared" si="36"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AI24" s="7">
+        <f t="shared" si="37"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AJ24" s="7">
+        <f t="shared" si="38"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AK24" s="7">
+        <f t="shared" si="39"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
     </row>
-    <row r="25" spans="2:26" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:135" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>41</v>
       </c>
@@ -1996,85 +3335,135 @@
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
       <c r="H25" s="7" t="e">
-        <f t="shared" ref="H25:K25" si="13">H11/#REF!-1</f>
+        <f t="shared" ref="H25:K25" si="43">H11/#REF!-1</f>
         <v>#REF!</v>
       </c>
       <c r="I25" s="7" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="43"/>
         <v>#REF!</v>
       </c>
       <c r="J25" s="7" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="43"/>
         <v>#REF!</v>
       </c>
       <c r="K25" s="7" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="43"/>
         <v>#REF!</v>
       </c>
       <c r="L25" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="41"/>
         <v>7.6767676767676818E-2</v>
       </c>
       <c r="U25" s="7"/>
       <c r="V25" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="42"/>
         <v>0.24781141811285812</v>
       </c>
       <c r="W25" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="42"/>
         <v>0.1378585187410537</v>
       </c>
       <c r="X25" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="42"/>
         <v>4.1715847673479578E-2</v>
       </c>
       <c r="Y25" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="42"/>
         <v>2.7521841548140857E-2</v>
       </c>
       <c r="Z25" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="42"/>
         <v>0.17147417295414979</v>
       </c>
+      <c r="AA25" s="7">
+        <f t="shared" si="29"/>
+        <v>7.2616611756546101E-2</v>
+      </c>
+      <c r="AB25" s="7">
+        <f t="shared" si="30"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AC25" s="7">
+        <f t="shared" si="31"/>
+        <v>3.2634623281138309E-2</v>
+      </c>
+      <c r="AD25" s="7">
+        <f t="shared" si="32"/>
+        <v>2.2653415013025313E-2</v>
+      </c>
+      <c r="AE25" s="7">
+        <f t="shared" si="33"/>
+        <v>1.5344953477481438E-2</v>
+      </c>
+      <c r="AF25" s="7">
+        <f t="shared" si="34"/>
+        <v>1.5422100206388567E-2</v>
+      </c>
+      <c r="AG25" s="7">
+        <f t="shared" si="35"/>
+        <v>1.5499942547483547E-2</v>
+      </c>
+      <c r="AH25" s="7">
+        <f t="shared" si="36"/>
+        <v>1.5578474785234109E-2</v>
+      </c>
+      <c r="AI25" s="7">
+        <f t="shared" si="37"/>
+        <v>1.5657690834779192E-2</v>
+      </c>
+      <c r="AJ25" s="7">
+        <f t="shared" si="38"/>
+        <v>1.573758423965943E-2</v>
+      </c>
+      <c r="AK25" s="7">
+        <f t="shared" si="39"/>
+        <v>1.5818148169906676E-2</v>
+      </c>
+      <c r="AN25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AO25" s="7">
+        <v>-0.01</v>
+      </c>
     </row>
-    <row r="26" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C26" s="7" t="e">
-        <f t="shared" ref="C26:K26" si="14">(C3-C6)/C3</f>
+        <f t="shared" ref="C26:K26" si="44">(C3-C6)/C3</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D26" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="44"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E26" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="44"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F26" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="44"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G26" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="44"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H26" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="44"/>
         <v>0.17314145104764744</v>
       </c>
       <c r="I26" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="44"/>
         <v>-7.8235635519442834E-2</v>
       </c>
       <c r="J26" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="44"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K26" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="44"/>
         <v>0.14591344473187443</v>
       </c>
       <c r="L26" s="7">
@@ -2090,60 +3479,110 @@
         <v>0.11962418338373462</v>
       </c>
       <c r="W26" s="7">
-        <f t="shared" ref="W26:Z26" si="15">(W3-W6)/W3</f>
+        <f t="shared" ref="W26:Z26" si="45">(W3-W6)/W3</f>
         <v>0.16592246803328597</v>
       </c>
       <c r="X26" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="45"/>
         <v>0.17422645894471472</v>
       </c>
       <c r="Y26" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="45"/>
         <v>0.1239837808396038</v>
       </c>
       <c r="Z26" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="45"/>
         <v>0.14835939072669932</v>
       </c>
+      <c r="AA26" s="7">
+        <f t="shared" ref="AA26:AK26" si="46">(AA3-AA6)/AA3</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="AB26" s="7">
+        <f t="shared" si="46"/>
+        <v>0.15</v>
+      </c>
+      <c r="AC26" s="7">
+        <f t="shared" si="46"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="AD26" s="7">
+        <f t="shared" si="46"/>
+        <v>0.14999999999999997</v>
+      </c>
+      <c r="AE26" s="7">
+        <f t="shared" si="46"/>
+        <v>0.15</v>
+      </c>
+      <c r="AF26" s="7">
+        <f t="shared" si="46"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="AG26" s="7">
+        <f t="shared" si="46"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="AH26" s="7">
+        <f t="shared" si="46"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="AI26" s="7">
+        <f t="shared" si="46"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="AJ26" s="7">
+        <f t="shared" si="46"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="AK26" s="7">
+        <f t="shared" si="46"/>
+        <v>0.15</v>
+      </c>
+      <c r="AN26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO26" s="7">
+        <v>0.06</v>
+      </c>
     </row>
-    <row r="27" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C27" s="7" t="e">
-        <f t="shared" ref="C27:K27" si="16">(C4-C7)/C4</f>
+        <f t="shared" ref="C27:K27" si="47">(C4-C7)/C4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D27" s="7" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E27" s="7" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F27" s="7" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G27" s="7" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H27" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="47"/>
         <v>0.30077487765089722</v>
       </c>
       <c r="I27" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="47"/>
         <v>0.28624458651268303</v>
       </c>
       <c r="J27" s="7" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K27" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="47"/>
         <v>0.29468212714914033</v>
       </c>
       <c r="L27" s="7">
@@ -2159,60 +3598,111 @@
         <v>0.25241181790774797</v>
       </c>
       <c r="W27" s="7">
-        <f t="shared" ref="W27:Z27" si="17">(W4-W7)/W4</f>
+        <f t="shared" ref="W27:Z27" si="48">(W4-W7)/W4</f>
         <v>0.28548749834634213</v>
       </c>
       <c r="X27" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="48"/>
         <v>0.29581007300165635</v>
       </c>
       <c r="Y27" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="48"/>
         <v>0.30714765620962325</v>
       </c>
       <c r="Z27" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="48"/>
         <v>0.3108018555334659</v>
       </c>
+      <c r="AA27" s="7">
+        <f t="shared" ref="AA27:AK27" si="49">(AA4-AA7)/AA4</f>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="AB27" s="7">
+        <f t="shared" si="49"/>
+        <v>0.31</v>
+      </c>
+      <c r="AC27" s="7">
+        <f t="shared" si="49"/>
+        <v>0.31000000000000011</v>
+      </c>
+      <c r="AD27" s="7">
+        <f t="shared" si="49"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="AE27" s="7">
+        <f t="shared" si="49"/>
+        <v>0.31000000000000011</v>
+      </c>
+      <c r="AF27" s="7">
+        <f t="shared" si="49"/>
+        <v>0.31</v>
+      </c>
+      <c r="AG27" s="7">
+        <f t="shared" si="49"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="AH27" s="7">
+        <f t="shared" si="49"/>
+        <v>0.31</v>
+      </c>
+      <c r="AI27" s="7">
+        <f t="shared" si="49"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="AJ27" s="7">
+        <f t="shared" si="49"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="AK27" s="7">
+        <f t="shared" si="49"/>
+        <v>0.31</v>
+      </c>
+      <c r="AN27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AO27" s="3">
+        <f>NPV(AO26,AA19:EE19)</f>
+        <v>114608.19006879516</v>
+      </c>
     </row>
-    <row r="28" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C28" s="7" t="e">
-        <f t="shared" ref="C28:K28" si="18">C9/C5</f>
+        <f t="shared" ref="C28:K28" si="50">C9/C5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="7" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E28" s="7" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F28" s="7" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="7" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H28" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="50"/>
         <v>0.20731640731640733</v>
       </c>
       <c r="I28" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="50"/>
         <v>5.3030303030303032E-2</v>
       </c>
       <c r="J28" s="7" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K28" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="50"/>
         <v>0.18445998445998446</v>
       </c>
       <c r="L28" s="7">
@@ -2228,23 +3718,74 @@
         <v>0.15075900825277891</v>
       </c>
       <c r="W28" s="7">
-        <f t="shared" ref="W28:Z28" si="19">W9/W5</f>
+        <f t="shared" ref="W28:Z28" si="51">W9/W5</f>
         <v>0.19399577561036219</v>
       </c>
       <c r="X28" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="51"/>
         <v>0.20377493514625639</v>
       </c>
       <c r="Y28" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="51"/>
         <v>0.17540626813697041</v>
       </c>
       <c r="Z28" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="51"/>
         <v>0.19086427704426664</v>
       </c>
+      <c r="AA28" s="7">
+        <f t="shared" ref="AA28:AK28" si="52">AA9/AA5</f>
+        <v>0.19215397249821378</v>
+      </c>
+      <c r="AB28" s="7">
+        <f t="shared" si="52"/>
+        <v>0.19215397249821375</v>
+      </c>
+      <c r="AC28" s="7">
+        <f t="shared" si="52"/>
+        <v>0.19245464020840466</v>
+      </c>
+      <c r="AD28" s="7">
+        <f t="shared" si="52"/>
+        <v>0.19275962781985115</v>
+      </c>
+      <c r="AE28" s="7">
+        <f t="shared" si="52"/>
+        <v>0.19337680165110857</v>
+      </c>
+      <c r="AF28" s="7">
+        <f t="shared" si="52"/>
+        <v>0.19399954037986841</v>
+      </c>
+      <c r="AG28" s="7">
+        <f t="shared" si="52"/>
+        <v>0.19462779828187485</v>
+      </c>
+      <c r="AH28" s="7">
+        <f t="shared" si="52"/>
+        <v>0.19526152667823291</v>
+      </c>
+      <c r="AI28" s="7">
+        <f t="shared" si="52"/>
+        <v>0.19590067391727528</v>
+      </c>
+      <c r="AJ28" s="7">
+        <f t="shared" si="52"/>
+        <v>0.19654518535925172</v>
+      </c>
+      <c r="AK28" s="7">
+        <f t="shared" si="52"/>
+        <v>0.19719500336393919</v>
+      </c>
+      <c r="AN28" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AO28" s="3">
+        <f>Main!D8</f>
+        <v>-36143</v>
+      </c>
     </row>
-    <row r="29" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>47</v>
       </c>
@@ -2254,19 +3795,19 @@
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7" t="e">
-        <f t="shared" ref="H29:K29" si="20">H10/D10-1</f>
+        <f t="shared" ref="H29:K29" si="53">H10/D10-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I29" s="7" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J29" s="7" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K29" s="7" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L29" s="7">
@@ -2279,60 +3820,111 @@
         <v>5.3017944535073358E-2</v>
       </c>
       <c r="W29" s="7">
-        <f t="shared" ref="W29:Z29" si="21">W10/V10-1</f>
+        <f t="shared" ref="W29:Z29" si="54">W10/V10-1</f>
         <v>5.8094500387296577E-2</v>
       </c>
       <c r="X29" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="54"/>
         <v>-7.6866764275256294E-3</v>
       </c>
       <c r="Y29" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="54"/>
         <v>3.4673552194762092E-2</v>
       </c>
       <c r="Z29" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="54"/>
         <v>4.5989304812834142E-2</v>
       </c>
+      <c r="AA29" s="7">
+        <f t="shared" ref="AA29" si="55">AA10/Z10-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AB29" s="7">
+        <f t="shared" ref="AB29" si="56">AB10/AA10-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AC29" s="7">
+        <f t="shared" ref="AC29" si="57">AC10/AB10-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AD29" s="7">
+        <f t="shared" ref="AD29" si="58">AD10/AC10-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AE29" s="7">
+        <f t="shared" ref="AE29" si="59">AE10/AD10-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AF29" s="7">
+        <f t="shared" ref="AF29" si="60">AF10/AE10-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AG29" s="7">
+        <f t="shared" ref="AG29" si="61">AG10/AF10-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AH29" s="7">
+        <f t="shared" ref="AH29" si="62">AH10/AG10-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AI29" s="7">
+        <f t="shared" ref="AI29" si="63">AI10/AH10-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AJ29" s="7">
+        <f t="shared" ref="AJ29" si="64">AJ10/AI10-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AK29" s="7">
+        <f t="shared" ref="AK29" si="65">AK10/AJ10-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AN29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO29" s="3">
+        <f>AO27+AO28</f>
+        <v>78465.190068795157</v>
+      </c>
     </row>
-    <row r="30" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C30" s="7" t="e">
-        <f t="shared" ref="C30:K30" si="22">C11/C5</f>
+        <f t="shared" ref="C30:K30" si="66">C11/C5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D30" s="7" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="66"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E30" s="7" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="66"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F30" s="7" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="66"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G30" s="7" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="66"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H30" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="66"/>
         <v>8.7360087360087366E-2</v>
       </c>
       <c r="I30" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="66"/>
         <v>0.10405525846702317</v>
       </c>
       <c r="J30" s="7" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="66"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K30" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="66"/>
         <v>7.2209272209272216E-2</v>
       </c>
       <c r="L30" s="7">
@@ -2348,60 +3940,111 @@
         <v>9.7902345061586585E-2</v>
       </c>
       <c r="W30" s="7">
-        <f t="shared" ref="W30:Z30" si="23">W11/W5</f>
+        <f t="shared" ref="W30:Z30" si="67">W11/W5</f>
         <v>8.1133130396968373E-2</v>
       </c>
       <c r="X30" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="67"/>
         <v>8.308733637475027E-2</v>
       </c>
       <c r="Y30" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="67"/>
         <v>8.4286128845037722E-2</v>
       </c>
       <c r="Z30" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="67"/>
         <v>7.1911615348410909E-2</v>
       </c>
+      <c r="AA30" s="7">
+        <f t="shared" ref="AA30:AK30" si="68">AA11/AA5</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AB30" s="7">
+        <f t="shared" si="68"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AC30" s="7">
+        <f t="shared" si="68"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AD30" s="7">
+        <f t="shared" si="68"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AE30" s="7">
+        <f t="shared" si="68"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AF30" s="7">
+        <f t="shared" si="68"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AG30" s="7">
+        <f t="shared" si="68"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AH30" s="7">
+        <f t="shared" si="68"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AI30" s="7">
+        <f t="shared" si="68"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AJ30" s="7">
+        <f t="shared" si="68"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AK30" s="7">
+        <f t="shared" si="68"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AN30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AO30" s="9">
+        <f>AO29/AK20</f>
+        <v>58.903378176409554</v>
+      </c>
     </row>
-    <row r="31" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C31" s="7" t="e">
-        <f t="shared" ref="C31:K31" si="24">C12/C5</f>
+        <f t="shared" ref="C31:K31" si="69">C12/C5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D31" s="7" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E31" s="7" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F31" s="7" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G31" s="7" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H31" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="69"/>
         <v>8.0152880152880149E-2</v>
       </c>
       <c r="I31" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="69"/>
         <v>-0.10390671420083185</v>
       </c>
       <c r="J31" s="7" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K31" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="69"/>
         <v>7.75964775964776E-2</v>
       </c>
       <c r="L31" s="7">
@@ -2417,60 +4060,111 @@
         <v>7.2278085072543163E-3</v>
       </c>
       <c r="W31" s="7">
-        <f t="shared" ref="W31:Z31" si="25">W12/W5</f>
+        <f t="shared" ref="W31:Z31" si="70">W12/W5</f>
         <v>7.043237870410636E-2</v>
       </c>
       <c r="X31" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="70"/>
         <v>8.0269553030980711E-2</v>
       </c>
       <c r="Y31" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="70"/>
         <v>5.0420777713290774E-2</v>
       </c>
       <c r="Z31" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="70"/>
         <v>8.2612896034085559E-2</v>
       </c>
+      <c r="AA31" s="7">
+        <f t="shared" ref="AA31:AK31" si="71">AA12/AA5</f>
+        <v>8.7596833844259536E-2</v>
+      </c>
+      <c r="AB31" s="7">
+        <f t="shared" si="71"/>
+        <v>8.8584180662943907E-2</v>
+      </c>
+      <c r="AC31" s="7">
+        <f t="shared" si="71"/>
+        <v>8.9295585785867687E-2</v>
+      </c>
+      <c r="AD31" s="7">
+        <f t="shared" si="71"/>
+        <v>8.9686609127045139E-2</v>
+      </c>
+      <c r="AE31" s="7">
+        <f t="shared" si="71"/>
+        <v>9.0152153268188012E-2</v>
+      </c>
+      <c r="AF31" s="7">
+        <f t="shared" si="71"/>
+        <v>9.0952303314682209E-2</v>
+      </c>
+      <c r="AG31" s="7">
+        <f t="shared" si="71"/>
+        <v>9.1759544885319524E-2</v>
+      </c>
+      <c r="AH31" s="7">
+        <f t="shared" si="71"/>
+        <v>9.2573815433130868E-2</v>
+      </c>
+      <c r="AI31" s="7">
+        <f t="shared" si="71"/>
+        <v>9.3395048591464899E-2</v>
+      </c>
+      <c r="AJ31" s="7">
+        <f t="shared" si="71"/>
+        <v>9.4223174154316178E-2</v>
+      </c>
+      <c r="AK31" s="7">
+        <f t="shared" si="71"/>
+        <v>9.5058118060404859E-2</v>
+      </c>
+      <c r="AN31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO31" s="9">
+        <f>Main!D3</f>
+        <v>119.35</v>
+      </c>
     </row>
-    <row r="32" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C32" s="7" t="e">
-        <f t="shared" ref="C32:K32" si="26">C17/C16</f>
+        <f t="shared" ref="C32:K32" si="72">C17/C16</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D32" s="7" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="72"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E32" s="7" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="72"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F32" s="7" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="72"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G32" s="7" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="72"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H32" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="72"/>
         <v>0.15432482887367766</v>
       </c>
       <c r="I32" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="72"/>
         <v>0.29425113464447805</v>
       </c>
       <c r="J32" s="7" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="72"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K32" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="72"/>
         <v>5.834683954619125E-2</v>
       </c>
       <c r="L32" s="7">
@@ -2486,60 +4180,111 @@
         <v>-0.24436889077773055</v>
       </c>
       <c r="W32" s="7">
-        <f t="shared" ref="W32:Z32" si="27">W17/W16</f>
+        <f t="shared" ref="W32:Z32" si="73">W17/W16</f>
         <v>0.15939971608193065</v>
       </c>
       <c r="X32" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="73"/>
         <v>0.12914827529834885</v>
       </c>
       <c r="Y32" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="73"/>
         <v>0.11887382690302398</v>
       </c>
       <c r="Z32" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="73"/>
         <v>0.19066838876331935</v>
       </c>
+      <c r="AA32" s="7">
+        <f t="shared" ref="AA32:AK32" si="74">AA17/AA16</f>
+        <v>0.15</v>
+      </c>
+      <c r="AB32" s="7">
+        <f t="shared" si="74"/>
+        <v>0.15</v>
+      </c>
+      <c r="AC32" s="7">
+        <f t="shared" si="74"/>
+        <v>0.15</v>
+      </c>
+      <c r="AD32" s="7">
+        <f t="shared" si="74"/>
+        <v>0.15</v>
+      </c>
+      <c r="AE32" s="7">
+        <f t="shared" si="74"/>
+        <v>0.15</v>
+      </c>
+      <c r="AF32" s="7">
+        <f t="shared" si="74"/>
+        <v>0.15</v>
+      </c>
+      <c r="AG32" s="7">
+        <f t="shared" si="74"/>
+        <v>0.15</v>
+      </c>
+      <c r="AH32" s="7">
+        <f t="shared" si="74"/>
+        <v>0.15</v>
+      </c>
+      <c r="AI32" s="7">
+        <f t="shared" si="74"/>
+        <v>0.15</v>
+      </c>
+      <c r="AJ32" s="7">
+        <f t="shared" si="74"/>
+        <v>0.15</v>
+      </c>
+      <c r="AK32" s="7">
+        <f t="shared" si="74"/>
+        <v>0.15</v>
+      </c>
+      <c r="AN32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO32" s="12">
+        <f>AO30/AO31-1</f>
+        <v>-0.50646520170582687</v>
+      </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C33" s="7" t="e">
-        <f t="shared" ref="C33:K33" si="28">C18/C5</f>
+        <f t="shared" ref="C33:K33" si="75">C18/C5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D33" s="7" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="75"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E33" s="7" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="75"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F33" s="7" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="75"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G33" s="7" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="75"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H33" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="75"/>
         <v>1.7472017472017472E-3</v>
       </c>
       <c r="I33" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="75"/>
         <v>3.787878787878788E-3</v>
       </c>
       <c r="J33" s="7" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="75"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K33" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="75"/>
         <v>1.7612017612017611E-3</v>
       </c>
       <c r="L33" s="7">
@@ -2547,68 +4292,118 @@
         <v>3.2452715379544649E-3</v>
       </c>
       <c r="U33" s="7">
-        <f>U18/U5</f>
-        <v>4.8733158393790381E-3</v>
+        <f t="shared" ref="U33:Z33" si="76">U18/U16</f>
+        <v>5.3227360308285163E-2</v>
       </c>
       <c r="V33" s="7">
-        <f>V18/V5</f>
-        <v>3.1986145227702475E-3</v>
+        <f t="shared" si="76"/>
+        <v>-7.6923076923076927E-2</v>
       </c>
       <c r="W33" s="7">
-        <f t="shared" ref="W33:Z33" si="29">W18/W5</f>
-        <v>3.8516493756600607E-3</v>
+        <f t="shared" si="76"/>
+        <v>5.0294058000405595E-2</v>
       </c>
       <c r="X33" s="7">
-        <f t="shared" si="29"/>
-        <v>1.6548886304678415E-3</v>
+        <f t="shared" si="76"/>
+        <v>1.8146150073565473E-2</v>
       </c>
       <c r="Y33" s="7">
-        <f t="shared" si="29"/>
-        <v>2.6842716192687173E-3</v>
+        <f t="shared" si="76"/>
+        <v>4.8227320125130341E-2</v>
       </c>
       <c r="Z33" s="7">
-        <f t="shared" si="29"/>
-        <v>2.9601922267086132E-3</v>
+        <f>Z18/Z16</f>
+        <v>3.8585728123990956E-2</v>
+      </c>
+      <c r="AA33" s="7">
+        <f t="shared" ref="AA33:AK33" si="77">AA18/AA16</f>
+        <v>0.03</v>
+      </c>
+      <c r="AB33" s="7">
+        <f t="shared" si="77"/>
+        <v>0.03</v>
+      </c>
+      <c r="AC33" s="7">
+        <f t="shared" si="77"/>
+        <v>0.03</v>
+      </c>
+      <c r="AD33" s="7">
+        <f t="shared" si="77"/>
+        <v>0.03</v>
+      </c>
+      <c r="AE33" s="7">
+        <f t="shared" si="77"/>
+        <v>0.03</v>
+      </c>
+      <c r="AF33" s="7">
+        <f t="shared" si="77"/>
+        <v>0.03</v>
+      </c>
+      <c r="AG33" s="7">
+        <f t="shared" si="77"/>
+        <v>3.0000000000000002E-2</v>
+      </c>
+      <c r="AH33" s="7">
+        <f t="shared" si="77"/>
+        <v>0.03</v>
+      </c>
+      <c r="AI33" s="7">
+        <f t="shared" si="77"/>
+        <v>0.03</v>
+      </c>
+      <c r="AJ33" s="7">
+        <f t="shared" si="77"/>
+        <v>0.03</v>
+      </c>
+      <c r="AK33" s="7">
+        <f t="shared" si="77"/>
+        <v>0.03</v>
+      </c>
+      <c r="AN33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO33" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C34" s="7" t="e">
-        <f t="shared" ref="C34:K34" si="30">C19/C5</f>
+        <f t="shared" ref="C34:K34" si="78">C19/C5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D34" s="7" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="78"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E34" s="7" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="78"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F34" s="7" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="78"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G34" s="7" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="78"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H34" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="78"/>
         <v>7.2454272454272453E-2</v>
       </c>
       <c r="I34" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="78"/>
         <v>-7.3083778966131913E-2</v>
       </c>
       <c r="J34" s="7" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="78"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K34" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="78"/>
         <v>8.8526288526288521E-2</v>
       </c>
       <c r="L34" s="7">
@@ -2624,20 +4419,64 @@
         <v>-5.4941947797197237E-2</v>
       </c>
       <c r="W34" s="7">
-        <f t="shared" ref="W34:Z34" si="31">W19/W5</f>
+        <f t="shared" ref="W34:Z34" si="79">W19/W5</f>
         <v>6.0523700068335712E-2</v>
       </c>
       <c r="X34" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="79"/>
         <v>7.7764856725407755E-2</v>
       </c>
       <c r="Y34" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="79"/>
         <v>4.6358096343586765E-2</v>
       </c>
       <c r="Z34" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="79"/>
         <v>5.9129530084966186E-2</v>
+      </c>
+      <c r="AA34" s="7">
+        <f t="shared" ref="AA34:AK34" si="80">AA19/AA5</f>
+        <v>6.8539591126745653E-2</v>
+      </c>
+      <c r="AB34" s="7">
+        <f t="shared" si="80"/>
+        <v>6.9474541713325788E-2</v>
+      </c>
+      <c r="AC34" s="7">
+        <f t="shared" si="80"/>
+        <v>7.0127257226773265E-2</v>
+      </c>
+      <c r="AD34" s="7">
+        <f t="shared" si="80"/>
+        <v>7.0486192701102318E-2</v>
+      </c>
+      <c r="AE34" s="7">
+        <f t="shared" si="80"/>
+        <v>7.0884030567840831E-2</v>
+      </c>
+      <c r="AF34" s="7">
+        <f t="shared" si="80"/>
+        <v>7.1556390371420961E-2</v>
+      </c>
+      <c r="AG34" s="7">
+        <f t="shared" si="80"/>
+        <v>7.2234709127076149E-2</v>
+      </c>
+      <c r="AH34" s="7">
+        <f t="shared" si="80"/>
+        <v>7.2918934277079295E-2</v>
+      </c>
+      <c r="AI34" s="7">
+        <f t="shared" si="80"/>
+        <v>7.3609010054054139E-2</v>
+      </c>
+      <c r="AJ34" s="7">
+        <f t="shared" si="80"/>
+        <v>7.430487746444539E-2</v>
+      </c>
+      <c r="AK34" s="7">
+        <f t="shared" si="80"/>
+        <v>7.5006474275140914E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/RTX.xlsx
+++ b/Financial Analysis/RTX.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD18CDC-A799-49FD-891B-9FCAB4610D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4455DDB6-80A9-4E5C-9025-17FEB4188569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4DC2FBA0-6E3D-459B-9C6A-21AC42B1058B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4DC2FBA0-6E3D-459B-9C6A-21AC42B1058B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Model" sheetId="2" r:id="rId2"/>
+    <sheet name="Charts" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -278,7 +279,7 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Heavily overvalued</t>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -353,7 +354,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -376,11 +377,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -402,6 +418,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -419,6 +436,2173 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Revenue line growth</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Model!$B$23</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Product revenue y/y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Model!$B$2:$P$2</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="1">
+                  <c:v>Q122</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Q222</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Q322</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Q422</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Q123</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Q223</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Q323</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Q423</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Q124</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Q224</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Q324</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Q424</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Q125</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Q225</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Model!$C$23:$P$23</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="4">
+                  <c:v>7.7980104535491535E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.4061021373796683E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.1955817802403335E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.11855791037772745</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.5825068973230945E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8.6800379455210797E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.0135635880584424E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.7916494986952403E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-83EF-4913-BFC3-209BA1DBF00F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Model!$B$24</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Service revenue y/y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Model!$B$2:$P$2</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="1">
+                  <c:v>Q122</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Q222</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Q322</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Q422</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Q123</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Q223</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Q323</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Q423</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Q124</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Q224</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Q324</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Q424</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Q125</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Q225</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Model!$C$24:$P$24</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="4">
+                  <c:v>0.14867669953295271</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20907297830374749</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.15589988081048878</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.23188751191611057</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.12988479783148854</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.1998368678629614E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.10971334295731072</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8.0286322306055258E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.14254298280687716</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.16883116883116878</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-83EF-4913-BFC3-209BA1DBF00F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="638473432"/>
+        <c:axId val="638472352"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="638473432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="10000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="638472352"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="638472352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="638473432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Model!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Product revenue</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Model!$C$2:$P$2</c:f>
+              <c:strCache>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>Q122</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Q222</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Q322</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Q422</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Q123</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Q223</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Q323</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Q423</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Q124</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Q224</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Q324</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Q424</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Q125</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Q225</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Model!$C$3:$P$3</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>11862</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12258</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12756</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13897</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12787</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>13411</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8615</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14758</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14303</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14562</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14708</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>16039</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14591</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15551</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9B07-44D2-AD22-42E6A0AC66C5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Model!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Service revenue</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Model!$C$2:$P$2</c:f>
+              <c:strCache>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>Q122</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Q222</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Q322</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Q422</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Q123</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Q223</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Q323</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Q423</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Q124</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Q224</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Q324</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Q424</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Q125</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Q225</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Model!$C$4:$P$4</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>3854</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4056</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4195</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4196</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4427</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4904</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4849</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5169</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5159</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5381</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5584</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5715</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6030</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9B07-44D2-AD22-42E6A0AC66C5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="687957384"/>
+        <c:axId val="687960264"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="687957384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="687960264"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="687960264"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="687957384"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -431,8 +2615,8 @@
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -447,8 +2631,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14142720" y="7620"/>
-          <a:ext cx="0" cy="6118860"/>
+          <a:off x="16581120" y="7620"/>
+          <a:ext cx="0" cy="7780020"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -473,16 +2657,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -497,8 +2681,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9265920" y="0"/>
-          <a:ext cx="0" cy="6111240"/>
+          <a:off x="10469880" y="0"/>
+          <a:ext cx="0" cy="7239000"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -519,6 +2703,87 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46CB6465-E1DA-4EEF-9D96-F3842D5081D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>281940</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>586740</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA491106-A963-4B6E-A46D-2649FB539930}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -849,17 +3114,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="9">
-        <v>119.35</v>
+        <v>157.52000000000001</v>
       </c>
       <c r="E3" s="10">
-        <v>45770</v>
+        <v>45906</v>
       </c>
       <c r="F3" s="10">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45906</v>
       </c>
       <c r="G3" s="10">
-        <v>45867</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -867,11 +3132,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="3">
-        <f>1336</f>
-        <v>1336</v>
+        <f>1338.5</f>
+        <v>1338.5</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -880,7 +3145,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>159451.6</v>
+        <v>210840.52000000002</v>
       </c>
       <c r="E5" s="11"/>
     </row>
@@ -889,11 +3154,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="3">
-        <f>5157</f>
-        <v>5157</v>
+        <f>4782</f>
+        <v>4782</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -901,11 +3166,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="3">
-        <f>212+2844+38244</f>
-        <v>41300</v>
+        <f>1635+2084+38259</f>
+        <v>41978</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -914,7 +3179,7 @@
       </c>
       <c r="D8" s="3">
         <f>D6-D7</f>
-        <v>-36143</v>
+        <v>-37196</v>
       </c>
       <c r="E8" s="11"/>
     </row>
@@ -924,7 +3189,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>195594.6</v>
+        <v>248036.52000000002</v>
       </c>
       <c r="E9" s="11"/>
     </row>
@@ -1051,12 +3316,32 @@
       <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="C3" s="3">
+        <v>11862</v>
+      </c>
+      <c r="D3" s="3">
+        <v>12258</v>
+      </c>
+      <c r="E3" s="3">
+        <v>12756</v>
+      </c>
+      <c r="F3" s="3">
+        <f>X3-E3-D3-C3</f>
+        <v>13897</v>
+      </c>
+      <c r="G3" s="3">
+        <v>12787</v>
+      </c>
       <c r="H3" s="3">
         <v>13411</v>
       </c>
       <c r="I3" s="3">
         <v>8615</v>
       </c>
+      <c r="J3" s="3">
+        <f>Y3-I3-H3-G3</f>
+        <v>14758</v>
+      </c>
       <c r="K3" s="3">
         <v>14303</v>
       </c>
@@ -1066,9 +3351,24 @@
       <c r="M3" s="3">
         <v>14708</v>
       </c>
+      <c r="N3" s="3">
+        <f>Z3-M3-L3-K3</f>
+        <v>16039</v>
+      </c>
       <c r="O3" s="3">
         <v>14591</v>
       </c>
+      <c r="P3" s="3">
+        <v>15551</v>
+      </c>
+      <c r="Q3" s="3">
+        <f>M3*1.06</f>
+        <v>15590.480000000001</v>
+      </c>
+      <c r="R3" s="3">
+        <f>N3*1.05</f>
+        <v>16840.95</v>
+      </c>
       <c r="U3" s="3">
         <v>32998</v>
       </c>
@@ -1088,60 +3388,80 @@
         <v>59612</v>
       </c>
       <c r="AA3" s="3">
-        <f>Z3*1.07</f>
-        <v>63784.840000000004</v>
+        <f>SUM(O3:R3)</f>
+        <v>62573.430000000008</v>
       </c>
       <c r="AB3" s="3">
-        <f>AA3*1.05</f>
-        <v>66974.082000000009</v>
+        <f>AA3*1.04</f>
+        <v>65076.367200000008</v>
       </c>
       <c r="AC3" s="3">
         <f>AB3*1.03</f>
-        <v>68983.304460000014</v>
+        <v>67028.658216000011</v>
       </c>
       <c r="AD3" s="3">
         <f>AC3*1.02</f>
-        <v>70362.970549200021</v>
+        <v>68369.231380320009</v>
       </c>
       <c r="AE3" s="3">
-        <f>AD3*1.01</f>
-        <v>71066.600254692021</v>
+        <f t="shared" ref="AE3:AK3" si="0">AD3*1.02</f>
+        <v>69736.616007926408</v>
       </c>
       <c r="AF3" s="3">
-        <f t="shared" ref="AF3:AK3" si="0">AE3*1.01</f>
-        <v>71777.266257238938</v>
+        <f t="shared" si="0"/>
+        <v>71131.348328084932</v>
       </c>
       <c r="AG3" s="3">
         <f t="shared" si="0"/>
-        <v>72495.038919811326</v>
+        <v>72553.975294646632</v>
       </c>
       <c r="AH3" s="3">
         <f t="shared" si="0"/>
-        <v>73219.989309009441</v>
+        <v>74005.054800539569</v>
       </c>
       <c r="AI3" s="3">
         <f t="shared" si="0"/>
-        <v>73952.189202099529</v>
+        <v>75485.155896550365</v>
       </c>
       <c r="AJ3" s="3">
         <f t="shared" si="0"/>
-        <v>74691.711094120532</v>
+        <v>76994.859014481379</v>
       </c>
       <c r="AK3" s="3">
         <f t="shared" si="0"/>
-        <v>75438.628205061745</v>
+        <v>78534.756194771006</v>
       </c>
     </row>
     <row r="4" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="C4" s="3">
+        <v>3854</v>
+      </c>
+      <c r="D4" s="3">
+        <v>4056</v>
+      </c>
+      <c r="E4" s="3">
+        <v>4195</v>
+      </c>
+      <c r="F4" s="3">
+        <f>X4-E4-D4-C4</f>
+        <v>4196</v>
+      </c>
+      <c r="G4" s="3">
+        <v>4427</v>
+      </c>
       <c r="H4" s="3">
         <v>4904</v>
       </c>
       <c r="I4" s="3">
         <v>4849</v>
       </c>
+      <c r="J4" s="3">
+        <f>Y4-I4-H4-G4</f>
+        <v>5169</v>
+      </c>
       <c r="K4" s="3">
         <v>5002</v>
       </c>
@@ -1151,9 +3471,24 @@
       <c r="M4" s="3">
         <v>5381</v>
       </c>
+      <c r="N4" s="3">
+        <f>Z4-M4-L4-K4</f>
+        <v>5584</v>
+      </c>
       <c r="O4" s="3">
         <v>5715</v>
       </c>
+      <c r="P4" s="3">
+        <v>6030</v>
+      </c>
+      <c r="Q4" s="3">
+        <f>M4*1.17</f>
+        <v>6295.7699999999995</v>
+      </c>
+      <c r="R4" s="3">
+        <f>N4*1.18</f>
+        <v>6589.12</v>
+      </c>
       <c r="U4" s="3">
         <v>12351</v>
       </c>
@@ -1173,157 +3508,217 @@
         <v>21126</v>
       </c>
       <c r="AA4" s="3">
-        <f>Z4*1.08</f>
-        <v>22816.080000000002</v>
+        <f>SUM(O4:R4)</f>
+        <v>24629.89</v>
       </c>
       <c r="AB4" s="3">
-        <f>AA4*1.05</f>
-        <v>23956.884000000002</v>
+        <f>AA4*1.13</f>
+        <v>27831.775699999998</v>
       </c>
       <c r="AC4" s="3">
-        <f>AB4*1.04</f>
-        <v>24915.159360000001</v>
+        <f>AB4*1.09</f>
+        <v>30336.635513000001</v>
       </c>
       <c r="AD4" s="3">
-        <f>AC4*1.03</f>
-        <v>25662.614140800004</v>
+        <f>AC4*1.05</f>
+        <v>31853.467288650001</v>
       </c>
       <c r="AE4" s="3">
-        <f t="shared" ref="AE4:AK4" si="1">AD4*1.03</f>
-        <v>26432.492565024004</v>
+        <f>AD4*1.04</f>
+        <v>33127.605980196</v>
       </c>
       <c r="AF4" s="3">
-        <f t="shared" si="1"/>
-        <v>27225.467341974723</v>
+        <f>AE4*1.03</f>
+        <v>34121.434159601878</v>
       </c>
       <c r="AG4" s="3">
-        <f t="shared" si="1"/>
-        <v>28042.231362233964</v>
+        <f t="shared" ref="AG4:AK4" si="1">AF4*1.03</f>
+        <v>35145.077184389935</v>
       </c>
       <c r="AH4" s="3">
         <f t="shared" si="1"/>
-        <v>28883.498303100983</v>
+        <v>36199.429499921636</v>
       </c>
       <c r="AI4" s="3">
         <f t="shared" si="1"/>
-        <v>29750.003252194012</v>
+        <v>37285.412384919284</v>
       </c>
       <c r="AJ4" s="3">
         <f t="shared" si="1"/>
-        <v>30642.503349759834</v>
+        <v>38403.974756466865</v>
       </c>
       <c r="AK4" s="3">
         <f t="shared" si="1"/>
-        <v>31561.77845025263</v>
+        <v>39556.093999160876</v>
       </c>
     </row>
     <row r="5" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="C5" s="5">
+        <f t="shared" ref="C5:P5" si="2">C3+C4</f>
+        <v>15716</v>
+      </c>
+      <c r="D5" s="5">
+        <f t="shared" si="2"/>
+        <v>16314</v>
+      </c>
+      <c r="E5" s="5">
+        <f t="shared" si="2"/>
+        <v>16951</v>
+      </c>
+      <c r="F5" s="5">
+        <f t="shared" si="2"/>
+        <v>18093</v>
+      </c>
+      <c r="G5" s="5">
+        <f t="shared" si="2"/>
+        <v>17214</v>
+      </c>
       <c r="H5" s="5">
-        <f>H3+H4</f>
+        <f t="shared" si="2"/>
         <v>18315</v>
       </c>
       <c r="I5" s="5">
-        <f>I3+I4</f>
+        <f t="shared" si="2"/>
         <v>13464</v>
       </c>
+      <c r="J5" s="5">
+        <f t="shared" si="2"/>
+        <v>19927</v>
+      </c>
       <c r="K5" s="5">
-        <f>K3+K4</f>
+        <f t="shared" si="2"/>
         <v>19305</v>
       </c>
       <c r="L5" s="5">
-        <f>L3+L4</f>
+        <f t="shared" si="2"/>
         <v>19721</v>
       </c>
       <c r="M5" s="5">
-        <f>M3+M4</f>
+        <f t="shared" si="2"/>
         <v>20089</v>
       </c>
+      <c r="N5" s="5">
+        <f t="shared" si="2"/>
+        <v>21623</v>
+      </c>
       <c r="O5" s="5">
-        <f>O3+O4</f>
+        <f t="shared" si="2"/>
         <v>20306</v>
       </c>
+      <c r="P5" s="5">
+        <f t="shared" si="2"/>
+        <v>21581</v>
+      </c>
+      <c r="Q5" s="5">
+        <f t="shared" ref="Q5:R5" si="3">Q3+Q4</f>
+        <v>21886.25</v>
+      </c>
+      <c r="R5" s="5">
+        <f t="shared" si="3"/>
+        <v>23430.07</v>
+      </c>
       <c r="U5" s="5">
-        <f t="shared" ref="U5:AK5" si="2">U3+U4</f>
+        <f t="shared" ref="U5:AK5" si="4">U3+U4</f>
         <v>45349</v>
       </c>
       <c r="V5" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>56587</v>
       </c>
       <c r="W5" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>64388</v>
       </c>
       <c r="X5" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>67074</v>
       </c>
       <c r="Y5" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>68920</v>
       </c>
       <c r="Z5" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>80738</v>
       </c>
       <c r="AA5" s="5">
-        <f t="shared" si="2"/>
-        <v>86600.920000000013</v>
+        <f t="shared" si="4"/>
+        <v>87203.32</v>
       </c>
       <c r="AB5" s="5">
-        <f t="shared" si="2"/>
-        <v>90930.966000000015</v>
+        <f t="shared" si="4"/>
+        <v>92908.142900000006</v>
       </c>
       <c r="AC5" s="5">
-        <f t="shared" si="2"/>
-        <v>93898.463820000019</v>
+        <f t="shared" si="4"/>
+        <v>97365.293729000012</v>
       </c>
       <c r="AD5" s="5">
-        <f t="shared" si="2"/>
-        <v>96025.584690000018</v>
+        <f t="shared" si="4"/>
+        <v>100222.69866897001</v>
       </c>
       <c r="AE5" s="5">
-        <f t="shared" si="2"/>
-        <v>97499.092819716025</v>
+        <f t="shared" si="4"/>
+        <v>102864.22198812242</v>
       </c>
       <c r="AF5" s="5">
-        <f t="shared" si="2"/>
-        <v>99002.733599213665</v>
+        <f t="shared" si="4"/>
+        <v>105252.78248768681</v>
       </c>
       <c r="AG5" s="5">
-        <f t="shared" si="2"/>
-        <v>100537.2702820453</v>
+        <f t="shared" si="4"/>
+        <v>107699.05247903656</v>
       </c>
       <c r="AH5" s="5">
-        <f t="shared" si="2"/>
-        <v>102103.48761211042</v>
+        <f t="shared" si="4"/>
+        <v>110204.4843004612</v>
       </c>
       <c r="AI5" s="5">
-        <f t="shared" si="2"/>
-        <v>103702.19245429354</v>
+        <f t="shared" si="4"/>
+        <v>112770.56828146965</v>
       </c>
       <c r="AJ5" s="5">
-        <f t="shared" si="2"/>
-        <v>105334.21444388037</v>
+        <f t="shared" si="4"/>
+        <v>115398.83377094824</v>
       </c>
       <c r="AK5" s="5">
-        <f t="shared" si="2"/>
-        <v>107000.40665531438</v>
+        <f t="shared" si="4"/>
+        <v>118090.85019393188</v>
       </c>
     </row>
     <row r="6" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="C6" s="3">
+        <v>9820</v>
+      </c>
+      <c r="D6" s="3">
+        <v>10040</v>
+      </c>
+      <c r="E6" s="3">
+        <v>10493</v>
+      </c>
+      <c r="F6" s="3">
+        <f t="shared" ref="F6:F7" si="5">X6-E6-D6-C6</f>
+        <v>11574</v>
+      </c>
+      <c r="G6" s="3">
+        <v>10700</v>
+      </c>
       <c r="H6" s="3">
         <v>11089</v>
       </c>
       <c r="I6" s="3">
         <v>9289</v>
       </c>
+      <c r="J6" s="3">
+        <f t="shared" ref="J6:J7" si="6">Y6-I6-H6-G6</f>
+        <v>12347</v>
+      </c>
       <c r="K6" s="3">
         <v>12216</v>
       </c>
@@ -1333,9 +3728,24 @@
       <c r="M6" s="3">
         <v>12336</v>
       </c>
+      <c r="N6" s="3">
+        <f t="shared" ref="N6:N7" si="7">Z6-M6-L6-K6</f>
+        <v>13591</v>
+      </c>
       <c r="O6" s="3">
         <v>12283</v>
       </c>
+      <c r="P6" s="3">
+        <v>12989</v>
+      </c>
+      <c r="Q6" s="3">
+        <f>Q3*0.84</f>
+        <v>13096.003200000001</v>
+      </c>
+      <c r="R6" s="3">
+        <f>R3*0.84</f>
+        <v>14146.397999999999</v>
+      </c>
       <c r="U6" s="3">
         <v>26910</v>
       </c>
@@ -1355,60 +3765,80 @@
         <v>50768</v>
       </c>
       <c r="AA6" s="3">
-        <f>AA3*0.85</f>
-        <v>54217.114000000001</v>
+        <f t="shared" ref="AA6:AA7" si="8">SUM(O6:R6)</f>
+        <v>52514.4012</v>
       </c>
       <c r="AB6" s="3">
-        <f t="shared" ref="AB6:AK6" si="3">AB3*0.85</f>
-        <v>56927.969700000009</v>
+        <f>AB3*0.84</f>
+        <v>54664.148448000007</v>
       </c>
       <c r="AC6" s="3">
-        <f t="shared" si="3"/>
-        <v>58635.80879100001</v>
+        <f t="shared" ref="AC6:AK6" si="9">AC3*0.84</f>
+        <v>56304.072901440006</v>
       </c>
       <c r="AD6" s="3">
-        <f t="shared" si="3"/>
-        <v>59808.524966820019</v>
+        <f t="shared" si="9"/>
+        <v>57430.154359468805</v>
       </c>
       <c r="AE6" s="3">
-        <f t="shared" si="3"/>
-        <v>60406.610216488218</v>
+        <f t="shared" si="9"/>
+        <v>58578.757446658179</v>
       </c>
       <c r="AF6" s="3">
-        <f t="shared" si="3"/>
-        <v>61010.676318653095</v>
+        <f t="shared" si="9"/>
+        <v>59750.332595591339</v>
       </c>
       <c r="AG6" s="3">
-        <f t="shared" si="3"/>
-        <v>61620.783081839625</v>
+        <f t="shared" si="9"/>
+        <v>60945.339247503172</v>
       </c>
       <c r="AH6" s="3">
-        <f t="shared" si="3"/>
-        <v>62236.990912658024</v>
+        <f t="shared" si="9"/>
+        <v>62164.246032453237</v>
       </c>
       <c r="AI6" s="3">
-        <f t="shared" si="3"/>
-        <v>62859.360821784598</v>
+        <f t="shared" si="9"/>
+        <v>63407.530953102301</v>
       </c>
       <c r="AJ6" s="3">
-        <f t="shared" si="3"/>
-        <v>63487.95443000245</v>
+        <f t="shared" si="9"/>
+        <v>64675.681572164358</v>
       </c>
       <c r="AK6" s="3">
-        <f t="shared" si="3"/>
-        <v>64122.833974302484</v>
+        <f t="shared" si="9"/>
+        <v>65969.19520360764</v>
       </c>
     </row>
     <row r="7" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="C7" s="3">
+        <v>2740</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2816</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2971</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" si="5"/>
+        <v>2952</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2945</v>
+      </c>
       <c r="H7" s="3">
         <v>3429</v>
       </c>
       <c r="I7" s="3">
         <v>3461</v>
       </c>
+      <c r="J7" s="3">
+        <f t="shared" si="6"/>
+        <v>3571</v>
+      </c>
       <c r="K7" s="3">
         <v>3528</v>
       </c>
@@ -1418,9 +3848,24 @@
       <c r="M7" s="3">
         <v>3719</v>
       </c>
+      <c r="N7" s="3">
+        <f t="shared" si="7"/>
+        <v>3797</v>
+      </c>
       <c r="O7" s="3">
         <v>3907</v>
       </c>
+      <c r="P7" s="3">
+        <v>4216</v>
+      </c>
+      <c r="Q7" s="3">
+        <f>Q4*0.69</f>
+        <v>4344.0812999999989</v>
+      </c>
+      <c r="R7" s="3">
+        <f>R4*0.69</f>
+        <v>4546.4928</v>
+      </c>
       <c r="U7" s="3">
         <v>7688</v>
       </c>
@@ -1440,254 +3885,354 @@
         <v>14560</v>
       </c>
       <c r="AA7" s="3">
-        <f>AA4*0.69</f>
-        <v>15743.0952</v>
+        <f t="shared" si="8"/>
+        <v>17013.574099999998</v>
       </c>
       <c r="AB7" s="3">
-        <f t="shared" ref="AB7:AK7" si="4">AB4*0.69</f>
-        <v>16530.249960000001</v>
+        <f t="shared" ref="AB7:AK7" si="10">AB4*0.69</f>
+        <v>19203.925232999998</v>
       </c>
       <c r="AC7" s="3">
-        <f t="shared" si="4"/>
-        <v>17191.459958399999</v>
+        <f t="shared" si="10"/>
+        <v>20932.278503969999</v>
       </c>
       <c r="AD7" s="3">
-        <f t="shared" si="4"/>
-        <v>17707.203757152001</v>
+        <f t="shared" si="10"/>
+        <v>21978.8924291685</v>
       </c>
       <c r="AE7" s="3">
-        <f t="shared" si="4"/>
-        <v>18238.41986986656</v>
+        <f t="shared" si="10"/>
+        <v>22858.048126335238</v>
       </c>
       <c r="AF7" s="3">
-        <f t="shared" si="4"/>
-        <v>18785.572465962559</v>
+        <f t="shared" si="10"/>
+        <v>23543.789570125293</v>
       </c>
       <c r="AG7" s="3">
-        <f t="shared" si="4"/>
-        <v>19349.139639941433</v>
+        <f t="shared" si="10"/>
+        <v>24250.103257229053</v>
       </c>
       <c r="AH7" s="3">
-        <f t="shared" si="4"/>
-        <v>19929.613829139678</v>
+        <f t="shared" si="10"/>
+        <v>24977.606354945929</v>
       </c>
       <c r="AI7" s="3">
-        <f t="shared" si="4"/>
-        <v>20527.502244013867</v>
+        <f t="shared" si="10"/>
+        <v>25726.934545594304</v>
       </c>
       <c r="AJ7" s="3">
-        <f t="shared" si="4"/>
-        <v>21143.327311334284</v>
+        <f t="shared" si="10"/>
+        <v>26498.742581962135</v>
       </c>
       <c r="AK7" s="3">
-        <f t="shared" si="4"/>
-        <v>21777.627130674315</v>
+        <f t="shared" si="10"/>
+        <v>27293.704859421003</v>
       </c>
     </row>
     <row r="8" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="C8" s="3">
+        <f t="shared" ref="C8:P8" si="11">C6+C7</f>
+        <v>12560</v>
+      </c>
+      <c r="D8" s="3">
+        <f t="shared" si="11"/>
+        <v>12856</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="11"/>
+        <v>13464</v>
+      </c>
+      <c r="F8" s="3">
+        <f t="shared" si="11"/>
+        <v>14526</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" si="11"/>
+        <v>13645</v>
+      </c>
       <c r="H8" s="3">
-        <f>H6+H7</f>
+        <f t="shared" si="11"/>
         <v>14518</v>
       </c>
       <c r="I8" s="3">
-        <f>I6+I7</f>
+        <f t="shared" si="11"/>
         <v>12750</v>
       </c>
+      <c r="J8" s="3">
+        <f t="shared" si="11"/>
+        <v>15918</v>
+      </c>
       <c r="K8" s="3">
-        <f>K6+K7</f>
+        <f t="shared" si="11"/>
         <v>15744</v>
       </c>
       <c r="L8" s="3">
-        <f>L6+L7</f>
+        <f t="shared" si="11"/>
         <v>16141</v>
       </c>
       <c r="M8" s="3">
-        <f>M6+M7</f>
+        <f t="shared" si="11"/>
         <v>16055</v>
       </c>
+      <c r="N8" s="3">
+        <f t="shared" si="11"/>
+        <v>17388</v>
+      </c>
       <c r="O8" s="3">
-        <f>O6+O7</f>
+        <f t="shared" si="11"/>
         <v>16190</v>
       </c>
+      <c r="P8" s="3">
+        <f t="shared" si="11"/>
+        <v>17205</v>
+      </c>
+      <c r="Q8" s="3">
+        <f t="shared" ref="Q8:R8" si="12">Q6+Q7</f>
+        <v>17440.084500000001</v>
+      </c>
+      <c r="R8" s="3">
+        <f t="shared" si="12"/>
+        <v>18692.890800000001</v>
+      </c>
       <c r="U8" s="3">
-        <f t="shared" ref="U8:Z8" si="5">U6+U7</f>
+        <f t="shared" ref="U8:Z8" si="13">U6+U7</f>
         <v>34598</v>
       </c>
       <c r="V8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>48056</v>
       </c>
       <c r="W8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>51897</v>
       </c>
       <c r="X8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>53406</v>
       </c>
       <c r="Y8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>56831</v>
       </c>
       <c r="Z8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>65328</v>
       </c>
       <c r="AA8" s="3">
-        <f t="shared" ref="AA8:AK8" si="6">AA6+AA7</f>
-        <v>69960.209199999998</v>
+        <f t="shared" ref="AA8:AK8" si="14">AA6+AA7</f>
+        <v>69527.975299999991</v>
       </c>
       <c r="AB8" s="3">
-        <f t="shared" si="6"/>
-        <v>73458.219660000002</v>
+        <f t="shared" si="14"/>
+        <v>73868.073681000009</v>
       </c>
       <c r="AC8" s="3">
-        <f t="shared" si="6"/>
-        <v>75827.268749400013</v>
+        <f t="shared" si="14"/>
+        <v>77236.351405410009</v>
       </c>
       <c r="AD8" s="3">
-        <f t="shared" si="6"/>
-        <v>77515.728723972017</v>
+        <f t="shared" si="14"/>
+        <v>79409.046788637308</v>
       </c>
       <c r="AE8" s="3">
-        <f t="shared" si="6"/>
-        <v>78645.030086354775</v>
+        <f t="shared" si="14"/>
+        <v>81436.805572993413</v>
       </c>
       <c r="AF8" s="3">
-        <f t="shared" si="6"/>
-        <v>79796.248784615658</v>
+        <f t="shared" si="14"/>
+        <v>83294.122165716632</v>
       </c>
       <c r="AG8" s="3">
-        <f t="shared" si="6"/>
-        <v>80969.922721781055</v>
+        <f t="shared" si="14"/>
+        <v>85195.442504732229</v>
       </c>
       <c r="AH8" s="3">
-        <f t="shared" si="6"/>
-        <v>82166.604741797695</v>
+        <f t="shared" si="14"/>
+        <v>87141.852387399165</v>
       </c>
       <c r="AI8" s="3">
-        <f t="shared" si="6"/>
-        <v>83386.863065798461</v>
+        <f t="shared" si="14"/>
+        <v>89134.465498696605</v>
       </c>
       <c r="AJ8" s="3">
-        <f t="shared" si="6"/>
-        <v>84631.28174133673</v>
+        <f t="shared" si="14"/>
+        <v>91174.424154126493</v>
       </c>
       <c r="AK8" s="3">
-        <f t="shared" si="6"/>
-        <v>85900.461104976799</v>
+        <f t="shared" si="14"/>
+        <v>93262.900063028646</v>
       </c>
     </row>
     <row r="9" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="C9" s="5">
+        <f t="shared" ref="C9:P9" si="15">C5-C8</f>
+        <v>3156</v>
+      </c>
+      <c r="D9" s="5">
+        <f t="shared" si="15"/>
+        <v>3458</v>
+      </c>
+      <c r="E9" s="5">
+        <f t="shared" si="15"/>
+        <v>3487</v>
+      </c>
+      <c r="F9" s="5">
+        <f t="shared" si="15"/>
+        <v>3567</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" si="15"/>
+        <v>3569</v>
+      </c>
       <c r="H9" s="5">
-        <f>H5-H8</f>
+        <f t="shared" si="15"/>
         <v>3797</v>
       </c>
       <c r="I9" s="5">
-        <f>I5-I8</f>
+        <f t="shared" si="15"/>
         <v>714</v>
       </c>
+      <c r="J9" s="5">
+        <f t="shared" si="15"/>
+        <v>4009</v>
+      </c>
       <c r="K9" s="5">
-        <f>K5-K8</f>
+        <f t="shared" si="15"/>
         <v>3561</v>
       </c>
       <c r="L9" s="5">
-        <f>L5-L8</f>
+        <f t="shared" si="15"/>
         <v>3580</v>
       </c>
       <c r="M9" s="5">
-        <f>M5-M8</f>
+        <f t="shared" si="15"/>
         <v>4034</v>
       </c>
+      <c r="N9" s="5">
+        <f t="shared" si="15"/>
+        <v>4235</v>
+      </c>
       <c r="O9" s="5">
-        <f>O5-O8</f>
+        <f t="shared" si="15"/>
         <v>4116</v>
       </c>
+      <c r="P9" s="5">
+        <f t="shared" si="15"/>
+        <v>4376</v>
+      </c>
+      <c r="Q9" s="5">
+        <f t="shared" ref="Q9:R9" si="16">Q5-Q8</f>
+        <v>4446.1654999999992</v>
+      </c>
+      <c r="R9" s="5">
+        <f t="shared" si="16"/>
+        <v>4737.1791999999987</v>
+      </c>
       <c r="U9" s="5">
-        <f t="shared" ref="U9:Z9" si="7">U5-U8</f>
+        <f t="shared" ref="U9:Z9" si="17">U5-U8</f>
         <v>10751</v>
       </c>
       <c r="V9" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v>8531</v>
       </c>
       <c r="W9" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v>12491</v>
       </c>
       <c r="X9" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v>13668</v>
       </c>
       <c r="Y9" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v>12089</v>
       </c>
       <c r="Z9" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v>15410</v>
       </c>
       <c r="AA9" s="5">
-        <f t="shared" ref="AA9:AK9" si="8">AA5-AA8</f>
-        <v>16640.710800000015</v>
+        <f t="shared" ref="AA9:AK9" si="18">AA5-AA8</f>
+        <v>17675.344700000016</v>
       </c>
       <c r="AB9" s="5">
-        <f t="shared" si="8"/>
-        <v>17472.746340000012</v>
+        <f t="shared" si="18"/>
+        <v>19040.069218999997</v>
       </c>
       <c r="AC9" s="5">
-        <f t="shared" si="8"/>
-        <v>18071.195070600006</v>
+        <f t="shared" si="18"/>
+        <v>20128.942323590003</v>
       </c>
       <c r="AD9" s="5">
-        <f t="shared" si="8"/>
-        <v>18509.855966028001</v>
+        <f t="shared" si="18"/>
+        <v>20813.651880332705</v>
       </c>
       <c r="AE9" s="5">
-        <f t="shared" si="8"/>
-        <v>18854.06273336125</v>
+        <f t="shared" si="18"/>
+        <v>21427.416415129002</v>
       </c>
       <c r="AF9" s="5">
-        <f t="shared" si="8"/>
-        <v>19206.484814598007</v>
+        <f t="shared" si="18"/>
+        <v>21958.660321970179</v>
       </c>
       <c r="AG9" s="5">
-        <f t="shared" si="8"/>
-        <v>19567.347560264243</v>
+        <f t="shared" si="18"/>
+        <v>22503.609974304331</v>
       </c>
       <c r="AH9" s="5">
-        <f t="shared" si="8"/>
-        <v>19936.882870312722</v>
+        <f t="shared" si="18"/>
+        <v>23062.63191306204</v>
       </c>
       <c r="AI9" s="5">
-        <f t="shared" si="8"/>
-        <v>20315.329388495084</v>
+        <f t="shared" si="18"/>
+        <v>23636.102782773043</v>
       </c>
       <c r="AJ9" s="5">
-        <f t="shared" si="8"/>
-        <v>20702.932702543636</v>
+        <f t="shared" si="18"/>
+        <v>24224.409616821751</v>
       </c>
       <c r="AK9" s="5">
-        <f t="shared" si="8"/>
-        <v>21099.945550337579</v>
+        <f t="shared" si="18"/>
+        <v>24827.950130903235</v>
       </c>
     </row>
     <row r="10" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="C10" s="3">
+        <v>635</v>
+      </c>
+      <c r="D10" s="3">
+        <v>698</v>
+      </c>
+      <c r="E10" s="3">
+        <v>662</v>
+      </c>
+      <c r="F10" s="3">
+        <f t="shared" ref="F10:F11" si="19">X10-E10-D10-C10</f>
+        <v>716</v>
+      </c>
+      <c r="G10" s="3">
+        <v>607</v>
+      </c>
       <c r="H10" s="3">
         <v>729</v>
       </c>
       <c r="I10" s="3">
         <v>712</v>
       </c>
+      <c r="J10" s="3">
+        <f t="shared" ref="J10:J11" si="20">Y10-I10-H10-G10</f>
+        <v>757</v>
+      </c>
       <c r="K10" s="3">
         <v>669</v>
       </c>
@@ -1697,9 +4242,24 @@
       <c r="M10" s="3">
         <v>751</v>
       </c>
+      <c r="N10" s="3">
+        <f t="shared" ref="N10:N11" si="21">Z10-M10-L10-K10</f>
+        <v>808</v>
+      </c>
       <c r="O10" s="3">
         <v>637</v>
       </c>
+      <c r="P10" s="3">
+        <v>697</v>
+      </c>
+      <c r="Q10" s="3">
+        <f>M10*0.98</f>
+        <v>735.98</v>
+      </c>
+      <c r="R10" s="3">
+        <f>N10*0.98</f>
+        <v>791.84</v>
+      </c>
       <c r="U10" s="3">
         <v>2452</v>
       </c>
@@ -1719,60 +4279,80 @@
         <v>2934</v>
       </c>
       <c r="AA10" s="3">
-        <f>Z10*1.02</f>
-        <v>2992.68</v>
+        <f t="shared" ref="AA10:AA11" si="22">SUM(O10:R10)</f>
+        <v>2861.82</v>
       </c>
       <c r="AB10" s="3">
-        <f t="shared" ref="AB10:AK10" si="9">AA10*1.02</f>
-        <v>3052.5335999999998</v>
+        <f>AA10*1.01</f>
+        <v>2890.4382000000001</v>
       </c>
       <c r="AC10" s="3">
-        <f t="shared" si="9"/>
-        <v>3113.5842719999996</v>
+        <f t="shared" ref="AC10:AE10" si="23">AB10*1.02</f>
+        <v>2948.2469639999999</v>
       </c>
       <c r="AD10" s="3">
-        <f t="shared" si="9"/>
-        <v>3175.8559574399997</v>
+        <f t="shared" si="23"/>
+        <v>3007.2119032800001</v>
       </c>
       <c r="AE10" s="3">
-        <f t="shared" si="9"/>
-        <v>3239.3730765887999</v>
+        <f t="shared" si="23"/>
+        <v>3067.3561413456</v>
       </c>
       <c r="AF10" s="3">
         <f>AE10*1.01</f>
-        <v>3271.7668073546879</v>
+        <v>3098.0297027590559</v>
       </c>
       <c r="AG10" s="3">
-        <f t="shared" ref="AG10:AK10" si="10">AF10*1.01</f>
-        <v>3304.4844754282349</v>
+        <f t="shared" ref="AG10:AK10" si="24">AF10*1.01</f>
+        <v>3129.0099997866464</v>
       </c>
       <c r="AH10" s="3">
-        <f t="shared" si="10"/>
-        <v>3337.529320182517</v>
+        <f t="shared" si="24"/>
+        <v>3160.3000997845129</v>
       </c>
       <c r="AI10" s="3">
-        <f t="shared" si="10"/>
-        <v>3370.9046133843422</v>
+        <f t="shared" si="24"/>
+        <v>3191.9031007823583</v>
       </c>
       <c r="AJ10" s="3">
-        <f t="shared" si="10"/>
-        <v>3404.6136595181856</v>
+        <f t="shared" si="24"/>
+        <v>3223.8221317901821</v>
       </c>
       <c r="AK10" s="3">
-        <f t="shared" si="10"/>
-        <v>3438.6597961133675</v>
+        <f t="shared" si="24"/>
+        <v>3256.0603531080837</v>
       </c>
     </row>
     <row r="11" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="C11" s="3">
+        <v>1469</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1424</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1351</v>
+      </c>
+      <c r="F11" s="3">
+        <f t="shared" si="19"/>
+        <v>1329</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1398</v>
+      </c>
       <c r="H11" s="3">
         <v>1600</v>
       </c>
       <c r="I11" s="3">
         <v>1401</v>
       </c>
+      <c r="J11" s="3">
+        <f t="shared" si="20"/>
+        <v>1410</v>
+      </c>
       <c r="K11" s="3">
         <v>1394</v>
       </c>
@@ -1782,9 +4362,24 @@
       <c r="M11" s="3">
         <v>1389</v>
       </c>
+      <c r="N11" s="3">
+        <f t="shared" si="21"/>
+        <v>1574</v>
+      </c>
       <c r="O11" s="3">
         <v>1448</v>
       </c>
+      <c r="P11" s="3">
+        <v>1573</v>
+      </c>
+      <c r="Q11" s="3">
+        <f>Q5*0.07</f>
+        <v>1532.0375000000001</v>
+      </c>
+      <c r="R11" s="3">
+        <f>R5*0.07</f>
+        <v>1640.1049</v>
+      </c>
       <c r="U11" s="3">
         <v>3711</v>
       </c>
@@ -1804,157 +4399,217 @@
         <v>5806</v>
       </c>
       <c r="AA11" s="3">
-        <f>AA5*0.07</f>
-        <v>6062.0644000000011</v>
+        <f t="shared" si="22"/>
+        <v>6193.1424000000006</v>
       </c>
       <c r="AB11" s="3">
-        <f t="shared" ref="AB11:AK11" si="11">AB5*0.07</f>
-        <v>6365.167620000002</v>
+        <f t="shared" ref="AB11:AK11" si="25">AB5*0.07</f>
+        <v>6503.5700030000007</v>
       </c>
       <c r="AC11" s="3">
-        <f t="shared" si="11"/>
-        <v>6572.8924674000018</v>
+        <f t="shared" si="25"/>
+        <v>6815.570561030001</v>
       </c>
       <c r="AD11" s="3">
-        <f t="shared" si="11"/>
-        <v>6721.7909283000017</v>
+        <f t="shared" si="25"/>
+        <v>7015.5889068279012</v>
       </c>
       <c r="AE11" s="3">
-        <f t="shared" si="11"/>
-        <v>6824.9364973801221</v>
+        <f t="shared" si="25"/>
+        <v>7200.4955391685698</v>
       </c>
       <c r="AF11" s="3">
-        <f t="shared" si="11"/>
-        <v>6930.1913519449572</v>
+        <f t="shared" si="25"/>
+        <v>7367.6947741380773</v>
       </c>
       <c r="AG11" s="3">
-        <f t="shared" si="11"/>
-        <v>7037.6089197431711</v>
+        <f t="shared" si="25"/>
+        <v>7538.9336735325596</v>
       </c>
       <c r="AH11" s="3">
-        <f t="shared" si="11"/>
-        <v>7147.2441328477298</v>
+        <f t="shared" si="25"/>
+        <v>7714.3139010322848</v>
       </c>
       <c r="AI11" s="3">
-        <f t="shared" si="11"/>
-        <v>7259.1534718005487</v>
+        <f t="shared" si="25"/>
+        <v>7893.939779702876</v>
       </c>
       <c r="AJ11" s="3">
-        <f t="shared" si="11"/>
-        <v>7373.395011071626</v>
+        <f t="shared" si="25"/>
+        <v>8077.9183639663779</v>
       </c>
       <c r="AK11" s="3">
-        <f t="shared" si="11"/>
-        <v>7490.0284658720075</v>
+        <f t="shared" si="25"/>
+        <v>8266.359513575233</v>
       </c>
     </row>
     <row r="12" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="C12" s="5">
+        <f t="shared" ref="C12:P12" si="26">C9-C10-C11</f>
+        <v>1052</v>
+      </c>
+      <c r="D12" s="5">
+        <f t="shared" si="26"/>
+        <v>1336</v>
+      </c>
+      <c r="E12" s="5">
+        <f t="shared" si="26"/>
+        <v>1474</v>
+      </c>
+      <c r="F12" s="5">
+        <f t="shared" si="26"/>
+        <v>1522</v>
+      </c>
+      <c r="G12" s="5">
+        <f t="shared" si="26"/>
+        <v>1564</v>
+      </c>
       <c r="H12" s="5">
-        <f>H9-H10-H11</f>
+        <f t="shared" si="26"/>
         <v>1468</v>
       </c>
       <c r="I12" s="5">
-        <f>I9-I10-I11</f>
+        <f t="shared" si="26"/>
         <v>-1399</v>
       </c>
+      <c r="J12" s="5">
+        <f t="shared" si="26"/>
+        <v>1842</v>
+      </c>
       <c r="K12" s="5">
-        <f>K9-K10-K11</f>
+        <f t="shared" si="26"/>
         <v>1498</v>
       </c>
       <c r="L12" s="5">
-        <f>L9-L10-L11</f>
+        <f t="shared" si="26"/>
         <v>1425</v>
       </c>
       <c r="M12" s="5">
-        <f>M9-M10-M11</f>
+        <f t="shared" si="26"/>
         <v>1894</v>
       </c>
+      <c r="N12" s="5">
+        <f t="shared" si="26"/>
+        <v>1853</v>
+      </c>
       <c r="O12" s="5">
-        <f>O9-O10-O11</f>
+        <f t="shared" si="26"/>
         <v>2031</v>
       </c>
+      <c r="P12" s="5">
+        <f t="shared" si="26"/>
+        <v>2106</v>
+      </c>
+      <c r="Q12" s="5">
+        <f t="shared" ref="Q12:R12" si="27">Q9-Q10-Q11</f>
+        <v>2178.1479999999992</v>
+      </c>
+      <c r="R12" s="5">
+        <f t="shared" si="27"/>
+        <v>2305.2342999999983</v>
+      </c>
       <c r="U12" s="5">
-        <f t="shared" ref="U12:AA12" si="12">U9-U10-U11</f>
+        <f t="shared" ref="U12:AA12" si="28">U9-U10-U11</f>
         <v>4588</v>
       </c>
       <c r="V12" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>409</v>
       </c>
       <c r="W12" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>4535</v>
       </c>
       <c r="X12" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>5384</v>
       </c>
       <c r="Y12" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>3475</v>
       </c>
       <c r="Z12" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>6670</v>
       </c>
       <c r="AA12" s="5">
-        <f t="shared" si="12"/>
-        <v>7585.9664000000139</v>
+        <f t="shared" si="28"/>
+        <v>8620.3823000000157</v>
       </c>
       <c r="AB12" s="5">
-        <f t="shared" ref="AB12:AK12" si="13">AB9-AB10-AB11</f>
-        <v>8055.0451200000116</v>
+        <f t="shared" ref="AB12:AK12" si="29">AB9-AB10-AB11</f>
+        <v>9646.061015999996</v>
       </c>
       <c r="AC12" s="5">
-        <f t="shared" si="13"/>
-        <v>8384.7183312000052</v>
+        <f t="shared" si="29"/>
+        <v>10365.124798560004</v>
       </c>
       <c r="AD12" s="5">
-        <f t="shared" si="13"/>
-        <v>8612.2090802880011</v>
+        <f t="shared" si="29"/>
+        <v>10790.851070224804</v>
       </c>
       <c r="AE12" s="5">
-        <f t="shared" si="13"/>
-        <v>8789.7531593923286</v>
+        <f t="shared" si="29"/>
+        <v>11159.564734614833</v>
       </c>
       <c r="AF12" s="5">
-        <f t="shared" si="13"/>
-        <v>9004.5266552983612</v>
+        <f t="shared" si="29"/>
+        <v>11492.935845073045</v>
       </c>
       <c r="AG12" s="5">
-        <f t="shared" si="13"/>
-        <v>9225.254165092836</v>
+        <f t="shared" si="29"/>
+        <v>11835.666300985125</v>
       </c>
       <c r="AH12" s="5">
-        <f t="shared" si="13"/>
-        <v>9452.1094172824742</v>
+        <f t="shared" si="29"/>
+        <v>12188.017912245243</v>
       </c>
       <c r="AI12" s="5">
-        <f t="shared" si="13"/>
-        <v>9685.27130331019</v>
+        <f t="shared" si="29"/>
+        <v>12550.259902287809</v>
       </c>
       <c r="AJ12" s="5">
-        <f t="shared" si="13"/>
-        <v>9924.9240319538258</v>
+        <f t="shared" si="29"/>
+        <v>12922.669121065192</v>
       </c>
       <c r="AK12" s="5">
-        <f t="shared" si="13"/>
-        <v>10171.257288352204</v>
+        <f t="shared" si="29"/>
+        <v>13305.530264219917</v>
       </c>
     </row>
     <row r="13" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="C13" s="3">
+        <v>-28</v>
+      </c>
+      <c r="D13" s="3">
+        <v>-17</v>
+      </c>
+      <c r="E13" s="3">
+        <v>-46</v>
+      </c>
+      <c r="F13" s="3">
+        <f t="shared" ref="F13:F15" si="30">X13-E13-D13-C13</f>
+        <v>-29</v>
+      </c>
+      <c r="G13" s="3">
+        <v>-88</v>
+      </c>
       <c r="H13" s="3">
         <v>-25</v>
       </c>
       <c r="I13" s="3">
         <v>-3</v>
       </c>
+      <c r="J13" s="3">
+        <f t="shared" ref="J13:J15" si="31">Y13-I13-H13-G13</f>
+        <v>30</v>
+      </c>
       <c r="K13" s="3">
         <v>-372</v>
       </c>
@@ -1964,8 +4619,21 @@
       <c r="M13" s="3">
         <v>-134</v>
       </c>
+      <c r="N13" s="3">
+        <f t="shared" ref="N13:N15" si="32">Z13-M13-L13-K13</f>
+        <v>-258</v>
+      </c>
       <c r="O13" s="3">
         <v>-4</v>
+      </c>
+      <c r="P13" s="3">
+        <v>-40</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
       </c>
       <c r="U13" s="3">
         <v>-326</v>
@@ -1987,7 +4655,8 @@
         <v>132</v>
       </c>
       <c r="AA13" s="3">
-        <v>0</v>
+        <f t="shared" ref="AA13:AA15" si="33">SUM(O13:R13)</f>
+        <v>-44</v>
       </c>
       <c r="AB13" s="3">
         <v>0</v>
@@ -2024,12 +4693,32 @@
       <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="C14" s="3">
+        <v>-480</v>
+      </c>
+      <c r="D14" s="3">
+        <v>-474</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-468</v>
+      </c>
+      <c r="F14" s="3">
+        <f t="shared" si="30"/>
+        <v>-467</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-444</v>
+      </c>
       <c r="H14" s="3">
         <v>-447</v>
       </c>
       <c r="I14" s="3">
         <v>-443</v>
       </c>
+      <c r="J14" s="3">
+        <f t="shared" si="31"/>
+        <v>-446</v>
+      </c>
       <c r="K14" s="3">
         <v>-386</v>
       </c>
@@ -2039,9 +4728,24 @@
       <c r="M14" s="3">
         <v>-374</v>
       </c>
+      <c r="N14" s="3">
+        <f t="shared" si="32"/>
+        <v>-384</v>
+      </c>
       <c r="O14" s="3">
         <v>-366</v>
       </c>
+      <c r="P14" s="3">
+        <v>-351</v>
+      </c>
+      <c r="Q14" s="3">
+        <f>M14*1.01</f>
+        <v>-377.74</v>
+      </c>
+      <c r="R14" s="3">
+        <f>N14*1.01</f>
+        <v>-387.84000000000003</v>
+      </c>
       <c r="U14" s="3">
         <v>-829</v>
       </c>
@@ -2061,60 +4765,80 @@
         <v>-1518</v>
       </c>
       <c r="AA14" s="3">
-        <f>Z14*1.01</f>
-        <v>-1533.18</v>
+        <f t="shared" si="33"/>
+        <v>-1482.58</v>
       </c>
       <c r="AB14" s="3">
-        <f t="shared" ref="AB14:AK14" si="14">AA14*1.01</f>
-        <v>-1548.5118</v>
+        <f t="shared" ref="AB14:AK14" si="34">AA14*1.01</f>
+        <v>-1497.4058</v>
       </c>
       <c r="AC14" s="3">
-        <f t="shared" si="14"/>
-        <v>-1563.9969180000001</v>
+        <f t="shared" si="34"/>
+        <v>-1512.379858</v>
       </c>
       <c r="AD14" s="3">
-        <f t="shared" si="14"/>
-        <v>-1579.63688718</v>
+        <f t="shared" si="34"/>
+        <v>-1527.5036565800001</v>
       </c>
       <c r="AE14" s="3">
-        <f t="shared" si="14"/>
-        <v>-1595.4332560518001</v>
+        <f t="shared" si="34"/>
+        <v>-1542.7786931458002</v>
       </c>
       <c r="AF14" s="3">
-        <f t="shared" si="14"/>
-        <v>-1611.387588612318</v>
+        <f t="shared" si="34"/>
+        <v>-1558.2064800772582</v>
       </c>
       <c r="AG14" s="3">
-        <f t="shared" si="14"/>
-        <v>-1627.5014644984412</v>
+        <f t="shared" si="34"/>
+        <v>-1573.7885448780307</v>
       </c>
       <c r="AH14" s="3">
-        <f t="shared" si="14"/>
-        <v>-1643.7764791434256</v>
+        <f t="shared" si="34"/>
+        <v>-1589.5264303268111</v>
       </c>
       <c r="AI14" s="3">
-        <f t="shared" si="14"/>
-        <v>-1660.21424393486</v>
+        <f t="shared" si="34"/>
+        <v>-1605.4216946300792</v>
       </c>
       <c r="AJ14" s="3">
-        <f t="shared" si="14"/>
-        <v>-1676.8163863742086</v>
+        <f t="shared" si="34"/>
+        <v>-1621.47591157638</v>
       </c>
       <c r="AK14" s="3">
-        <f t="shared" si="14"/>
-        <v>-1693.5845502379507</v>
+        <f t="shared" si="34"/>
+        <v>-1637.6906706921438</v>
       </c>
     </row>
     <row r="15" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="C15" s="3">
+        <v>318</v>
+      </c>
+      <c r="D15" s="3">
+        <v>329</v>
+      </c>
+      <c r="E15" s="3">
+        <v>311</v>
+      </c>
+      <c r="F15" s="3">
+        <f t="shared" si="30"/>
+        <v>318</v>
+      </c>
+      <c r="G15" s="3">
+        <v>315</v>
+      </c>
       <c r="H15" s="3">
         <v>333</v>
       </c>
       <c r="I15" s="3">
         <v>369</v>
       </c>
+      <c r="J15" s="3">
+        <f t="shared" si="31"/>
+        <v>488</v>
+      </c>
       <c r="K15" s="3">
         <v>405</v>
       </c>
@@ -2124,8 +4848,23 @@
       <c r="M15" s="3">
         <v>496</v>
       </c>
+      <c r="N15" s="3">
+        <f t="shared" si="32"/>
+        <v>486</v>
+      </c>
       <c r="O15" s="3">
         <v>443</v>
+      </c>
+      <c r="P15" s="3">
+        <v>457</v>
+      </c>
+      <c r="Q15" s="3">
+        <f t="shared" ref="Q15:R15" si="35">M15*1.01</f>
+        <v>500.96</v>
+      </c>
+      <c r="R15" s="3">
+        <f t="shared" si="35"/>
+        <v>490.86</v>
       </c>
       <c r="U15" s="3">
         <v>1591</v>
@@ -2147,157 +4886,217 @@
         <v>1862</v>
       </c>
       <c r="AA15" s="3">
-        <f>Z15*1.01</f>
-        <v>1880.6200000000001</v>
+        <f t="shared" si="33"/>
+        <v>1891.8200000000002</v>
       </c>
       <c r="AB15" s="3">
-        <f t="shared" ref="AB15:AK15" si="15">AA15*1.01</f>
-        <v>1899.4262000000001</v>
+        <f t="shared" ref="AB15:AK15" si="36">AA15*1.01</f>
+        <v>1910.7382000000002</v>
       </c>
       <c r="AC15" s="3">
-        <f t="shared" si="15"/>
-        <v>1918.420462</v>
+        <f t="shared" si="36"/>
+        <v>1929.8455820000001</v>
       </c>
       <c r="AD15" s="3">
-        <f t="shared" si="15"/>
-        <v>1937.60466662</v>
+        <f t="shared" si="36"/>
+        <v>1949.1440378200002</v>
       </c>
       <c r="AE15" s="3">
-        <f t="shared" si="15"/>
-        <v>1956.9807132861999</v>
+        <f t="shared" si="36"/>
+        <v>1968.6354781982002</v>
       </c>
       <c r="AF15" s="3">
-        <f t="shared" si="15"/>
-        <v>1976.550520419062</v>
+        <f t="shared" si="36"/>
+        <v>1988.3218329801823</v>
       </c>
       <c r="AG15" s="3">
-        <f t="shared" si="15"/>
-        <v>1996.3160256232527</v>
+        <f t="shared" si="36"/>
+        <v>2008.2050513099841</v>
       </c>
       <c r="AH15" s="3">
-        <f t="shared" si="15"/>
-        <v>2016.2791858794853</v>
+        <f t="shared" si="36"/>
+        <v>2028.287101823084</v>
       </c>
       <c r="AI15" s="3">
-        <f t="shared" si="15"/>
-        <v>2036.4419777382802</v>
+        <f t="shared" si="36"/>
+        <v>2048.5699728413147</v>
       </c>
       <c r="AJ15" s="3">
-        <f t="shared" si="15"/>
-        <v>2056.8063975156629</v>
+        <f t="shared" si="36"/>
+        <v>2069.0556725697279</v>
       </c>
       <c r="AK15" s="3">
-        <f t="shared" si="15"/>
-        <v>2077.3744614908196</v>
+        <f t="shared" si="36"/>
+        <v>2089.7462292954251</v>
       </c>
     </row>
     <row r="16" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>36</v>
       </c>
+      <c r="C16" s="5">
+        <f t="shared" ref="C16:P16" si="37">C12-C13-C14-C15</f>
+        <v>1242</v>
+      </c>
+      <c r="D16" s="5">
+        <f t="shared" si="37"/>
+        <v>1498</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="37"/>
+        <v>1677</v>
+      </c>
+      <c r="F16" s="5">
+        <f t="shared" si="37"/>
+        <v>1700</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="37"/>
+        <v>1781</v>
+      </c>
       <c r="H16" s="5">
-        <f>H12-H13-H14-H15</f>
+        <f t="shared" si="37"/>
         <v>1607</v>
       </c>
       <c r="I16" s="5">
-        <f>I12-I13-I14-I15</f>
+        <f t="shared" si="37"/>
         <v>-1322</v>
       </c>
+      <c r="J16" s="5">
+        <f t="shared" si="37"/>
+        <v>1770</v>
+      </c>
       <c r="K16" s="5">
-        <f>K12-K13-K14-K15</f>
+        <f t="shared" si="37"/>
         <v>1851</v>
       </c>
       <c r="L16" s="5">
-        <f>L12-L13-L14-L15</f>
+        <f t="shared" si="37"/>
         <v>428</v>
       </c>
       <c r="M16" s="5">
-        <f>M12-M13-M14-M15</f>
+        <f t="shared" si="37"/>
         <v>1906</v>
       </c>
+      <c r="N16" s="5">
+        <f t="shared" si="37"/>
+        <v>2009</v>
+      </c>
       <c r="O16" s="5">
-        <f>O12-O13-O14-O15</f>
+        <f t="shared" si="37"/>
         <v>1958</v>
       </c>
+      <c r="P16" s="5">
+        <f t="shared" si="37"/>
+        <v>2040</v>
+      </c>
+      <c r="Q16" s="5">
+        <f t="shared" ref="Q16:R16" si="38">Q12-Q13-Q14-Q15</f>
+        <v>2054.927999999999</v>
+      </c>
+      <c r="R16" s="5">
+        <f t="shared" si="38"/>
+        <v>2202.2142999999983</v>
+      </c>
       <c r="U16" s="5">
-        <f t="shared" ref="U16:AA16" si="16">U12-U13-U14-U15</f>
+        <f t="shared" ref="U16:AA16" si="39">U12-U13-U14-U15</f>
         <v>4152</v>
       </c>
       <c r="V16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="39"/>
         <v>-2353</v>
       </c>
       <c r="W16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="39"/>
         <v>4931</v>
       </c>
       <c r="X16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="39"/>
         <v>6117</v>
       </c>
       <c r="Y16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="39"/>
         <v>3836</v>
       </c>
       <c r="Z16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="39"/>
         <v>6194</v>
       </c>
       <c r="AA16" s="5">
-        <f t="shared" si="16"/>
-        <v>7238.5264000000143</v>
+        <f t="shared" si="39"/>
+        <v>8255.1423000000159</v>
       </c>
       <c r="AB16" s="5">
-        <f t="shared" ref="AB16:AK16" si="17">AB12-AB13-AB14-AB15</f>
-        <v>7704.1307200000119</v>
+        <f t="shared" ref="AB16:AK16" si="40">AB12-AB13-AB14-AB15</f>
+        <v>9232.7286159999967</v>
       </c>
       <c r="AC16" s="5">
-        <f t="shared" si="17"/>
-        <v>8030.2947872000059</v>
+        <f t="shared" si="40"/>
+        <v>9947.6590745600042</v>
       </c>
       <c r="AD16" s="5">
-        <f t="shared" si="17"/>
-        <v>8254.2413008480016</v>
+        <f t="shared" si="40"/>
+        <v>10369.210688984804</v>
       </c>
       <c r="AE16" s="5">
-        <f t="shared" si="17"/>
-        <v>8428.2057021579276</v>
+        <f t="shared" si="40"/>
+        <v>10733.707949562431</v>
       </c>
       <c r="AF16" s="5">
-        <f t="shared" si="17"/>
-        <v>8639.3637234916187</v>
+        <f t="shared" si="40"/>
+        <v>11062.820492170122</v>
       </c>
       <c r="AG16" s="5">
-        <f t="shared" si="17"/>
-        <v>8856.4396039680232</v>
+        <f t="shared" si="40"/>
+        <v>11401.249794553172</v>
       </c>
       <c r="AH16" s="5">
-        <f t="shared" si="17"/>
-        <v>9079.6067105464135</v>
+        <f t="shared" si="40"/>
+        <v>11749.25724074897</v>
       </c>
       <c r="AI16" s="5">
-        <f t="shared" si="17"/>
-        <v>9309.0435695067699</v>
+        <f t="shared" si="40"/>
+        <v>12107.111624076573</v>
       </c>
       <c r="AJ16" s="5">
-        <f t="shared" si="17"/>
-        <v>9544.9340208123722</v>
+        <f t="shared" si="40"/>
+        <v>12475.089360071845</v>
       </c>
       <c r="AK16" s="5">
-        <f t="shared" si="17"/>
-        <v>9787.4673770993359</v>
+        <f t="shared" si="40"/>
+        <v>12853.474705616634</v>
       </c>
     </row>
     <row r="17" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="C17" s="3">
+        <v>116</v>
+      </c>
+      <c r="D17" s="3">
+        <v>160</v>
+      </c>
+      <c r="E17" s="3">
+        <v>282</v>
+      </c>
+      <c r="F17" s="3">
+        <f t="shared" ref="F17:F18" si="41">X17-E17-D17-C17</f>
+        <v>232</v>
+      </c>
+      <c r="G17" s="3">
+        <v>300</v>
+      </c>
       <c r="H17" s="3">
         <v>248</v>
       </c>
       <c r="I17" s="3">
         <v>-389</v>
       </c>
+      <c r="J17" s="3">
+        <f t="shared" ref="J17:J18" si="42">Y17-I17-H17-G17</f>
+        <v>297</v>
+      </c>
       <c r="K17" s="3">
         <v>108</v>
       </c>
@@ -2307,9 +5106,24 @@
       <c r="M17" s="3">
         <v>371</v>
       </c>
+      <c r="N17" s="3">
+        <f t="shared" ref="N17:N18" si="43">Z17-M17-L17-K17</f>
+        <v>449</v>
+      </c>
       <c r="O17" s="3">
         <v>333</v>
       </c>
+      <c r="P17" s="3">
+        <v>315</v>
+      </c>
+      <c r="Q17" s="3">
+        <f>Q16*0.17</f>
+        <v>349.33775999999983</v>
+      </c>
+      <c r="R17" s="3">
+        <f>R16*0.17</f>
+        <v>374.37643099999974</v>
+      </c>
       <c r="U17" s="3">
         <v>421</v>
       </c>
@@ -2329,60 +5143,80 @@
         <v>1181</v>
       </c>
       <c r="AA17" s="3">
-        <f>AA16*0.15</f>
-        <v>1085.7789600000021</v>
+        <f t="shared" ref="AA17:AA18" si="44">SUM(O17:R17)</f>
+        <v>1371.7141909999996</v>
       </c>
       <c r="AB17" s="3">
-        <f t="shared" ref="AB17:AK17" si="18">AB16*0.15</f>
-        <v>1155.6196080000018</v>
+        <f t="shared" ref="AB17:AK17" si="45">AB16*0.15</f>
+        <v>1384.9092923999995</v>
       </c>
       <c r="AC17" s="3">
-        <f t="shared" si="18"/>
-        <v>1204.5442180800007</v>
+        <f t="shared" si="45"/>
+        <v>1492.1488611840007</v>
       </c>
       <c r="AD17" s="3">
-        <f t="shared" si="18"/>
-        <v>1238.1361951272002</v>
+        <f t="shared" si="45"/>
+        <v>1555.3816033477206</v>
       </c>
       <c r="AE17" s="3">
-        <f t="shared" si="18"/>
-        <v>1264.2308553236892</v>
+        <f t="shared" si="45"/>
+        <v>1610.0561924343647</v>
       </c>
       <c r="AF17" s="3">
-        <f t="shared" si="18"/>
-        <v>1295.9045585237427</v>
+        <f t="shared" si="45"/>
+        <v>1659.4230738255183</v>
       </c>
       <c r="AG17" s="3">
-        <f t="shared" si="18"/>
-        <v>1328.4659405952034</v>
+        <f t="shared" si="45"/>
+        <v>1710.1874691829757</v>
       </c>
       <c r="AH17" s="3">
-        <f t="shared" si="18"/>
-        <v>1361.941006581962</v>
+        <f t="shared" si="45"/>
+        <v>1762.3885861123454</v>
       </c>
       <c r="AI17" s="3">
-        <f t="shared" si="18"/>
-        <v>1396.3565354260154</v>
+        <f t="shared" si="45"/>
+        <v>1816.0667436114859</v>
       </c>
       <c r="AJ17" s="3">
-        <f t="shared" si="18"/>
-        <v>1431.7401031218558</v>
+        <f t="shared" si="45"/>
+        <v>1871.2634040107766</v>
       </c>
       <c r="AK17" s="3">
-        <f t="shared" si="18"/>
-        <v>1468.1201065649004</v>
+        <f t="shared" si="45"/>
+        <v>1928.021205842495</v>
       </c>
     </row>
     <row r="18" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="C18" s="3">
+        <v>23</v>
+      </c>
+      <c r="D18" s="3">
+        <v>34</v>
+      </c>
+      <c r="E18" s="3">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3">
+        <f t="shared" si="41"/>
+        <v>46</v>
+      </c>
+      <c r="G18" s="3">
+        <v>55</v>
+      </c>
       <c r="H18" s="3">
         <v>32</v>
       </c>
       <c r="I18" s="3">
         <v>51</v>
       </c>
+      <c r="J18" s="3">
+        <f t="shared" si="42"/>
+        <v>47</v>
+      </c>
       <c r="K18" s="3">
         <v>34</v>
       </c>
@@ -2392,9 +5226,24 @@
       <c r="M18" s="3">
         <v>63</v>
       </c>
+      <c r="N18" s="3">
+        <f t="shared" si="43"/>
+        <v>78</v>
+      </c>
       <c r="O18" s="3">
         <v>90</v>
       </c>
+      <c r="P18" s="3">
+        <v>68</v>
+      </c>
+      <c r="Q18" s="3">
+        <f>Q16*0.03</f>
+        <v>61.647839999999967</v>
+      </c>
+      <c r="R18" s="3">
+        <f>R16*0.03</f>
+        <v>66.066428999999943</v>
+      </c>
       <c r="U18" s="3">
         <v>221</v>
       </c>
@@ -2414,549 +5263,607 @@
         <v>239</v>
       </c>
       <c r="AA18" s="3">
-        <f>AA16*0.03</f>
-        <v>217.15579200000042</v>
+        <f t="shared" si="44"/>
+        <v>285.71426899999994</v>
       </c>
       <c r="AB18" s="3">
-        <f t="shared" ref="AB18:AK18" si="19">AB16*0.03</f>
-        <v>231.12392160000036</v>
+        <f t="shared" ref="AB18:AK18" si="46">AB16*0.03</f>
+        <v>276.98185847999991</v>
       </c>
       <c r="AC18" s="3">
-        <f t="shared" si="19"/>
-        <v>240.90884361600015</v>
+        <f t="shared" si="46"/>
+        <v>298.42977223680009</v>
       </c>
       <c r="AD18" s="3">
-        <f t="shared" si="19"/>
-        <v>247.62723902544005</v>
+        <f t="shared" si="46"/>
+        <v>311.07632066954409</v>
       </c>
       <c r="AE18" s="3">
-        <f t="shared" si="19"/>
-        <v>252.84617106473783</v>
+        <f t="shared" si="46"/>
+        <v>322.01123848687291</v>
       </c>
       <c r="AF18" s="3">
-        <f t="shared" si="19"/>
-        <v>259.18091170474855</v>
+        <f t="shared" si="46"/>
+        <v>331.88461476510366</v>
       </c>
       <c r="AG18" s="3">
-        <f t="shared" si="19"/>
-        <v>265.69318811904071</v>
+        <f t="shared" si="46"/>
+        <v>342.03749383659516</v>
       </c>
       <c r="AH18" s="3">
-        <f t="shared" si="19"/>
-        <v>272.38820131639238</v>
+        <f t="shared" si="46"/>
+        <v>352.4777172224691</v>
       </c>
       <c r="AI18" s="3">
-        <f t="shared" si="19"/>
-        <v>279.27130708520309</v>
+        <f t="shared" si="46"/>
+        <v>363.21334872229716</v>
       </c>
       <c r="AJ18" s="3">
-        <f t="shared" si="19"/>
-        <v>286.34802062437115</v>
+        <f t="shared" si="46"/>
+        <v>374.25268080215534</v>
       </c>
       <c r="AK18" s="3">
-        <f t="shared" si="19"/>
-        <v>293.62402131298006</v>
+        <f t="shared" si="46"/>
+        <v>385.60424116849902</v>
       </c>
     </row>
     <row r="19" spans="2:135" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>39</v>
       </c>
+      <c r="C19" s="5">
+        <f t="shared" ref="C19:P19" si="47">C16-C17-C18</f>
+        <v>1103</v>
+      </c>
+      <c r="D19" s="5">
+        <f t="shared" si="47"/>
+        <v>1304</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" si="47"/>
+        <v>1387</v>
+      </c>
+      <c r="F19" s="5">
+        <f t="shared" si="47"/>
+        <v>1422</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" si="47"/>
+        <v>1426</v>
+      </c>
       <c r="H19" s="5">
-        <f>H16-H17-H18</f>
+        <f t="shared" si="47"/>
         <v>1327</v>
       </c>
       <c r="I19" s="5">
-        <f>I16-I17-I18</f>
+        <f t="shared" si="47"/>
         <v>-984</v>
       </c>
+      <c r="J19" s="5">
+        <f t="shared" si="47"/>
+        <v>1426</v>
+      </c>
       <c r="K19" s="5">
-        <f>K16-K17-K18</f>
+        <f t="shared" si="47"/>
         <v>1709</v>
       </c>
       <c r="L19" s="5">
-        <f>L16-L17-L18</f>
+        <f t="shared" si="47"/>
         <v>111</v>
       </c>
       <c r="M19" s="5">
-        <f>M16-M17-M18</f>
+        <f t="shared" si="47"/>
         <v>1472</v>
       </c>
+      <c r="N19" s="5">
+        <f t="shared" si="47"/>
+        <v>1482</v>
+      </c>
       <c r="O19" s="5">
-        <f>O16-O17-O18</f>
+        <f t="shared" si="47"/>
         <v>1535</v>
       </c>
+      <c r="P19" s="5">
+        <f t="shared" si="47"/>
+        <v>1657</v>
+      </c>
+      <c r="Q19" s="5">
+        <f t="shared" ref="Q19:R19" si="48">Q16-Q17-Q18</f>
+        <v>1643.9423999999992</v>
+      </c>
+      <c r="R19" s="5">
+        <f t="shared" si="48"/>
+        <v>1761.7714399999986</v>
+      </c>
       <c r="U19" s="5">
-        <f t="shared" ref="U19:Z19" si="20">U16-U17-U18</f>
+        <f t="shared" ref="U19:Z19" si="49">U16-U17-U18</f>
         <v>3510</v>
       </c>
       <c r="V19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="49"/>
         <v>-3109</v>
       </c>
       <c r="W19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="49"/>
         <v>3897</v>
       </c>
       <c r="X19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="49"/>
         <v>5216</v>
       </c>
       <c r="Y19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="49"/>
         <v>3195</v>
       </c>
       <c r="Z19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="49"/>
         <v>4774</v>
       </c>
       <c r="AA19" s="5">
-        <f t="shared" ref="AA19:AK19" si="21">AA16-AA17-AA18</f>
-        <v>5935.5916480000114</v>
+        <f t="shared" ref="AA19:AK19" si="50">AA16-AA17-AA18</f>
+        <v>6597.7138400000167</v>
       </c>
       <c r="AB19" s="5">
-        <f t="shared" si="21"/>
-        <v>6317.3871904000098</v>
+        <f t="shared" si="50"/>
+        <v>7570.8374651199974</v>
       </c>
       <c r="AC19" s="5">
-        <f t="shared" si="21"/>
-        <v>6584.8417255040049</v>
+        <f t="shared" si="50"/>
+        <v>8157.0804411392028</v>
       </c>
       <c r="AD19" s="5">
-        <f t="shared" si="21"/>
-        <v>6768.4778666953616</v>
+        <f t="shared" si="50"/>
+        <v>8502.7527649675394</v>
       </c>
       <c r="AE19" s="5">
-        <f t="shared" si="21"/>
-        <v>6911.1286757695007</v>
+        <f t="shared" si="50"/>
+        <v>8801.6405186411939</v>
       </c>
       <c r="AF19" s="5">
-        <f t="shared" si="21"/>
-        <v>7084.2782532631272</v>
+        <f t="shared" si="50"/>
+        <v>9071.5128035795005</v>
       </c>
       <c r="AG19" s="5">
-        <f t="shared" si="21"/>
-        <v>7262.2804752537795</v>
+        <f t="shared" si="50"/>
+        <v>9349.0248315336012</v>
       </c>
       <c r="AH19" s="5">
-        <f t="shared" si="21"/>
-        <v>7445.2775026480595</v>
+        <f t="shared" si="50"/>
+        <v>9634.3909374141549</v>
       </c>
       <c r="AI19" s="5">
-        <f t="shared" si="21"/>
-        <v>7633.4157269955513</v>
+        <f t="shared" si="50"/>
+        <v>9927.8315317427914</v>
       </c>
       <c r="AJ19" s="5">
-        <f t="shared" si="21"/>
-        <v>7826.845897066145</v>
+        <f t="shared" si="50"/>
+        <v>10229.573275258912</v>
       </c>
       <c r="AK19" s="5">
-        <f t="shared" si="21"/>
-        <v>8025.7232492214553</v>
+        <f t="shared" si="50"/>
+        <v>10539.84925860564</v>
       </c>
       <c r="AL19" s="4">
         <f>AK19*(1+$AO$25)</f>
-        <v>7945.4660167292404</v>
+        <v>10434.450766019583</v>
       </c>
       <c r="AM19" s="4">
-        <f t="shared" ref="AM19:CX19" si="22">AL19*(1+$AO$25)</f>
-        <v>7866.0113565619477</v>
+        <f t="shared" ref="AM19:CX19" si="51">AL19*(1+$AO$25)</f>
+        <v>10330.106258359387</v>
       </c>
       <c r="AN19" s="4">
-        <f t="shared" si="22"/>
-        <v>7787.3512429963284</v>
+        <f t="shared" si="51"/>
+        <v>10226.805195775793</v>
       </c>
       <c r="AO19" s="4">
-        <f t="shared" si="22"/>
-        <v>7709.4777305663647</v>
+        <f t="shared" si="51"/>
+        <v>10124.537143818034</v>
       </c>
       <c r="AP19" s="4">
-        <f t="shared" si="22"/>
-        <v>7632.3829532607006</v>
+        <f t="shared" si="51"/>
+        <v>10023.291772379853</v>
       </c>
       <c r="AQ19" s="4">
-        <f t="shared" si="22"/>
-        <v>7556.0591237280933</v>
+        <f t="shared" si="51"/>
+        <v>9923.0588546560539</v>
       </c>
       <c r="AR19" s="4">
-        <f t="shared" si="22"/>
-        <v>7480.4985324908121</v>
+        <f t="shared" si="51"/>
+        <v>9823.8282661094927</v>
       </c>
       <c r="AS19" s="4">
-        <f t="shared" si="22"/>
-        <v>7405.6935471659035</v>
+        <f t="shared" si="51"/>
+        <v>9725.5899834483971</v>
       </c>
       <c r="AT19" s="4">
-        <f t="shared" si="22"/>
-        <v>7331.6366116942445</v>
+        <f t="shared" si="51"/>
+        <v>9628.3340836139123</v>
       </c>
       <c r="AU19" s="4">
-        <f t="shared" si="22"/>
-        <v>7258.3202455773016</v>
+        <f t="shared" si="51"/>
+        <v>9532.0507427777738</v>
       </c>
       <c r="AV19" s="4">
-        <f t="shared" si="22"/>
-        <v>7185.7370431215286</v>
+        <f t="shared" si="51"/>
+        <v>9436.7302353499963</v>
       </c>
       <c r="AW19" s="4">
-        <f t="shared" si="22"/>
-        <v>7113.8796726903129</v>
+        <f t="shared" si="51"/>
+        <v>9342.362932996497</v>
       </c>
       <c r="AX19" s="4">
-        <f t="shared" si="22"/>
-        <v>7042.74087596341</v>
+        <f t="shared" si="51"/>
+        <v>9248.9393036665315</v>
       </c>
       <c r="AY19" s="4">
-        <f t="shared" si="22"/>
-        <v>6972.3134672037759</v>
+        <f t="shared" si="51"/>
+        <v>9156.4499106298663</v>
       </c>
       <c r="AZ19" s="4">
-        <f t="shared" si="22"/>
-        <v>6902.5903325317377</v>
+        <f t="shared" si="51"/>
+        <v>9064.8854115235681</v>
       </c>
       <c r="BA19" s="4">
-        <f t="shared" si="22"/>
-        <v>6833.5644292064198</v>
+        <f t="shared" si="51"/>
+        <v>8974.2365574083324</v>
       </c>
       <c r="BB19" s="4">
-        <f t="shared" si="22"/>
-        <v>6765.2287849143559</v>
+        <f t="shared" si="51"/>
+        <v>8884.4941918342483</v>
       </c>
       <c r="BC19" s="4">
-        <f t="shared" si="22"/>
-        <v>6697.5764970652126</v>
+        <f t="shared" si="51"/>
+        <v>8795.6492499159049</v>
       </c>
       <c r="BD19" s="4">
-        <f t="shared" si="22"/>
-        <v>6630.60073209456</v>
+        <f t="shared" si="51"/>
+        <v>8707.6927574167457</v>
       </c>
       <c r="BE19" s="4">
-        <f t="shared" si="22"/>
-        <v>6564.2947247736147</v>
+        <f t="shared" si="51"/>
+        <v>8620.615829842578</v>
       </c>
       <c r="BF19" s="4">
-        <f t="shared" si="22"/>
-        <v>6498.6517775258781</v>
+        <f t="shared" si="51"/>
+        <v>8534.4096715441519</v>
       </c>
       <c r="BG19" s="4">
-        <f t="shared" si="22"/>
-        <v>6433.665259750619</v>
+        <f t="shared" si="51"/>
+        <v>8449.0655748287099</v>
       </c>
       <c r="BH19" s="4">
-        <f t="shared" si="22"/>
-        <v>6369.3286071531129</v>
+        <f t="shared" si="51"/>
+        <v>8364.5749190804236</v>
       </c>
       <c r="BI19" s="4">
-        <f t="shared" si="22"/>
-        <v>6305.6353210815814</v>
+        <f t="shared" si="51"/>
+        <v>8280.9291698896195</v>
       </c>
       <c r="BJ19" s="4">
-        <f t="shared" si="22"/>
-        <v>6242.5789678707652</v>
+        <f t="shared" si="51"/>
+        <v>8198.1198781907224</v>
       </c>
       <c r="BK19" s="4">
-        <f t="shared" si="22"/>
-        <v>6180.1531781920576</v>
+        <f t="shared" si="51"/>
+        <v>8116.1386794088148</v>
       </c>
       <c r="BL19" s="4">
-        <f t="shared" si="22"/>
-        <v>6118.3516464101367</v>
+        <f t="shared" si="51"/>
+        <v>8034.977292614727</v>
       </c>
       <c r="BM19" s="4">
-        <f t="shared" si="22"/>
-        <v>6057.1681299460352</v>
+        <f t="shared" si="51"/>
+        <v>7954.6275196885799</v>
       </c>
       <c r="BN19" s="4">
-        <f t="shared" si="22"/>
-        <v>5996.5964486465746</v>
+        <f t="shared" si="51"/>
+        <v>7875.0812444916937</v>
       </c>
       <c r="BO19" s="4">
-        <f t="shared" si="22"/>
-        <v>5936.6304841601086</v>
+        <f t="shared" si="51"/>
+        <v>7796.3304320467769</v>
       </c>
       <c r="BP19" s="4">
-        <f t="shared" si="22"/>
-        <v>5877.2641793185076</v>
+        <f t="shared" si="51"/>
+        <v>7718.3671277263093</v>
       </c>
       <c r="BQ19" s="4">
-        <f t="shared" si="22"/>
-        <v>5818.4915375253222</v>
+        <f t="shared" si="51"/>
+        <v>7641.1834564490464</v>
       </c>
       <c r="BR19" s="4">
-        <f t="shared" si="22"/>
-        <v>5760.3066221500685</v>
+        <f t="shared" si="51"/>
+        <v>7564.7716218845562</v>
       </c>
       <c r="BS19" s="4">
-        <f t="shared" si="22"/>
-        <v>5702.7035559285678</v>
+        <f t="shared" si="51"/>
+        <v>7489.1239056657105</v>
       </c>
       <c r="BT19" s="4">
-        <f t="shared" si="22"/>
-        <v>5645.6765203692821</v>
+        <f t="shared" si="51"/>
+        <v>7414.232666609053</v>
       </c>
       <c r="BU19" s="4">
-        <f t="shared" si="22"/>
-        <v>5589.219755165589</v>
+        <f t="shared" si="51"/>
+        <v>7340.0903399429626</v>
       </c>
       <c r="BV19" s="4">
-        <f t="shared" si="22"/>
-        <v>5533.3275576139331</v>
+        <f t="shared" si="51"/>
+        <v>7266.6894365435328</v>
       </c>
       <c r="BW19" s="4">
-        <f t="shared" si="22"/>
-        <v>5477.9942820377937</v>
+        <f t="shared" si="51"/>
+        <v>7194.022542178097</v>
       </c>
       <c r="BX19" s="4">
-        <f t="shared" si="22"/>
-        <v>5423.2143392174157</v>
+        <f t="shared" si="51"/>
+        <v>7122.0823167563158</v>
       </c>
       <c r="BY19" s="4">
-        <f t="shared" si="22"/>
-        <v>5368.9821958252414</v>
+        <f t="shared" si="51"/>
+        <v>7050.8614935887526</v>
       </c>
       <c r="BZ19" s="4">
-        <f t="shared" si="22"/>
-        <v>5315.2923738669888</v>
+        <f t="shared" si="51"/>
+        <v>6980.352878652865</v>
       </c>
       <c r="CA19" s="4">
-        <f t="shared" si="22"/>
-        <v>5262.1394501283185</v>
+        <f t="shared" si="51"/>
+        <v>6910.5493498663363</v>
       </c>
       <c r="CB19" s="4">
-        <f t="shared" si="22"/>
-        <v>5209.5180556270352</v>
+        <f t="shared" si="51"/>
+        <v>6841.4438563676731</v>
       </c>
       <c r="CC19" s="4">
-        <f t="shared" si="22"/>
-        <v>5157.4228750707653</v>
+        <f t="shared" si="51"/>
+        <v>6773.0294178039967</v>
       </c>
       <c r="CD19" s="4">
-        <f t="shared" si="22"/>
-        <v>5105.8486463200579</v>
+        <f t="shared" si="51"/>
+        <v>6705.2991236259568</v>
       </c>
       <c r="CE19" s="4">
-        <f t="shared" si="22"/>
-        <v>5054.7901598568569</v>
+        <f t="shared" si="51"/>
+        <v>6638.2461323896969</v>
       </c>
       <c r="CF19" s="4">
-        <f t="shared" si="22"/>
-        <v>5004.2422582582885</v>
+        <f t="shared" si="51"/>
+        <v>6571.8636710658002</v>
       </c>
       <c r="CG19" s="4">
-        <f t="shared" si="22"/>
-        <v>4954.1998356757058</v>
+        <f t="shared" si="51"/>
+        <v>6506.1450343551423</v>
       </c>
       <c r="CH19" s="4">
-        <f t="shared" si="22"/>
-        <v>4904.6578373189486</v>
+        <f t="shared" si="51"/>
+        <v>6441.0835840115906</v>
       </c>
       <c r="CI19" s="4">
-        <f t="shared" si="22"/>
-        <v>4855.6112589457589</v>
+        <f t="shared" si="51"/>
+        <v>6376.6727481714743</v>
       </c>
       <c r="CJ19" s="4">
-        <f t="shared" si="22"/>
-        <v>4807.0551463563015</v>
+        <f t="shared" si="51"/>
+        <v>6312.9060206897593</v>
       </c>
       <c r="CK19" s="4">
-        <f t="shared" si="22"/>
-        <v>4758.9845948927386</v>
+        <f t="shared" si="51"/>
+        <v>6249.7769604828618</v>
       </c>
       <c r="CL19" s="4">
-        <f t="shared" si="22"/>
-        <v>4711.3947489438115</v>
+        <f t="shared" si="51"/>
+        <v>6187.2791908780328</v>
       </c>
       <c r="CM19" s="4">
-        <f t="shared" si="22"/>
-        <v>4664.2808014543734</v>
+        <f t="shared" si="51"/>
+        <v>6125.4063989692522</v>
       </c>
       <c r="CN19" s="4">
-        <f t="shared" si="22"/>
-        <v>4617.6379934398301</v>
+        <f t="shared" si="51"/>
+        <v>6064.1523349795598</v>
       </c>
       <c r="CO19" s="4">
-        <f t="shared" si="22"/>
-        <v>4571.4616135054321</v>
+        <f t="shared" si="51"/>
+        <v>6003.5108116297642</v>
       </c>
       <c r="CP19" s="4">
-        <f t="shared" si="22"/>
-        <v>4525.7469973703774</v>
+        <f t="shared" si="51"/>
+        <v>5943.4757035134662</v>
       </c>
       <c r="CQ19" s="4">
-        <f t="shared" si="22"/>
-        <v>4480.4895273966731</v>
+        <f t="shared" si="51"/>
+        <v>5884.0409464783315</v>
       </c>
       <c r="CR19" s="4">
-        <f t="shared" si="22"/>
-        <v>4435.6846321227067</v>
+        <f t="shared" si="51"/>
+        <v>5825.2005370135485</v>
       </c>
       <c r="CS19" s="4">
-        <f t="shared" si="22"/>
-        <v>4391.3277858014799</v>
+        <f t="shared" si="51"/>
+        <v>5766.9485316434129</v>
       </c>
       <c r="CT19" s="4">
-        <f t="shared" si="22"/>
-        <v>4347.4145079434647</v>
+        <f t="shared" si="51"/>
+        <v>5709.2790463269785</v>
       </c>
       <c r="CU19" s="4">
-        <f t="shared" si="22"/>
-        <v>4303.9403628640302</v>
+        <f t="shared" si="51"/>
+        <v>5652.1862558637085</v>
       </c>
       <c r="CV19" s="4">
-        <f t="shared" si="22"/>
-        <v>4260.9009592353896</v>
+        <f t="shared" si="51"/>
+        <v>5595.6643933050718</v>
       </c>
       <c r="CW19" s="4">
-        <f t="shared" si="22"/>
-        <v>4218.2919496430359</v>
+        <f t="shared" si="51"/>
+        <v>5539.7077493720208</v>
       </c>
       <c r="CX19" s="4">
-        <f t="shared" si="22"/>
-        <v>4176.1090301466056</v>
+        <f t="shared" si="51"/>
+        <v>5484.3106718783001</v>
       </c>
       <c r="CY19" s="4">
-        <f t="shared" ref="CY19:EE19" si="23">CX19*(1+$AO$25)</f>
-        <v>4134.3479398451391</v>
+        <f t="shared" ref="CY19:EE19" si="52">CX19*(1+$AO$25)</f>
+        <v>5429.4675651595171</v>
       </c>
       <c r="CZ19" s="4">
-        <f t="shared" si="23"/>
-        <v>4093.0044604466875</v>
+        <f t="shared" si="52"/>
+        <v>5375.1728895079223</v>
       </c>
       <c r="DA19" s="4">
-        <f t="shared" si="23"/>
-        <v>4052.0744158422208</v>
+        <f t="shared" si="52"/>
+        <v>5321.4211606128429</v>
       </c>
       <c r="DB19" s="4">
-        <f t="shared" si="23"/>
-        <v>4011.5536716837987</v>
+        <f t="shared" si="52"/>
+        <v>5268.2069490067142</v>
       </c>
       <c r="DC19" s="4">
-        <f t="shared" si="23"/>
-        <v>3971.4381349669607</v>
+        <f t="shared" si="52"/>
+        <v>5215.5248795166472</v>
       </c>
       <c r="DD19" s="4">
-        <f t="shared" si="23"/>
-        <v>3931.7237536172911</v>
+        <f t="shared" si="52"/>
+        <v>5163.3696307214805</v>
       </c>
       <c r="DE19" s="4">
-        <f t="shared" si="23"/>
-        <v>3892.4065160811183</v>
+        <f t="shared" si="52"/>
+        <v>5111.735934414266</v>
       </c>
       <c r="DF19" s="4">
-        <f t="shared" si="23"/>
-        <v>3853.4824509203072</v>
+        <f t="shared" si="52"/>
+        <v>5060.6185750701234</v>
       </c>
       <c r="DG19" s="4">
-        <f t="shared" si="23"/>
-        <v>3814.947626411104</v>
+        <f t="shared" si="52"/>
+        <v>5010.0123893194223</v>
       </c>
       <c r="DH19" s="4">
-        <f t="shared" si="23"/>
-        <v>3776.7981501469931</v>
+        <f t="shared" si="52"/>
+        <v>4959.9122654262283</v>
       </c>
       <c r="DI19" s="4">
-        <f t="shared" si="23"/>
-        <v>3739.0301686455232</v>
+        <f t="shared" si="52"/>
+        <v>4910.3131427719663</v>
       </c>
       <c r="DJ19" s="4">
-        <f t="shared" si="23"/>
-        <v>3701.6398669590681</v>
+        <f t="shared" si="52"/>
+        <v>4861.2100113442466</v>
       </c>
       <c r="DK19" s="4">
-        <f t="shared" si="23"/>
-        <v>3664.6234682894774</v>
+        <f t="shared" si="52"/>
+        <v>4812.5979112308041</v>
       </c>
       <c r="DL19" s="4">
-        <f t="shared" si="23"/>
-        <v>3627.9772336065826</v>
+        <f t="shared" si="52"/>
+        <v>4764.4719321184957</v>
       </c>
       <c r="DM19" s="4">
-        <f t="shared" si="23"/>
-        <v>3591.6974612705167</v>
+        <f t="shared" si="52"/>
+        <v>4716.8272127973105</v>
       </c>
       <c r="DN19" s="4">
-        <f t="shared" si="23"/>
-        <v>3555.7804866578113</v>
+        <f t="shared" si="52"/>
+        <v>4669.6589406693374</v>
       </c>
       <c r="DO19" s="4">
-        <f t="shared" si="23"/>
-        <v>3520.2226817912333</v>
+        <f t="shared" si="52"/>
+        <v>4622.962351262644</v>
       </c>
       <c r="DP19" s="4">
-        <f t="shared" si="23"/>
-        <v>3485.0204549733207</v>
+        <f t="shared" si="52"/>
+        <v>4576.7327277500171</v>
       </c>
       <c r="DQ19" s="4">
-        <f t="shared" si="23"/>
-        <v>3450.1702504235873</v>
+        <f t="shared" si="52"/>
+        <v>4530.9654004725171</v>
       </c>
       <c r="DR19" s="4">
-        <f t="shared" si="23"/>
-        <v>3415.6685479193516</v>
+        <f t="shared" si="52"/>
+        <v>4485.6557464677917</v>
       </c>
       <c r="DS19" s="4">
-        <f t="shared" si="23"/>
-        <v>3381.511862440158</v>
+        <f t="shared" si="52"/>
+        <v>4440.7991890031135</v>
       </c>
       <c r="DT19" s="4">
-        <f t="shared" si="23"/>
-        <v>3347.6967438157562</v>
+        <f t="shared" si="52"/>
+        <v>4396.3911971130819</v>
       </c>
       <c r="DU19" s="4">
-        <f t="shared" si="23"/>
-        <v>3314.2197763775985</v>
+        <f t="shared" si="52"/>
+        <v>4352.427285141951</v>
       </c>
       <c r="DV19" s="4">
-        <f t="shared" si="23"/>
-        <v>3281.0775786138224</v>
+        <f t="shared" si="52"/>
+        <v>4308.9030122905315</v>
       </c>
       <c r="DW19" s="4">
-        <f t="shared" si="23"/>
-        <v>3248.2668028276844</v>
+        <f t="shared" si="52"/>
+        <v>4265.8139821676259</v>
       </c>
       <c r="DX19" s="4">
-        <f t="shared" si="23"/>
-        <v>3215.7841347994076</v>
+        <f t="shared" si="52"/>
+        <v>4223.1558423459492</v>
       </c>
       <c r="DY19" s="4">
-        <f t="shared" si="23"/>
-        <v>3183.6262934514134</v>
+        <f t="shared" si="52"/>
+        <v>4180.9242839224898</v>
       </c>
       <c r="DZ19" s="4">
-        <f t="shared" si="23"/>
-        <v>3151.7900305168992</v>
+        <f t="shared" si="52"/>
+        <v>4139.1150410832652</v>
       </c>
       <c r="EA19" s="4">
-        <f t="shared" si="23"/>
-        <v>3120.2721302117302</v>
+        <f t="shared" si="52"/>
+        <v>4097.7238906724324</v>
       </c>
       <c r="EB19" s="4">
-        <f t="shared" si="23"/>
-        <v>3089.0694089096128</v>
+        <f t="shared" si="52"/>
+        <v>4056.7466517657081</v>
       </c>
       <c r="EC19" s="4">
-        <f t="shared" si="23"/>
-        <v>3058.1787148205167</v>
+        <f t="shared" si="52"/>
+        <v>4016.179185248051</v>
       </c>
       <c r="ED19" s="4">
-        <f t="shared" si="23"/>
-        <v>3027.5969276723117</v>
+        <f t="shared" si="52"/>
+        <v>3976.0173933955703</v>
       </c>
       <c r="EE19" s="4">
-        <f t="shared" si="23"/>
-        <v>2997.3209583955886</v>
+        <f t="shared" si="52"/>
+        <v>3936.2572194616146</v>
       </c>
     </row>
     <row r="20" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C20" s="3">
+        <v>1330</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1330</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1330</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1330</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1330</v>
+      </c>
       <c r="H20" s="3">
         <v>1330</v>
       </c>
       <c r="I20" s="3">
         <v>1330</v>
       </c>
+      <c r="J20" s="3">
+        <v>1330</v>
+      </c>
       <c r="K20" s="3">
         <v>1330</v>
       </c>
@@ -2966,173 +5873,228 @@
       <c r="M20" s="3">
         <v>1330</v>
       </c>
+      <c r="N20" s="3">
+        <v>1330</v>
+      </c>
       <c r="O20" s="3">
         <v>1330</v>
       </c>
+      <c r="P20" s="3">
+        <f>1338.5</f>
+        <v>1338.5</v>
+      </c>
+      <c r="Q20" s="3">
+        <f t="shared" ref="Q20:R20" si="53">1338.5</f>
+        <v>1338.5</v>
+      </c>
+      <c r="R20" s="3">
+        <f t="shared" si="53"/>
+        <v>1338.5</v>
+      </c>
       <c r="U20" s="3">
-        <f t="shared" ref="U20:AK20" si="24">1332.1</f>
+        <f t="shared" ref="U20:Z20" si="54">1332.1</f>
         <v>1332.1</v>
       </c>
       <c r="V20" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="54"/>
         <v>1332.1</v>
       </c>
       <c r="W20" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="54"/>
         <v>1332.1</v>
       </c>
       <c r="X20" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="54"/>
         <v>1332.1</v>
       </c>
       <c r="Y20" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="54"/>
         <v>1332.1</v>
       </c>
       <c r="Z20" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="54"/>
         <v>1332.1</v>
       </c>
       <c r="AA20" s="3">
-        <f t="shared" si="24"/>
-        <v>1332.1</v>
+        <f t="shared" ref="AA20:AK20" si="55">1338.5</f>
+        <v>1338.5</v>
       </c>
       <c r="AB20" s="3">
-        <f t="shared" si="24"/>
-        <v>1332.1</v>
+        <f t="shared" si="55"/>
+        <v>1338.5</v>
       </c>
       <c r="AC20" s="3">
-        <f t="shared" si="24"/>
-        <v>1332.1</v>
+        <f t="shared" si="55"/>
+        <v>1338.5</v>
       </c>
       <c r="AD20" s="3">
-        <f t="shared" si="24"/>
-        <v>1332.1</v>
+        <f t="shared" si="55"/>
+        <v>1338.5</v>
       </c>
       <c r="AE20" s="3">
-        <f t="shared" si="24"/>
-        <v>1332.1</v>
+        <f t="shared" si="55"/>
+        <v>1338.5</v>
       </c>
       <c r="AF20" s="3">
-        <f t="shared" si="24"/>
-        <v>1332.1</v>
+        <f t="shared" si="55"/>
+        <v>1338.5</v>
       </c>
       <c r="AG20" s="3">
-        <f t="shared" si="24"/>
-        <v>1332.1</v>
+        <f t="shared" si="55"/>
+        <v>1338.5</v>
       </c>
       <c r="AH20" s="3">
-        <f t="shared" si="24"/>
-        <v>1332.1</v>
+        <f t="shared" si="55"/>
+        <v>1338.5</v>
       </c>
       <c r="AI20" s="3">
-        <f t="shared" si="24"/>
-        <v>1332.1</v>
+        <f t="shared" si="55"/>
+        <v>1338.5</v>
       </c>
       <c r="AJ20" s="3">
-        <f t="shared" si="24"/>
-        <v>1332.1</v>
+        <f t="shared" si="55"/>
+        <v>1338.5</v>
       </c>
       <c r="AK20" s="3">
-        <f t="shared" si="24"/>
-        <v>1332.1</v>
+        <f t="shared" si="55"/>
+        <v>1338.5</v>
       </c>
     </row>
     <row r="21" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="C21" s="6">
+        <f t="shared" ref="C21:P21" si="56">C19/C20</f>
+        <v>0.82932330827067668</v>
+      </c>
+      <c r="D21" s="6">
+        <f t="shared" si="56"/>
+        <v>0.98045112781954891</v>
+      </c>
+      <c r="E21" s="6">
+        <f t="shared" si="56"/>
+        <v>1.0428571428571429</v>
+      </c>
+      <c r="F21" s="6">
+        <f t="shared" si="56"/>
+        <v>1.069172932330827</v>
+      </c>
+      <c r="G21" s="6">
+        <f t="shared" si="56"/>
+        <v>1.0721804511278195</v>
+      </c>
       <c r="H21" s="6">
-        <f>H19/H20</f>
+        <f t="shared" si="56"/>
         <v>0.9977443609022556</v>
       </c>
       <c r="I21" s="6">
-        <f>I19/I20</f>
+        <f t="shared" si="56"/>
         <v>-0.73984962406015042</v>
       </c>
+      <c r="J21" s="6">
+        <f t="shared" si="56"/>
+        <v>1.0721804511278195</v>
+      </c>
       <c r="K21" s="6">
-        <f>K19/K20</f>
+        <f t="shared" si="56"/>
         <v>1.2849624060150375</v>
       </c>
       <c r="L21" s="6">
-        <f>L19/L20</f>
+        <f t="shared" si="56"/>
         <v>8.3458646616541357E-2</v>
       </c>
       <c r="M21" s="6">
-        <f>M19/M20</f>
+        <f t="shared" si="56"/>
         <v>1.1067669172932331</v>
       </c>
+      <c r="N21" s="6">
+        <f t="shared" si="56"/>
+        <v>1.1142857142857143</v>
+      </c>
       <c r="O21" s="6">
-        <f>O19/O20</f>
+        <f t="shared" si="56"/>
         <v>1.1541353383458646</v>
       </c>
+      <c r="P21" s="6">
+        <f t="shared" si="56"/>
+        <v>1.2379529323870004</v>
+      </c>
+      <c r="Q21" s="6">
+        <f t="shared" ref="Q21:R21" si="57">Q19/Q20</f>
+        <v>1.2281975345536043</v>
+      </c>
+      <c r="R21" s="6">
+        <f t="shared" si="57"/>
+        <v>1.3162281957415007</v>
+      </c>
       <c r="U21" s="6">
-        <f t="shared" ref="U21:Z21" si="25">U19/U20</f>
+        <f t="shared" ref="U21:Z21" si="58">U19/U20</f>
         <v>2.6349373170182422</v>
       </c>
       <c r="V21" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="58"/>
         <v>-2.3339088657007734</v>
       </c>
       <c r="W21" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="58"/>
         <v>2.9254560468433302</v>
       </c>
       <c r="X21" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="58"/>
         <v>3.9156219503040317</v>
       </c>
       <c r="Y21" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="58"/>
         <v>2.3984685834396817</v>
       </c>
       <c r="Z21" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="58"/>
         <v>3.5838150289017343</v>
       </c>
       <c r="AA21" s="6">
-        <f t="shared" ref="AA21:AK21" si="26">AA19/AA20</f>
-        <v>4.4558153652128309</v>
+        <f t="shared" ref="AA21:AK21" si="59">AA19/AA20</f>
+        <v>4.9291847889428588</v>
       </c>
       <c r="AB21" s="6">
-        <f t="shared" si="26"/>
-        <v>4.7424271379025678</v>
+        <f t="shared" si="59"/>
+        <v>5.6562102839895383</v>
       </c>
       <c r="AC21" s="6">
-        <f t="shared" si="26"/>
-        <v>4.9432037576037873</v>
+        <f t="shared" si="59"/>
+        <v>6.0941953239740032</v>
       </c>
       <c r="AD21" s="6">
-        <f t="shared" si="26"/>
-        <v>5.0810583790221173</v>
+        <f t="shared" si="59"/>
+        <v>6.352448834491998</v>
       </c>
       <c r="AE21" s="6">
-        <f t="shared" si="26"/>
-        <v>5.18814554145297</v>
+        <f t="shared" si="59"/>
+        <v>6.5757493602100814</v>
       </c>
       <c r="AF21" s="6">
-        <f t="shared" si="26"/>
-        <v>5.3181279583087813</v>
+        <f t="shared" si="59"/>
+        <v>6.7773722850799407</v>
       </c>
       <c r="AG21" s="6">
-        <f t="shared" si="26"/>
-        <v>5.4517532281763978</v>
+        <f t="shared" si="59"/>
+        <v>6.9847028999130378</v>
       </c>
       <c r="AH21" s="6">
-        <f t="shared" si="26"/>
-        <v>5.5891280704512125</v>
+        <f t="shared" si="59"/>
+        <v>7.1979013353859953</v>
       </c>
       <c r="AI21" s="6">
-        <f t="shared" si="26"/>
-        <v>5.7303623804485788</v>
+        <f t="shared" si="59"/>
+        <v>7.4171322612945767</v>
       </c>
       <c r="AJ21" s="6">
-        <f t="shared" si="26"/>
-        <v>5.8755693244247018</v>
+        <f t="shared" si="59"/>
+        <v>7.6425650170032959</v>
       </c>
       <c r="AK21" s="6">
-        <f t="shared" si="26"/>
-        <v>6.0248654374457296</v>
+        <f t="shared" si="59"/>
+        <v>7.8743737456896827</v>
       </c>
     </row>
     <row r="23" spans="2:135" x14ac:dyDescent="0.3">
@@ -3143,26 +6105,47 @@
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7" t="e">
-        <f t="shared" ref="H23:K23" si="27">H9/D9-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I23" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J23" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K23" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
+      <c r="G23" s="7">
+        <f t="shared" ref="G23:P25" si="60">G3/C3-1</f>
+        <v>7.7980104535491535E-2</v>
+      </c>
+      <c r="H23" s="7">
+        <f t="shared" si="60"/>
+        <v>9.4061021373796683E-2</v>
+      </c>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7">
+        <f t="shared" si="60"/>
+        <v>6.1955817802403335E-2</v>
+      </c>
+      <c r="K23" s="7">
+        <f t="shared" si="60"/>
+        <v>0.11855791037772745</v>
       </c>
       <c r="L23" s="7">
-        <f>L3/H3-1</f>
+        <f t="shared" si="60"/>
         <v>8.5825068973230945E-2</v>
+      </c>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7">
+        <f t="shared" si="60"/>
+        <v>8.6800379455210797E-2</v>
+      </c>
+      <c r="O23" s="7">
+        <f t="shared" si="60"/>
+        <v>2.0135635880584424E-2</v>
+      </c>
+      <c r="P23" s="7">
+        <f t="shared" si="60"/>
+        <v>6.7916494986952403E-2</v>
+      </c>
+      <c r="Q23" s="7">
+        <f t="shared" ref="Q23:Q25" si="61">Q3/M3-1</f>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="R23" s="7">
+        <f t="shared" ref="R23:R25" si="62">R3/N3-1</f>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="U23" s="7"/>
       <c r="V23" s="7">
@@ -3170,64 +6153,64 @@
         <v>0.31277653191102495</v>
       </c>
       <c r="W23" s="7">
-        <f t="shared" ref="W23:Z23" si="28">W3/V3-1</f>
+        <f t="shared" ref="W23:Z23" si="63">W3/V3-1</f>
         <v>0.13737620905376402</v>
       </c>
       <c r="X23" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="63"/>
         <v>3.0505378526486604E-2</v>
       </c>
       <c r="Y23" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="63"/>
         <v>-2.3673999960609038E-2</v>
       </c>
       <c r="Z23" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="63"/>
         <v>0.20255794718686326</v>
       </c>
       <c r="AA23" s="7">
-        <f t="shared" ref="AA23:AA25" si="29">AA3/Z3-1</f>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" ref="AA23:AA25" si="64">AA3/Z3-1</f>
+        <v>4.967842045225801E-2</v>
       </c>
       <c r="AB23" s="7">
-        <f t="shared" ref="AB23:AB25" si="30">AB3/AA3-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="AB23:AB25" si="65">AB3/AA3-1</f>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AC23" s="7">
-        <f t="shared" ref="AC23:AC25" si="31">AC3/AB3-1</f>
+        <f t="shared" ref="AC23:AC25" si="66">AC3/AB3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD23" s="7">
-        <f t="shared" ref="AD23:AD25" si="32">AD3/AC3-1</f>
+        <f t="shared" ref="AD23:AD25" si="67">AD3/AC3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE23" s="7">
-        <f t="shared" ref="AE23:AE25" si="33">AE3/AD3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AE23:AE25" si="68">AE3/AD3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF23" s="7">
-        <f t="shared" ref="AF23:AF25" si="34">AF3/AE3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AF23:AF25" si="69">AF3/AE3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG23" s="7">
-        <f t="shared" ref="AG23:AG25" si="35">AG3/AF3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AG23:AG25" si="70">AG3/AF3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH23" s="7">
-        <f t="shared" ref="AH23:AH25" si="36">AH3/AG3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AH23:AH25" si="71">AH3/AG3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI23" s="7">
-        <f t="shared" ref="AI23:AI25" si="37">AI3/AH3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AI23:AI25" si="72">AI3/AH3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ23" s="7">
-        <f t="shared" ref="AJ23:AJ25" si="38">AJ3/AI3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AJ23:AJ25" si="73">AJ3/AI3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK23" s="7">
-        <f t="shared" ref="AK23:AK25" si="39">AK3/AJ3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AK23:AK25" si="74">AK3/AJ3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
     </row>
     <row r="24" spans="2:135" x14ac:dyDescent="0.3">
@@ -3238,90 +6221,117 @@
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7" t="e">
-        <f t="shared" ref="H24:K24" si="40">H10/#REF!-1</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I24" s="7" t="e">
-        <f t="shared" si="40"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J24" s="7" t="e">
-        <f t="shared" si="40"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K24" s="7" t="e">
-        <f t="shared" si="40"/>
-        <v>#REF!</v>
+      <c r="G24" s="7">
+        <f t="shared" si="60"/>
+        <v>0.14867669953295271</v>
+      </c>
+      <c r="H24" s="7">
+        <f t="shared" si="60"/>
+        <v>0.20907297830374749</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="60"/>
+        <v>0.15589988081048878</v>
+      </c>
+      <c r="J24" s="7">
+        <f t="shared" si="60"/>
+        <v>0.23188751191611057</v>
+      </c>
+      <c r="K24" s="7">
+        <f t="shared" si="60"/>
+        <v>0.12988479783148854</v>
       </c>
       <c r="L24" s="7">
-        <f t="shared" ref="L24:L25" si="41">L4/H4-1</f>
+        <f t="shared" si="60"/>
         <v>5.1998368678629614E-2</v>
+      </c>
+      <c r="M24" s="7">
+        <f t="shared" si="60"/>
+        <v>0.10971334295731072</v>
+      </c>
+      <c r="N24" s="7">
+        <f t="shared" si="60"/>
+        <v>8.0286322306055258E-2</v>
+      </c>
+      <c r="O24" s="7">
+        <f t="shared" si="60"/>
+        <v>0.14254298280687716</v>
+      </c>
+      <c r="P24" s="7">
+        <f t="shared" si="60"/>
+        <v>0.16883116883116878</v>
+      </c>
+      <c r="Q24" s="7">
+        <f t="shared" si="61"/>
+        <v>0.16999999999999993</v>
+      </c>
+      <c r="R24" s="7">
+        <f t="shared" si="62"/>
+        <v>0.17999999999999994</v>
       </c>
       <c r="U24" s="7"/>
       <c r="V24" s="7">
-        <f t="shared" ref="V24:Z25" si="42">V4/U4-1</f>
+        <f t="shared" ref="V24:Z25" si="75">V4/U4-1</f>
         <v>7.4245000404825623E-2</v>
       </c>
       <c r="W24" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="75"/>
         <v>0.13943322279167925</v>
       </c>
       <c r="X24" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="75"/>
         <v>7.8251091414208274E-2</v>
       </c>
       <c r="Y24" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="75"/>
         <v>0.18698239371817671</v>
       </c>
       <c r="Z24" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="75"/>
         <v>9.1839371543749104E-2</v>
       </c>
       <c r="AA24" s="7">
-        <f t="shared" si="29"/>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" si="64"/>
+        <v>0.16585676417684359</v>
       </c>
       <c r="AB24" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="65"/>
+        <v>0.12999999999999989</v>
+      </c>
+      <c r="AC24" s="7">
+        <f t="shared" si="66"/>
+        <v>9.000000000000008E-2</v>
+      </c>
+      <c r="AD24" s="7">
+        <f t="shared" si="67"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AC24" s="7">
-        <f t="shared" si="31"/>
+      <c r="AE24" s="7">
+        <f t="shared" si="68"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AD24" s="7">
-        <f t="shared" si="32"/>
+      <c r="AF24" s="7">
+        <f t="shared" si="69"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AE24" s="7">
-        <f t="shared" si="33"/>
+      <c r="AG24" s="7">
+        <f t="shared" si="70"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AF24" s="7">
-        <f t="shared" si="34"/>
+      <c r="AH24" s="7">
+        <f t="shared" si="71"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AG24" s="7">
-        <f t="shared" si="35"/>
+      <c r="AI24" s="7">
+        <f t="shared" si="72"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AH24" s="7">
-        <f t="shared" si="36"/>
+      <c r="AJ24" s="7">
+        <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AI24" s="7">
-        <f t="shared" si="37"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AJ24" s="7">
-        <f t="shared" si="38"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
       <c r="AK24" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="74"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -3333,91 +6343,118 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7" t="e">
-        <f t="shared" ref="H25:K25" si="43">H11/#REF!-1</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I25" s="7" t="e">
-        <f t="shared" si="43"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J25" s="7" t="e">
-        <f t="shared" si="43"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K25" s="7" t="e">
-        <f t="shared" si="43"/>
-        <v>#REF!</v>
+      <c r="G25" s="7">
+        <f t="shared" si="60"/>
+        <v>9.531687452277926E-2</v>
+      </c>
+      <c r="H25" s="7">
+        <f t="shared" si="60"/>
+        <v>0.12265538801029785</v>
+      </c>
+      <c r="I25" s="7">
+        <f t="shared" si="60"/>
+        <v>-0.20571057754704736</v>
+      </c>
+      <c r="J25" s="7">
+        <f t="shared" si="60"/>
+        <v>0.10136516884983138</v>
+      </c>
+      <c r="K25" s="7">
+        <f t="shared" si="60"/>
+        <v>0.12147089578250259</v>
       </c>
       <c r="L25" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="60"/>
         <v>7.6767676767676818E-2</v>
+      </c>
+      <c r="M25" s="7">
+        <f t="shared" si="60"/>
+        <v>0.49205288175876416</v>
+      </c>
+      <c r="N25" s="7">
+        <f t="shared" si="60"/>
+        <v>8.5110653886686372E-2</v>
+      </c>
+      <c r="O25" s="7">
+        <f t="shared" si="60"/>
+        <v>5.1851851851851816E-2</v>
+      </c>
+      <c r="P25" s="7">
+        <f t="shared" si="60"/>
+        <v>9.4315704071801676E-2</v>
+      </c>
+      <c r="Q25" s="7">
+        <f t="shared" si="61"/>
+        <v>8.9464383493454092E-2</v>
+      </c>
+      <c r="R25" s="7">
+        <f t="shared" si="62"/>
+        <v>8.3571659806687348E-2</v>
       </c>
       <c r="U25" s="7"/>
       <c r="V25" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="75"/>
         <v>0.24781141811285812</v>
       </c>
       <c r="W25" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="75"/>
         <v>0.1378585187410537</v>
       </c>
       <c r="X25" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="75"/>
         <v>4.1715847673479578E-2</v>
       </c>
       <c r="Y25" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="75"/>
         <v>2.7521841548140857E-2</v>
       </c>
       <c r="Z25" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="75"/>
         <v>0.17147417295414979</v>
       </c>
       <c r="AA25" s="7">
-        <f t="shared" si="29"/>
-        <v>7.2616611756546101E-2</v>
+        <f t="shared" si="64"/>
+        <v>8.0077782456835722E-2</v>
       </c>
       <c r="AB25" s="7">
-        <f t="shared" si="30"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="65"/>
+        <v>6.5419790209822359E-2</v>
       </c>
       <c r="AC25" s="7">
-        <f t="shared" si="31"/>
-        <v>3.2634623281138309E-2</v>
+        <f t="shared" si="66"/>
+        <v>4.7973737176055575E-2</v>
       </c>
       <c r="AD25" s="7">
-        <f t="shared" si="32"/>
-        <v>2.2653415013025313E-2</v>
+        <f t="shared" si="67"/>
+        <v>2.9347263593977546E-2</v>
       </c>
       <c r="AE25" s="7">
-        <f t="shared" si="33"/>
-        <v>1.5344953477481438E-2</v>
+        <f t="shared" si="68"/>
+        <v>2.6356537533250846E-2</v>
       </c>
       <c r="AF25" s="7">
-        <f t="shared" si="34"/>
-        <v>1.5422100206388567E-2</v>
+        <f t="shared" si="69"/>
+        <v>2.3220517818529851E-2</v>
       </c>
       <c r="AG25" s="7">
-        <f t="shared" si="35"/>
-        <v>1.5499942547483547E-2</v>
+        <f t="shared" si="70"/>
+        <v>2.3241855783108889E-2</v>
       </c>
       <c r="AH25" s="7">
-        <f t="shared" si="36"/>
-        <v>1.5578474785234109E-2</v>
+        <f t="shared" si="71"/>
+        <v>2.326326707388926E-2</v>
       </c>
       <c r="AI25" s="7">
-        <f t="shared" si="37"/>
-        <v>1.5657690834779192E-2</v>
+        <f t="shared" si="72"/>
+        <v>2.3284751045268504E-2</v>
       </c>
       <c r="AJ25" s="7">
-        <f t="shared" si="38"/>
-        <v>1.573758423965943E-2</v>
+        <f t="shared" si="73"/>
+        <v>2.3306307040313667E-2</v>
       </c>
       <c r="AK25" s="7">
-        <f t="shared" si="39"/>
-        <v>1.5818148169906676E-2</v>
+        <f t="shared" si="74"/>
+        <v>2.3327934390801053E-2</v>
       </c>
       <c r="AN25" s="1" t="s">
         <v>55</v>
@@ -3430,45 +6467,69 @@
       <c r="B26" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="7" t="e">
-        <f t="shared" ref="C26:K26" si="44">(C3-C6)/C3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D26" s="7" t="e">
-        <f t="shared" si="44"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E26" s="7" t="e">
-        <f t="shared" si="44"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F26" s="7" t="e">
-        <f t="shared" si="44"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G26" s="7" t="e">
-        <f t="shared" si="44"/>
-        <v>#DIV/0!</v>
+      <c r="C26" s="7">
+        <f t="shared" ref="C26" si="76">(C3-C6)/C3</f>
+        <v>0.17214634968807957</v>
+      </c>
+      <c r="D26" s="7">
+        <f t="shared" ref="D26:N26" si="77">(D3-D6)/D3</f>
+        <v>0.18094305759503998</v>
+      </c>
+      <c r="E26" s="7">
+        <f t="shared" si="77"/>
+        <v>0.17740671056757604</v>
+      </c>
+      <c r="F26" s="7">
+        <f t="shared" si="77"/>
+        <v>0.16715837950636828</v>
+      </c>
+      <c r="G26" s="7">
+        <f t="shared" si="77"/>
+        <v>0.16321263783530149</v>
       </c>
       <c r="H26" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="77"/>
         <v>0.17314145104764744</v>
       </c>
       <c r="I26" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="77"/>
         <v>-7.8235635519442834E-2</v>
       </c>
-      <c r="J26" s="7" t="e">
-        <f t="shared" si="44"/>
-        <v>#DIV/0!</v>
+      <c r="J26" s="7">
+        <f t="shared" si="77"/>
+        <v>0.16336902019243799</v>
       </c>
       <c r="K26" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="77"/>
         <v>0.14591344473187443</v>
       </c>
       <c r="L26" s="7">
-        <f>(L3-L6)/L3</f>
+        <f t="shared" si="77"/>
         <v>0.13301744265897542</v>
+      </c>
+      <c r="M26" s="7">
+        <f t="shared" si="77"/>
+        <v>0.16127277672015231</v>
+      </c>
+      <c r="N26" s="7">
+        <f t="shared" si="77"/>
+        <v>0.15262796932477088</v>
+      </c>
+      <c r="O26" s="7">
+        <f t="shared" ref="O26" si="78">(O3-O6)/O3</f>
+        <v>0.15817969981495442</v>
+      </c>
+      <c r="P26" s="7">
+        <f t="shared" ref="P26" si="79">(P3-P6)/P3</f>
+        <v>0.16474824770111246</v>
+      </c>
+      <c r="Q26" s="7">
+        <f t="shared" ref="Q26:R26" si="80">(Q3-Q6)/Q3</f>
+        <v>0.16</v>
+      </c>
+      <c r="R26" s="7">
+        <f t="shared" si="80"/>
+        <v>0.16000000000000009</v>
       </c>
       <c r="U26" s="7">
         <f>(U3-U6)/U3</f>
@@ -3479,64 +6540,64 @@
         <v>0.11962418338373462</v>
       </c>
       <c r="W26" s="7">
-        <f t="shared" ref="W26:Z26" si="45">(W3-W6)/W3</f>
+        <f t="shared" ref="W26:Z26" si="81">(W3-W6)/W3</f>
         <v>0.16592246803328597</v>
       </c>
       <c r="X26" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="81"/>
         <v>0.17422645894471472</v>
       </c>
       <c r="Y26" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="81"/>
         <v>0.1239837808396038</v>
       </c>
       <c r="Z26" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="81"/>
         <v>0.14835939072669932</v>
       </c>
       <c r="AA26" s="7">
-        <f t="shared" ref="AA26:AK26" si="46">(AA3-AA6)/AA3</f>
-        <v>0.15000000000000002</v>
+        <f t="shared" ref="AA26:AK26" si="82">(AA3-AA6)/AA3</f>
+        <v>0.16075559226975422</v>
       </c>
       <c r="AB26" s="7">
-        <f t="shared" si="46"/>
-        <v>0.15</v>
+        <f t="shared" si="82"/>
+        <v>0.16</v>
       </c>
       <c r="AC26" s="7">
-        <f t="shared" si="46"/>
-        <v>0.15000000000000002</v>
+        <f t="shared" si="82"/>
+        <v>0.16000000000000006</v>
       </c>
       <c r="AD26" s="7">
-        <f t="shared" si="46"/>
-        <v>0.14999999999999997</v>
+        <f t="shared" si="82"/>
+        <v>0.16000000000000003</v>
       </c>
       <c r="AE26" s="7">
-        <f t="shared" si="46"/>
-        <v>0.15</v>
+        <f t="shared" si="82"/>
+        <v>0.16000000000000006</v>
       </c>
       <c r="AF26" s="7">
-        <f t="shared" si="46"/>
-        <v>0.15000000000000002</v>
+        <f t="shared" si="82"/>
+        <v>0.16000000000000006</v>
       </c>
       <c r="AG26" s="7">
-        <f t="shared" si="46"/>
-        <v>0.15000000000000002</v>
+        <f t="shared" si="82"/>
+        <v>0.15999999999999998</v>
       </c>
       <c r="AH26" s="7">
-        <f t="shared" si="46"/>
-        <v>0.15000000000000002</v>
+        <f t="shared" si="82"/>
+        <v>0.16</v>
       </c>
       <c r="AI26" s="7">
-        <f t="shared" si="46"/>
-        <v>0.15000000000000002</v>
+        <f t="shared" si="82"/>
+        <v>0.16000000000000006</v>
       </c>
       <c r="AJ26" s="7">
-        <f t="shared" si="46"/>
-        <v>0.15000000000000002</v>
+        <f t="shared" si="82"/>
+        <v>0.16</v>
       </c>
       <c r="AK26" s="7">
-        <f t="shared" si="46"/>
-        <v>0.15</v>
+        <f t="shared" si="82"/>
+        <v>0.16000000000000006</v>
       </c>
       <c r="AN26" s="1" t="s">
         <v>56</v>
@@ -3549,45 +6610,69 @@
       <c r="B27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="7" t="e">
-        <f t="shared" ref="C27:K27" si="47">(C4-C7)/C4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D27" s="7" t="e">
-        <f t="shared" si="47"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E27" s="7" t="e">
-        <f t="shared" si="47"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F27" s="7" t="e">
-        <f t="shared" si="47"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G27" s="7" t="e">
-        <f t="shared" si="47"/>
-        <v>#DIV/0!</v>
+      <c r="C27" s="7">
+        <f t="shared" ref="C27" si="83">(C4-C7)/C4</f>
+        <v>0.28905033731188373</v>
+      </c>
+      <c r="D27" s="7">
+        <f t="shared" ref="D27:N27" si="84">(D4-D7)/D4</f>
+        <v>0.3057199211045365</v>
+      </c>
+      <c r="E27" s="7">
+        <f t="shared" si="84"/>
+        <v>0.29177592371871275</v>
+      </c>
+      <c r="F27" s="7">
+        <f t="shared" si="84"/>
+        <v>0.29647283126787416</v>
+      </c>
+      <c r="G27" s="7">
+        <f t="shared" si="84"/>
+        <v>0.33476394849785407</v>
       </c>
       <c r="H27" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="84"/>
         <v>0.30077487765089722</v>
       </c>
       <c r="I27" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="84"/>
         <v>0.28624458651268303</v>
       </c>
-      <c r="J27" s="7" t="e">
-        <f t="shared" si="47"/>
-        <v>#DIV/0!</v>
+      <c r="J27" s="7">
+        <f t="shared" si="84"/>
+        <v>0.30915070613271428</v>
       </c>
       <c r="K27" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="84"/>
         <v>0.29468212714914033</v>
       </c>
       <c r="L27" s="7">
-        <f>(L4-L7)/L4</f>
+        <f t="shared" si="84"/>
         <v>0.3184725722039155</v>
+      </c>
+      <c r="M27" s="7">
+        <f t="shared" si="84"/>
+        <v>0.30886452332280245</v>
+      </c>
+      <c r="N27" s="7">
+        <f t="shared" si="84"/>
+        <v>0.32002148997134672</v>
+      </c>
+      <c r="O27" s="7">
+        <f t="shared" ref="O27" si="85">(O4-O7)/O4</f>
+        <v>0.31636045494313209</v>
+      </c>
+      <c r="P27" s="7">
+        <f t="shared" ref="P27" si="86">(P4-P7)/P4</f>
+        <v>0.30082918739635156</v>
+      </c>
+      <c r="Q27" s="7">
+        <f t="shared" ref="Q27:R27" si="87">(Q4-Q7)/Q4</f>
+        <v>0.31000000000000011</v>
+      </c>
+      <c r="R27" s="7">
+        <f t="shared" si="87"/>
+        <v>0.31</v>
       </c>
       <c r="U27" s="7">
         <f>(U4-U7)/U4</f>
@@ -3598,116 +6683,140 @@
         <v>0.25241181790774797</v>
       </c>
       <c r="W27" s="7">
-        <f t="shared" ref="W27:Z27" si="48">(W4-W7)/W4</f>
+        <f t="shared" ref="W27:Z27" si="88">(W4-W7)/W4</f>
         <v>0.28548749834634213</v>
       </c>
       <c r="X27" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="88"/>
         <v>0.29581007300165635</v>
       </c>
       <c r="Y27" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="88"/>
         <v>0.30714765620962325</v>
       </c>
       <c r="Z27" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="88"/>
         <v>0.3108018555334659</v>
       </c>
       <c r="AA27" s="7">
-        <f t="shared" ref="AA27:AK27" si="49">(AA4-AA7)/AA4</f>
+        <f t="shared" ref="AA27:AK27" si="89">(AA4-AA7)/AA4</f>
+        <v>0.30923060963731475</v>
+      </c>
+      <c r="AB27" s="7">
+        <f t="shared" si="89"/>
         <v>0.31000000000000005</v>
       </c>
-      <c r="AB27" s="7">
-        <f t="shared" si="49"/>
+      <c r="AC27" s="7">
+        <f t="shared" si="89"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="AD27" s="7">
+        <f t="shared" si="89"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="AE27" s="7">
+        <f t="shared" si="89"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="AF27" s="7">
+        <f t="shared" si="89"/>
+        <v>0.31000000000000011</v>
+      </c>
+      <c r="AG27" s="7">
+        <f t="shared" si="89"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="AH27" s="7">
+        <f t="shared" si="89"/>
         <v>0.31</v>
       </c>
-      <c r="AC27" s="7">
-        <f t="shared" si="49"/>
-        <v>0.31000000000000011</v>
-      </c>
-      <c r="AD27" s="7">
-        <f t="shared" si="49"/>
+      <c r="AI27" s="7">
+        <f t="shared" si="89"/>
         <v>0.31000000000000005</v>
       </c>
-      <c r="AE27" s="7">
-        <f t="shared" si="49"/>
-        <v>0.31000000000000011</v>
-      </c>
-      <c r="AF27" s="7">
-        <f t="shared" si="49"/>
-        <v>0.31</v>
-      </c>
-      <c r="AG27" s="7">
-        <f t="shared" si="49"/>
+      <c r="AJ27" s="7">
+        <f t="shared" si="89"/>
         <v>0.31000000000000005</v>
       </c>
-      <c r="AH27" s="7">
-        <f t="shared" si="49"/>
-        <v>0.31</v>
-      </c>
-      <c r="AI27" s="7">
-        <f t="shared" si="49"/>
+      <c r="AK27" s="7">
+        <f t="shared" si="89"/>
         <v>0.31000000000000005</v>
-      </c>
-      <c r="AJ27" s="7">
-        <f t="shared" si="49"/>
-        <v>0.31000000000000005</v>
-      </c>
-      <c r="AK27" s="7">
-        <f t="shared" si="49"/>
-        <v>0.31</v>
       </c>
       <c r="AN27" s="1" t="s">
         <v>57</v>
       </c>
       <c r="AO27" s="3">
         <f>NPV(AO26,AA19:EE19)</f>
-        <v>114608.19006879516</v>
+        <v>147349.01469148142</v>
       </c>
     </row>
     <row r="28" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="7" t="e">
-        <f t="shared" ref="C28:K28" si="50">C9/C5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D28" s="7" t="e">
-        <f t="shared" si="50"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E28" s="7" t="e">
-        <f t="shared" si="50"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F28" s="7" t="e">
-        <f t="shared" si="50"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G28" s="7" t="e">
-        <f t="shared" si="50"/>
-        <v>#DIV/0!</v>
+      <c r="C28" s="7">
+        <f t="shared" ref="C28" si="90">C9/C5</f>
+        <v>0.20081445660473402</v>
+      </c>
+      <c r="D28" s="7">
+        <f t="shared" ref="D28:N28" si="91">D9/D5</f>
+        <v>0.21196518327816599</v>
+      </c>
+      <c r="E28" s="7">
+        <f t="shared" si="91"/>
+        <v>0.20571057754704739</v>
+      </c>
+      <c r="F28" s="7">
+        <f t="shared" si="91"/>
+        <v>0.19714806831371248</v>
+      </c>
+      <c r="G28" s="7">
+        <f t="shared" si="91"/>
+        <v>0.20733124201231556</v>
       </c>
       <c r="H28" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="91"/>
         <v>0.20731640731640733</v>
       </c>
       <c r="I28" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="91"/>
         <v>5.3030303030303032E-2</v>
       </c>
-      <c r="J28" s="7" t="e">
-        <f t="shared" si="50"/>
-        <v>#DIV/0!</v>
+      <c r="J28" s="7">
+        <f t="shared" si="91"/>
+        <v>0.20118432277814022</v>
       </c>
       <c r="K28" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="91"/>
         <v>0.18445998445998446</v>
       </c>
       <c r="L28" s="7">
-        <f>L9/L5</f>
+        <f t="shared" si="91"/>
         <v>0.18153237665432786</v>
+      </c>
+      <c r="M28" s="7">
+        <f t="shared" si="91"/>
+        <v>0.20080641146896311</v>
+      </c>
+      <c r="N28" s="7">
+        <f t="shared" si="91"/>
+        <v>0.1958562641631596</v>
+      </c>
+      <c r="O28" s="7">
+        <f t="shared" ref="O28" si="92">O9/O5</f>
+        <v>0.20269870974096327</v>
+      </c>
+      <c r="P28" s="7">
+        <f t="shared" ref="P28" si="93">P9/P5</f>
+        <v>0.20277095593345998</v>
+      </c>
+      <c r="Q28" s="7">
+        <f t="shared" ref="Q28:R28" si="94">Q9/Q5</f>
+        <v>0.20314880347249981</v>
+      </c>
+      <c r="R28" s="7">
+        <f t="shared" si="94"/>
+        <v>0.20218374080828605</v>
       </c>
       <c r="U28" s="7">
         <f>U9/U5</f>
@@ -3718,71 +6827,71 @@
         <v>0.15075900825277891</v>
       </c>
       <c r="W28" s="7">
-        <f t="shared" ref="W28:Z28" si="51">W9/W5</f>
+        <f t="shared" ref="W28:Z28" si="95">W9/W5</f>
         <v>0.19399577561036219</v>
       </c>
       <c r="X28" s="7">
-        <f t="shared" si="51"/>
+        <f t="shared" si="95"/>
         <v>0.20377493514625639</v>
       </c>
       <c r="Y28" s="7">
-        <f t="shared" si="51"/>
+        <f t="shared" si="95"/>
         <v>0.17540626813697041</v>
       </c>
       <c r="Z28" s="7">
-        <f t="shared" si="51"/>
+        <f t="shared" si="95"/>
         <v>0.19086427704426664</v>
       </c>
       <c r="AA28" s="7">
-        <f t="shared" ref="AA28:AK28" si="52">AA9/AA5</f>
-        <v>0.19215397249821378</v>
+        <f t="shared" ref="AA28:AK28" si="96">AA9/AA5</f>
+        <v>0.2026911899684555</v>
       </c>
       <c r="AB28" s="7">
-        <f t="shared" si="52"/>
-        <v>0.19215397249821375</v>
+        <f t="shared" si="96"/>
+        <v>0.20493434294013851</v>
       </c>
       <c r="AC28" s="7">
-        <f t="shared" si="52"/>
-        <v>0.19245464020840466</v>
+        <f t="shared" si="96"/>
+        <v>0.20673631796988712</v>
       </c>
       <c r="AD28" s="7">
-        <f t="shared" si="52"/>
-        <v>0.19275962781985115</v>
+        <f t="shared" si="96"/>
+        <v>0.20767403149938157</v>
       </c>
       <c r="AE28" s="7">
-        <f t="shared" si="52"/>
-        <v>0.19337680165110857</v>
+        <f t="shared" si="96"/>
+        <v>0.20830776727794817</v>
       </c>
       <c r="AF28" s="7">
-        <f t="shared" si="52"/>
-        <v>0.19399954037986841</v>
+        <f t="shared" si="96"/>
+        <v>0.20862783674663474</v>
       </c>
       <c r="AG28" s="7">
-        <f t="shared" si="52"/>
-        <v>0.19462779828187485</v>
+        <f t="shared" si="96"/>
+        <v>0.20894900610833711</v>
       </c>
       <c r="AH28" s="7">
-        <f t="shared" si="52"/>
-        <v>0.19526152667823291</v>
+        <f t="shared" si="96"/>
+        <v>0.20927126567902757</v>
       </c>
       <c r="AI28" s="7">
-        <f t="shared" si="52"/>
-        <v>0.19590067391727528</v>
+        <f t="shared" si="96"/>
+        <v>0.20959460560470461</v>
       </c>
       <c r="AJ28" s="7">
-        <f t="shared" si="52"/>
-        <v>0.19654518535925172</v>
+        <f t="shared" si="96"/>
+        <v>0.20991901586201531</v>
       </c>
       <c r="AK28" s="7">
-        <f t="shared" si="52"/>
-        <v>0.19719500336393919</v>
+        <f t="shared" si="96"/>
+        <v>0.210244486258928</v>
       </c>
       <c r="AN28" s="1" t="s">
         <v>58</v>
       </c>
       <c r="AO28" s="3">
         <f>Main!D8</f>
-        <v>-36143</v>
+        <v>-37196</v>
       </c>
     </row>
     <row r="29" spans="2:135" x14ac:dyDescent="0.3">
@@ -3793,26 +6902,53 @@
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7" t="e">
-        <f t="shared" ref="H29:K29" si="53">H10/D10-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I29" s="7" t="e">
-        <f t="shared" si="53"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J29" s="7" t="e">
-        <f t="shared" si="53"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K29" s="7" t="e">
-        <f t="shared" si="53"/>
-        <v>#DIV/0!</v>
+      <c r="G29" s="7">
+        <f t="shared" ref="G29:P29" si="97">G10/C10-1</f>
+        <v>-4.4094488188976433E-2</v>
+      </c>
+      <c r="H29" s="7">
+        <f t="shared" si="97"/>
+        <v>4.4412607449856756E-2</v>
+      </c>
+      <c r="I29" s="7">
+        <f t="shared" si="97"/>
+        <v>7.5528700906344337E-2</v>
+      </c>
+      <c r="J29" s="7">
+        <f t="shared" si="97"/>
+        <v>5.7262569832402299E-2</v>
+      </c>
+      <c r="K29" s="7">
+        <f t="shared" si="97"/>
+        <v>0.10214168039538718</v>
       </c>
       <c r="L29" s="7">
-        <f>L10/H10-1</f>
+        <f t="shared" si="97"/>
         <v>-3.1550068587105629E-2</v>
+      </c>
+      <c r="M29" s="7">
+        <f t="shared" si="97"/>
+        <v>5.47752808988764E-2</v>
+      </c>
+      <c r="N29" s="7">
+        <f t="shared" si="97"/>
+        <v>6.7371202113606365E-2</v>
+      </c>
+      <c r="O29" s="7">
+        <f t="shared" si="97"/>
+        <v>-4.783258594917783E-2</v>
+      </c>
+      <c r="P29" s="7">
+        <f t="shared" si="97"/>
+        <v>-1.2747875354107596E-2</v>
+      </c>
+      <c r="Q29" s="7">
+        <f t="shared" ref="Q29" si="98">Q10/M10-1</f>
+        <v>-2.0000000000000018E-2</v>
+      </c>
+      <c r="R29" s="7">
+        <f t="shared" ref="R29" si="99">R10/N10-1</f>
+        <v>-1.9999999999999907E-2</v>
       </c>
       <c r="U29" s="7"/>
       <c r="V29" s="7">
@@ -3820,63 +6956,63 @@
         <v>5.3017944535073358E-2</v>
       </c>
       <c r="W29" s="7">
-        <f t="shared" ref="W29:Z29" si="54">W10/V10-1</f>
+        <f t="shared" ref="W29:Z29" si="100">W10/V10-1</f>
         <v>5.8094500387296577E-2</v>
       </c>
       <c r="X29" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="100"/>
         <v>-7.6866764275256294E-3</v>
       </c>
       <c r="Y29" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="100"/>
         <v>3.4673552194762092E-2</v>
       </c>
       <c r="Z29" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="100"/>
         <v>4.5989304812834142E-2</v>
       </c>
       <c r="AA29" s="7">
-        <f t="shared" ref="AA29" si="55">AA10/Z10-1</f>
+        <f t="shared" ref="AA29" si="101">AA10/Z10-1</f>
+        <v>-2.4601226993865022E-2</v>
+      </c>
+      <c r="AB29" s="7">
+        <f t="shared" ref="AB29" si="102">AB10/AA10-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AC29" s="7">
+        <f t="shared" ref="AC29" si="103">AC10/AB10-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AB29" s="7">
-        <f t="shared" ref="AB29" si="56">AB10/AA10-1</f>
+      <c r="AD29" s="7">
+        <f t="shared" ref="AD29" si="104">AD10/AC10-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AC29" s="7">
-        <f t="shared" ref="AC29" si="57">AC10/AB10-1</f>
+      <c r="AE29" s="7">
+        <f t="shared" ref="AE29" si="105">AE10/AD10-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AD29" s="7">
-        <f t="shared" ref="AD29" si="58">AD10/AC10-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AE29" s="7">
-        <f t="shared" ref="AE29" si="59">AE10/AD10-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AF29" s="7">
-        <f t="shared" ref="AF29" si="60">AF10/AE10-1</f>
+        <f t="shared" ref="AF29" si="106">AF10/AE10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG29" s="7">
-        <f t="shared" ref="AG29" si="61">AG10/AF10-1</f>
+        <f t="shared" ref="AG29" si="107">AG10/AF10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH29" s="7">
-        <f t="shared" ref="AH29" si="62">AH10/AG10-1</f>
+        <f t="shared" ref="AH29" si="108">AH10/AG10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI29" s="7">
-        <f t="shared" ref="AI29" si="63">AI10/AH10-1</f>
+        <f t="shared" ref="AI29" si="109">AI10/AH10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ29" s="7">
-        <f t="shared" ref="AJ29" si="64">AJ10/AI10-1</f>
+        <f t="shared" ref="AJ29" si="110">AJ10/AI10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK29" s="7">
-        <f t="shared" ref="AK29" si="65">AK10/AJ10-1</f>
+        <f t="shared" ref="AK29" si="111">AK10/AJ10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN29" s="1" t="s">
@@ -3884,52 +7020,76 @@
       </c>
       <c r="AO29" s="3">
         <f>AO27+AO28</f>
-        <v>78465.190068795157</v>
+        <v>110153.01469148142</v>
       </c>
     </row>
     <row r="30" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="7" t="e">
-        <f t="shared" ref="C30:K30" si="66">C11/C5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D30" s="7" t="e">
-        <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E30" s="7" t="e">
-        <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F30" s="7" t="e">
-        <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G30" s="7" t="e">
-        <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
+      <c r="C30" s="7">
+        <f t="shared" ref="C30" si="112">C11/C5</f>
+        <v>9.3471621277678801E-2</v>
+      </c>
+      <c r="D30" s="7">
+        <f t="shared" ref="D30:N30" si="113">D11/D5</f>
+        <v>8.7286992766948637E-2</v>
+      </c>
+      <c r="E30" s="7">
+        <f t="shared" si="113"/>
+        <v>7.9700312665919412E-2</v>
+      </c>
+      <c r="F30" s="7">
+        <f t="shared" si="113"/>
+        <v>7.3453821920079584E-2</v>
+      </c>
+      <c r="G30" s="7">
+        <f t="shared" si="113"/>
+        <v>8.121296619031021E-2</v>
       </c>
       <c r="H30" s="7">
-        <f t="shared" si="66"/>
+        <f t="shared" si="113"/>
         <v>8.7360087360087366E-2</v>
       </c>
       <c r="I30" s="7">
-        <f t="shared" si="66"/>
+        <f t="shared" si="113"/>
         <v>0.10405525846702317</v>
       </c>
-      <c r="J30" s="7" t="e">
-        <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
+      <c r="J30" s="7">
+        <f t="shared" si="113"/>
+        <v>7.0758267677021133E-2</v>
       </c>
       <c r="K30" s="7">
-        <f t="shared" si="66"/>
+        <f t="shared" si="113"/>
         <v>7.2209272209272216E-2</v>
       </c>
       <c r="L30" s="7">
-        <f>L11/L5</f>
+        <f t="shared" si="113"/>
         <v>7.3474975914000304E-2</v>
+      </c>
+      <c r="M30" s="7">
+        <f t="shared" si="113"/>
+        <v>6.9142316690726263E-2</v>
+      </c>
+      <c r="N30" s="7">
+        <f t="shared" si="113"/>
+        <v>7.2792859455209732E-2</v>
+      </c>
+      <c r="O30" s="7">
+        <f t="shared" ref="O30" si="114">O11/O5</f>
+        <v>7.1308972717423424E-2</v>
+      </c>
+      <c r="P30" s="7">
+        <f t="shared" ref="P30" si="115">P11/P5</f>
+        <v>7.2888188684490984E-2</v>
+      </c>
+      <c r="Q30" s="7">
+        <f t="shared" ref="Q30:R30" si="116">Q11/Q5</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="R30" s="7">
+        <f t="shared" si="116"/>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="U30" s="7">
         <f>U11/U5</f>
@@ -3940,63 +7100,63 @@
         <v>9.7902345061586585E-2</v>
       </c>
       <c r="W30" s="7">
-        <f t="shared" ref="W30:Z30" si="67">W11/W5</f>
+        <f t="shared" ref="W30:Z30" si="117">W11/W5</f>
         <v>8.1133130396968373E-2</v>
       </c>
       <c r="X30" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="117"/>
         <v>8.308733637475027E-2</v>
       </c>
       <c r="Y30" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="117"/>
         <v>8.4286128845037722E-2</v>
       </c>
       <c r="Z30" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="117"/>
         <v>7.1911615348410909E-2</v>
       </c>
       <c r="AA30" s="7">
-        <f t="shared" ref="AA30:AK30" si="68">AA11/AA5</f>
+        <f t="shared" ref="AA30:AK30" si="118">AA11/AA5</f>
+        <v>7.1019571273203824E-2</v>
+      </c>
+      <c r="AB30" s="7">
+        <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AB30" s="7">
-        <f t="shared" si="68"/>
+      <c r="AC30" s="7">
+        <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AC30" s="7">
-        <f t="shared" si="68"/>
+      <c r="AD30" s="7">
+        <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AD30" s="7">
-        <f t="shared" si="68"/>
+      <c r="AE30" s="7">
+        <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AE30" s="7">
-        <f t="shared" si="68"/>
+      <c r="AF30" s="7">
+        <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AF30" s="7">
-        <f t="shared" si="68"/>
+      <c r="AG30" s="7">
+        <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AG30" s="7">
-        <f t="shared" si="68"/>
+      <c r="AH30" s="7">
+        <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AH30" s="7">
-        <f t="shared" si="68"/>
+      <c r="AI30" s="7">
+        <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AI30" s="7">
-        <f t="shared" si="68"/>
+      <c r="AJ30" s="7">
+        <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AJ30" s="7">
-        <f t="shared" si="68"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
       <c r="AK30" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AN30" s="1" t="s">
@@ -4004,52 +7164,76 @@
       </c>
       <c r="AO30" s="9">
         <f>AO29/AK20</f>
-        <v>58.903378176409554</v>
+        <v>82.29586454350499</v>
       </c>
     </row>
     <row r="31" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="7" t="e">
-        <f t="shared" ref="C31:K31" si="69">C12/C5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D31" s="7" t="e">
-        <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E31" s="7" t="e">
-        <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F31" s="7" t="e">
-        <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G31" s="7" t="e">
-        <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
+      <c r="C31" s="7">
+        <f t="shared" ref="C31" si="119">C12/C5</f>
+        <v>6.6938152201578005E-2</v>
+      </c>
+      <c r="D31" s="7">
+        <f t="shared" ref="D31:N31" si="120">D12/D5</f>
+        <v>8.1892852764496746E-2</v>
+      </c>
+      <c r="E31" s="7">
+        <f t="shared" si="120"/>
+        <v>8.6956521739130432E-2</v>
+      </c>
+      <c r="F31" s="7">
+        <f t="shared" si="120"/>
+        <v>8.4120930746697617E-2</v>
+      </c>
+      <c r="G31" s="7">
+        <f t="shared" si="120"/>
+        <v>9.0856279772278378E-2</v>
       </c>
       <c r="H31" s="7">
-        <f t="shared" si="69"/>
+        <f t="shared" si="120"/>
         <v>8.0152880152880149E-2</v>
       </c>
       <c r="I31" s="7">
-        <f t="shared" si="69"/>
+        <f t="shared" si="120"/>
         <v>-0.10390671420083185</v>
       </c>
-      <c r="J31" s="7" t="e">
-        <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
+      <c r="J31" s="7">
+        <f t="shared" si="120"/>
+        <v>9.243739649721483E-2</v>
       </c>
       <c r="K31" s="7">
-        <f t="shared" si="69"/>
+        <f t="shared" si="120"/>
         <v>7.75964775964776E-2</v>
       </c>
       <c r="L31" s="7">
-        <f>L12/L5</f>
+        <f t="shared" si="120"/>
         <v>7.2257999087267377E-2</v>
+      </c>
+      <c r="M31" s="7">
+        <f t="shared" si="120"/>
+        <v>9.428045198865051E-2</v>
+      </c>
+      <c r="N31" s="7">
+        <f t="shared" si="120"/>
+        <v>8.5695786893585535E-2</v>
+      </c>
+      <c r="O31" s="7">
+        <f t="shared" ref="O31" si="121">O12/O5</f>
+        <v>0.1000196986112479</v>
+      </c>
+      <c r="P31" s="7">
+        <f t="shared" ref="P31" si="122">P12/P5</f>
+        <v>9.758583939576479E-2</v>
+      </c>
+      <c r="Q31" s="7">
+        <f t="shared" ref="Q31:R31" si="123">Q12/Q5</f>
+        <v>9.9521297618367657E-2</v>
+      </c>
+      <c r="R31" s="7">
+        <f t="shared" si="123"/>
+        <v>9.8387853728136465E-2</v>
       </c>
       <c r="U31" s="7">
         <f>U12/U5</f>
@@ -4060,116 +7244,140 @@
         <v>7.2278085072543163E-3</v>
       </c>
       <c r="W31" s="7">
-        <f t="shared" ref="W31:Z31" si="70">W12/W5</f>
+        <f t="shared" ref="W31:Z31" si="124">W12/W5</f>
         <v>7.043237870410636E-2</v>
       </c>
       <c r="X31" s="7">
-        <f t="shared" si="70"/>
+        <f t="shared" si="124"/>
         <v>8.0269553030980711E-2</v>
       </c>
       <c r="Y31" s="7">
-        <f t="shared" si="70"/>
+        <f t="shared" si="124"/>
         <v>5.0420777713290774E-2</v>
       </c>
       <c r="Z31" s="7">
-        <f t="shared" si="70"/>
+        <f t="shared" si="124"/>
         <v>8.2612896034085559E-2</v>
       </c>
       <c r="AA31" s="7">
-        <f t="shared" ref="AA31:AK31" si="71">AA12/AA5</f>
-        <v>8.7596833844259536E-2</v>
+        <f t="shared" ref="AA31:AK31" si="125">AA12/AA5</f>
+        <v>9.8853831482562993E-2</v>
       </c>
       <c r="AB31" s="7">
-        <f t="shared" si="71"/>
-        <v>8.8584180662943907E-2</v>
+        <f t="shared" si="125"/>
+        <v>0.10382363391314751</v>
       </c>
       <c r="AC31" s="7">
-        <f t="shared" si="71"/>
-        <v>8.9295585785867687E-2</v>
+        <f t="shared" si="125"/>
+        <v>0.10645605227063344</v>
       </c>
       <c r="AD31" s="7">
-        <f t="shared" si="71"/>
-        <v>8.9686609127045139E-2</v>
+        <f t="shared" si="125"/>
+        <v>0.10766873386503374</v>
       </c>
       <c r="AE31" s="7">
-        <f t="shared" si="71"/>
-        <v>9.0152153268188012E-2</v>
+        <f t="shared" si="125"/>
+        <v>0.10848830155837286</v>
       </c>
       <c r="AF31" s="7">
-        <f t="shared" si="71"/>
-        <v>9.0952303314682209E-2</v>
+        <f t="shared" si="125"/>
+        <v>0.10919365334990139</v>
       </c>
       <c r="AG31" s="7">
-        <f t="shared" si="71"/>
-        <v>9.1759544885319524E-2</v>
+        <f t="shared" si="125"/>
+        <v>0.10989573286439933</v>
       </c>
       <c r="AH31" s="7">
-        <f t="shared" si="71"/>
-        <v>9.2573815433130868E-2</v>
+        <f t="shared" si="125"/>
+        <v>0.11059457325725389</v>
       </c>
       <c r="AI31" s="7">
-        <f t="shared" si="71"/>
-        <v>9.3395048591464899E-2</v>
+        <f t="shared" si="125"/>
+        <v>0.11129020713066723</v>
       </c>
       <c r="AJ31" s="7">
-        <f t="shared" si="71"/>
-        <v>9.4223174154316178E-2</v>
+        <f t="shared" si="125"/>
+        <v>0.11198266653816466</v>
       </c>
       <c r="AK31" s="7">
-        <f t="shared" si="71"/>
-        <v>9.5058118060404859E-2</v>
+        <f t="shared" si="125"/>
+        <v>0.11267198298910734</v>
       </c>
       <c r="AN31" s="1" t="s">
         <v>61</v>
       </c>
       <c r="AO31" s="9">
         <f>Main!D3</f>
-        <v>119.35</v>
+        <v>157.52000000000001</v>
       </c>
     </row>
     <row r="32" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="7" t="e">
-        <f t="shared" ref="C32:K32" si="72">C17/C16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D32" s="7" t="e">
-        <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E32" s="7" t="e">
-        <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F32" s="7" t="e">
-        <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G32" s="7" t="e">
-        <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
+      <c r="C32" s="7">
+        <f t="shared" ref="C32" si="126">C17/C16</f>
+        <v>9.3397745571658614E-2</v>
+      </c>
+      <c r="D32" s="7">
+        <f t="shared" ref="D32:N32" si="127">D17/D16</f>
+        <v>0.1068090787716956</v>
+      </c>
+      <c r="E32" s="7">
+        <f t="shared" si="127"/>
+        <v>0.16815742397137745</v>
+      </c>
+      <c r="F32" s="7">
+        <f t="shared" si="127"/>
+        <v>0.13647058823529412</v>
+      </c>
+      <c r="G32" s="7">
+        <f t="shared" si="127"/>
+        <v>0.16844469399213924</v>
       </c>
       <c r="H32" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="127"/>
         <v>0.15432482887367766</v>
       </c>
       <c r="I32" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="127"/>
         <v>0.29425113464447805</v>
       </c>
-      <c r="J32" s="7" t="e">
-        <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
+      <c r="J32" s="7">
+        <f t="shared" si="127"/>
+        <v>0.16779661016949152</v>
       </c>
       <c r="K32" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="127"/>
         <v>5.834683954619125E-2</v>
       </c>
       <c r="L32" s="7">
-        <f>L17/L16</f>
+        <f t="shared" si="127"/>
         <v>0.59112149532710279</v>
+      </c>
+      <c r="M32" s="7">
+        <f t="shared" si="127"/>
+        <v>0.19464847848898217</v>
+      </c>
+      <c r="N32" s="7">
+        <f t="shared" si="127"/>
+        <v>0.22349427575908412</v>
+      </c>
+      <c r="O32" s="7">
+        <f t="shared" ref="O32" si="128">O17/O16</f>
+        <v>0.17007150153217568</v>
+      </c>
+      <c r="P32" s="7">
+        <f t="shared" ref="P32" si="129">P17/P16</f>
+        <v>0.15441176470588236</v>
+      </c>
+      <c r="Q32" s="7">
+        <f t="shared" ref="Q32:R32" si="130">Q17/Q16</f>
+        <v>0.17</v>
+      </c>
+      <c r="R32" s="7">
+        <f t="shared" si="130"/>
+        <v>0.17</v>
       </c>
       <c r="U32" s="7">
         <f>U17/U16</f>
@@ -4180,63 +7388,63 @@
         <v>-0.24436889077773055</v>
       </c>
       <c r="W32" s="7">
-        <f t="shared" ref="W32:Z32" si="73">W17/W16</f>
+        <f t="shared" ref="W32:Z32" si="131">W17/W16</f>
         <v>0.15939971608193065</v>
       </c>
       <c r="X32" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="131"/>
         <v>0.12914827529834885</v>
       </c>
       <c r="Y32" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="131"/>
         <v>0.11887382690302398</v>
       </c>
       <c r="Z32" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="131"/>
         <v>0.19066838876331935</v>
       </c>
       <c r="AA32" s="7">
-        <f t="shared" ref="AA32:AK32" si="74">AA17/AA16</f>
+        <f t="shared" ref="AA32:AK32" si="132">AA17/AA16</f>
+        <v>0.16616481474825659</v>
+      </c>
+      <c r="AB32" s="7">
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AB32" s="7">
-        <f t="shared" si="74"/>
+      <c r="AC32" s="7">
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AC32" s="7">
-        <f t="shared" si="74"/>
+      <c r="AD32" s="7">
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AD32" s="7">
-        <f t="shared" si="74"/>
+      <c r="AE32" s="7">
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AE32" s="7">
-        <f t="shared" si="74"/>
+      <c r="AF32" s="7">
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AF32" s="7">
-        <f t="shared" si="74"/>
+      <c r="AG32" s="7">
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AG32" s="7">
-        <f t="shared" si="74"/>
+      <c r="AH32" s="7">
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AH32" s="7">
-        <f t="shared" si="74"/>
+      <c r="AI32" s="7">
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AI32" s="7">
-        <f t="shared" si="74"/>
+      <c r="AJ32" s="7">
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AJ32" s="7">
-        <f t="shared" si="74"/>
-        <v>0.15</v>
-      </c>
       <c r="AK32" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
       <c r="AN32" s="4" t="s">
@@ -4244,71 +7452,95 @@
       </c>
       <c r="AO32" s="12">
         <f>AO30/AO31-1</f>
-        <v>-0.50646520170582687</v>
+        <v>-0.47755291681370626</v>
       </c>
     </row>
     <row r="33" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="7" t="e">
-        <f t="shared" ref="C33:K33" si="75">C18/C5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D33" s="7" t="e">
-        <f t="shared" si="75"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E33" s="7" t="e">
-        <f t="shared" si="75"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F33" s="7" t="e">
-        <f t="shared" si="75"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G33" s="7" t="e">
-        <f t="shared" si="75"/>
-        <v>#DIV/0!</v>
+      <c r="C33" s="7">
+        <f t="shared" ref="C33:O33" si="133">C18/C16</f>
+        <v>1.8518518518518517E-2</v>
+      </c>
+      <c r="D33" s="7">
+        <f t="shared" si="133"/>
+        <v>2.2696929238985315E-2</v>
+      </c>
+      <c r="E33" s="7">
+        <f t="shared" si="133"/>
+        <v>4.7704233750745376E-3</v>
+      </c>
+      <c r="F33" s="7">
+        <f t="shared" si="133"/>
+        <v>2.7058823529411764E-2</v>
+      </c>
+      <c r="G33" s="7">
+        <f t="shared" si="133"/>
+        <v>3.0881527231892195E-2</v>
       </c>
       <c r="H33" s="7">
-        <f t="shared" si="75"/>
-        <v>1.7472017472017472E-3</v>
+        <f t="shared" si="133"/>
+        <v>1.9912881144990666E-2</v>
       </c>
       <c r="I33" s="7">
-        <f t="shared" si="75"/>
-        <v>3.787878787878788E-3</v>
-      </c>
-      <c r="J33" s="7" t="e">
-        <f t="shared" si="75"/>
-        <v>#DIV/0!</v>
+        <f t="shared" si="133"/>
+        <v>-3.8577912254160365E-2</v>
+      </c>
+      <c r="J33" s="7">
+        <f t="shared" si="133"/>
+        <v>2.655367231638418E-2</v>
       </c>
       <c r="K33" s="7">
-        <f t="shared" si="75"/>
-        <v>1.7612017612017611E-3</v>
+        <f t="shared" si="133"/>
+        <v>1.8368449486763912E-2</v>
       </c>
       <c r="L33" s="7">
-        <f>L18/L5</f>
-        <v>3.2452715379544649E-3</v>
+        <f t="shared" si="133"/>
+        <v>0.14953271028037382</v>
+      </c>
+      <c r="M33" s="7">
+        <f t="shared" si="133"/>
+        <v>3.3053515215110178E-2</v>
+      </c>
+      <c r="N33" s="7">
+        <f t="shared" si="133"/>
+        <v>3.8825286212045791E-2</v>
+      </c>
+      <c r="O33" s="7">
+        <f t="shared" si="133"/>
+        <v>4.5965270684371805E-2</v>
+      </c>
+      <c r="P33" s="7">
+        <f>P18/P16</f>
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="Q33" s="7">
+        <f t="shared" ref="Q33:R33" si="134">Q18/Q16</f>
+        <v>0.03</v>
+      </c>
+      <c r="R33" s="7">
+        <f t="shared" si="134"/>
+        <v>0.03</v>
       </c>
       <c r="U33" s="7">
-        <f t="shared" ref="U33:Z33" si="76">U18/U16</f>
+        <f t="shared" ref="U33:Y33" si="135">U18/U16</f>
         <v>5.3227360308285163E-2</v>
       </c>
       <c r="V33" s="7">
-        <f t="shared" si="76"/>
+        <f t="shared" si="135"/>
         <v>-7.6923076923076927E-2</v>
       </c>
       <c r="W33" s="7">
-        <f t="shared" si="76"/>
+        <f t="shared" si="135"/>
         <v>5.0294058000405595E-2</v>
       </c>
       <c r="X33" s="7">
-        <f t="shared" si="76"/>
+        <f t="shared" si="135"/>
         <v>1.8146150073565473E-2</v>
       </c>
       <c r="Y33" s="7">
-        <f t="shared" si="76"/>
+        <f t="shared" si="135"/>
         <v>4.8227320125130341E-2</v>
       </c>
       <c r="Z33" s="7">
@@ -4316,47 +7548,47 @@
         <v>3.8585728123990956E-2</v>
       </c>
       <c r="AA33" s="7">
-        <f t="shared" ref="AA33:AK33" si="77">AA18/AA16</f>
+        <f t="shared" ref="AA33:AK33" si="136">AA18/AA16</f>
+        <v>3.4610459591956327E-2</v>
+      </c>
+      <c r="AB33" s="7">
+        <f t="shared" si="136"/>
+        <v>3.0000000000000002E-2</v>
+      </c>
+      <c r="AC33" s="7">
+        <f t="shared" si="136"/>
+        <v>2.9999999999999995E-2</v>
+      </c>
+      <c r="AD33" s="7">
+        <f t="shared" si="136"/>
         <v>0.03</v>
       </c>
-      <c r="AB33" s="7">
-        <f t="shared" si="77"/>
+      <c r="AE33" s="7">
+        <f t="shared" si="136"/>
         <v>0.03</v>
       </c>
-      <c r="AC33" s="7">
-        <f t="shared" si="77"/>
+      <c r="AF33" s="7">
+        <f t="shared" si="136"/>
+        <v>3.0000000000000002E-2</v>
+      </c>
+      <c r="AG33" s="7">
+        <f t="shared" si="136"/>
         <v>0.03</v>
       </c>
-      <c r="AD33" s="7">
-        <f t="shared" si="77"/>
+      <c r="AH33" s="7">
+        <f t="shared" si="136"/>
         <v>0.03</v>
       </c>
-      <c r="AE33" s="7">
-        <f t="shared" si="77"/>
+      <c r="AI33" s="7">
+        <f t="shared" si="136"/>
+        <v>2.9999999999999995E-2</v>
+      </c>
+      <c r="AJ33" s="7">
+        <f t="shared" si="136"/>
         <v>0.03</v>
       </c>
-      <c r="AF33" s="7">
-        <f t="shared" si="77"/>
-        <v>0.03</v>
-      </c>
-      <c r="AG33" s="7">
-        <f t="shared" si="77"/>
-        <v>3.0000000000000002E-2</v>
-      </c>
-      <c r="AH33" s="7">
-        <f t="shared" si="77"/>
-        <v>0.03</v>
-      </c>
-      <c r="AI33" s="7">
-        <f t="shared" si="77"/>
-        <v>0.03</v>
-      </c>
-      <c r="AJ33" s="7">
-        <f t="shared" si="77"/>
-        <v>0.03</v>
-      </c>
       <c r="AK33" s="7">
-        <f t="shared" si="77"/>
+        <f t="shared" si="136"/>
         <v>0.03</v>
       </c>
       <c r="AN33" s="1" t="s">
@@ -4370,45 +7602,69 @@
       <c r="B34" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="7" t="e">
-        <f t="shared" ref="C34:K34" si="78">C19/C5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D34" s="7" t="e">
-        <f t="shared" si="78"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E34" s="7" t="e">
-        <f t="shared" si="78"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F34" s="7" t="e">
-        <f t="shared" si="78"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G34" s="7" t="e">
-        <f t="shared" si="78"/>
-        <v>#DIV/0!</v>
+      <c r="C34" s="7">
+        <f t="shared" ref="C34" si="137">C19/C5</f>
+        <v>7.0183252736065155E-2</v>
+      </c>
+      <c r="D34" s="7">
+        <f t="shared" ref="D34:N34" si="138">D19/D5</f>
+        <v>7.9931347309059708E-2</v>
+      </c>
+      <c r="E34" s="7">
+        <f t="shared" si="138"/>
+        <v>8.1824081175151914E-2</v>
+      </c>
+      <c r="F34" s="7">
+        <f t="shared" si="138"/>
+        <v>7.8593931354667551E-2</v>
+      </c>
+      <c r="G34" s="7">
+        <f t="shared" si="138"/>
+        <v>8.2839549204136165E-2</v>
       </c>
       <c r="H34" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="138"/>
         <v>7.2454272454272453E-2</v>
       </c>
       <c r="I34" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="138"/>
         <v>-7.3083778966131913E-2</v>
       </c>
-      <c r="J34" s="7" t="e">
-        <f t="shared" si="78"/>
-        <v>#DIV/0!</v>
+      <c r="J34" s="7">
+        <f t="shared" si="138"/>
+        <v>7.1561198374065341E-2</v>
       </c>
       <c r="K34" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="138"/>
         <v>8.8526288526288521E-2</v>
       </c>
       <c r="L34" s="7">
-        <f>L19/L5</f>
+        <f t="shared" si="138"/>
         <v>5.6285178236397749E-3</v>
+      </c>
+      <c r="M34" s="7">
+        <f t="shared" si="138"/>
+        <v>7.3273931007018761E-2</v>
+      </c>
+      <c r="N34" s="7">
+        <f t="shared" si="138"/>
+        <v>6.8538130694168253E-2</v>
+      </c>
+      <c r="O34" s="7">
+        <f t="shared" ref="O34" si="139">O19/O5</f>
+        <v>7.5593420663843197E-2</v>
+      </c>
+      <c r="P34" s="7">
+        <f t="shared" ref="P34" si="140">P19/P5</f>
+        <v>7.6780501366943144E-2</v>
+      </c>
+      <c r="Q34" s="7">
+        <f t="shared" ref="Q34:R34" si="141">Q19/Q5</f>
+        <v>7.5113023016734212E-2</v>
+      </c>
+      <c r="R34" s="7">
+        <f t="shared" si="141"/>
+        <v>7.5192751878248712E-2</v>
       </c>
       <c r="U34" s="7">
         <f>U19/U5</f>
@@ -4419,64 +7675,64 @@
         <v>-5.4941947797197237E-2</v>
       </c>
       <c r="W34" s="7">
-        <f t="shared" ref="W34:Z34" si="79">W19/W5</f>
+        <f t="shared" ref="W34:Z34" si="142">W19/W5</f>
         <v>6.0523700068335712E-2</v>
       </c>
       <c r="X34" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="142"/>
         <v>7.7764856725407755E-2</v>
       </c>
       <c r="Y34" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="142"/>
         <v>4.6358096343586765E-2</v>
       </c>
       <c r="Z34" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="142"/>
         <v>5.9129530084966186E-2</v>
       </c>
       <c r="AA34" s="7">
-        <f t="shared" ref="AA34:AK34" si="80">AA19/AA5</f>
-        <v>6.8539591126745653E-2</v>
+        <f t="shared" ref="AA34:AK34" si="143">AA19/AA5</f>
+        <v>7.5658975369286591E-2</v>
       </c>
       <c r="AB34" s="7">
-        <f t="shared" si="80"/>
-        <v>6.9474541713325788E-2</v>
+        <f t="shared" si="143"/>
+        <v>8.1487340385963059E-2</v>
       </c>
       <c r="AC34" s="7">
-        <f t="shared" si="80"/>
-        <v>7.0127257226773265E-2</v>
+        <f t="shared" si="143"/>
+        <v>8.3778111570669833E-2</v>
       </c>
       <c r="AD34" s="7">
-        <f t="shared" si="80"/>
-        <v>7.0486192701102318E-2</v>
+        <f t="shared" si="143"/>
+        <v>8.4838593231775353E-2</v>
       </c>
       <c r="AE34" s="7">
-        <f t="shared" si="80"/>
-        <v>7.0884030567840831E-2</v>
+        <f t="shared" si="143"/>
+        <v>8.5565615998704644E-2</v>
       </c>
       <c r="AF34" s="7">
-        <f t="shared" si="80"/>
-        <v>7.1556390371420961E-2</v>
+        <f t="shared" si="143"/>
+        <v>8.6187866858918896E-2</v>
       </c>
       <c r="AG34" s="7">
-        <f t="shared" si="80"/>
-        <v>7.2234709127076149E-2</v>
+        <f t="shared" si="143"/>
+        <v>8.6806936703118842E-2</v>
       </c>
       <c r="AH34" s="7">
-        <f t="shared" si="80"/>
-        <v>7.2918934277079295E-2</v>
+        <f t="shared" si="143"/>
+        <v>8.7422857595766956E-2</v>
       </c>
       <c r="AI34" s="7">
-        <f t="shared" si="80"/>
-        <v>7.3609010054054139E-2</v>
+        <f t="shared" si="143"/>
+        <v>8.803566110408724E-2</v>
       </c>
       <c r="AJ34" s="7">
-        <f t="shared" si="80"/>
-        <v>7.430487746444539E-2</v>
+        <f t="shared" si="143"/>
+        <v>8.8645378302204439E-2</v>
       </c>
       <c r="AK34" s="7">
-        <f t="shared" si="80"/>
-        <v>7.5006474275140914E-2</v>
+        <f t="shared" si="143"/>
+        <v>8.9252039775281691E-2</v>
       </c>
     </row>
   </sheetData>
@@ -4485,4 +7741,17 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF47B37D-5C25-469B-9D0C-C2E6A30B3F3A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="8.88671875" style="13"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Financial Analysis/RTX.xlsx
+++ b/Financial Analysis/RTX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4455DDB6-80A9-4E5C-9025-17FEB4188569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D3E817-BABA-4B61-8FD5-B6CB2F82B5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4DC2FBA0-6E3D-459B-9C6A-21AC42B1058B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4DC2FBA0-6E3D-459B-9C6A-21AC42B1058B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="F3" s="10">
         <f ca="1">TODAY()</f>
-        <v>45906</v>
+        <v>45928</v>
       </c>
       <c r="G3" s="10">
         <v>45958</v>

--- a/Financial Analysis/RTX.xlsx
+++ b/Financial Analysis/RTX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D3E817-BABA-4B61-8FD5-B6CB2F82B5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB385D7-951C-4F15-9334-2DBA92593D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4DC2FBA0-6E3D-459B-9C6A-21AC42B1058B}"/>
   </bookViews>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="68">
   <si>
     <t>RTX</t>
   </si>
@@ -279,17 +279,27 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Overvalued</t>
+    <t>L+S/E</t>
+  </si>
+  <si>
+    <t>EV/B</t>
+  </si>
+  <si>
+    <t>B/EV</t>
+  </si>
+  <si>
+    <t>Heavily overvalued</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,6 +343,15 @@
     </font>
     <font>
       <i/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -396,7 +415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -419,6 +438,8 @@
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3114,14 +3135,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="9">
-        <v>157.52000000000001</v>
+        <v>166.58</v>
       </c>
       <c r="E3" s="10">
-        <v>45906</v>
+        <v>45934</v>
       </c>
       <c r="F3" s="10">
         <f ca="1">TODAY()</f>
-        <v>45928</v>
+        <v>45939</v>
       </c>
       <c r="G3" s="10">
         <v>45958</v>
@@ -3145,7 +3166,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>210840.52000000002</v>
+        <v>222967.33000000002</v>
       </c>
       <c r="E5" s="11"/>
     </row>
@@ -3189,7 +3210,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>248036.52000000002</v>
+        <v>260163.33000000002</v>
       </c>
       <c r="E9" s="11"/>
     </row>
@@ -3200,7 +3221,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37BCCFEA-4609-4B74-A80E-9BDBF53DBD8A}">
-  <dimension ref="B2:EE34"/>
+  <dimension ref="B2:EE41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -7308,7 +7329,7 @@
       </c>
       <c r="AO31" s="9">
         <f>Main!D3</f>
-        <v>157.52000000000001</v>
+        <v>166.58</v>
       </c>
     </row>
     <row r="32" spans="2:135" x14ac:dyDescent="0.3">
@@ -7452,7 +7473,7 @@
       </c>
       <c r="AO32" s="12">
         <f>AO30/AO31-1</f>
-        <v>-0.47755291681370626</v>
+        <v>-0.50596791605531888</v>
       </c>
     </row>
     <row r="33" spans="2:41" x14ac:dyDescent="0.3">
@@ -7595,7 +7616,7 @@
         <v>63</v>
       </c>
       <c r="AO33" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="2:41" x14ac:dyDescent="0.3">
@@ -7734,6 +7755,38 @@
         <f t="shared" si="143"/>
         <v>8.9252039775281691E-2</v>
       </c>
+    </row>
+    <row r="37" spans="2:41" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="N37" s="14">
+        <v>162861</v>
+      </c>
+      <c r="P37" s="14">
+        <v>167139</v>
+      </c>
+    </row>
+    <row r="39" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P39" s="15">
+        <f>Main!D9/Model!P37</f>
+        <v>1.556568664405076</v>
+      </c>
+    </row>
+    <row r="40" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P40" s="7">
+        <f>P37/Main!D9-1</f>
+        <v>-0.35756126737768923</v>
+      </c>
+    </row>
+    <row r="41" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="P41" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Financial Analysis/RTX.xlsx
+++ b/Financial Analysis/RTX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB385D7-951C-4F15-9334-2DBA92593D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3DF538-6C94-44E7-A8A9-6587148DFBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4DC2FBA0-6E3D-459B-9C6A-21AC42B1058B}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Model" sheetId="2" r:id="rId2"/>
     <sheet name="Charts" sheetId="3" r:id="rId3"/>
+    <sheet name="Products" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
     <author>Anton Mniszek</author>
   </authors>
   <commentList>
-    <comment ref="V13" authorId="0" shapeId="0" xr:uid="{E96EA7C2-9517-4C2A-93C8-3EFDE14F9423}">
+    <comment ref="V36" authorId="0" shapeId="0" xr:uid="{E96EA7C2-9517-4C2A-93C8-3EFDE14F9423}">
       <text>
         <r>
           <rPr>
@@ -56,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W15" authorId="0" shapeId="0" xr:uid="{937DA12A-65A9-4053-ABBD-DC872F223AF8}">
+    <comment ref="W38" authorId="0" shapeId="0" xr:uid="{937DA12A-65A9-4053-ABBD-DC872F223AF8}">
       <text>
         <r>
           <rPr>
@@ -85,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="121">
   <si>
     <t>RTX</t>
   </si>
@@ -289,6 +290,561 @@
   </si>
   <si>
     <t>Heavily overvalued</t>
+  </si>
+  <si>
+    <t>Business segments: Collins Aerospace (Collins), Pratt &amp; Whitney, Raytheon</t>
+  </si>
+  <si>
+    <t>Collins Aerospace</t>
+  </si>
+  <si>
+    <r>
+      <t>Collins Aerospace</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Global provider of aerospace &amp; defence products</t>
+    </r>
+  </si>
+  <si>
+    <t>Pratt &amp; Whitney</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pratt &amp; Whitney </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Supplier of aircraft engines</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Avionics and flight control systems</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – integrated avionics suites, flight management systems, cockpit displays, sensors, and actuation systems used across F-35, B-21, KC-46, C-130J, and FLRAA.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Power generation and environmental control systems</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – electric power generation, distribution, cooling, and environmental control units for aircraft and space vehicles.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanical and structural systems</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – engine nacelles, thrust reversers, pylons, landing gear, brakes, propeller systems, and control actuation assemblies.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Communication, navigation, and surveillance systems</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – CNS/ATM avionics, tactical data links, and connected-battlespace technologies for both commercial and defence aircraft.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Aftermarket and sustainment services</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – global MRO, spares, engineering support, fleet management, and technical training for civil and military operators.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Digital and connected aviation solutions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – air traffic management software, data connectivity, airport systems, and JADC2-aligned communication networks.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Crew systems and safety equipment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – crew escape systems, oxygen systems, evacuation systems, and fire and ice protection hardware.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cabin and interior systems</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – seating, galleys, lavatories, oxygen delivery, lighting, and other interior components for transport and VIP aircraft.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Space and extravehicular systems</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – environmental control and power systems for spacecraft, plus extravehicular (EVA) suits for human spaceflight.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Sustainability and advanced materials technologies</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – thermoplastics, lightweight composites, and hybrid-electric or alternative-energy architectures for next-generation platforms.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>F135 engine family</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – powers all F-35 variants; includes the new Engine Core Upgrade (ECU).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>F100 engine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – legacy fighter engine for F-15 and F-16 fleets worldwide.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Next Generation Adaptive Propulsion (NGAP)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – under development for future sixth-gen fighters (e.g. NGAD).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B-21 Raider engines</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – classified derivative believed to be a P&amp;W design (likely the F130 series derivative).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Auxiliary power units (APUs)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – military and commercial, including for bombers, tankers, and transports.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>PW1000G Geared Turbofan (GTF) family</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – commercial core product powering A320neo, A220, E2 jets; partially dual-use tech base.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Pratt &amp; Whitney Canada small engines</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – regional, business, and helicopter engines (PW200, PW500, PW800 series).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Hybrid-Electric Flight Demonstrator systems</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – GTF hybrid-electric project, mobile charging unit (MCU).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Fleet management, MRO, and aftermarket services</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – maintenance, repair, overhaul, and technical support for all engine types.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Collaborative engine programmes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – cost- and revenue-sharing ventures across multiple new-engine developments.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Raytheon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Provider of threat detection, tracking and mitigation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Integrated Air and Missile Defense Systems</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Patriot (PAC-3/GEM-T), NASAMS, LTAMDS, and other layered land-based defence architectures.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Naval missile and sensor systems</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Standard Missile series (SM-2, SM-3, SM-6), Tomahawk cruise missile, Evolved SeaSparrow (ESSM), shipboard fire-control and SPY-6 radars.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Air-to-air and air-to-ground weapons</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – AMRAAM, AIM-9X Sidewinder, StormBreaker, Javelin, Excalibur, Stinger, and related precision-guided munitions.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Command, Control, Communications, and Sensor Integration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – early-warning and fire-control radars (e.g. AN/TPY-2), battlefield C2 systems, and integrated multi-domain sensor networks.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Electronic Warfare and Countermeasures</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Next Generation Jammer (Mid-Band / Low-Band) and other airborne EW suites for the Navy and allied forces.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Space and Exo-atmospheric Systems</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – missile-tracking sensors, interceptors (SM-3 exo-atmospheric), satellite control and mission-orchestration software.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Hypersonic and Counter-Hypersonic Technologies</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – development of hypersonic glide and defence interceptors, next-generation seekers, and advanced materials.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Advanced Radars and EO/IR Sensors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – multi-band surveillance radars, electro-optical and infrared systems, and space-qualified components.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Unmanned and Autonomous Systems</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Coyote expendable UAS and autonomous swarm systems for reconnaissance and interception roles.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Classified and Advanced Development Programs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – next-generation radar, sensor experimentation, and undisclosed strategic systems across air, sea, and space domains.</t>
+    </r>
+  </si>
+  <si>
+    <t>Of the total RPO as of December 31, 2024, we expect approximately 25% will be recognized as revenue over the next 12 months.</t>
+  </si>
+  <si>
+    <t>RPO rec guidance</t>
+  </si>
+  <si>
+    <t>Expected RPO rec</t>
+  </si>
+  <si>
+    <t>U.S. govt sales</t>
+  </si>
+  <si>
+    <t>International sales</t>
+  </si>
+  <si>
+    <t>U.S. govt %</t>
+  </si>
+  <si>
+    <t>International %</t>
+  </si>
+  <si>
+    <t>Employees</t>
+  </si>
+  <si>
+    <t>Raytheon</t>
+  </si>
+  <si>
+    <t>Eliminations</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>P&amp;W Backlog</t>
+  </si>
+  <si>
+    <t>Collins Backlog</t>
+  </si>
+  <si>
+    <t>Raytheon Backlog</t>
+  </si>
+  <si>
+    <t>Total RPO</t>
+  </si>
+  <si>
+    <t>Defence backlog</t>
+  </si>
+  <si>
+    <t>Commercial backlog</t>
   </si>
 </sst>
 </file>
@@ -373,7 +929,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -411,11 +967,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.249977111117893"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1" tint="0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1" tint="0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -440,6 +1035,17 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -549,7 +1155,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$23</c:f>
+              <c:f>Model!$B$46</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -628,7 +1234,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$C$23:$P$23</c:f>
+              <c:f>Model!$C$46:$P$46</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="14"/>
@@ -671,7 +1277,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$24</c:f>
+              <c:f>Model!$B$47</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -750,7 +1356,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$C$24:$P$24</c:f>
+              <c:f>Model!$C$47:$P$47</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="14"/>
@@ -1052,7 +1658,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$3</c:f>
+              <c:f>Model!$B$26</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1125,7 +1731,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Model!$C$3:$P$3</c:f>
+              <c:f>Model!$C$26:$P$26</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="14"/>
@@ -1186,7 +1792,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$4</c:f>
+              <c:f>Model!$B$27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1259,7 +1865,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Model!$C$4:$P$4</c:f>
+              <c:f>Model!$C$27:$P$27</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="14"/>
@@ -2636,7 +3242,7 @@
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2686,7 +3292,7 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3107,16 +3713,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED3AC179-4CC4-4BFB-BB5F-20A759FB583E}">
-  <dimension ref="B2:G9"/>
+  <dimension ref="B1:J52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="8.88671875" style="1"/>
     <col min="5" max="7" width="12.6640625" style="8" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="8" max="8" width="8.88671875" style="16" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="13"/>
+    <col min="10" max="10" width="8.88671875" style="17"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E2" s="8" t="s">
         <v>8</v>
       </c>
@@ -3126,8 +3739,11 @@
       <c r="G2" s="8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
@@ -3142,13 +3758,16 @@
       </c>
       <c r="F3" s="10">
         <f ca="1">TODAY()</f>
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="G3" s="10">
         <v>45958</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
@@ -3159,8 +3778,11 @@
       <c r="E4" s="11" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="H4" s="1"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
@@ -3169,8 +3791,11 @@
         <v>222967.33000000002</v>
       </c>
       <c r="E5" s="11"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I5" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
@@ -3181,8 +3806,10 @@
       <c r="E6" s="11" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="H6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="s">
         <v>5</v>
       </c>
@@ -3193,8 +3820,10 @@
       <c r="E7" s="11" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="H7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
@@ -3203,8 +3832,10 @@
         <v>-37196</v>
       </c>
       <c r="E8" s="11"/>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="H8" s="1"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
@@ -3213,6 +3844,191 @@
         <v>260163.33000000002</v>
       </c>
       <c r="E9" s="11"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="13"/>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B18" s="20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B19" s="20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B20" s="20" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B21" s="20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B22" s="20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B23" s="20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B24" s="20" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B25" s="20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B26" s="20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B27" s="13"/>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B28" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B29" s="19"/>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B30" s="20" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B31" s="20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B32" s="20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B36" s="20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B37" s="20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B38" s="20" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B39" s="20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B40" s="19"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B41" s="21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B42" s="21"/>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B43" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B44" s="20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B45" s="20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B46" s="20" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B47" s="20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B48" s="20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B49" s="20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B50" s="20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B51" s="20" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B52" s="20" t="s">
+        <v>103</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3221,7 +4037,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37BCCFEA-4609-4B74-A80E-9BDBF53DBD8A}">
-  <dimension ref="B2:EE41"/>
+  <dimension ref="B2:EE64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -3335,4458 +4151,5073 @@
     </row>
     <row r="3" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="X3" s="3">
+        <v>30317</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>31628</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>32246</v>
+      </c>
+    </row>
+    <row r="4" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="X4" s="7">
+        <f>X3/X28</f>
+        <v>0.45199332080985183</v>
+      </c>
+      <c r="Y4" s="7">
+        <f>Y3/Y28</f>
+        <v>0.45890887986070805</v>
+      </c>
+      <c r="Z4" s="7">
+        <f>Z3/Z28</f>
+        <v>0.39939062151651017</v>
+      </c>
+    </row>
+    <row r="5" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="X5" s="3">
+        <v>25884</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>29440</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>34651</v>
+      </c>
+    </row>
+    <row r="6" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="X6" s="7">
+        <f>X5/X28</f>
+        <v>0.38590213793720368</v>
+      </c>
+      <c r="Y6" s="7">
+        <f>Y5/Y28</f>
+        <v>0.42716192687173532</v>
+      </c>
+      <c r="Z6" s="7">
+        <f>Z5/Z28</f>
+        <v>0.42917832990661153</v>
+      </c>
+    </row>
+    <row r="7" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+    </row>
+    <row r="8" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="3">
+        <v>186000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="Y10" s="3">
+        <v>78000</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>93000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="Y11" s="3">
+        <v>118000</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+    </row>
+    <row r="13" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="Y13" s="3">
+        <v>30000</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="Y14" s="3">
+        <v>114000</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>119000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="Y15" s="3">
+        <v>52000</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>63000</v>
+      </c>
+    </row>
+    <row r="16" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="Y16" s="5">
+        <f>SUM(Y13:Y15)</f>
+        <v>196000</v>
+      </c>
+      <c r="Z16" s="5">
+        <f>SUM(Z13:Z15)</f>
+        <v>218000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="Z17" s="7"/>
+      <c r="AA17" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="18" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="3">
+        <f>Z16*AA17</f>
+        <v>54500</v>
+      </c>
+    </row>
+    <row r="19" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+    </row>
+    <row r="20" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="X20" s="3">
+        <v>23052</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>26253</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>28284</v>
+      </c>
+    </row>
+    <row r="21" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="X21" s="3">
+        <v>20530</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>18296</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>28066</v>
+      </c>
+    </row>
+    <row r="22" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="X22" s="3">
+        <v>25176</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>26350</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>26713</v>
+      </c>
+    </row>
+    <row r="23" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B23" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="X23" s="3">
+        <v>-1684</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>-1979</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>-2325</v>
+      </c>
+    </row>
+    <row r="24" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22"/>
+      <c r="R24" s="22"/>
+      <c r="X24" s="5">
+        <f>SUM(X20:X23)</f>
+        <v>67074</v>
+      </c>
+      <c r="Y24" s="5">
+        <f>SUM(Y20:Y23)</f>
+        <v>68920</v>
+      </c>
+      <c r="Z24" s="5">
+        <f>SUM(Z20:Z23)</f>
+        <v>80738</v>
+      </c>
+    </row>
+    <row r="25" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+    </row>
+    <row r="26" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C26" s="3">
         <v>11862</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D26" s="3">
         <v>12258</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E26" s="3">
         <v>12756</v>
       </c>
-      <c r="F3" s="3">
-        <f>X3-E3-D3-C3</f>
+      <c r="F26" s="3">
+        <f>X26-E26-D26-C26</f>
         <v>13897</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G26" s="3">
         <v>12787</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H26" s="3">
         <v>13411</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I26" s="3">
         <v>8615</v>
       </c>
-      <c r="J3" s="3">
-        <f>Y3-I3-H3-G3</f>
+      <c r="J26" s="3">
+        <f>Y26-I26-H26-G26</f>
         <v>14758</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K26" s="3">
         <v>14303</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L26" s="3">
         <v>14562</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M26" s="3">
         <v>14708</v>
       </c>
-      <c r="N3" s="3">
-        <f>Z3-M3-L3-K3</f>
+      <c r="N26" s="3">
+        <f>Z26-M26-L26-K26</f>
         <v>16039</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O26" s="3">
         <v>14591</v>
       </c>
-      <c r="P3" s="3">
+      <c r="P26" s="3">
         <v>15551</v>
       </c>
-      <c r="Q3" s="3">
-        <f>M3*1.06</f>
+      <c r="Q26" s="3">
+        <f>M26*1.06</f>
         <v>15590.480000000001</v>
       </c>
-      <c r="R3" s="3">
-        <f>N3*1.05</f>
+      <c r="R26" s="3">
+        <f>N26*1.05</f>
         <v>16840.95</v>
       </c>
-      <c r="U3" s="3">
+      <c r="U26" s="3">
         <v>32998</v>
       </c>
-      <c r="V3" s="3">
+      <c r="V26" s="3">
         <v>43319</v>
       </c>
-      <c r="W3" s="3">
+      <c r="W26" s="3">
         <v>49270</v>
       </c>
-      <c r="X3" s="3">
+      <c r="X26" s="3">
         <v>50773</v>
       </c>
-      <c r="Y3" s="3">
+      <c r="Y26" s="3">
         <v>49571</v>
       </c>
-      <c r="Z3" s="3">
+      <c r="Z26" s="3">
         <v>59612</v>
       </c>
-      <c r="AA3" s="3">
-        <f>SUM(O3:R3)</f>
+      <c r="AA26" s="3">
+        <f>SUM(O26:R26)</f>
         <v>62573.430000000008</v>
       </c>
-      <c r="AB3" s="3">
-        <f>AA3*1.04</f>
+      <c r="AB26" s="3">
+        <f>AA26*1.04</f>
         <v>65076.367200000008</v>
       </c>
-      <c r="AC3" s="3">
-        <f>AB3*1.03</f>
+      <c r="AC26" s="3">
+        <f>AB26*1.03</f>
         <v>67028.658216000011</v>
       </c>
-      <c r="AD3" s="3">
-        <f>AC3*1.02</f>
+      <c r="AD26" s="3">
+        <f>AC26*1.02</f>
         <v>68369.231380320009</v>
       </c>
-      <c r="AE3" s="3">
-        <f t="shared" ref="AE3:AK3" si="0">AD3*1.02</f>
+      <c r="AE26" s="3">
+        <f t="shared" ref="AE26:AK26" si="0">AD26*1.02</f>
         <v>69736.616007926408</v>
       </c>
-      <c r="AF3" s="3">
+      <c r="AF26" s="3">
         <f t="shared" si="0"/>
         <v>71131.348328084932</v>
       </c>
-      <c r="AG3" s="3">
+      <c r="AG26" s="3">
         <f t="shared" si="0"/>
         <v>72553.975294646632</v>
       </c>
-      <c r="AH3" s="3">
+      <c r="AH26" s="3">
         <f t="shared" si="0"/>
         <v>74005.054800539569</v>
       </c>
-      <c r="AI3" s="3">
+      <c r="AI26" s="3">
         <f t="shared" si="0"/>
         <v>75485.155896550365</v>
       </c>
-      <c r="AJ3" s="3">
+      <c r="AJ26" s="3">
         <f t="shared" si="0"/>
         <v>76994.859014481379</v>
       </c>
-      <c r="AK3" s="3">
+      <c r="AK26" s="3">
         <f t="shared" si="0"/>
         <v>78534.756194771006</v>
       </c>
     </row>
-    <row r="4" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
+    <row r="27" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C27" s="3">
         <v>3854</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D27" s="3">
         <v>4056</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E27" s="3">
         <v>4195</v>
       </c>
-      <c r="F4" s="3">
-        <f>X4-E4-D4-C4</f>
+      <c r="F27" s="3">
+        <f>X27-E27-D27-C27</f>
         <v>4196</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G27" s="3">
         <v>4427</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H27" s="3">
         <v>4904</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I27" s="3">
         <v>4849</v>
       </c>
-      <c r="J4" s="3">
-        <f>Y4-I4-H4-G4</f>
+      <c r="J27" s="3">
+        <f>Y27-I27-H27-G27</f>
         <v>5169</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K27" s="3">
         <v>5002</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L27" s="3">
         <v>5159</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M27" s="3">
         <v>5381</v>
       </c>
-      <c r="N4" s="3">
-        <f>Z4-M4-L4-K4</f>
+      <c r="N27" s="3">
+        <f>Z27-M27-L27-K27</f>
         <v>5584</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O27" s="3">
         <v>5715</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P27" s="3">
         <v>6030</v>
       </c>
-      <c r="Q4" s="3">
-        <f>M4*1.17</f>
+      <c r="Q27" s="3">
+        <f>M27*1.17</f>
         <v>6295.7699999999995</v>
       </c>
-      <c r="R4" s="3">
-        <f>N4*1.18</f>
+      <c r="R27" s="3">
+        <f>N27*1.18</f>
         <v>6589.12</v>
       </c>
-      <c r="U4" s="3">
+      <c r="U27" s="3">
         <v>12351</v>
       </c>
-      <c r="V4" s="3">
+      <c r="V27" s="3">
         <v>13268</v>
       </c>
-      <c r="W4" s="3">
+      <c r="W27" s="3">
         <v>15118</v>
       </c>
-      <c r="X4" s="3">
+      <c r="X27" s="3">
         <v>16301</v>
       </c>
-      <c r="Y4" s="3">
+      <c r="Y27" s="3">
         <v>19349</v>
       </c>
-      <c r="Z4" s="3">
+      <c r="Z27" s="3">
         <v>21126</v>
       </c>
-      <c r="AA4" s="3">
-        <f>SUM(O4:R4)</f>
+      <c r="AA27" s="3">
+        <f>SUM(O27:R27)</f>
         <v>24629.89</v>
       </c>
-      <c r="AB4" s="3">
-        <f>AA4*1.13</f>
+      <c r="AB27" s="3">
+        <f>AA27*1.13</f>
         <v>27831.775699999998</v>
       </c>
-      <c r="AC4" s="3">
-        <f>AB4*1.09</f>
+      <c r="AC27" s="3">
+        <f>AB27*1.09</f>
         <v>30336.635513000001</v>
       </c>
-      <c r="AD4" s="3">
-        <f>AC4*1.05</f>
+      <c r="AD27" s="3">
+        <f>AC27*1.05</f>
         <v>31853.467288650001</v>
       </c>
-      <c r="AE4" s="3">
-        <f>AD4*1.04</f>
+      <c r="AE27" s="3">
+        <f>AD27*1.04</f>
         <v>33127.605980196</v>
       </c>
-      <c r="AF4" s="3">
-        <f>AE4*1.03</f>
+      <c r="AF27" s="3">
+        <f>AE27*1.03</f>
         <v>34121.434159601878</v>
       </c>
-      <c r="AG4" s="3">
-        <f t="shared" ref="AG4:AK4" si="1">AF4*1.03</f>
+      <c r="AG27" s="3">
+        <f t="shared" ref="AG27:AK27" si="1">AF27*1.03</f>
         <v>35145.077184389935</v>
       </c>
-      <c r="AH4" s="3">
+      <c r="AH27" s="3">
         <f t="shared" si="1"/>
         <v>36199.429499921636</v>
       </c>
-      <c r="AI4" s="3">
+      <c r="AI27" s="3">
         <f t="shared" si="1"/>
         <v>37285.412384919284</v>
       </c>
-      <c r="AJ4" s="3">
+      <c r="AJ27" s="3">
         <f t="shared" si="1"/>
         <v>38403.974756466865</v>
       </c>
-      <c r="AK4" s="3">
+      <c r="AK27" s="3">
         <f t="shared" si="1"/>
         <v>39556.093999160876</v>
       </c>
     </row>
-    <row r="5" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="4" t="s">
+    <row r="28" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="5">
-        <f t="shared" ref="C5:P5" si="2">C3+C4</f>
+      <c r="C28" s="5">
+        <f t="shared" ref="C28:P28" si="2">C26+C27</f>
         <v>15716</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D28" s="5">
         <f t="shared" si="2"/>
         <v>16314</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E28" s="5">
         <f t="shared" si="2"/>
         <v>16951</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F28" s="5">
         <f t="shared" si="2"/>
         <v>18093</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G28" s="5">
         <f t="shared" si="2"/>
         <v>17214</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H28" s="5">
         <f t="shared" si="2"/>
         <v>18315</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I28" s="5">
         <f t="shared" si="2"/>
         <v>13464</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J28" s="5">
         <f t="shared" si="2"/>
         <v>19927</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K28" s="5">
         <f t="shared" si="2"/>
         <v>19305</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L28" s="5">
         <f t="shared" si="2"/>
         <v>19721</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M28" s="5">
         <f t="shared" si="2"/>
         <v>20089</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N28" s="5">
         <f t="shared" si="2"/>
         <v>21623</v>
       </c>
-      <c r="O5" s="5">
+      <c r="O28" s="5">
         <f t="shared" si="2"/>
         <v>20306</v>
       </c>
-      <c r="P5" s="5">
+      <c r="P28" s="5">
         <f t="shared" si="2"/>
         <v>21581</v>
       </c>
-      <c r="Q5" s="5">
-        <f t="shared" ref="Q5:R5" si="3">Q3+Q4</f>
+      <c r="Q28" s="5">
+        <f t="shared" ref="Q28:R28" si="3">Q26+Q27</f>
         <v>21886.25</v>
       </c>
-      <c r="R5" s="5">
+      <c r="R28" s="5">
         <f t="shared" si="3"/>
         <v>23430.07</v>
       </c>
-      <c r="U5" s="5">
-        <f t="shared" ref="U5:AK5" si="4">U3+U4</f>
+      <c r="U28" s="5">
+        <f t="shared" ref="U28:AK28" si="4">U26+U27</f>
         <v>45349</v>
       </c>
-      <c r="V5" s="5">
+      <c r="V28" s="5">
         <f t="shared" si="4"/>
         <v>56587</v>
       </c>
-      <c r="W5" s="5">
+      <c r="W28" s="5">
         <f t="shared" si="4"/>
         <v>64388</v>
       </c>
-      <c r="X5" s="5">
+      <c r="X28" s="5">
         <f t="shared" si="4"/>
         <v>67074</v>
       </c>
-      <c r="Y5" s="5">
+      <c r="Y28" s="5">
         <f t="shared" si="4"/>
         <v>68920</v>
       </c>
-      <c r="Z5" s="5">
+      <c r="Z28" s="5">
         <f t="shared" si="4"/>
         <v>80738</v>
       </c>
-      <c r="AA5" s="5">
+      <c r="AA28" s="5">
         <f t="shared" si="4"/>
         <v>87203.32</v>
       </c>
-      <c r="AB5" s="5">
+      <c r="AB28" s="5">
         <f t="shared" si="4"/>
         <v>92908.142900000006</v>
       </c>
-      <c r="AC5" s="5">
+      <c r="AC28" s="5">
         <f t="shared" si="4"/>
         <v>97365.293729000012</v>
       </c>
-      <c r="AD5" s="5">
+      <c r="AD28" s="5">
         <f t="shared" si="4"/>
         <v>100222.69866897001</v>
       </c>
-      <c r="AE5" s="5">
+      <c r="AE28" s="5">
         <f t="shared" si="4"/>
         <v>102864.22198812242</v>
       </c>
-      <c r="AF5" s="5">
+      <c r="AF28" s="5">
         <f t="shared" si="4"/>
         <v>105252.78248768681</v>
       </c>
-      <c r="AG5" s="5">
+      <c r="AG28" s="5">
         <f t="shared" si="4"/>
         <v>107699.05247903656</v>
       </c>
-      <c r="AH5" s="5">
+      <c r="AH28" s="5">
         <f t="shared" si="4"/>
         <v>110204.4843004612</v>
       </c>
-      <c r="AI5" s="5">
+      <c r="AI28" s="5">
         <f t="shared" si="4"/>
         <v>112770.56828146965</v>
       </c>
-      <c r="AJ5" s="5">
+      <c r="AJ28" s="5">
         <f t="shared" si="4"/>
         <v>115398.83377094824</v>
       </c>
-      <c r="AK5" s="5">
+      <c r="AK28" s="5">
         <f t="shared" si="4"/>
         <v>118090.85019393188</v>
       </c>
     </row>
-    <row r="6" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
+    <row r="29" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C29" s="3">
         <v>9820</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D29" s="3">
         <v>10040</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E29" s="3">
         <v>10493</v>
       </c>
-      <c r="F6" s="3">
-        <f t="shared" ref="F6:F7" si="5">X6-E6-D6-C6</f>
+      <c r="F29" s="3">
+        <f t="shared" ref="F29:F30" si="5">X29-E29-D29-C29</f>
         <v>11574</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G29" s="3">
         <v>10700</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H29" s="3">
         <v>11089</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I29" s="3">
         <v>9289</v>
       </c>
-      <c r="J6" s="3">
-        <f t="shared" ref="J6:J7" si="6">Y6-I6-H6-G6</f>
+      <c r="J29" s="3">
+        <f t="shared" ref="J29:J30" si="6">Y29-I29-H29-G29</f>
         <v>12347</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K29" s="3">
         <v>12216</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L29" s="3">
         <v>12625</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M29" s="3">
         <v>12336</v>
       </c>
-      <c r="N6" s="3">
-        <f t="shared" ref="N6:N7" si="7">Z6-M6-L6-K6</f>
+      <c r="N29" s="3">
+        <f t="shared" ref="N29:N30" si="7">Z29-M29-L29-K29</f>
         <v>13591</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O29" s="3">
         <v>12283</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P29" s="3">
         <v>12989</v>
       </c>
-      <c r="Q6" s="3">
-        <f>Q3*0.84</f>
+      <c r="Q29" s="3">
+        <f>Q26*0.84</f>
         <v>13096.003200000001</v>
       </c>
-      <c r="R6" s="3">
-        <f>R3*0.84</f>
+      <c r="R29" s="3">
+        <f>R26*0.84</f>
         <v>14146.397999999999</v>
       </c>
-      <c r="U6" s="3">
+      <c r="U29" s="3">
         <v>26910</v>
       </c>
-      <c r="V6" s="3">
+      <c r="V29" s="3">
         <v>38137</v>
       </c>
-      <c r="W6" s="3">
+      <c r="W29" s="3">
         <v>41095</v>
       </c>
-      <c r="X6" s="3">
+      <c r="X29" s="3">
         <v>41927</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="Y29" s="3">
         <v>43425</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="Z29" s="3">
         <v>50768</v>
       </c>
-      <c r="AA6" s="3">
-        <f t="shared" ref="AA6:AA7" si="8">SUM(O6:R6)</f>
+      <c r="AA29" s="3">
+        <f t="shared" ref="AA29:AA30" si="8">SUM(O29:R29)</f>
         <v>52514.4012</v>
       </c>
-      <c r="AB6" s="3">
-        <f>AB3*0.84</f>
+      <c r="AB29" s="3">
+        <f>AB26*0.84</f>
         <v>54664.148448000007</v>
       </c>
-      <c r="AC6" s="3">
-        <f t="shared" ref="AC6:AK6" si="9">AC3*0.84</f>
+      <c r="AC29" s="3">
+        <f t="shared" ref="AC29:AK29" si="9">AC26*0.84</f>
         <v>56304.072901440006</v>
       </c>
-      <c r="AD6" s="3">
+      <c r="AD29" s="3">
         <f t="shared" si="9"/>
         <v>57430.154359468805</v>
       </c>
-      <c r="AE6" s="3">
+      <c r="AE29" s="3">
         <f t="shared" si="9"/>
         <v>58578.757446658179</v>
       </c>
-      <c r="AF6" s="3">
+      <c r="AF29" s="3">
         <f t="shared" si="9"/>
         <v>59750.332595591339</v>
       </c>
-      <c r="AG6" s="3">
+      <c r="AG29" s="3">
         <f t="shared" si="9"/>
         <v>60945.339247503172</v>
       </c>
-      <c r="AH6" s="3">
+      <c r="AH29" s="3">
         <f t="shared" si="9"/>
         <v>62164.246032453237</v>
       </c>
-      <c r="AI6" s="3">
+      <c r="AI29" s="3">
         <f t="shared" si="9"/>
         <v>63407.530953102301</v>
       </c>
-      <c r="AJ6" s="3">
+      <c r="AJ29" s="3">
         <f t="shared" si="9"/>
         <v>64675.681572164358</v>
       </c>
-      <c r="AK6" s="3">
+      <c r="AK29" s="3">
         <f t="shared" si="9"/>
         <v>65969.19520360764</v>
       </c>
     </row>
-    <row r="7" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
+    <row r="30" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C30" s="3">
         <v>2740</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D30" s="3">
         <v>2816</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E30" s="3">
         <v>2971</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F30" s="3">
         <f t="shared" si="5"/>
         <v>2952</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G30" s="3">
         <v>2945</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H30" s="3">
         <v>3429</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I30" s="3">
         <v>3461</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J30" s="3">
         <f t="shared" si="6"/>
         <v>3571</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K30" s="3">
         <v>3528</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L30" s="3">
         <v>3516</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M30" s="3">
         <v>3719</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N30" s="3">
         <f t="shared" si="7"/>
         <v>3797</v>
       </c>
-      <c r="O7" s="3">
+      <c r="O30" s="3">
         <v>3907</v>
       </c>
-      <c r="P7" s="3">
+      <c r="P30" s="3">
         <v>4216</v>
       </c>
-      <c r="Q7" s="3">
-        <f>Q4*0.69</f>
+      <c r="Q30" s="3">
+        <f>Q27*0.69</f>
         <v>4344.0812999999989</v>
       </c>
-      <c r="R7" s="3">
-        <f>R4*0.69</f>
+      <c r="R30" s="3">
+        <f>R27*0.69</f>
         <v>4546.4928</v>
       </c>
-      <c r="U7" s="3">
+      <c r="U30" s="3">
         <v>7688</v>
       </c>
-      <c r="V7" s="3">
+      <c r="V30" s="3">
         <v>9919</v>
       </c>
-      <c r="W7" s="3">
+      <c r="W30" s="3">
         <v>10802</v>
       </c>
-      <c r="X7" s="3">
+      <c r="X30" s="3">
         <v>11479</v>
       </c>
-      <c r="Y7" s="3">
+      <c r="Y30" s="3">
         <v>13406</v>
       </c>
-      <c r="Z7" s="3">
+      <c r="Z30" s="3">
         <v>14560</v>
       </c>
-      <c r="AA7" s="3">
+      <c r="AA30" s="3">
         <f t="shared" si="8"/>
         <v>17013.574099999998</v>
       </c>
-      <c r="AB7" s="3">
-        <f t="shared" ref="AB7:AK7" si="10">AB4*0.69</f>
+      <c r="AB30" s="3">
+        <f t="shared" ref="AB30:AK30" si="10">AB27*0.69</f>
         <v>19203.925232999998</v>
       </c>
-      <c r="AC7" s="3">
+      <c r="AC30" s="3">
         <f t="shared" si="10"/>
         <v>20932.278503969999</v>
       </c>
-      <c r="AD7" s="3">
+      <c r="AD30" s="3">
         <f t="shared" si="10"/>
         <v>21978.8924291685</v>
       </c>
-      <c r="AE7" s="3">
+      <c r="AE30" s="3">
         <f t="shared" si="10"/>
         <v>22858.048126335238</v>
       </c>
-      <c r="AF7" s="3">
+      <c r="AF30" s="3">
         <f t="shared" si="10"/>
         <v>23543.789570125293</v>
       </c>
-      <c r="AG7" s="3">
+      <c r="AG30" s="3">
         <f t="shared" si="10"/>
         <v>24250.103257229053</v>
       </c>
-      <c r="AH7" s="3">
+      <c r="AH30" s="3">
         <f t="shared" si="10"/>
         <v>24977.606354945929</v>
       </c>
-      <c r="AI7" s="3">
+      <c r="AI30" s="3">
         <f t="shared" si="10"/>
         <v>25726.934545594304</v>
       </c>
-      <c r="AJ7" s="3">
+      <c r="AJ30" s="3">
         <f t="shared" si="10"/>
         <v>26498.742581962135</v>
       </c>
-      <c r="AK7" s="3">
+      <c r="AK30" s="3">
         <f t="shared" si="10"/>
         <v>27293.704859421003</v>
       </c>
     </row>
-    <row r="8" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
+    <row r="31" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B31" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="3">
-        <f t="shared" ref="C8:P8" si="11">C6+C7</f>
+      <c r="C31" s="3">
+        <f t="shared" ref="C31:P31" si="11">C29+C30</f>
         <v>12560</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D31" s="3">
         <f t="shared" si="11"/>
         <v>12856</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E31" s="3">
         <f t="shared" si="11"/>
         <v>13464</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F31" s="3">
         <f t="shared" si="11"/>
         <v>14526</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G31" s="3">
         <f t="shared" si="11"/>
         <v>13645</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H31" s="3">
         <f t="shared" si="11"/>
         <v>14518</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I31" s="3">
         <f t="shared" si="11"/>
         <v>12750</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J31" s="3">
         <f t="shared" si="11"/>
         <v>15918</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K31" s="3">
         <f t="shared" si="11"/>
         <v>15744</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L31" s="3">
         <f t="shared" si="11"/>
         <v>16141</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M31" s="3">
         <f t="shared" si="11"/>
         <v>16055</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N31" s="3">
         <f t="shared" si="11"/>
         <v>17388</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O31" s="3">
         <f t="shared" si="11"/>
         <v>16190</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P31" s="3">
         <f t="shared" si="11"/>
         <v>17205</v>
       </c>
-      <c r="Q8" s="3">
-        <f t="shared" ref="Q8:R8" si="12">Q6+Q7</f>
+      <c r="Q31" s="3">
+        <f t="shared" ref="Q31:R31" si="12">Q29+Q30</f>
         <v>17440.084500000001</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R31" s="3">
         <f t="shared" si="12"/>
         <v>18692.890800000001</v>
       </c>
-      <c r="U8" s="3">
-        <f t="shared" ref="U8:Z8" si="13">U6+U7</f>
+      <c r="U31" s="3">
+        <f t="shared" ref="U31:Z31" si="13">U29+U30</f>
         <v>34598</v>
       </c>
-      <c r="V8" s="3">
+      <c r="V31" s="3">
         <f t="shared" si="13"/>
         <v>48056</v>
       </c>
-      <c r="W8" s="3">
+      <c r="W31" s="3">
         <f t="shared" si="13"/>
         <v>51897</v>
       </c>
-      <c r="X8" s="3">
+      <c r="X31" s="3">
         <f t="shared" si="13"/>
         <v>53406</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Y31" s="3">
         <f t="shared" si="13"/>
         <v>56831</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="Z31" s="3">
         <f t="shared" si="13"/>
         <v>65328</v>
       </c>
-      <c r="AA8" s="3">
-        <f t="shared" ref="AA8:AK8" si="14">AA6+AA7</f>
+      <c r="AA31" s="3">
+        <f t="shared" ref="AA31:AK31" si="14">AA29+AA30</f>
         <v>69527.975299999991</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AB31" s="3">
         <f t="shared" si="14"/>
         <v>73868.073681000009</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AC31" s="3">
         <f t="shared" si="14"/>
         <v>77236.351405410009</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AD31" s="3">
         <f t="shared" si="14"/>
         <v>79409.046788637308</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AE31" s="3">
         <f t="shared" si="14"/>
         <v>81436.805572993413</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AF31" s="3">
         <f t="shared" si="14"/>
         <v>83294.122165716632</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AG31" s="3">
         <f t="shared" si="14"/>
         <v>85195.442504732229</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AH31" s="3">
         <f t="shared" si="14"/>
         <v>87141.852387399165</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AI31" s="3">
         <f t="shared" si="14"/>
         <v>89134.465498696605</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AJ31" s="3">
         <f t="shared" si="14"/>
         <v>91174.424154126493</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AK31" s="3">
         <f t="shared" si="14"/>
         <v>93262.900063028646</v>
       </c>
     </row>
-    <row r="9" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="4" t="s">
+    <row r="32" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="5">
-        <f t="shared" ref="C9:P9" si="15">C5-C8</f>
+      <c r="C32" s="5">
+        <f t="shared" ref="C32:P32" si="15">C28-C31</f>
         <v>3156</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D32" s="5">
         <f t="shared" si="15"/>
         <v>3458</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E32" s="5">
         <f t="shared" si="15"/>
         <v>3487</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F32" s="5">
         <f t="shared" si="15"/>
         <v>3567</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G32" s="5">
         <f t="shared" si="15"/>
         <v>3569</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H32" s="5">
         <f t="shared" si="15"/>
         <v>3797</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I32" s="5">
         <f t="shared" si="15"/>
         <v>714</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J32" s="5">
         <f t="shared" si="15"/>
         <v>4009</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K32" s="5">
         <f t="shared" si="15"/>
         <v>3561</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L32" s="5">
         <f t="shared" si="15"/>
         <v>3580</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M32" s="5">
         <f t="shared" si="15"/>
         <v>4034</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N32" s="5">
         <f t="shared" si="15"/>
         <v>4235</v>
       </c>
-      <c r="O9" s="5">
+      <c r="O32" s="5">
         <f t="shared" si="15"/>
         <v>4116</v>
       </c>
-      <c r="P9" s="5">
+      <c r="P32" s="5">
         <f t="shared" si="15"/>
         <v>4376</v>
       </c>
-      <c r="Q9" s="5">
-        <f t="shared" ref="Q9:R9" si="16">Q5-Q8</f>
+      <c r="Q32" s="5">
+        <f t="shared" ref="Q32:R32" si="16">Q28-Q31</f>
         <v>4446.1654999999992</v>
       </c>
-      <c r="R9" s="5">
+      <c r="R32" s="5">
         <f t="shared" si="16"/>
         <v>4737.1791999999987</v>
       </c>
-      <c r="U9" s="5">
-        <f t="shared" ref="U9:Z9" si="17">U5-U8</f>
+      <c r="U32" s="5">
+        <f t="shared" ref="U32:Z32" si="17">U28-U31</f>
         <v>10751</v>
       </c>
-      <c r="V9" s="5">
+      <c r="V32" s="5">
         <f t="shared" si="17"/>
         <v>8531</v>
       </c>
-      <c r="W9" s="5">
+      <c r="W32" s="5">
         <f t="shared" si="17"/>
         <v>12491</v>
       </c>
-      <c r="X9" s="5">
+      <c r="X32" s="5">
         <f t="shared" si="17"/>
         <v>13668</v>
       </c>
-      <c r="Y9" s="5">
+      <c r="Y32" s="5">
         <f t="shared" si="17"/>
         <v>12089</v>
       </c>
-      <c r="Z9" s="5">
+      <c r="Z32" s="5">
         <f t="shared" si="17"/>
         <v>15410</v>
       </c>
-      <c r="AA9" s="5">
-        <f t="shared" ref="AA9:AK9" si="18">AA5-AA8</f>
+      <c r="AA32" s="5">
+        <f t="shared" ref="AA32:AK32" si="18">AA28-AA31</f>
         <v>17675.344700000016</v>
       </c>
-      <c r="AB9" s="5">
+      <c r="AB32" s="5">
         <f t="shared" si="18"/>
         <v>19040.069218999997</v>
       </c>
-      <c r="AC9" s="5">
+      <c r="AC32" s="5">
         <f t="shared" si="18"/>
         <v>20128.942323590003</v>
       </c>
-      <c r="AD9" s="5">
+      <c r="AD32" s="5">
         <f t="shared" si="18"/>
         <v>20813.651880332705</v>
       </c>
-      <c r="AE9" s="5">
+      <c r="AE32" s="5">
         <f t="shared" si="18"/>
         <v>21427.416415129002</v>
       </c>
-      <c r="AF9" s="5">
+      <c r="AF32" s="5">
         <f t="shared" si="18"/>
         <v>21958.660321970179</v>
       </c>
-      <c r="AG9" s="5">
+      <c r="AG32" s="5">
         <f t="shared" si="18"/>
         <v>22503.609974304331</v>
       </c>
-      <c r="AH9" s="5">
+      <c r="AH32" s="5">
         <f t="shared" si="18"/>
         <v>23062.63191306204</v>
       </c>
-      <c r="AI9" s="5">
+      <c r="AI32" s="5">
         <f t="shared" si="18"/>
         <v>23636.102782773043</v>
       </c>
-      <c r="AJ9" s="5">
+      <c r="AJ32" s="5">
         <f t="shared" si="18"/>
         <v>24224.409616821751</v>
       </c>
-      <c r="AK9" s="5">
+      <c r="AK32" s="5">
         <f t="shared" si="18"/>
         <v>24827.950130903235</v>
       </c>
     </row>
-    <row r="10" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
+    <row r="33" spans="2:135" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C33" s="3">
         <v>635</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D33" s="3">
         <v>698</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E33" s="3">
         <v>662</v>
       </c>
-      <c r="F10" s="3">
-        <f t="shared" ref="F10:F11" si="19">X10-E10-D10-C10</f>
+      <c r="F33" s="3">
+        <f t="shared" ref="F33:F34" si="19">X33-E33-D33-C33</f>
         <v>716</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G33" s="3">
         <v>607</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H33" s="3">
         <v>729</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I33" s="3">
         <v>712</v>
       </c>
-      <c r="J10" s="3">
-        <f t="shared" ref="J10:J11" si="20">Y10-I10-H10-G10</f>
+      <c r="J33" s="3">
+        <f t="shared" ref="J33:J34" si="20">Y33-I33-H33-G33</f>
         <v>757</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K33" s="3">
         <v>669</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L33" s="3">
         <v>706</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M33" s="3">
         <v>751</v>
       </c>
-      <c r="N10" s="3">
-        <f t="shared" ref="N10:N11" si="21">Z10-M10-L10-K10</f>
+      <c r="N33" s="3">
+        <f t="shared" ref="N33:N34" si="21">Z33-M33-L33-K33</f>
         <v>808</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O33" s="3">
         <v>637</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P33" s="3">
         <v>697</v>
       </c>
-      <c r="Q10" s="3">
-        <f>M10*0.98</f>
+      <c r="Q33" s="3">
+        <f>M33*0.98</f>
         <v>735.98</v>
       </c>
-      <c r="R10" s="3">
-        <f>N10*0.98</f>
+      <c r="R33" s="3">
+        <f>N33*0.98</f>
         <v>791.84</v>
       </c>
-      <c r="U10" s="3">
+      <c r="U33" s="3">
         <v>2452</v>
       </c>
-      <c r="V10" s="3">
+      <c r="V33" s="3">
         <v>2582</v>
       </c>
-      <c r="W10" s="3">
+      <c r="W33" s="3">
         <v>2732</v>
       </c>
-      <c r="X10" s="3">
+      <c r="X33" s="3">
         <v>2711</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Y33" s="3">
         <v>2805</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="Z33" s="3">
         <v>2934</v>
       </c>
-      <c r="AA10" s="3">
-        <f t="shared" ref="AA10:AA11" si="22">SUM(O10:R10)</f>
+      <c r="AA33" s="3">
+        <f t="shared" ref="AA33:AA34" si="22">SUM(O33:R33)</f>
         <v>2861.82</v>
       </c>
-      <c r="AB10" s="3">
-        <f>AA10*1.01</f>
+      <c r="AB33" s="3">
+        <f>AA33*1.01</f>
         <v>2890.4382000000001</v>
       </c>
-      <c r="AC10" s="3">
-        <f t="shared" ref="AC10:AE10" si="23">AB10*1.02</f>
+      <c r="AC33" s="3">
+        <f t="shared" ref="AC33:AE33" si="23">AB33*1.02</f>
         <v>2948.2469639999999</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AD33" s="3">
         <f t="shared" si="23"/>
         <v>3007.2119032800001</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AE33" s="3">
         <f t="shared" si="23"/>
         <v>3067.3561413456</v>
       </c>
-      <c r="AF10" s="3">
-        <f>AE10*1.01</f>
+      <c r="AF33" s="3">
+        <f>AE33*1.01</f>
         <v>3098.0297027590559</v>
       </c>
-      <c r="AG10" s="3">
-        <f t="shared" ref="AG10:AK10" si="24">AF10*1.01</f>
+      <c r="AG33" s="3">
+        <f t="shared" ref="AG33:AK33" si="24">AF33*1.01</f>
         <v>3129.0099997866464</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AH33" s="3">
         <f t="shared" si="24"/>
         <v>3160.3000997845129</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AI33" s="3">
         <f t="shared" si="24"/>
         <v>3191.9031007823583</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AJ33" s="3">
         <f t="shared" si="24"/>
         <v>3223.8221317901821</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AK33" s="3">
         <f t="shared" si="24"/>
         <v>3256.0603531080837</v>
       </c>
     </row>
-    <row r="11" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
+    <row r="34" spans="2:135" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C34" s="3">
         <v>1469</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D34" s="3">
         <v>1424</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E34" s="3">
         <v>1351</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F34" s="3">
         <f t="shared" si="19"/>
         <v>1329</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G34" s="3">
         <v>1398</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H34" s="3">
         <v>1600</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I34" s="3">
         <v>1401</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J34" s="3">
         <f t="shared" si="20"/>
         <v>1410</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K34" s="3">
         <v>1394</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L34" s="3">
         <v>1449</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M34" s="3">
         <v>1389</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N34" s="3">
         <f t="shared" si="21"/>
         <v>1574</v>
       </c>
-      <c r="O11" s="3">
+      <c r="O34" s="3">
         <v>1448</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P34" s="3">
         <v>1573</v>
       </c>
-      <c r="Q11" s="3">
-        <f>Q5*0.07</f>
+      <c r="Q34" s="3">
+        <f>Q28*0.07</f>
         <v>1532.0375000000001</v>
       </c>
-      <c r="R11" s="3">
-        <f>R5*0.07</f>
+      <c r="R34" s="3">
+        <f>R28*0.07</f>
         <v>1640.1049</v>
       </c>
-      <c r="U11" s="3">
+      <c r="U34" s="3">
         <v>3711</v>
       </c>
-      <c r="V11" s="3">
+      <c r="V34" s="3">
         <v>5540</v>
       </c>
-      <c r="W11" s="3">
+      <c r="W34" s="3">
         <v>5224</v>
       </c>
-      <c r="X11" s="3">
+      <c r="X34" s="3">
         <v>5573</v>
       </c>
-      <c r="Y11" s="3">
+      <c r="Y34" s="3">
         <v>5809</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="Z34" s="3">
         <v>5806</v>
       </c>
-      <c r="AA11" s="3">
+      <c r="AA34" s="3">
         <f t="shared" si="22"/>
         <v>6193.1424000000006</v>
       </c>
-      <c r="AB11" s="3">
-        <f t="shared" ref="AB11:AK11" si="25">AB5*0.07</f>
+      <c r="AB34" s="3">
+        <f t="shared" ref="AB34:AK34" si="25">AB28*0.07</f>
         <v>6503.5700030000007</v>
       </c>
-      <c r="AC11" s="3">
+      <c r="AC34" s="3">
         <f t="shared" si="25"/>
         <v>6815.570561030001</v>
       </c>
-      <c r="AD11" s="3">
+      <c r="AD34" s="3">
         <f t="shared" si="25"/>
         <v>7015.5889068279012</v>
       </c>
-      <c r="AE11" s="3">
+      <c r="AE34" s="3">
         <f t="shared" si="25"/>
         <v>7200.4955391685698</v>
       </c>
-      <c r="AF11" s="3">
+      <c r="AF34" s="3">
         <f t="shared" si="25"/>
         <v>7367.6947741380773</v>
       </c>
-      <c r="AG11" s="3">
+      <c r="AG34" s="3">
         <f t="shared" si="25"/>
         <v>7538.9336735325596</v>
       </c>
-      <c r="AH11" s="3">
+      <c r="AH34" s="3">
         <f t="shared" si="25"/>
         <v>7714.3139010322848</v>
       </c>
-      <c r="AI11" s="3">
+      <c r="AI34" s="3">
         <f t="shared" si="25"/>
         <v>7893.939779702876</v>
       </c>
-      <c r="AJ11" s="3">
+      <c r="AJ34" s="3">
         <f t="shared" si="25"/>
         <v>8077.9183639663779</v>
       </c>
-      <c r="AK11" s="3">
+      <c r="AK34" s="3">
         <f t="shared" si="25"/>
         <v>8266.359513575233</v>
       </c>
     </row>
-    <row r="12" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="4" t="s">
+    <row r="35" spans="2:135" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="5">
-        <f t="shared" ref="C12:P12" si="26">C9-C10-C11</f>
+      <c r="C35" s="5">
+        <f t="shared" ref="C35:P35" si="26">C32-C33-C34</f>
         <v>1052</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D35" s="5">
         <f t="shared" si="26"/>
         <v>1336</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E35" s="5">
         <f t="shared" si="26"/>
         <v>1474</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F35" s="5">
         <f t="shared" si="26"/>
         <v>1522</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G35" s="5">
         <f t="shared" si="26"/>
         <v>1564</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H35" s="5">
         <f t="shared" si="26"/>
         <v>1468</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I35" s="5">
         <f t="shared" si="26"/>
         <v>-1399</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J35" s="5">
         <f t="shared" si="26"/>
         <v>1842</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K35" s="5">
         <f t="shared" si="26"/>
         <v>1498</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L35" s="5">
         <f t="shared" si="26"/>
         <v>1425</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M35" s="5">
         <f t="shared" si="26"/>
         <v>1894</v>
       </c>
-      <c r="N12" s="5">
+      <c r="N35" s="5">
         <f t="shared" si="26"/>
         <v>1853</v>
       </c>
-      <c r="O12" s="5">
+      <c r="O35" s="5">
         <f t="shared" si="26"/>
         <v>2031</v>
       </c>
-      <c r="P12" s="5">
+      <c r="P35" s="5">
         <f t="shared" si="26"/>
         <v>2106</v>
       </c>
-      <c r="Q12" s="5">
-        <f t="shared" ref="Q12:R12" si="27">Q9-Q10-Q11</f>
+      <c r="Q35" s="5">
+        <f t="shared" ref="Q35:R35" si="27">Q32-Q33-Q34</f>
         <v>2178.1479999999992</v>
       </c>
-      <c r="R12" s="5">
+      <c r="R35" s="5">
         <f t="shared" si="27"/>
         <v>2305.2342999999983</v>
       </c>
-      <c r="U12" s="5">
-        <f t="shared" ref="U12:AA12" si="28">U9-U10-U11</f>
+      <c r="U35" s="5">
+        <f t="shared" ref="U35:AA35" si="28">U32-U33-U34</f>
         <v>4588</v>
       </c>
-      <c r="V12" s="5">
+      <c r="V35" s="5">
         <f t="shared" si="28"/>
         <v>409</v>
       </c>
-      <c r="W12" s="5">
+      <c r="W35" s="5">
         <f t="shared" si="28"/>
         <v>4535</v>
       </c>
-      <c r="X12" s="5">
+      <c r="X35" s="5">
         <f t="shared" si="28"/>
         <v>5384</v>
       </c>
-      <c r="Y12" s="5">
+      <c r="Y35" s="5">
         <f t="shared" si="28"/>
         <v>3475</v>
       </c>
-      <c r="Z12" s="5">
+      <c r="Z35" s="5">
         <f t="shared" si="28"/>
         <v>6670</v>
       </c>
-      <c r="AA12" s="5">
+      <c r="AA35" s="5">
         <f t="shared" si="28"/>
         <v>8620.3823000000157</v>
       </c>
-      <c r="AB12" s="5">
-        <f t="shared" ref="AB12:AK12" si="29">AB9-AB10-AB11</f>
+      <c r="AB35" s="5">
+        <f t="shared" ref="AB35:AK35" si="29">AB32-AB33-AB34</f>
         <v>9646.061015999996</v>
       </c>
-      <c r="AC12" s="5">
+      <c r="AC35" s="5">
         <f t="shared" si="29"/>
         <v>10365.124798560004</v>
       </c>
-      <c r="AD12" s="5">
+      <c r="AD35" s="5">
         <f t="shared" si="29"/>
         <v>10790.851070224804</v>
       </c>
-      <c r="AE12" s="5">
+      <c r="AE35" s="5">
         <f t="shared" si="29"/>
         <v>11159.564734614833</v>
       </c>
-      <c r="AF12" s="5">
+      <c r="AF35" s="5">
         <f t="shared" si="29"/>
         <v>11492.935845073045</v>
       </c>
-      <c r="AG12" s="5">
+      <c r="AG35" s="5">
         <f t="shared" si="29"/>
         <v>11835.666300985125</v>
       </c>
-      <c r="AH12" s="5">
+      <c r="AH35" s="5">
         <f t="shared" si="29"/>
         <v>12188.017912245243</v>
       </c>
-      <c r="AI12" s="5">
+      <c r="AI35" s="5">
         <f t="shared" si="29"/>
         <v>12550.259902287809</v>
       </c>
-      <c r="AJ12" s="5">
+      <c r="AJ35" s="5">
         <f t="shared" si="29"/>
         <v>12922.669121065192</v>
       </c>
-      <c r="AK12" s="5">
+      <c r="AK35" s="5">
         <f t="shared" si="29"/>
         <v>13305.530264219917</v>
       </c>
     </row>
-    <row r="13" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
+    <row r="36" spans="2:135" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C36" s="3">
         <v>-28</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D36" s="3">
         <v>-17</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E36" s="3">
         <v>-46</v>
       </c>
-      <c r="F13" s="3">
-        <f t="shared" ref="F13:F15" si="30">X13-E13-D13-C13</f>
+      <c r="F36" s="3">
+        <f t="shared" ref="F36:F38" si="30">X36-E36-D36-C36</f>
         <v>-29</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G36" s="3">
         <v>-88</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H36" s="3">
         <v>-25</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I36" s="3">
         <v>-3</v>
       </c>
-      <c r="J13" s="3">
-        <f t="shared" ref="J13:J15" si="31">Y13-I13-H13-G13</f>
+      <c r="J36" s="3">
+        <f t="shared" ref="J36:J38" si="31">Y36-I36-H36-G36</f>
         <v>30</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K36" s="3">
         <v>-372</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L36" s="3">
         <v>896</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M36" s="3">
         <v>-134</v>
       </c>
-      <c r="N13" s="3">
-        <f t="shared" ref="N13:N15" si="32">Z13-M13-L13-K13</f>
+      <c r="N36" s="3">
+        <f t="shared" ref="N36:N38" si="32">Z36-M36-L36-K36</f>
         <v>-258</v>
       </c>
-      <c r="O13" s="3">
+      <c r="O36" s="3">
         <v>-4</v>
       </c>
-      <c r="P13" s="3">
+      <c r="P36" s="3">
         <v>-40</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="Q36" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3">
+      <c r="R36" s="3">
         <v>0</v>
       </c>
-      <c r="U13" s="3">
+      <c r="U36" s="3">
         <v>-326</v>
       </c>
-      <c r="V13" s="3">
+      <c r="V36" s="3">
         <f>3183-885</f>
         <v>2298</v>
       </c>
-      <c r="W13" s="3">
+      <c r="W36" s="3">
         <v>-423</v>
       </c>
-      <c r="X13" s="3">
+      <c r="X36" s="3">
         <v>-120</v>
       </c>
-      <c r="Y13" s="3">
+      <c r="Y36" s="3">
         <v>-86</v>
       </c>
-      <c r="Z13" s="3">
+      <c r="Z36" s="3">
         <v>132</v>
       </c>
-      <c r="AA13" s="3">
-        <f t="shared" ref="AA13:AA15" si="33">SUM(O13:R13)</f>
+      <c r="AA36" s="3">
+        <f t="shared" ref="AA36:AA38" si="33">SUM(O36:R36)</f>
         <v>-44</v>
       </c>
-      <c r="AB13" s="3">
+      <c r="AB36" s="3">
         <v>0</v>
       </c>
-      <c r="AC13" s="3">
+      <c r="AC36" s="3">
         <v>0</v>
       </c>
-      <c r="AD13" s="3">
+      <c r="AD36" s="3">
         <v>0</v>
       </c>
-      <c r="AE13" s="3">
+      <c r="AE36" s="3">
         <v>0</v>
       </c>
-      <c r="AF13" s="3">
+      <c r="AF36" s="3">
         <v>0</v>
       </c>
-      <c r="AG13" s="3">
+      <c r="AG36" s="3">
         <v>0</v>
       </c>
-      <c r="AH13" s="3">
+      <c r="AH36" s="3">
         <v>0</v>
       </c>
-      <c r="AI13" s="3">
+      <c r="AI36" s="3">
         <v>0</v>
       </c>
-      <c r="AJ13" s="3">
+      <c r="AJ36" s="3">
         <v>0</v>
       </c>
-      <c r="AK13" s="3">
+      <c r="AK36" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
+    <row r="37" spans="2:135" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C37" s="3">
         <v>-480</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D37" s="3">
         <v>-474</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E37" s="3">
         <v>-468</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F37" s="3">
         <f t="shared" si="30"/>
         <v>-467</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G37" s="3">
         <v>-444</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H37" s="3">
         <v>-447</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I37" s="3">
         <v>-443</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J37" s="3">
         <f t="shared" si="31"/>
         <v>-446</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K37" s="3">
         <v>-386</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L37" s="3">
         <v>-374</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M37" s="3">
         <v>-374</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N37" s="3">
         <f t="shared" si="32"/>
         <v>-384</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O37" s="3">
         <v>-366</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P37" s="3">
         <v>-351</v>
       </c>
-      <c r="Q14" s="3">
-        <f>M14*1.01</f>
+      <c r="Q37" s="3">
+        <f>M37*1.01</f>
         <v>-377.74</v>
       </c>
-      <c r="R14" s="3">
-        <f>N14*1.01</f>
+      <c r="R37" s="3">
+        <f>N37*1.01</f>
         <v>-387.84000000000003</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U37" s="3">
         <v>-829</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V37" s="3">
         <v>-902</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W37" s="3">
         <v>-1944</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X37" s="3">
         <v>-1889</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y37" s="3">
         <v>-1780</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z37" s="3">
         <v>-1518</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA37" s="3">
         <f t="shared" si="33"/>
         <v>-1482.58</v>
       </c>
-      <c r="AB14" s="3">
-        <f t="shared" ref="AB14:AK14" si="34">AA14*1.01</f>
+      <c r="AB37" s="3">
+        <f t="shared" ref="AB37:AK37" si="34">AA37*1.01</f>
         <v>-1497.4058</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC37" s="3">
         <f t="shared" si="34"/>
         <v>-1512.379858</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD37" s="3">
         <f t="shared" si="34"/>
         <v>-1527.5036565800001</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE37" s="3">
         <f t="shared" si="34"/>
         <v>-1542.7786931458002</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AF37" s="3">
         <f t="shared" si="34"/>
         <v>-1558.2064800772582</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG37" s="3">
         <f t="shared" si="34"/>
         <v>-1573.7885448780307</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AH37" s="3">
         <f t="shared" si="34"/>
         <v>-1589.5264303268111</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AI37" s="3">
         <f t="shared" si="34"/>
         <v>-1605.4216946300792</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AJ37" s="3">
         <f t="shared" si="34"/>
         <v>-1621.47591157638</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AK37" s="3">
         <f t="shared" si="34"/>
         <v>-1637.6906706921438</v>
       </c>
     </row>
-    <row r="15" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
+    <row r="38" spans="2:135" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C38" s="3">
         <v>318</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D38" s="3">
         <v>329</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E38" s="3">
         <v>311</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F38" s="3">
         <f t="shared" si="30"/>
         <v>318</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G38" s="3">
         <v>315</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H38" s="3">
         <v>333</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I38" s="3">
         <v>369</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J38" s="3">
         <f t="shared" si="31"/>
         <v>488</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K38" s="3">
         <v>405</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L38" s="3">
         <v>475</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M38" s="3">
         <v>496</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N38" s="3">
         <f t="shared" si="32"/>
         <v>486</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O38" s="3">
         <v>443</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P38" s="3">
         <v>457</v>
       </c>
-      <c r="Q15" s="3">
-        <f t="shared" ref="Q15:R15" si="35">M15*1.01</f>
+      <c r="Q38" s="3">
+        <f t="shared" ref="Q38:R38" si="35">M38*1.01</f>
         <v>500.96</v>
       </c>
-      <c r="R15" s="3">
+      <c r="R38" s="3">
         <f t="shared" si="35"/>
         <v>490.86</v>
       </c>
-      <c r="U15" s="3">
+      <c r="U38" s="3">
         <v>1591</v>
       </c>
-      <c r="V15" s="3">
+      <c r="V38" s="3">
         <v>1366</v>
       </c>
-      <c r="W15" s="3">
+      <c r="W38" s="3">
         <f>1322+649</f>
         <v>1971</v>
       </c>
-      <c r="X15" s="3">
+      <c r="X38" s="3">
         <v>1276</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Y38" s="3">
         <v>1505</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="Z38" s="3">
         <v>1862</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AA38" s="3">
         <f t="shared" si="33"/>
         <v>1891.8200000000002</v>
       </c>
-      <c r="AB15" s="3">
-        <f t="shared" ref="AB15:AK15" si="36">AA15*1.01</f>
+      <c r="AB38" s="3">
+        <f t="shared" ref="AB38:AK38" si="36">AA38*1.01</f>
         <v>1910.7382000000002</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AC38" s="3">
         <f t="shared" si="36"/>
         <v>1929.8455820000001</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AD38" s="3">
         <f t="shared" si="36"/>
         <v>1949.1440378200002</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AE38" s="3">
         <f t="shared" si="36"/>
         <v>1968.6354781982002</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AF38" s="3">
         <f t="shared" si="36"/>
         <v>1988.3218329801823</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AG38" s="3">
         <f t="shared" si="36"/>
         <v>2008.2050513099841</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AH38" s="3">
         <f t="shared" si="36"/>
         <v>2028.287101823084</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AI38" s="3">
         <f t="shared" si="36"/>
         <v>2048.5699728413147</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AJ38" s="3">
         <f t="shared" si="36"/>
         <v>2069.0556725697279</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AK38" s="3">
         <f t="shared" si="36"/>
         <v>2089.7462292954251</v>
       </c>
     </row>
-    <row r="16" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="4" t="s">
+    <row r="39" spans="2:135" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="5">
-        <f t="shared" ref="C16:P16" si="37">C12-C13-C14-C15</f>
+      <c r="C39" s="5">
+        <f t="shared" ref="C39:P39" si="37">C35-C36-C37-C38</f>
         <v>1242</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D39" s="5">
         <f t="shared" si="37"/>
         <v>1498</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E39" s="5">
         <f t="shared" si="37"/>
         <v>1677</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F39" s="5">
         <f t="shared" si="37"/>
         <v>1700</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G39" s="5">
         <f t="shared" si="37"/>
         <v>1781</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H39" s="5">
         <f t="shared" si="37"/>
         <v>1607</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I39" s="5">
         <f t="shared" si="37"/>
         <v>-1322</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J39" s="5">
         <f t="shared" si="37"/>
         <v>1770</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K39" s="5">
         <f t="shared" si="37"/>
         <v>1851</v>
       </c>
-      <c r="L16" s="5">
+      <c r="L39" s="5">
         <f t="shared" si="37"/>
         <v>428</v>
       </c>
-      <c r="M16" s="5">
+      <c r="M39" s="5">
         <f t="shared" si="37"/>
         <v>1906</v>
       </c>
-      <c r="N16" s="5">
+      <c r="N39" s="5">
         <f t="shared" si="37"/>
         <v>2009</v>
       </c>
-      <c r="O16" s="5">
+      <c r="O39" s="5">
         <f t="shared" si="37"/>
         <v>1958</v>
       </c>
-      <c r="P16" s="5">
+      <c r="P39" s="5">
         <f t="shared" si="37"/>
         <v>2040</v>
       </c>
-      <c r="Q16" s="5">
-        <f t="shared" ref="Q16:R16" si="38">Q12-Q13-Q14-Q15</f>
+      <c r="Q39" s="5">
+        <f t="shared" ref="Q39:R39" si="38">Q35-Q36-Q37-Q38</f>
         <v>2054.927999999999</v>
       </c>
-      <c r="R16" s="5">
+      <c r="R39" s="5">
         <f t="shared" si="38"/>
         <v>2202.2142999999983</v>
       </c>
-      <c r="U16" s="5">
-        <f t="shared" ref="U16:AA16" si="39">U12-U13-U14-U15</f>
+      <c r="U39" s="5">
+        <f t="shared" ref="U39:AA39" si="39">U35-U36-U37-U38</f>
         <v>4152</v>
       </c>
-      <c r="V16" s="5">
+      <c r="V39" s="5">
         <f t="shared" si="39"/>
         <v>-2353</v>
       </c>
-      <c r="W16" s="5">
+      <c r="W39" s="5">
         <f t="shared" si="39"/>
         <v>4931</v>
       </c>
-      <c r="X16" s="5">
+      <c r="X39" s="5">
         <f t="shared" si="39"/>
         <v>6117</v>
       </c>
-      <c r="Y16" s="5">
+      <c r="Y39" s="5">
         <f t="shared" si="39"/>
         <v>3836</v>
       </c>
-      <c r="Z16" s="5">
+      <c r="Z39" s="5">
         <f t="shared" si="39"/>
         <v>6194</v>
       </c>
-      <c r="AA16" s="5">
+      <c r="AA39" s="5">
         <f t="shared" si="39"/>
         <v>8255.1423000000159</v>
       </c>
-      <c r="AB16" s="5">
-        <f t="shared" ref="AB16:AK16" si="40">AB12-AB13-AB14-AB15</f>
+      <c r="AB39" s="5">
+        <f t="shared" ref="AB39:AK39" si="40">AB35-AB36-AB37-AB38</f>
         <v>9232.7286159999967</v>
       </c>
-      <c r="AC16" s="5">
+      <c r="AC39" s="5">
         <f t="shared" si="40"/>
         <v>9947.6590745600042</v>
       </c>
-      <c r="AD16" s="5">
+      <c r="AD39" s="5">
         <f t="shared" si="40"/>
         <v>10369.210688984804</v>
       </c>
-      <c r="AE16" s="5">
+      <c r="AE39" s="5">
         <f t="shared" si="40"/>
         <v>10733.707949562431</v>
       </c>
-      <c r="AF16" s="5">
+      <c r="AF39" s="5">
         <f t="shared" si="40"/>
         <v>11062.820492170122</v>
       </c>
-      <c r="AG16" s="5">
+      <c r="AG39" s="5">
         <f t="shared" si="40"/>
         <v>11401.249794553172</v>
       </c>
-      <c r="AH16" s="5">
+      <c r="AH39" s="5">
         <f t="shared" si="40"/>
         <v>11749.25724074897</v>
       </c>
-      <c r="AI16" s="5">
+      <c r="AI39" s="5">
         <f t="shared" si="40"/>
         <v>12107.111624076573</v>
       </c>
-      <c r="AJ16" s="5">
+      <c r="AJ39" s="5">
         <f t="shared" si="40"/>
         <v>12475.089360071845</v>
       </c>
-      <c r="AK16" s="5">
+      <c r="AK39" s="5">
         <f t="shared" si="40"/>
         <v>12853.474705616634</v>
       </c>
     </row>
-    <row r="17" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B17" s="1" t="s">
+    <row r="40" spans="2:135" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C40" s="3">
         <v>116</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D40" s="3">
         <v>160</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E40" s="3">
         <v>282</v>
       </c>
-      <c r="F17" s="3">
-        <f t="shared" ref="F17:F18" si="41">X17-E17-D17-C17</f>
+      <c r="F40" s="3">
+        <f t="shared" ref="F40:F41" si="41">X40-E40-D40-C40</f>
         <v>232</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G40" s="3">
         <v>300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H40" s="3">
         <v>248</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I40" s="3">
         <v>-389</v>
       </c>
-      <c r="J17" s="3">
-        <f t="shared" ref="J17:J18" si="42">Y17-I17-H17-G17</f>
+      <c r="J40" s="3">
+        <f t="shared" ref="J40:J41" si="42">Y40-I40-H40-G40</f>
         <v>297</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K40" s="3">
         <v>108</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L40" s="3">
         <v>253</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M40" s="3">
         <v>371</v>
       </c>
-      <c r="N17" s="3">
-        <f t="shared" ref="N17:N18" si="43">Z17-M17-L17-K17</f>
+      <c r="N40" s="3">
+        <f t="shared" ref="N40:N41" si="43">Z40-M40-L40-K40</f>
         <v>449</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O40" s="3">
         <v>333</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P40" s="3">
         <v>315</v>
       </c>
-      <c r="Q17" s="3">
-        <f>Q16*0.17</f>
+      <c r="Q40" s="3">
+        <f>Q39*0.17</f>
         <v>349.33775999999983</v>
       </c>
-      <c r="R17" s="3">
-        <f>R16*0.17</f>
+      <c r="R40" s="3">
+        <f>R39*0.17</f>
         <v>374.37643099999974</v>
       </c>
-      <c r="U17" s="3">
+      <c r="U40" s="3">
         <v>421</v>
       </c>
-      <c r="V17" s="3">
+      <c r="V40" s="3">
         <v>575</v>
       </c>
-      <c r="W17" s="3">
+      <c r="W40" s="3">
         <v>786</v>
       </c>
-      <c r="X17" s="3">
+      <c r="X40" s="3">
         <v>790</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Y40" s="3">
         <v>456</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="Z40" s="3">
         <v>1181</v>
       </c>
-      <c r="AA17" s="3">
-        <f t="shared" ref="AA17:AA18" si="44">SUM(O17:R17)</f>
+      <c r="AA40" s="3">
+        <f t="shared" ref="AA40:AA41" si="44">SUM(O40:R40)</f>
         <v>1371.7141909999996</v>
       </c>
-      <c r="AB17" s="3">
-        <f t="shared" ref="AB17:AK17" si="45">AB16*0.15</f>
+      <c r="AB40" s="3">
+        <f t="shared" ref="AB40:AK40" si="45">AB39*0.15</f>
         <v>1384.9092923999995</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AC40" s="3">
         <f t="shared" si="45"/>
         <v>1492.1488611840007</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AD40" s="3">
         <f t="shared" si="45"/>
         <v>1555.3816033477206</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AE40" s="3">
         <f t="shared" si="45"/>
         <v>1610.0561924343647</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AF40" s="3">
         <f t="shared" si="45"/>
         <v>1659.4230738255183</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AG40" s="3">
         <f t="shared" si="45"/>
         <v>1710.1874691829757</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AH40" s="3">
         <f t="shared" si="45"/>
         <v>1762.3885861123454</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AI40" s="3">
         <f t="shared" si="45"/>
         <v>1816.0667436114859</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AJ40" s="3">
         <f t="shared" si="45"/>
         <v>1871.2634040107766</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AK40" s="3">
         <f t="shared" si="45"/>
         <v>1928.021205842495</v>
       </c>
     </row>
-    <row r="18" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B18" s="1" t="s">
+    <row r="41" spans="2:135" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C41" s="3">
         <v>23</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D41" s="3">
         <v>34</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E41" s="3">
         <v>8</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F41" s="3">
         <f t="shared" si="41"/>
         <v>46</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G41" s="3">
         <v>55</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H41" s="3">
         <v>32</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I41" s="3">
         <v>51</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J41" s="3">
         <f t="shared" si="42"/>
         <v>47</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K41" s="3">
         <v>34</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L41" s="3">
         <v>64</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M41" s="3">
         <v>63</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N41" s="3">
         <f t="shared" si="43"/>
         <v>78</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O41" s="3">
         <v>90</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P41" s="3">
         <v>68</v>
       </c>
-      <c r="Q18" s="3">
-        <f>Q16*0.03</f>
+      <c r="Q41" s="3">
+        <f>Q39*0.03</f>
         <v>61.647839999999967</v>
       </c>
-      <c r="R18" s="3">
-        <f>R16*0.03</f>
+      <c r="R41" s="3">
+        <f>R39*0.03</f>
         <v>66.066428999999943</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U41" s="3">
         <v>221</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V41" s="3">
         <v>181</v>
       </c>
-      <c r="W18" s="3">
+      <c r="W41" s="3">
         <v>248</v>
       </c>
-      <c r="X18" s="3">
+      <c r="X41" s="3">
         <v>111</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Y41" s="3">
         <v>185</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="Z41" s="3">
         <v>239</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AA41" s="3">
         <f t="shared" si="44"/>
         <v>285.71426899999994</v>
       </c>
-      <c r="AB18" s="3">
-        <f t="shared" ref="AB18:AK18" si="46">AB16*0.03</f>
+      <c r="AB41" s="3">
+        <f t="shared" ref="AB41:AK41" si="46">AB39*0.03</f>
         <v>276.98185847999991</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AC41" s="3">
         <f t="shared" si="46"/>
         <v>298.42977223680009</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AD41" s="3">
         <f t="shared" si="46"/>
         <v>311.07632066954409</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AE41" s="3">
         <f t="shared" si="46"/>
         <v>322.01123848687291</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AF41" s="3">
         <f t="shared" si="46"/>
         <v>331.88461476510366</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AG41" s="3">
         <f t="shared" si="46"/>
         <v>342.03749383659516</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AH41" s="3">
         <f t="shared" si="46"/>
         <v>352.4777172224691</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AI41" s="3">
         <f t="shared" si="46"/>
         <v>363.21334872229716</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AJ41" s="3">
         <f t="shared" si="46"/>
         <v>374.25268080215534</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AK41" s="3">
         <f t="shared" si="46"/>
         <v>385.60424116849902</v>
       </c>
     </row>
-    <row r="19" spans="2:135" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="4" t="s">
+    <row r="42" spans="2:135" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="5">
-        <f t="shared" ref="C19:P19" si="47">C16-C17-C18</f>
+      <c r="C42" s="5">
+        <f t="shared" ref="C42:P42" si="47">C39-C40-C41</f>
         <v>1103</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D42" s="5">
         <f t="shared" si="47"/>
         <v>1304</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E42" s="5">
         <f t="shared" si="47"/>
         <v>1387</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F42" s="5">
         <f t="shared" si="47"/>
         <v>1422</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G42" s="5">
         <f t="shared" si="47"/>
         <v>1426</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H42" s="5">
         <f t="shared" si="47"/>
         <v>1327</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I42" s="5">
         <f t="shared" si="47"/>
         <v>-984</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J42" s="5">
         <f t="shared" si="47"/>
         <v>1426</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K42" s="5">
         <f t="shared" si="47"/>
         <v>1709</v>
       </c>
-      <c r="L19" s="5">
+      <c r="L42" s="5">
         <f t="shared" si="47"/>
         <v>111</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M42" s="5">
         <f t="shared" si="47"/>
         <v>1472</v>
       </c>
-      <c r="N19" s="5">
+      <c r="N42" s="5">
         <f t="shared" si="47"/>
         <v>1482</v>
       </c>
-      <c r="O19" s="5">
+      <c r="O42" s="5">
         <f t="shared" si="47"/>
         <v>1535</v>
       </c>
-      <c r="P19" s="5">
+      <c r="P42" s="5">
         <f t="shared" si="47"/>
         <v>1657</v>
       </c>
-      <c r="Q19" s="5">
-        <f t="shared" ref="Q19:R19" si="48">Q16-Q17-Q18</f>
+      <c r="Q42" s="5">
+        <f t="shared" ref="Q42:R42" si="48">Q39-Q40-Q41</f>
         <v>1643.9423999999992</v>
       </c>
-      <c r="R19" s="5">
+      <c r="R42" s="5">
         <f t="shared" si="48"/>
         <v>1761.7714399999986</v>
       </c>
-      <c r="U19" s="5">
-        <f t="shared" ref="U19:Z19" si="49">U16-U17-U18</f>
+      <c r="U42" s="5">
+        <f t="shared" ref="U42:Z42" si="49">U39-U40-U41</f>
         <v>3510</v>
       </c>
-      <c r="V19" s="5">
+      <c r="V42" s="5">
         <f t="shared" si="49"/>
         <v>-3109</v>
       </c>
-      <c r="W19" s="5">
+      <c r="W42" s="5">
         <f t="shared" si="49"/>
         <v>3897</v>
       </c>
-      <c r="X19" s="5">
+      <c r="X42" s="5">
         <f t="shared" si="49"/>
         <v>5216</v>
       </c>
-      <c r="Y19" s="5">
+      <c r="Y42" s="5">
         <f t="shared" si="49"/>
         <v>3195</v>
       </c>
-      <c r="Z19" s="5">
+      <c r="Z42" s="5">
         <f t="shared" si="49"/>
         <v>4774</v>
       </c>
-      <c r="AA19" s="5">
-        <f t="shared" ref="AA19:AK19" si="50">AA16-AA17-AA18</f>
+      <c r="AA42" s="5">
+        <f t="shared" ref="AA42:AK42" si="50">AA39-AA40-AA41</f>
         <v>6597.7138400000167</v>
       </c>
-      <c r="AB19" s="5">
+      <c r="AB42" s="5">
         <f t="shared" si="50"/>
         <v>7570.8374651199974</v>
       </c>
-      <c r="AC19" s="5">
+      <c r="AC42" s="5">
         <f t="shared" si="50"/>
         <v>8157.0804411392028</v>
       </c>
-      <c r="AD19" s="5">
+      <c r="AD42" s="5">
         <f t="shared" si="50"/>
         <v>8502.7527649675394</v>
       </c>
-      <c r="AE19" s="5">
+      <c r="AE42" s="5">
         <f t="shared" si="50"/>
         <v>8801.6405186411939</v>
       </c>
-      <c r="AF19" s="5">
+      <c r="AF42" s="5">
         <f t="shared" si="50"/>
         <v>9071.5128035795005</v>
       </c>
-      <c r="AG19" s="5">
+      <c r="AG42" s="5">
         <f t="shared" si="50"/>
         <v>9349.0248315336012</v>
       </c>
-      <c r="AH19" s="5">
+      <c r="AH42" s="5">
         <f t="shared" si="50"/>
         <v>9634.3909374141549</v>
       </c>
-      <c r="AI19" s="5">
+      <c r="AI42" s="5">
         <f t="shared" si="50"/>
         <v>9927.8315317427914</v>
       </c>
-      <c r="AJ19" s="5">
+      <c r="AJ42" s="5">
         <f t="shared" si="50"/>
         <v>10229.573275258912</v>
       </c>
-      <c r="AK19" s="5">
+      <c r="AK42" s="5">
         <f t="shared" si="50"/>
         <v>10539.84925860564</v>
       </c>
-      <c r="AL19" s="4">
-        <f>AK19*(1+$AO$25)</f>
+      <c r="AL42" s="4">
+        <f>AK42*(1+$AO$48)</f>
         <v>10434.450766019583</v>
       </c>
-      <c r="AM19" s="4">
-        <f t="shared" ref="AM19:CX19" si="51">AL19*(1+$AO$25)</f>
+      <c r="AM42" s="4">
+        <f t="shared" ref="AM42:CX42" si="51">AL42*(1+$AO$48)</f>
         <v>10330.106258359387</v>
       </c>
-      <c r="AN19" s="4">
+      <c r="AN42" s="4">
         <f t="shared" si="51"/>
         <v>10226.805195775793</v>
       </c>
-      <c r="AO19" s="4">
+      <c r="AO42" s="4">
         <f t="shared" si="51"/>
         <v>10124.537143818034</v>
       </c>
-      <c r="AP19" s="4">
+      <c r="AP42" s="4">
         <f t="shared" si="51"/>
         <v>10023.291772379853</v>
       </c>
-      <c r="AQ19" s="4">
+      <c r="AQ42" s="4">
         <f t="shared" si="51"/>
         <v>9923.0588546560539</v>
       </c>
-      <c r="AR19" s="4">
+      <c r="AR42" s="4">
         <f t="shared" si="51"/>
         <v>9823.8282661094927</v>
       </c>
-      <c r="AS19" s="4">
+      <c r="AS42" s="4">
         <f t="shared" si="51"/>
         <v>9725.5899834483971</v>
       </c>
-      <c r="AT19" s="4">
+      <c r="AT42" s="4">
         <f t="shared" si="51"/>
         <v>9628.3340836139123</v>
       </c>
-      <c r="AU19" s="4">
+      <c r="AU42" s="4">
         <f t="shared" si="51"/>
         <v>9532.0507427777738</v>
       </c>
-      <c r="AV19" s="4">
+      <c r="AV42" s="4">
         <f t="shared" si="51"/>
         <v>9436.7302353499963</v>
       </c>
-      <c r="AW19" s="4">
+      <c r="AW42" s="4">
         <f t="shared" si="51"/>
         <v>9342.362932996497</v>
       </c>
-      <c r="AX19" s="4">
+      <c r="AX42" s="4">
         <f t="shared" si="51"/>
         <v>9248.9393036665315</v>
       </c>
-      <c r="AY19" s="4">
+      <c r="AY42" s="4">
         <f t="shared" si="51"/>
         <v>9156.4499106298663</v>
       </c>
-      <c r="AZ19" s="4">
+      <c r="AZ42" s="4">
         <f t="shared" si="51"/>
         <v>9064.8854115235681</v>
       </c>
-      <c r="BA19" s="4">
+      <c r="BA42" s="4">
         <f t="shared" si="51"/>
         <v>8974.2365574083324</v>
       </c>
-      <c r="BB19" s="4">
+      <c r="BB42" s="4">
         <f t="shared" si="51"/>
         <v>8884.4941918342483</v>
       </c>
-      <c r="BC19" s="4">
+      <c r="BC42" s="4">
         <f t="shared" si="51"/>
         <v>8795.6492499159049</v>
       </c>
-      <c r="BD19" s="4">
+      <c r="BD42" s="4">
         <f t="shared" si="51"/>
         <v>8707.6927574167457</v>
       </c>
-      <c r="BE19" s="4">
+      <c r="BE42" s="4">
         <f t="shared" si="51"/>
         <v>8620.615829842578</v>
       </c>
-      <c r="BF19" s="4">
+      <c r="BF42" s="4">
         <f t="shared" si="51"/>
         <v>8534.4096715441519</v>
       </c>
-      <c r="BG19" s="4">
+      <c r="BG42" s="4">
         <f t="shared" si="51"/>
         <v>8449.0655748287099</v>
       </c>
-      <c r="BH19" s="4">
+      <c r="BH42" s="4">
         <f t="shared" si="51"/>
         <v>8364.5749190804236</v>
       </c>
-      <c r="BI19" s="4">
+      <c r="BI42" s="4">
         <f t="shared" si="51"/>
         <v>8280.9291698896195</v>
       </c>
-      <c r="BJ19" s="4">
+      <c r="BJ42" s="4">
         <f t="shared" si="51"/>
         <v>8198.1198781907224</v>
       </c>
-      <c r="BK19" s="4">
+      <c r="BK42" s="4">
         <f t="shared" si="51"/>
         <v>8116.1386794088148</v>
       </c>
-      <c r="BL19" s="4">
+      <c r="BL42" s="4">
         <f t="shared" si="51"/>
         <v>8034.977292614727</v>
       </c>
-      <c r="BM19" s="4">
+      <c r="BM42" s="4">
         <f t="shared" si="51"/>
         <v>7954.6275196885799</v>
       </c>
-      <c r="BN19" s="4">
+      <c r="BN42" s="4">
         <f t="shared" si="51"/>
         <v>7875.0812444916937</v>
       </c>
-      <c r="BO19" s="4">
+      <c r="BO42" s="4">
         <f t="shared" si="51"/>
         <v>7796.3304320467769</v>
       </c>
-      <c r="BP19" s="4">
+      <c r="BP42" s="4">
         <f t="shared" si="51"/>
         <v>7718.3671277263093</v>
       </c>
-      <c r="BQ19" s="4">
+      <c r="BQ42" s="4">
         <f t="shared" si="51"/>
         <v>7641.1834564490464</v>
       </c>
-      <c r="BR19" s="4">
+      <c r="BR42" s="4">
         <f t="shared" si="51"/>
         <v>7564.7716218845562</v>
       </c>
-      <c r="BS19" s="4">
+      <c r="BS42" s="4">
         <f t="shared" si="51"/>
         <v>7489.1239056657105</v>
       </c>
-      <c r="BT19" s="4">
+      <c r="BT42" s="4">
         <f t="shared" si="51"/>
         <v>7414.232666609053</v>
       </c>
-      <c r="BU19" s="4">
+      <c r="BU42" s="4">
         <f t="shared" si="51"/>
         <v>7340.0903399429626</v>
       </c>
-      <c r="BV19" s="4">
+      <c r="BV42" s="4">
         <f t="shared" si="51"/>
         <v>7266.6894365435328</v>
       </c>
-      <c r="BW19" s="4">
+      <c r="BW42" s="4">
         <f t="shared" si="51"/>
         <v>7194.022542178097</v>
       </c>
-      <c r="BX19" s="4">
+      <c r="BX42" s="4">
         <f t="shared" si="51"/>
         <v>7122.0823167563158</v>
       </c>
-      <c r="BY19" s="4">
+      <c r="BY42" s="4">
         <f t="shared" si="51"/>
         <v>7050.8614935887526</v>
       </c>
-      <c r="BZ19" s="4">
+      <c r="BZ42" s="4">
         <f t="shared" si="51"/>
         <v>6980.352878652865</v>
       </c>
-      <c r="CA19" s="4">
+      <c r="CA42" s="4">
         <f t="shared" si="51"/>
         <v>6910.5493498663363</v>
       </c>
-      <c r="CB19" s="4">
+      <c r="CB42" s="4">
         <f t="shared" si="51"/>
         <v>6841.4438563676731</v>
       </c>
-      <c r="CC19" s="4">
+      <c r="CC42" s="4">
         <f t="shared" si="51"/>
         <v>6773.0294178039967</v>
       </c>
-      <c r="CD19" s="4">
+      <c r="CD42" s="4">
         <f t="shared" si="51"/>
         <v>6705.2991236259568</v>
       </c>
-      <c r="CE19" s="4">
+      <c r="CE42" s="4">
         <f t="shared" si="51"/>
         <v>6638.2461323896969</v>
       </c>
-      <c r="CF19" s="4">
+      <c r="CF42" s="4">
         <f t="shared" si="51"/>
         <v>6571.8636710658002</v>
       </c>
-      <c r="CG19" s="4">
+      <c r="CG42" s="4">
         <f t="shared" si="51"/>
         <v>6506.1450343551423</v>
       </c>
-      <c r="CH19" s="4">
+      <c r="CH42" s="4">
         <f t="shared" si="51"/>
         <v>6441.0835840115906</v>
       </c>
-      <c r="CI19" s="4">
+      <c r="CI42" s="4">
         <f t="shared" si="51"/>
         <v>6376.6727481714743</v>
       </c>
-      <c r="CJ19" s="4">
+      <c r="CJ42" s="4">
         <f t="shared" si="51"/>
         <v>6312.9060206897593</v>
       </c>
-      <c r="CK19" s="4">
+      <c r="CK42" s="4">
         <f t="shared" si="51"/>
         <v>6249.7769604828618</v>
       </c>
-      <c r="CL19" s="4">
+      <c r="CL42" s="4">
         <f t="shared" si="51"/>
         <v>6187.2791908780328</v>
       </c>
-      <c r="CM19" s="4">
+      <c r="CM42" s="4">
         <f t="shared" si="51"/>
         <v>6125.4063989692522</v>
       </c>
-      <c r="CN19" s="4">
+      <c r="CN42" s="4">
         <f t="shared" si="51"/>
         <v>6064.1523349795598</v>
       </c>
-      <c r="CO19" s="4">
+      <c r="CO42" s="4">
         <f t="shared" si="51"/>
         <v>6003.5108116297642</v>
       </c>
-      <c r="CP19" s="4">
+      <c r="CP42" s="4">
         <f t="shared" si="51"/>
         <v>5943.4757035134662</v>
       </c>
-      <c r="CQ19" s="4">
+      <c r="CQ42" s="4">
         <f t="shared" si="51"/>
         <v>5884.0409464783315</v>
       </c>
-      <c r="CR19" s="4">
+      <c r="CR42" s="4">
         <f t="shared" si="51"/>
         <v>5825.2005370135485</v>
       </c>
-      <c r="CS19" s="4">
+      <c r="CS42" s="4">
         <f t="shared" si="51"/>
         <v>5766.9485316434129</v>
       </c>
-      <c r="CT19" s="4">
+      <c r="CT42" s="4">
         <f t="shared" si="51"/>
         <v>5709.2790463269785</v>
       </c>
-      <c r="CU19" s="4">
+      <c r="CU42" s="4">
         <f t="shared" si="51"/>
         <v>5652.1862558637085</v>
       </c>
-      <c r="CV19" s="4">
+      <c r="CV42" s="4">
         <f t="shared" si="51"/>
         <v>5595.6643933050718</v>
       </c>
-      <c r="CW19" s="4">
+      <c r="CW42" s="4">
         <f t="shared" si="51"/>
         <v>5539.7077493720208</v>
       </c>
-      <c r="CX19" s="4">
+      <c r="CX42" s="4">
         <f t="shared" si="51"/>
         <v>5484.3106718783001</v>
       </c>
-      <c r="CY19" s="4">
-        <f t="shared" ref="CY19:EE19" si="52">CX19*(1+$AO$25)</f>
+      <c r="CY42" s="4">
+        <f t="shared" ref="CY42:EE42" si="52">CX42*(1+$AO$48)</f>
         <v>5429.4675651595171</v>
       </c>
-      <c r="CZ19" s="4">
+      <c r="CZ42" s="4">
         <f t="shared" si="52"/>
         <v>5375.1728895079223</v>
       </c>
-      <c r="DA19" s="4">
+      <c r="DA42" s="4">
         <f t="shared" si="52"/>
         <v>5321.4211606128429</v>
       </c>
-      <c r="DB19" s="4">
+      <c r="DB42" s="4">
         <f t="shared" si="52"/>
         <v>5268.2069490067142</v>
       </c>
-      <c r="DC19" s="4">
+      <c r="DC42" s="4">
         <f t="shared" si="52"/>
         <v>5215.5248795166472</v>
       </c>
-      <c r="DD19" s="4">
+      <c r="DD42" s="4">
         <f t="shared" si="52"/>
         <v>5163.3696307214805</v>
       </c>
-      <c r="DE19" s="4">
+      <c r="DE42" s="4">
         <f t="shared" si="52"/>
         <v>5111.735934414266</v>
       </c>
-      <c r="DF19" s="4">
+      <c r="DF42" s="4">
         <f t="shared" si="52"/>
         <v>5060.6185750701234</v>
       </c>
-      <c r="DG19" s="4">
+      <c r="DG42" s="4">
         <f t="shared" si="52"/>
         <v>5010.0123893194223</v>
       </c>
-      <c r="DH19" s="4">
+      <c r="DH42" s="4">
         <f t="shared" si="52"/>
         <v>4959.9122654262283</v>
       </c>
-      <c r="DI19" s="4">
+      <c r="DI42" s="4">
         <f t="shared" si="52"/>
         <v>4910.3131427719663</v>
       </c>
-      <c r="DJ19" s="4">
+      <c r="DJ42" s="4">
         <f t="shared" si="52"/>
         <v>4861.2100113442466</v>
       </c>
-      <c r="DK19" s="4">
+      <c r="DK42" s="4">
         <f t="shared" si="52"/>
         <v>4812.5979112308041</v>
       </c>
-      <c r="DL19" s="4">
+      <c r="DL42" s="4">
         <f t="shared" si="52"/>
         <v>4764.4719321184957</v>
       </c>
-      <c r="DM19" s="4">
+      <c r="DM42" s="4">
         <f t="shared" si="52"/>
         <v>4716.8272127973105</v>
       </c>
-      <c r="DN19" s="4">
+      <c r="DN42" s="4">
         <f t="shared" si="52"/>
         <v>4669.6589406693374</v>
       </c>
-      <c r="DO19" s="4">
+      <c r="DO42" s="4">
         <f t="shared" si="52"/>
         <v>4622.962351262644</v>
       </c>
-      <c r="DP19" s="4">
+      <c r="DP42" s="4">
         <f t="shared" si="52"/>
         <v>4576.7327277500171</v>
       </c>
-      <c r="DQ19" s="4">
+      <c r="DQ42" s="4">
         <f t="shared" si="52"/>
         <v>4530.9654004725171</v>
       </c>
-      <c r="DR19" s="4">
+      <c r="DR42" s="4">
         <f t="shared" si="52"/>
         <v>4485.6557464677917</v>
       </c>
-      <c r="DS19" s="4">
+      <c r="DS42" s="4">
         <f t="shared" si="52"/>
         <v>4440.7991890031135</v>
       </c>
-      <c r="DT19" s="4">
+      <c r="DT42" s="4">
         <f t="shared" si="52"/>
         <v>4396.3911971130819</v>
       </c>
-      <c r="DU19" s="4">
+      <c r="DU42" s="4">
         <f t="shared" si="52"/>
         <v>4352.427285141951</v>
       </c>
-      <c r="DV19" s="4">
+      <c r="DV42" s="4">
         <f t="shared" si="52"/>
         <v>4308.9030122905315</v>
       </c>
-      <c r="DW19" s="4">
+      <c r="DW42" s="4">
         <f t="shared" si="52"/>
         <v>4265.8139821676259</v>
       </c>
-      <c r="DX19" s="4">
+      <c r="DX42" s="4">
         <f t="shared" si="52"/>
         <v>4223.1558423459492</v>
       </c>
-      <c r="DY19" s="4">
+      <c r="DY42" s="4">
         <f t="shared" si="52"/>
         <v>4180.9242839224898</v>
       </c>
-      <c r="DZ19" s="4">
+      <c r="DZ42" s="4">
         <f t="shared" si="52"/>
         <v>4139.1150410832652</v>
       </c>
-      <c r="EA19" s="4">
+      <c r="EA42" s="4">
         <f t="shared" si="52"/>
         <v>4097.7238906724324</v>
       </c>
-      <c r="EB19" s="4">
+      <c r="EB42" s="4">
         <f t="shared" si="52"/>
         <v>4056.7466517657081</v>
       </c>
-      <c r="EC19" s="4">
+      <c r="EC42" s="4">
         <f t="shared" si="52"/>
         <v>4016.179185248051</v>
       </c>
-      <c r="ED19" s="4">
+      <c r="ED42" s="4">
         <f t="shared" si="52"/>
         <v>3976.0173933955703</v>
       </c>
-      <c r="EE19" s="4">
+      <c r="EE42" s="4">
         <f t="shared" si="52"/>
         <v>3936.2572194616146</v>
       </c>
     </row>
-    <row r="20" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
+    <row r="43" spans="2:135" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C43" s="3">
         <v>1330</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D43" s="3">
         <v>1330</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E43" s="3">
         <v>1330</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F43" s="3">
         <v>1330</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G43" s="3">
         <v>1330</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H43" s="3">
         <v>1330</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I43" s="3">
         <v>1330</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J43" s="3">
         <v>1330</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K43" s="3">
         <v>1330</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L43" s="3">
         <v>1330</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M43" s="3">
         <v>1330</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N43" s="3">
         <v>1330</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O43" s="3">
         <v>1330</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P43" s="3">
         <f>1338.5</f>
         <v>1338.5</v>
       </c>
-      <c r="Q20" s="3">
-        <f t="shared" ref="Q20:R20" si="53">1338.5</f>
+      <c r="Q43" s="3">
+        <f t="shared" ref="Q43:R43" si="53">1338.5</f>
         <v>1338.5</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R43" s="3">
         <f t="shared" si="53"/>
         <v>1338.5</v>
       </c>
-      <c r="U20" s="3">
-        <f t="shared" ref="U20:Z20" si="54">1332.1</f>
+      <c r="U43" s="3">
+        <f t="shared" ref="U43:Z43" si="54">1332.1</f>
         <v>1332.1</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V43" s="3">
         <f t="shared" si="54"/>
         <v>1332.1</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W43" s="3">
         <f t="shared" si="54"/>
         <v>1332.1</v>
       </c>
-      <c r="X20" s="3">
+      <c r="X43" s="3">
         <f t="shared" si="54"/>
         <v>1332.1</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Y43" s="3">
         <f t="shared" si="54"/>
         <v>1332.1</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="Z43" s="3">
         <f t="shared" si="54"/>
         <v>1332.1</v>
       </c>
-      <c r="AA20" s="3">
-        <f t="shared" ref="AA20:AK20" si="55">1338.5</f>
+      <c r="AA43" s="3">
+        <f t="shared" ref="AA43:AK43" si="55">1338.5</f>
         <v>1338.5</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AB43" s="3">
         <f t="shared" si="55"/>
         <v>1338.5</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AC43" s="3">
         <f t="shared" si="55"/>
         <v>1338.5</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AD43" s="3">
         <f t="shared" si="55"/>
         <v>1338.5</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AE43" s="3">
         <f t="shared" si="55"/>
         <v>1338.5</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AF43" s="3">
         <f t="shared" si="55"/>
         <v>1338.5</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AG43" s="3">
         <f t="shared" si="55"/>
         <v>1338.5</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AH43" s="3">
         <f t="shared" si="55"/>
         <v>1338.5</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AI43" s="3">
         <f t="shared" si="55"/>
         <v>1338.5</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AJ43" s="3">
         <f t="shared" si="55"/>
         <v>1338.5</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AK43" s="3">
         <f t="shared" si="55"/>
         <v>1338.5</v>
       </c>
     </row>
-    <row r="21" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B21" s="1" t="s">
+    <row r="44" spans="2:135" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="6">
-        <f t="shared" ref="C21:P21" si="56">C19/C20</f>
+      <c r="C44" s="6">
+        <f t="shared" ref="C44:P44" si="56">C42/C43</f>
         <v>0.82932330827067668</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D44" s="6">
         <f t="shared" si="56"/>
         <v>0.98045112781954891</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E44" s="6">
         <f t="shared" si="56"/>
         <v>1.0428571428571429</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F44" s="6">
         <f t="shared" si="56"/>
         <v>1.069172932330827</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G44" s="6">
         <f t="shared" si="56"/>
         <v>1.0721804511278195</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H44" s="6">
         <f t="shared" si="56"/>
         <v>0.9977443609022556</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I44" s="6">
         <f t="shared" si="56"/>
         <v>-0.73984962406015042</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J44" s="6">
         <f t="shared" si="56"/>
         <v>1.0721804511278195</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K44" s="6">
         <f t="shared" si="56"/>
         <v>1.2849624060150375</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L44" s="6">
         <f t="shared" si="56"/>
         <v>8.3458646616541357E-2</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M44" s="6">
         <f t="shared" si="56"/>
         <v>1.1067669172932331</v>
       </c>
-      <c r="N21" s="6">
+      <c r="N44" s="6">
         <f t="shared" si="56"/>
         <v>1.1142857142857143</v>
       </c>
-      <c r="O21" s="6">
+      <c r="O44" s="6">
         <f t="shared" si="56"/>
         <v>1.1541353383458646</v>
       </c>
-      <c r="P21" s="6">
+      <c r="P44" s="6">
         <f t="shared" si="56"/>
         <v>1.2379529323870004</v>
       </c>
-      <c r="Q21" s="6">
-        <f t="shared" ref="Q21:R21" si="57">Q19/Q20</f>
+      <c r="Q44" s="6">
+        <f t="shared" ref="Q44:R44" si="57">Q42/Q43</f>
         <v>1.2281975345536043</v>
       </c>
-      <c r="R21" s="6">
+      <c r="R44" s="6">
         <f t="shared" si="57"/>
         <v>1.3162281957415007</v>
       </c>
-      <c r="U21" s="6">
-        <f t="shared" ref="U21:Z21" si="58">U19/U20</f>
+      <c r="U44" s="6">
+        <f t="shared" ref="U44:Z44" si="58">U42/U43</f>
         <v>2.6349373170182422</v>
       </c>
-      <c r="V21" s="6">
+      <c r="V44" s="6">
         <f t="shared" si="58"/>
         <v>-2.3339088657007734</v>
       </c>
-      <c r="W21" s="6">
+      <c r="W44" s="6">
         <f t="shared" si="58"/>
         <v>2.9254560468433302</v>
       </c>
-      <c r="X21" s="6">
+      <c r="X44" s="6">
         <f t="shared" si="58"/>
         <v>3.9156219503040317</v>
       </c>
-      <c r="Y21" s="6">
+      <c r="Y44" s="6">
         <f t="shared" si="58"/>
         <v>2.3984685834396817</v>
       </c>
-      <c r="Z21" s="6">
+      <c r="Z44" s="6">
         <f t="shared" si="58"/>
         <v>3.5838150289017343</v>
       </c>
-      <c r="AA21" s="6">
-        <f t="shared" ref="AA21:AK21" si="59">AA19/AA20</f>
+      <c r="AA44" s="6">
+        <f t="shared" ref="AA44:AK44" si="59">AA42/AA43</f>
         <v>4.9291847889428588</v>
       </c>
-      <c r="AB21" s="6">
+      <c r="AB44" s="6">
         <f t="shared" si="59"/>
         <v>5.6562102839895383</v>
       </c>
-      <c r="AC21" s="6">
+      <c r="AC44" s="6">
         <f t="shared" si="59"/>
         <v>6.0941953239740032</v>
       </c>
-      <c r="AD21" s="6">
+      <c r="AD44" s="6">
         <f t="shared" si="59"/>
         <v>6.352448834491998</v>
       </c>
-      <c r="AE21" s="6">
+      <c r="AE44" s="6">
         <f t="shared" si="59"/>
         <v>6.5757493602100814</v>
       </c>
-      <c r="AF21" s="6">
+      <c r="AF44" s="6">
         <f t="shared" si="59"/>
         <v>6.7773722850799407</v>
       </c>
-      <c r="AG21" s="6">
+      <c r="AG44" s="6">
         <f t="shared" si="59"/>
         <v>6.9847028999130378</v>
       </c>
-      <c r="AH21" s="6">
+      <c r="AH44" s="6">
         <f t="shared" si="59"/>
         <v>7.1979013353859953</v>
       </c>
-      <c r="AI21" s="6">
+      <c r="AI44" s="6">
         <f t="shared" si="59"/>
         <v>7.4171322612945767</v>
       </c>
-      <c r="AJ21" s="6">
+      <c r="AJ44" s="6">
         <f t="shared" si="59"/>
         <v>7.6425650170032959</v>
       </c>
-      <c r="AK21" s="6">
+      <c r="AK44" s="6">
         <f t="shared" si="59"/>
         <v>7.8743737456896827</v>
       </c>
     </row>
-    <row r="23" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B23" s="1" t="s">
+    <row r="46" spans="2:135" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7">
-        <f t="shared" ref="G23:P25" si="60">G3/C3-1</f>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7">
+        <f t="shared" ref="G46:P48" si="60">G26/C26-1</f>
         <v>7.7980104535491535E-2</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H46" s="7">
         <f t="shared" si="60"/>
         <v>9.4061021373796683E-2</v>
       </c>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7">
+      <c r="I46" s="7"/>
+      <c r="J46" s="7">
         <f t="shared" si="60"/>
         <v>6.1955817802403335E-2</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K46" s="7">
         <f t="shared" si="60"/>
         <v>0.11855791037772745</v>
       </c>
-      <c r="L23" s="7">
+      <c r="L46" s="7">
         <f t="shared" si="60"/>
         <v>8.5825068973230945E-2</v>
       </c>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7">
+      <c r="M46" s="7"/>
+      <c r="N46" s="7">
         <f t="shared" si="60"/>
         <v>8.6800379455210797E-2</v>
       </c>
-      <c r="O23" s="7">
+      <c r="O46" s="7">
         <f t="shared" si="60"/>
         <v>2.0135635880584424E-2</v>
       </c>
-      <c r="P23" s="7">
+      <c r="P46" s="7">
         <f t="shared" si="60"/>
         <v>6.7916494986952403E-2</v>
       </c>
-      <c r="Q23" s="7">
-        <f t="shared" ref="Q23:Q25" si="61">Q3/M3-1</f>
+      <c r="Q46" s="7">
+        <f t="shared" ref="Q46:Q48" si="61">Q26/M26-1</f>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="R23" s="7">
-        <f t="shared" ref="R23:R25" si="62">R3/N3-1</f>
+      <c r="R46" s="7">
+        <f t="shared" ref="R46:R48" si="62">R26/N26-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="U23" s="7"/>
-      <c r="V23" s="7">
-        <f>V3/U3-1</f>
+      <c r="U46" s="7"/>
+      <c r="V46" s="7">
+        <f>V26/U26-1</f>
         <v>0.31277653191102495</v>
       </c>
-      <c r="W23" s="7">
-        <f t="shared" ref="W23:Z23" si="63">W3/V3-1</f>
+      <c r="W46" s="7">
+        <f t="shared" ref="W46:Z46" si="63">W26/V26-1</f>
         <v>0.13737620905376402</v>
       </c>
-      <c r="X23" s="7">
+      <c r="X46" s="7">
         <f t="shared" si="63"/>
         <v>3.0505378526486604E-2</v>
       </c>
-      <c r="Y23" s="7">
+      <c r="Y46" s="7">
         <f t="shared" si="63"/>
         <v>-2.3673999960609038E-2</v>
       </c>
-      <c r="Z23" s="7">
+      <c r="Z46" s="7">
         <f t="shared" si="63"/>
         <v>0.20255794718686326</v>
       </c>
-      <c r="AA23" s="7">
-        <f t="shared" ref="AA23:AA25" si="64">AA3/Z3-1</f>
+      <c r="AA46" s="7">
+        <f t="shared" ref="AA46:AA48" si="64">AA26/Z26-1</f>
         <v>4.967842045225801E-2</v>
       </c>
-      <c r="AB23" s="7">
-        <f t="shared" ref="AB23:AB25" si="65">AB3/AA3-1</f>
+      <c r="AB46" s="7">
+        <f t="shared" ref="AB46:AB48" si="65">AB26/AA26-1</f>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AC23" s="7">
-        <f t="shared" ref="AC23:AC25" si="66">AC3/AB3-1</f>
+      <c r="AC46" s="7">
+        <f t="shared" ref="AC46:AC48" si="66">AC26/AB26-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AD23" s="7">
-        <f t="shared" ref="AD23:AD25" si="67">AD3/AC3-1</f>
+      <c r="AD46" s="7">
+        <f t="shared" ref="AD46:AD48" si="67">AD26/AC26-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE23" s="7">
-        <f t="shared" ref="AE23:AE25" si="68">AE3/AD3-1</f>
+      <c r="AE46" s="7">
+        <f t="shared" ref="AE46:AE48" si="68">AE26/AD26-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AF23" s="7">
-        <f t="shared" ref="AF23:AF25" si="69">AF3/AE3-1</f>
+      <c r="AF46" s="7">
+        <f t="shared" ref="AF46:AF48" si="69">AF26/AE26-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG23" s="7">
-        <f t="shared" ref="AG23:AG25" si="70">AG3/AF3-1</f>
+      <c r="AG46" s="7">
+        <f t="shared" ref="AG46:AG48" si="70">AG26/AF26-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH23" s="7">
-        <f t="shared" ref="AH23:AH25" si="71">AH3/AG3-1</f>
+      <c r="AH46" s="7">
+        <f t="shared" ref="AH46:AH48" si="71">AH26/AG26-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AI23" s="7">
-        <f t="shared" ref="AI23:AI25" si="72">AI3/AH3-1</f>
+      <c r="AI46" s="7">
+        <f t="shared" ref="AI46:AI48" si="72">AI26/AH26-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AJ23" s="7">
-        <f t="shared" ref="AJ23:AJ25" si="73">AJ3/AI3-1</f>
+      <c r="AJ46" s="7">
+        <f t="shared" ref="AJ46:AJ48" si="73">AJ26/AI26-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AK23" s="7">
-        <f t="shared" ref="AK23:AK25" si="74">AK3/AJ3-1</f>
+      <c r="AK46" s="7">
+        <f t="shared" ref="AK46:AK48" si="74">AK26/AJ26-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
-    <row r="24" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B24" s="1" t="s">
+    <row r="47" spans="2:135" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7">
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7">
         <f t="shared" si="60"/>
         <v>0.14867669953295271</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H47" s="7">
         <f t="shared" si="60"/>
         <v>0.20907297830374749</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I47" s="7">
         <f t="shared" si="60"/>
         <v>0.15589988081048878</v>
       </c>
-      <c r="J24" s="7">
+      <c r="J47" s="7">
         <f t="shared" si="60"/>
         <v>0.23188751191611057</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K47" s="7">
         <f t="shared" si="60"/>
         <v>0.12988479783148854</v>
       </c>
-      <c r="L24" s="7">
+      <c r="L47" s="7">
         <f t="shared" si="60"/>
         <v>5.1998368678629614E-2</v>
       </c>
-      <c r="M24" s="7">
+      <c r="M47" s="7">
         <f t="shared" si="60"/>
         <v>0.10971334295731072</v>
       </c>
-      <c r="N24" s="7">
+      <c r="N47" s="7">
         <f t="shared" si="60"/>
         <v>8.0286322306055258E-2</v>
       </c>
-      <c r="O24" s="7">
+      <c r="O47" s="7">
         <f t="shared" si="60"/>
         <v>0.14254298280687716</v>
       </c>
-      <c r="P24" s="7">
+      <c r="P47" s="7">
         <f t="shared" si="60"/>
         <v>0.16883116883116878</v>
       </c>
-      <c r="Q24" s="7">
+      <c r="Q47" s="7">
         <f t="shared" si="61"/>
         <v>0.16999999999999993</v>
       </c>
-      <c r="R24" s="7">
+      <c r="R47" s="7">
         <f t="shared" si="62"/>
         <v>0.17999999999999994</v>
       </c>
-      <c r="U24" s="7"/>
-      <c r="V24" s="7">
-        <f t="shared" ref="V24:Z25" si="75">V4/U4-1</f>
+      <c r="U47" s="7"/>
+      <c r="V47" s="7">
+        <f t="shared" ref="V47:Z48" si="75">V27/U27-1</f>
         <v>7.4245000404825623E-2</v>
       </c>
-      <c r="W24" s="7">
+      <c r="W47" s="7">
         <f t="shared" si="75"/>
         <v>0.13943322279167925</v>
       </c>
-      <c r="X24" s="7">
+      <c r="X47" s="7">
         <f t="shared" si="75"/>
         <v>7.8251091414208274E-2</v>
       </c>
-      <c r="Y24" s="7">
+      <c r="Y47" s="7">
         <f t="shared" si="75"/>
         <v>0.18698239371817671</v>
       </c>
-      <c r="Z24" s="7">
+      <c r="Z47" s="7">
         <f t="shared" si="75"/>
         <v>9.1839371543749104E-2</v>
       </c>
-      <c r="AA24" s="7">
+      <c r="AA47" s="7">
         <f t="shared" si="64"/>
         <v>0.16585676417684359</v>
       </c>
-      <c r="AB24" s="7">
+      <c r="AB47" s="7">
         <f t="shared" si="65"/>
         <v>0.12999999999999989</v>
       </c>
-      <c r="AC24" s="7">
+      <c r="AC47" s="7">
         <f t="shared" si="66"/>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="AD24" s="7">
+      <c r="AD47" s="7">
         <f t="shared" si="67"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AE24" s="7">
+      <c r="AE47" s="7">
         <f t="shared" si="68"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AF24" s="7">
+      <c r="AF47" s="7">
         <f t="shared" si="69"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AG24" s="7">
+      <c r="AG47" s="7">
         <f t="shared" si="70"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AH24" s="7">
+      <c r="AH47" s="7">
         <f t="shared" si="71"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AI24" s="7">
+      <c r="AI47" s="7">
         <f t="shared" si="72"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AJ24" s="7">
+      <c r="AJ47" s="7">
         <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AK24" s="7">
+      <c r="AK47" s="7">
         <f t="shared" si="74"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="25" spans="2:135" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="4" t="s">
+    <row r="48" spans="2:135" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7">
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7">
         <f t="shared" si="60"/>
         <v>9.531687452277926E-2</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H48" s="7">
         <f t="shared" si="60"/>
         <v>0.12265538801029785</v>
       </c>
-      <c r="I25" s="7">
+      <c r="I48" s="7">
         <f t="shared" si="60"/>
         <v>-0.20571057754704736</v>
       </c>
-      <c r="J25" s="7">
+      <c r="J48" s="7">
         <f t="shared" si="60"/>
         <v>0.10136516884983138</v>
       </c>
-      <c r="K25" s="7">
+      <c r="K48" s="7">
         <f t="shared" si="60"/>
         <v>0.12147089578250259</v>
       </c>
-      <c r="L25" s="7">
+      <c r="L48" s="7">
         <f t="shared" si="60"/>
         <v>7.6767676767676818E-2</v>
       </c>
-      <c r="M25" s="7">
+      <c r="M48" s="7">
         <f t="shared" si="60"/>
         <v>0.49205288175876416</v>
       </c>
-      <c r="N25" s="7">
+      <c r="N48" s="7">
         <f t="shared" si="60"/>
         <v>8.5110653886686372E-2</v>
       </c>
-      <c r="O25" s="7">
+      <c r="O48" s="7">
         <f t="shared" si="60"/>
         <v>5.1851851851851816E-2</v>
       </c>
-      <c r="P25" s="7">
+      <c r="P48" s="7">
         <f t="shared" si="60"/>
         <v>9.4315704071801676E-2</v>
       </c>
-      <c r="Q25" s="7">
+      <c r="Q48" s="7">
         <f t="shared" si="61"/>
         <v>8.9464383493454092E-2</v>
       </c>
-      <c r="R25" s="7">
+      <c r="R48" s="7">
         <f t="shared" si="62"/>
         <v>8.3571659806687348E-2</v>
       </c>
-      <c r="U25" s="7"/>
-      <c r="V25" s="7">
+      <c r="U48" s="7"/>
+      <c r="V48" s="7">
         <f t="shared" si="75"/>
         <v>0.24781141811285812</v>
       </c>
-      <c r="W25" s="7">
+      <c r="W48" s="7">
         <f t="shared" si="75"/>
         <v>0.1378585187410537</v>
       </c>
-      <c r="X25" s="7">
+      <c r="X48" s="7">
         <f t="shared" si="75"/>
         <v>4.1715847673479578E-2</v>
       </c>
-      <c r="Y25" s="7">
+      <c r="Y48" s="7">
         <f t="shared" si="75"/>
         <v>2.7521841548140857E-2</v>
       </c>
-      <c r="Z25" s="7">
+      <c r="Z48" s="7">
         <f t="shared" si="75"/>
         <v>0.17147417295414979</v>
       </c>
-      <c r="AA25" s="7">
+      <c r="AA48" s="7">
         <f t="shared" si="64"/>
         <v>8.0077782456835722E-2</v>
       </c>
-      <c r="AB25" s="7">
+      <c r="AB48" s="7">
         <f t="shared" si="65"/>
         <v>6.5419790209822359E-2</v>
       </c>
-      <c r="AC25" s="7">
+      <c r="AC48" s="7">
         <f t="shared" si="66"/>
         <v>4.7973737176055575E-2</v>
       </c>
-      <c r="AD25" s="7">
+      <c r="AD48" s="7">
         <f t="shared" si="67"/>
         <v>2.9347263593977546E-2</v>
       </c>
-      <c r="AE25" s="7">
+      <c r="AE48" s="7">
         <f t="shared" si="68"/>
         <v>2.6356537533250846E-2</v>
       </c>
-      <c r="AF25" s="7">
+      <c r="AF48" s="7">
         <f t="shared" si="69"/>
         <v>2.3220517818529851E-2</v>
       </c>
-      <c r="AG25" s="7">
+      <c r="AG48" s="7">
         <f t="shared" si="70"/>
         <v>2.3241855783108889E-2</v>
       </c>
-      <c r="AH25" s="7">
+      <c r="AH48" s="7">
         <f t="shared" si="71"/>
         <v>2.326326707388926E-2</v>
       </c>
-      <c r="AI25" s="7">
+      <c r="AI48" s="7">
         <f t="shared" si="72"/>
         <v>2.3284751045268504E-2</v>
       </c>
-      <c r="AJ25" s="7">
+      <c r="AJ48" s="7">
         <f t="shared" si="73"/>
         <v>2.3306307040313667E-2</v>
       </c>
-      <c r="AK25" s="7">
+      <c r="AK48" s="7">
         <f t="shared" si="74"/>
         <v>2.3327934390801053E-2</v>
       </c>
-      <c r="AN25" s="1" t="s">
+      <c r="AN48" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AO25" s="7">
+      <c r="AO48" s="7">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="26" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B26" s="1" t="s">
+    <row r="49" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="7">
-        <f t="shared" ref="C26" si="76">(C3-C6)/C3</f>
+      <c r="C49" s="7">
+        <f t="shared" ref="C49" si="76">(C26-C29)/C26</f>
         <v>0.17214634968807957</v>
       </c>
-      <c r="D26" s="7">
-        <f t="shared" ref="D26:N26" si="77">(D3-D6)/D3</f>
+      <c r="D49" s="7">
+        <f t="shared" ref="D49:N49" si="77">(D26-D29)/D26</f>
         <v>0.18094305759503998</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E49" s="7">
         <f t="shared" si="77"/>
         <v>0.17740671056757604</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F49" s="7">
         <f t="shared" si="77"/>
         <v>0.16715837950636828</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G49" s="7">
         <f t="shared" si="77"/>
         <v>0.16321263783530149</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H49" s="7">
         <f t="shared" si="77"/>
         <v>0.17314145104764744</v>
       </c>
-      <c r="I26" s="7">
+      <c r="I49" s="7">
         <f t="shared" si="77"/>
         <v>-7.8235635519442834E-2</v>
       </c>
-      <c r="J26" s="7">
+      <c r="J49" s="7">
         <f t="shared" si="77"/>
         <v>0.16336902019243799</v>
       </c>
-      <c r="K26" s="7">
+      <c r="K49" s="7">
         <f t="shared" si="77"/>
         <v>0.14591344473187443</v>
       </c>
-      <c r="L26" s="7">
+      <c r="L49" s="7">
         <f t="shared" si="77"/>
         <v>0.13301744265897542</v>
       </c>
-      <c r="M26" s="7">
+      <c r="M49" s="7">
         <f t="shared" si="77"/>
         <v>0.16127277672015231</v>
       </c>
-      <c r="N26" s="7">
+      <c r="N49" s="7">
         <f t="shared" si="77"/>
         <v>0.15262796932477088</v>
       </c>
-      <c r="O26" s="7">
-        <f t="shared" ref="O26" si="78">(O3-O6)/O3</f>
+      <c r="O49" s="7">
+        <f t="shared" ref="O49" si="78">(O26-O29)/O26</f>
         <v>0.15817969981495442</v>
       </c>
-      <c r="P26" s="7">
-        <f t="shared" ref="P26" si="79">(P3-P6)/P3</f>
+      <c r="P49" s="7">
+        <f t="shared" ref="P49" si="79">(P26-P29)/P26</f>
         <v>0.16474824770111246</v>
       </c>
-      <c r="Q26" s="7">
-        <f t="shared" ref="Q26:R26" si="80">(Q3-Q6)/Q3</f>
+      <c r="Q49" s="7">
+        <f t="shared" ref="Q49:R49" si="80">(Q26-Q29)/Q26</f>
         <v>0.16</v>
       </c>
-      <c r="R26" s="7">
+      <c r="R49" s="7">
         <f t="shared" si="80"/>
         <v>0.16000000000000009</v>
       </c>
-      <c r="U26" s="7">
-        <f>(U3-U6)/U3</f>
+      <c r="U49" s="7">
+        <f>(U26-U29)/U26</f>
         <v>0.18449603006242801</v>
       </c>
-      <c r="V26" s="7">
-        <f>(V3-V6)/V3</f>
+      <c r="V49" s="7">
+        <f>(V26-V29)/V26</f>
         <v>0.11962418338373462</v>
       </c>
-      <c r="W26" s="7">
-        <f t="shared" ref="W26:Z26" si="81">(W3-W6)/W3</f>
+      <c r="W49" s="7">
+        <f t="shared" ref="W49:Z49" si="81">(W26-W29)/W26</f>
         <v>0.16592246803328597</v>
       </c>
-      <c r="X26" s="7">
+      <c r="X49" s="7">
         <f t="shared" si="81"/>
         <v>0.17422645894471472</v>
       </c>
-      <c r="Y26" s="7">
+      <c r="Y49" s="7">
         <f t="shared" si="81"/>
         <v>0.1239837808396038</v>
       </c>
-      <c r="Z26" s="7">
+      <c r="Z49" s="7">
         <f t="shared" si="81"/>
         <v>0.14835939072669932</v>
       </c>
-      <c r="AA26" s="7">
-        <f t="shared" ref="AA26:AK26" si="82">(AA3-AA6)/AA3</f>
+      <c r="AA49" s="7">
+        <f t="shared" ref="AA49:AK49" si="82">(AA26-AA29)/AA26</f>
         <v>0.16075559226975422</v>
       </c>
-      <c r="AB26" s="7">
+      <c r="AB49" s="7">
         <f t="shared" si="82"/>
         <v>0.16</v>
       </c>
-      <c r="AC26" s="7">
+      <c r="AC49" s="7">
         <f t="shared" si="82"/>
         <v>0.16000000000000006</v>
       </c>
-      <c r="AD26" s="7">
+      <c r="AD49" s="7">
         <f t="shared" si="82"/>
         <v>0.16000000000000003</v>
       </c>
-      <c r="AE26" s="7">
+      <c r="AE49" s="7">
         <f t="shared" si="82"/>
         <v>0.16000000000000006</v>
       </c>
-      <c r="AF26" s="7">
+      <c r="AF49" s="7">
         <f t="shared" si="82"/>
         <v>0.16000000000000006</v>
       </c>
-      <c r="AG26" s="7">
+      <c r="AG49" s="7">
         <f t="shared" si="82"/>
         <v>0.15999999999999998</v>
       </c>
-      <c r="AH26" s="7">
+      <c r="AH49" s="7">
         <f t="shared" si="82"/>
         <v>0.16</v>
       </c>
-      <c r="AI26" s="7">
+      <c r="AI49" s="7">
         <f t="shared" si="82"/>
         <v>0.16000000000000006</v>
       </c>
-      <c r="AJ26" s="7">
+      <c r="AJ49" s="7">
         <f t="shared" si="82"/>
         <v>0.16</v>
       </c>
-      <c r="AK26" s="7">
+      <c r="AK49" s="7">
         <f t="shared" si="82"/>
         <v>0.16000000000000006</v>
       </c>
-      <c r="AN26" s="1" t="s">
+      <c r="AN49" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AO26" s="7">
+      <c r="AO49" s="7">
         <v>0.06</v>
       </c>
     </row>
-    <row r="27" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B27" s="1" t="s">
+    <row r="50" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="7">
-        <f t="shared" ref="C27" si="83">(C4-C7)/C4</f>
+      <c r="C50" s="7">
+        <f t="shared" ref="C50" si="83">(C27-C30)/C27</f>
         <v>0.28905033731188373</v>
       </c>
-      <c r="D27" s="7">
-        <f t="shared" ref="D27:N27" si="84">(D4-D7)/D4</f>
+      <c r="D50" s="7">
+        <f t="shared" ref="D50:N50" si="84">(D27-D30)/D27</f>
         <v>0.3057199211045365</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E50" s="7">
         <f t="shared" si="84"/>
         <v>0.29177592371871275</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F50" s="7">
         <f t="shared" si="84"/>
         <v>0.29647283126787416</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G50" s="7">
         <f t="shared" si="84"/>
         <v>0.33476394849785407</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H50" s="7">
         <f t="shared" si="84"/>
         <v>0.30077487765089722</v>
       </c>
-      <c r="I27" s="7">
+      <c r="I50" s="7">
         <f t="shared" si="84"/>
         <v>0.28624458651268303</v>
       </c>
-      <c r="J27" s="7">
+      <c r="J50" s="7">
         <f t="shared" si="84"/>
         <v>0.30915070613271428</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K50" s="7">
         <f t="shared" si="84"/>
         <v>0.29468212714914033</v>
       </c>
-      <c r="L27" s="7">
+      <c r="L50" s="7">
         <f t="shared" si="84"/>
         <v>0.3184725722039155</v>
       </c>
-      <c r="M27" s="7">
+      <c r="M50" s="7">
         <f t="shared" si="84"/>
         <v>0.30886452332280245</v>
       </c>
-      <c r="N27" s="7">
+      <c r="N50" s="7">
         <f t="shared" si="84"/>
         <v>0.32002148997134672</v>
       </c>
-      <c r="O27" s="7">
-        <f t="shared" ref="O27" si="85">(O4-O7)/O4</f>
+      <c r="O50" s="7">
+        <f t="shared" ref="O50" si="85">(O27-O30)/O27</f>
         <v>0.31636045494313209</v>
       </c>
-      <c r="P27" s="7">
-        <f t="shared" ref="P27" si="86">(P4-P7)/P4</f>
+      <c r="P50" s="7">
+        <f t="shared" ref="P50" si="86">(P27-P30)/P27</f>
         <v>0.30082918739635156</v>
       </c>
-      <c r="Q27" s="7">
-        <f t="shared" ref="Q27:R27" si="87">(Q4-Q7)/Q4</f>
+      <c r="Q50" s="7">
+        <f t="shared" ref="Q50:R50" si="87">(Q27-Q30)/Q27</f>
         <v>0.31000000000000011</v>
       </c>
-      <c r="R27" s="7">
+      <c r="R50" s="7">
         <f t="shared" si="87"/>
         <v>0.31</v>
       </c>
-      <c r="U27" s="7">
-        <f>(U4-U7)/U4</f>
+      <c r="U50" s="7">
+        <f>(U27-U30)/U27</f>
         <v>0.37754028013926</v>
       </c>
-      <c r="V27" s="7">
-        <f>(V4-V7)/V4</f>
+      <c r="V50" s="7">
+        <f>(V27-V30)/V27</f>
         <v>0.25241181790774797</v>
       </c>
-      <c r="W27" s="7">
-        <f t="shared" ref="W27:Z27" si="88">(W4-W7)/W4</f>
+      <c r="W50" s="7">
+        <f t="shared" ref="W50:Z50" si="88">(W27-W30)/W27</f>
         <v>0.28548749834634213</v>
       </c>
-      <c r="X27" s="7">
+      <c r="X50" s="7">
         <f t="shared" si="88"/>
         <v>0.29581007300165635</v>
       </c>
-      <c r="Y27" s="7">
+      <c r="Y50" s="7">
         <f t="shared" si="88"/>
         <v>0.30714765620962325</v>
       </c>
-      <c r="Z27" s="7">
+      <c r="Z50" s="7">
         <f t="shared" si="88"/>
         <v>0.3108018555334659</v>
       </c>
-      <c r="AA27" s="7">
-        <f t="shared" ref="AA27:AK27" si="89">(AA4-AA7)/AA4</f>
+      <c r="AA50" s="7">
+        <f t="shared" ref="AA50:AK50" si="89">(AA27-AA30)/AA27</f>
         <v>0.30923060963731475</v>
       </c>
-      <c r="AB27" s="7">
+      <c r="AB50" s="7">
         <f t="shared" si="89"/>
         <v>0.31000000000000005</v>
       </c>
-      <c r="AC27" s="7">
+      <c r="AC50" s="7">
         <f t="shared" si="89"/>
         <v>0.31000000000000005</v>
       </c>
-      <c r="AD27" s="7">
+      <c r="AD50" s="7">
         <f t="shared" si="89"/>
         <v>0.31000000000000005</v>
       </c>
-      <c r="AE27" s="7">
+      <c r="AE50" s="7">
         <f t="shared" si="89"/>
         <v>0.31000000000000005</v>
       </c>
-      <c r="AF27" s="7">
+      <c r="AF50" s="7">
         <f t="shared" si="89"/>
         <v>0.31000000000000011</v>
       </c>
-      <c r="AG27" s="7">
+      <c r="AG50" s="7">
         <f t="shared" si="89"/>
         <v>0.31000000000000005</v>
       </c>
-      <c r="AH27" s="7">
+      <c r="AH50" s="7">
         <f t="shared" si="89"/>
         <v>0.31</v>
       </c>
-      <c r="AI27" s="7">
+      <c r="AI50" s="7">
         <f t="shared" si="89"/>
         <v>0.31000000000000005</v>
       </c>
-      <c r="AJ27" s="7">
+      <c r="AJ50" s="7">
         <f t="shared" si="89"/>
         <v>0.31000000000000005</v>
       </c>
-      <c r="AK27" s="7">
+      <c r="AK50" s="7">
         <f t="shared" si="89"/>
         <v>0.31000000000000005</v>
       </c>
-      <c r="AN27" s="1" t="s">
+      <c r="AN50" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AO27" s="3">
-        <f>NPV(AO26,AA19:EE19)</f>
+      <c r="AO50" s="3">
+        <f>NPV(AO49,AA42:EE42)</f>
         <v>147349.01469148142</v>
       </c>
     </row>
-    <row r="28" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B28" s="1" t="s">
+    <row r="51" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="7">
-        <f t="shared" ref="C28" si="90">C9/C5</f>
+      <c r="C51" s="7">
+        <f t="shared" ref="C51" si="90">C32/C28</f>
         <v>0.20081445660473402</v>
       </c>
-      <c r="D28" s="7">
-        <f t="shared" ref="D28:N28" si="91">D9/D5</f>
+      <c r="D51" s="7">
+        <f t="shared" ref="D51:N51" si="91">D32/D28</f>
         <v>0.21196518327816599</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E51" s="7">
         <f t="shared" si="91"/>
         <v>0.20571057754704739</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F51" s="7">
         <f t="shared" si="91"/>
         <v>0.19714806831371248</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G51" s="7">
         <f t="shared" si="91"/>
         <v>0.20733124201231556</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H51" s="7">
         <f t="shared" si="91"/>
         <v>0.20731640731640733</v>
       </c>
-      <c r="I28" s="7">
+      <c r="I51" s="7">
         <f t="shared" si="91"/>
         <v>5.3030303030303032E-2</v>
       </c>
-      <c r="J28" s="7">
+      <c r="J51" s="7">
         <f t="shared" si="91"/>
         <v>0.20118432277814022</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K51" s="7">
         <f t="shared" si="91"/>
         <v>0.18445998445998446</v>
       </c>
-      <c r="L28" s="7">
+      <c r="L51" s="7">
         <f t="shared" si="91"/>
         <v>0.18153237665432786</v>
       </c>
-      <c r="M28" s="7">
+      <c r="M51" s="7">
         <f t="shared" si="91"/>
         <v>0.20080641146896311</v>
       </c>
-      <c r="N28" s="7">
+      <c r="N51" s="7">
         <f t="shared" si="91"/>
         <v>0.1958562641631596</v>
       </c>
-      <c r="O28" s="7">
-        <f t="shared" ref="O28" si="92">O9/O5</f>
+      <c r="O51" s="7">
+        <f t="shared" ref="O51" si="92">O32/O28</f>
         <v>0.20269870974096327</v>
       </c>
-      <c r="P28" s="7">
-        <f t="shared" ref="P28" si="93">P9/P5</f>
+      <c r="P51" s="7">
+        <f t="shared" ref="P51" si="93">P32/P28</f>
         <v>0.20277095593345998</v>
       </c>
-      <c r="Q28" s="7">
-        <f t="shared" ref="Q28:R28" si="94">Q9/Q5</f>
+      <c r="Q51" s="7">
+        <f t="shared" ref="Q51:R51" si="94">Q32/Q28</f>
         <v>0.20314880347249981</v>
       </c>
-      <c r="R28" s="7">
+      <c r="R51" s="7">
         <f t="shared" si="94"/>
         <v>0.20218374080828605</v>
       </c>
-      <c r="U28" s="7">
-        <f>U9/U5</f>
+      <c r="U51" s="7">
+        <f>U32/U28</f>
         <v>0.23707248230390968</v>
       </c>
-      <c r="V28" s="7">
-        <f>V9/V5</f>
+      <c r="V51" s="7">
+        <f>V32/V28</f>
         <v>0.15075900825277891</v>
       </c>
-      <c r="W28" s="7">
-        <f t="shared" ref="W28:Z28" si="95">W9/W5</f>
+      <c r="W51" s="7">
+        <f t="shared" ref="W51:Z51" si="95">W32/W28</f>
         <v>0.19399577561036219</v>
       </c>
-      <c r="X28" s="7">
+      <c r="X51" s="7">
         <f t="shared" si="95"/>
         <v>0.20377493514625639</v>
       </c>
-      <c r="Y28" s="7">
+      <c r="Y51" s="7">
         <f t="shared" si="95"/>
         <v>0.17540626813697041</v>
       </c>
-      <c r="Z28" s="7">
+      <c r="Z51" s="7">
         <f t="shared" si="95"/>
         <v>0.19086427704426664</v>
       </c>
-      <c r="AA28" s="7">
-        <f t="shared" ref="AA28:AK28" si="96">AA9/AA5</f>
+      <c r="AA51" s="7">
+        <f t="shared" ref="AA51:AK51" si="96">AA32/AA28</f>
         <v>0.2026911899684555</v>
       </c>
-      <c r="AB28" s="7">
+      <c r="AB51" s="7">
         <f t="shared" si="96"/>
         <v>0.20493434294013851</v>
       </c>
-      <c r="AC28" s="7">
+      <c r="AC51" s="7">
         <f t="shared" si="96"/>
         <v>0.20673631796988712</v>
       </c>
-      <c r="AD28" s="7">
+      <c r="AD51" s="7">
         <f t="shared" si="96"/>
         <v>0.20767403149938157</v>
       </c>
-      <c r="AE28" s="7">
+      <c r="AE51" s="7">
         <f t="shared" si="96"/>
         <v>0.20830776727794817</v>
       </c>
-      <c r="AF28" s="7">
+      <c r="AF51" s="7">
         <f t="shared" si="96"/>
         <v>0.20862783674663474</v>
       </c>
-      <c r="AG28" s="7">
+      <c r="AG51" s="7">
         <f t="shared" si="96"/>
         <v>0.20894900610833711</v>
       </c>
-      <c r="AH28" s="7">
+      <c r="AH51" s="7">
         <f t="shared" si="96"/>
         <v>0.20927126567902757</v>
       </c>
-      <c r="AI28" s="7">
+      <c r="AI51" s="7">
         <f t="shared" si="96"/>
         <v>0.20959460560470461</v>
       </c>
-      <c r="AJ28" s="7">
+      <c r="AJ51" s="7">
         <f t="shared" si="96"/>
         <v>0.20991901586201531</v>
       </c>
-      <c r="AK28" s="7">
+      <c r="AK51" s="7">
         <f t="shared" si="96"/>
         <v>0.210244486258928</v>
       </c>
-      <c r="AN28" s="1" t="s">
+      <c r="AN51" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AO28" s="3">
+      <c r="AO51" s="3">
         <f>Main!D8</f>
         <v>-37196</v>
       </c>
     </row>
-    <row r="29" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B29" s="1" t="s">
+    <row r="52" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7">
-        <f t="shared" ref="G29:P29" si="97">G10/C10-1</f>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7">
+        <f t="shared" ref="G52:P52" si="97">G33/C33-1</f>
         <v>-4.4094488188976433E-2</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H52" s="7">
         <f t="shared" si="97"/>
         <v>4.4412607449856756E-2</v>
       </c>
-      <c r="I29" s="7">
+      <c r="I52" s="7">
         <f t="shared" si="97"/>
         <v>7.5528700906344337E-2</v>
       </c>
-      <c r="J29" s="7">
+      <c r="J52" s="7">
         <f t="shared" si="97"/>
         <v>5.7262569832402299E-2</v>
       </c>
-      <c r="K29" s="7">
+      <c r="K52" s="7">
         <f t="shared" si="97"/>
         <v>0.10214168039538718</v>
       </c>
-      <c r="L29" s="7">
+      <c r="L52" s="7">
         <f t="shared" si="97"/>
         <v>-3.1550068587105629E-2</v>
       </c>
-      <c r="M29" s="7">
+      <c r="M52" s="7">
         <f t="shared" si="97"/>
         <v>5.47752808988764E-2</v>
       </c>
-      <c r="N29" s="7">
+      <c r="N52" s="7">
         <f t="shared" si="97"/>
         <v>6.7371202113606365E-2</v>
       </c>
-      <c r="O29" s="7">
+      <c r="O52" s="7">
         <f t="shared" si="97"/>
         <v>-4.783258594917783E-2</v>
       </c>
-      <c r="P29" s="7">
+      <c r="P52" s="7">
         <f t="shared" si="97"/>
         <v>-1.2747875354107596E-2</v>
       </c>
-      <c r="Q29" s="7">
-        <f t="shared" ref="Q29" si="98">Q10/M10-1</f>
+      <c r="Q52" s="7">
+        <f t="shared" ref="Q52" si="98">Q33/M33-1</f>
         <v>-2.0000000000000018E-2</v>
       </c>
-      <c r="R29" s="7">
-        <f t="shared" ref="R29" si="99">R10/N10-1</f>
+      <c r="R52" s="7">
+        <f t="shared" ref="R52" si="99">R33/N33-1</f>
         <v>-1.9999999999999907E-2</v>
       </c>
-      <c r="U29" s="7"/>
-      <c r="V29" s="7">
-        <f>V10/U10-1</f>
+      <c r="U52" s="7"/>
+      <c r="V52" s="7">
+        <f>V33/U33-1</f>
         <v>5.3017944535073358E-2</v>
       </c>
-      <c r="W29" s="7">
-        <f t="shared" ref="W29:Z29" si="100">W10/V10-1</f>
+      <c r="W52" s="7">
+        <f t="shared" ref="W52:Z52" si="100">W33/V33-1</f>
         <v>5.8094500387296577E-2</v>
       </c>
-      <c r="X29" s="7">
+      <c r="X52" s="7">
         <f t="shared" si="100"/>
         <v>-7.6866764275256294E-3</v>
       </c>
-      <c r="Y29" s="7">
+      <c r="Y52" s="7">
         <f t="shared" si="100"/>
         <v>3.4673552194762092E-2</v>
       </c>
-      <c r="Z29" s="7">
+      <c r="Z52" s="7">
         <f t="shared" si="100"/>
         <v>4.5989304812834142E-2</v>
       </c>
-      <c r="AA29" s="7">
-        <f t="shared" ref="AA29" si="101">AA10/Z10-1</f>
+      <c r="AA52" s="7">
+        <f t="shared" ref="AA52" si="101">AA33/Z33-1</f>
         <v>-2.4601226993865022E-2</v>
       </c>
-      <c r="AB29" s="7">
-        <f t="shared" ref="AB29" si="102">AB10/AA10-1</f>
+      <c r="AB52" s="7">
+        <f t="shared" ref="AB52" si="102">AB33/AA33-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AC29" s="7">
-        <f t="shared" ref="AC29" si="103">AC10/AB10-1</f>
+      <c r="AC52" s="7">
+        <f t="shared" ref="AC52" si="103">AC33/AB33-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AD29" s="7">
-        <f t="shared" ref="AD29" si="104">AD10/AC10-1</f>
+      <c r="AD52" s="7">
+        <f t="shared" ref="AD52" si="104">AD33/AC33-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE29" s="7">
-        <f t="shared" ref="AE29" si="105">AE10/AD10-1</f>
+      <c r="AE52" s="7">
+        <f t="shared" ref="AE52" si="105">AE33/AD33-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AF29" s="7">
-        <f t="shared" ref="AF29" si="106">AF10/AE10-1</f>
+      <c r="AF52" s="7">
+        <f t="shared" ref="AF52" si="106">AF33/AE33-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AG29" s="7">
-        <f t="shared" ref="AG29" si="107">AG10/AF10-1</f>
+      <c r="AG52" s="7">
+        <f t="shared" ref="AG52" si="107">AG33/AF33-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH29" s="7">
-        <f t="shared" ref="AH29" si="108">AH10/AG10-1</f>
+      <c r="AH52" s="7">
+        <f t="shared" ref="AH52" si="108">AH33/AG33-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AI29" s="7">
-        <f t="shared" ref="AI29" si="109">AI10/AH10-1</f>
+      <c r="AI52" s="7">
+        <f t="shared" ref="AI52" si="109">AI33/AH33-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AJ29" s="7">
-        <f t="shared" ref="AJ29" si="110">AJ10/AI10-1</f>
+      <c r="AJ52" s="7">
+        <f t="shared" ref="AJ52" si="110">AJ33/AI33-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AK29" s="7">
-        <f t="shared" ref="AK29" si="111">AK10/AJ10-1</f>
+      <c r="AK52" s="7">
+        <f t="shared" ref="AK52" si="111">AK33/AJ33-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AN29" s="1" t="s">
+      <c r="AN52" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AO29" s="3">
-        <f>AO27+AO28</f>
+      <c r="AO52" s="3">
+        <f>AO50+AO51</f>
         <v>110153.01469148142</v>
       </c>
     </row>
-    <row r="30" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B30" s="1" t="s">
+    <row r="53" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="7">
-        <f t="shared" ref="C30" si="112">C11/C5</f>
+      <c r="C53" s="7">
+        <f t="shared" ref="C53" si="112">C34/C28</f>
         <v>9.3471621277678801E-2</v>
       </c>
-      <c r="D30" s="7">
-        <f t="shared" ref="D30:N30" si="113">D11/D5</f>
+      <c r="D53" s="7">
+        <f t="shared" ref="D53:N53" si="113">D34/D28</f>
         <v>8.7286992766948637E-2</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E53" s="7">
         <f t="shared" si="113"/>
         <v>7.9700312665919412E-2</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F53" s="7">
         <f t="shared" si="113"/>
         <v>7.3453821920079584E-2</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G53" s="7">
         <f t="shared" si="113"/>
         <v>8.121296619031021E-2</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H53" s="7">
         <f t="shared" si="113"/>
         <v>8.7360087360087366E-2</v>
       </c>
-      <c r="I30" s="7">
+      <c r="I53" s="7">
         <f t="shared" si="113"/>
         <v>0.10405525846702317</v>
       </c>
-      <c r="J30" s="7">
+      <c r="J53" s="7">
         <f t="shared" si="113"/>
         <v>7.0758267677021133E-2</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K53" s="7">
         <f t="shared" si="113"/>
         <v>7.2209272209272216E-2</v>
       </c>
-      <c r="L30" s="7">
+      <c r="L53" s="7">
         <f t="shared" si="113"/>
         <v>7.3474975914000304E-2</v>
       </c>
-      <c r="M30" s="7">
+      <c r="M53" s="7">
         <f t="shared" si="113"/>
         <v>6.9142316690726263E-2</v>
       </c>
-      <c r="N30" s="7">
+      <c r="N53" s="7">
         <f t="shared" si="113"/>
         <v>7.2792859455209732E-2</v>
       </c>
-      <c r="O30" s="7">
-        <f t="shared" ref="O30" si="114">O11/O5</f>
+      <c r="O53" s="7">
+        <f t="shared" ref="O53" si="114">O34/O28</f>
         <v>7.1308972717423424E-2</v>
       </c>
-      <c r="P30" s="7">
-        <f t="shared" ref="P30" si="115">P11/P5</f>
+      <c r="P53" s="7">
+        <f t="shared" ref="P53" si="115">P34/P28</f>
         <v>7.2888188684490984E-2</v>
       </c>
-      <c r="Q30" s="7">
-        <f t="shared" ref="Q30:R30" si="116">Q11/Q5</f>
+      <c r="Q53" s="7">
+        <f t="shared" ref="Q53:R53" si="116">Q34/Q28</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="R30" s="7">
+      <c r="R53" s="7">
         <f t="shared" si="116"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="U30" s="7">
-        <f>U11/U5</f>
+      <c r="U53" s="7">
+        <f>U34/U28</f>
         <v>8.1832013936360234E-2</v>
       </c>
-      <c r="V30" s="7">
-        <f>V11/V5</f>
+      <c r="V53" s="7">
+        <f>V34/V28</f>
         <v>9.7902345061586585E-2</v>
       </c>
-      <c r="W30" s="7">
-        <f t="shared" ref="W30:Z30" si="117">W11/W5</f>
+      <c r="W53" s="7">
+        <f t="shared" ref="W53:Z53" si="117">W34/W28</f>
         <v>8.1133130396968373E-2</v>
       </c>
-      <c r="X30" s="7">
+      <c r="X53" s="7">
         <f t="shared" si="117"/>
         <v>8.308733637475027E-2</v>
       </c>
-      <c r="Y30" s="7">
+      <c r="Y53" s="7">
         <f t="shared" si="117"/>
         <v>8.4286128845037722E-2</v>
       </c>
-      <c r="Z30" s="7">
+      <c r="Z53" s="7">
         <f t="shared" si="117"/>
         <v>7.1911615348410909E-2</v>
       </c>
-      <c r="AA30" s="7">
-        <f t="shared" ref="AA30:AK30" si="118">AA11/AA5</f>
+      <c r="AA53" s="7">
+        <f t="shared" ref="AA53:AK53" si="118">AA34/AA28</f>
         <v>7.1019571273203824E-2</v>
       </c>
-      <c r="AB30" s="7">
+      <c r="AB53" s="7">
         <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AC30" s="7">
+      <c r="AC53" s="7">
         <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AD30" s="7">
+      <c r="AD53" s="7">
         <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AE30" s="7">
+      <c r="AE53" s="7">
         <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AF30" s="7">
+      <c r="AF53" s="7">
         <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AG30" s="7">
+      <c r="AG53" s="7">
         <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AH30" s="7">
+      <c r="AH53" s="7">
         <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AI30" s="7">
+      <c r="AI53" s="7">
         <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AJ30" s="7">
+      <c r="AJ53" s="7">
         <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AK30" s="7">
+      <c r="AK53" s="7">
         <f t="shared" si="118"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AN30" s="1" t="s">
+      <c r="AN53" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AO30" s="9">
-        <f>AO29/AK20</f>
+      <c r="AO53" s="9">
+        <f>AO52/AK43</f>
         <v>82.29586454350499</v>
       </c>
     </row>
-    <row r="31" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B31" s="1" t="s">
+    <row r="54" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="7">
-        <f t="shared" ref="C31" si="119">C12/C5</f>
+      <c r="C54" s="7">
+        <f t="shared" ref="C54" si="119">C35/C28</f>
         <v>6.6938152201578005E-2</v>
       </c>
-      <c r="D31" s="7">
-        <f t="shared" ref="D31:N31" si="120">D12/D5</f>
+      <c r="D54" s="7">
+        <f t="shared" ref="D54:N54" si="120">D35/D28</f>
         <v>8.1892852764496746E-2</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E54" s="7">
         <f t="shared" si="120"/>
         <v>8.6956521739130432E-2</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F54" s="7">
         <f t="shared" si="120"/>
         <v>8.4120930746697617E-2</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G54" s="7">
         <f t="shared" si="120"/>
         <v>9.0856279772278378E-2</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H54" s="7">
         <f t="shared" si="120"/>
         <v>8.0152880152880149E-2</v>
       </c>
-      <c r="I31" s="7">
+      <c r="I54" s="7">
         <f t="shared" si="120"/>
         <v>-0.10390671420083185</v>
       </c>
-      <c r="J31" s="7">
+      <c r="J54" s="7">
         <f t="shared" si="120"/>
         <v>9.243739649721483E-2</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K54" s="7">
         <f t="shared" si="120"/>
         <v>7.75964775964776E-2</v>
       </c>
-      <c r="L31" s="7">
+      <c r="L54" s="7">
         <f t="shared" si="120"/>
         <v>7.2257999087267377E-2</v>
       </c>
-      <c r="M31" s="7">
+      <c r="M54" s="7">
         <f t="shared" si="120"/>
         <v>9.428045198865051E-2</v>
       </c>
-      <c r="N31" s="7">
+      <c r="N54" s="7">
         <f t="shared" si="120"/>
         <v>8.5695786893585535E-2</v>
       </c>
-      <c r="O31" s="7">
-        <f t="shared" ref="O31" si="121">O12/O5</f>
+      <c r="O54" s="7">
+        <f t="shared" ref="O54" si="121">O35/O28</f>
         <v>0.1000196986112479</v>
       </c>
-      <c r="P31" s="7">
-        <f t="shared" ref="P31" si="122">P12/P5</f>
+      <c r="P54" s="7">
+        <f t="shared" ref="P54" si="122">P35/P28</f>
         <v>9.758583939576479E-2</v>
       </c>
-      <c r="Q31" s="7">
-        <f t="shared" ref="Q31:R31" si="123">Q12/Q5</f>
+      <c r="Q54" s="7">
+        <f t="shared" ref="Q54:R54" si="123">Q35/Q28</f>
         <v>9.9521297618367657E-2</v>
       </c>
-      <c r="R31" s="7">
+      <c r="R54" s="7">
         <f t="shared" si="123"/>
         <v>9.8387853728136465E-2</v>
       </c>
-      <c r="U31" s="7">
-        <f>U12/U5</f>
+      <c r="U54" s="7">
+        <f>U35/U28</f>
         <v>0.10117091887362456</v>
       </c>
-      <c r="V31" s="7">
-        <f>V12/V5</f>
+      <c r="V54" s="7">
+        <f>V35/V28</f>
         <v>7.2278085072543163E-3</v>
       </c>
-      <c r="W31" s="7">
-        <f t="shared" ref="W31:Z31" si="124">W12/W5</f>
+      <c r="W54" s="7">
+        <f t="shared" ref="W54:Z54" si="124">W35/W28</f>
         <v>7.043237870410636E-2</v>
       </c>
-      <c r="X31" s="7">
+      <c r="X54" s="7">
         <f t="shared" si="124"/>
         <v>8.0269553030980711E-2</v>
       </c>
-      <c r="Y31" s="7">
+      <c r="Y54" s="7">
         <f t="shared" si="124"/>
         <v>5.0420777713290774E-2</v>
       </c>
-      <c r="Z31" s="7">
+      <c r="Z54" s="7">
         <f t="shared" si="124"/>
         <v>8.2612896034085559E-2</v>
       </c>
-      <c r="AA31" s="7">
-        <f t="shared" ref="AA31:AK31" si="125">AA12/AA5</f>
+      <c r="AA54" s="7">
+        <f t="shared" ref="AA54:AK54" si="125">AA35/AA28</f>
         <v>9.8853831482562993E-2</v>
       </c>
-      <c r="AB31" s="7">
+      <c r="AB54" s="7">
         <f t="shared" si="125"/>
         <v>0.10382363391314751</v>
       </c>
-      <c r="AC31" s="7">
+      <c r="AC54" s="7">
         <f t="shared" si="125"/>
         <v>0.10645605227063344</v>
       </c>
-      <c r="AD31" s="7">
+      <c r="AD54" s="7">
         <f t="shared" si="125"/>
         <v>0.10766873386503374</v>
       </c>
-      <c r="AE31" s="7">
+      <c r="AE54" s="7">
         <f t="shared" si="125"/>
         <v>0.10848830155837286</v>
       </c>
-      <c r="AF31" s="7">
+      <c r="AF54" s="7">
         <f t="shared" si="125"/>
         <v>0.10919365334990139</v>
       </c>
-      <c r="AG31" s="7">
+      <c r="AG54" s="7">
         <f t="shared" si="125"/>
         <v>0.10989573286439933</v>
       </c>
-      <c r="AH31" s="7">
+      <c r="AH54" s="7">
         <f t="shared" si="125"/>
         <v>0.11059457325725389</v>
       </c>
-      <c r="AI31" s="7">
+      <c r="AI54" s="7">
         <f t="shared" si="125"/>
         <v>0.11129020713066723</v>
       </c>
-      <c r="AJ31" s="7">
+      <c r="AJ54" s="7">
         <f t="shared" si="125"/>
         <v>0.11198266653816466</v>
       </c>
-      <c r="AK31" s="7">
+      <c r="AK54" s="7">
         <f t="shared" si="125"/>
         <v>0.11267198298910734</v>
       </c>
-      <c r="AN31" s="1" t="s">
+      <c r="AN54" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AO31" s="9">
+      <c r="AO54" s="9">
         <f>Main!D3</f>
         <v>166.58</v>
       </c>
     </row>
-    <row r="32" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B32" s="1" t="s">
+    <row r="55" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="7">
-        <f t="shared" ref="C32" si="126">C17/C16</f>
+      <c r="C55" s="7">
+        <f t="shared" ref="C55" si="126">C40/C39</f>
         <v>9.3397745571658614E-2</v>
       </c>
-      <c r="D32" s="7">
-        <f t="shared" ref="D32:N32" si="127">D17/D16</f>
+      <c r="D55" s="7">
+        <f t="shared" ref="D55:N55" si="127">D40/D39</f>
         <v>0.1068090787716956</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E55" s="7">
         <f t="shared" si="127"/>
         <v>0.16815742397137745</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F55" s="7">
         <f t="shared" si="127"/>
         <v>0.13647058823529412</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G55" s="7">
         <f t="shared" si="127"/>
         <v>0.16844469399213924</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H55" s="7">
         <f t="shared" si="127"/>
         <v>0.15432482887367766</v>
       </c>
-      <c r="I32" s="7">
+      <c r="I55" s="7">
         <f t="shared" si="127"/>
         <v>0.29425113464447805</v>
       </c>
-      <c r="J32" s="7">
+      <c r="J55" s="7">
         <f t="shared" si="127"/>
         <v>0.16779661016949152</v>
       </c>
-      <c r="K32" s="7">
+      <c r="K55" s="7">
         <f t="shared" si="127"/>
         <v>5.834683954619125E-2</v>
       </c>
-      <c r="L32" s="7">
+      <c r="L55" s="7">
         <f t="shared" si="127"/>
         <v>0.59112149532710279</v>
       </c>
-      <c r="M32" s="7">
+      <c r="M55" s="7">
         <f t="shared" si="127"/>
         <v>0.19464847848898217</v>
       </c>
-      <c r="N32" s="7">
+      <c r="N55" s="7">
         <f t="shared" si="127"/>
         <v>0.22349427575908412</v>
       </c>
-      <c r="O32" s="7">
-        <f t="shared" ref="O32" si="128">O17/O16</f>
+      <c r="O55" s="7">
+        <f t="shared" ref="O55" si="128">O40/O39</f>
         <v>0.17007150153217568</v>
       </c>
-      <c r="P32" s="7">
-        <f t="shared" ref="P32" si="129">P17/P16</f>
+      <c r="P55" s="7">
+        <f t="shared" ref="P55" si="129">P40/P39</f>
         <v>0.15441176470588236</v>
       </c>
-      <c r="Q32" s="7">
-        <f t="shared" ref="Q32:R32" si="130">Q17/Q16</f>
+      <c r="Q55" s="7">
+        <f t="shared" ref="Q55:R55" si="130">Q40/Q39</f>
         <v>0.17</v>
       </c>
-      <c r="R32" s="7">
+      <c r="R55" s="7">
         <f t="shared" si="130"/>
         <v>0.17</v>
       </c>
-      <c r="U32" s="7">
-        <f>U17/U16</f>
+      <c r="U55" s="7">
+        <f>U40/U39</f>
         <v>0.10139691714836223</v>
       </c>
-      <c r="V32" s="7">
-        <f>V17/V16</f>
+      <c r="V55" s="7">
+        <f>V40/V39</f>
         <v>-0.24436889077773055</v>
       </c>
-      <c r="W32" s="7">
-        <f t="shared" ref="W32:Z32" si="131">W17/W16</f>
+      <c r="W55" s="7">
+        <f t="shared" ref="W55:Z55" si="131">W40/W39</f>
         <v>0.15939971608193065</v>
       </c>
-      <c r="X32" s="7">
+      <c r="X55" s="7">
         <f t="shared" si="131"/>
         <v>0.12914827529834885</v>
       </c>
-      <c r="Y32" s="7">
+      <c r="Y55" s="7">
         <f t="shared" si="131"/>
         <v>0.11887382690302398</v>
       </c>
-      <c r="Z32" s="7">
+      <c r="Z55" s="7">
         <f t="shared" si="131"/>
         <v>0.19066838876331935</v>
       </c>
-      <c r="AA32" s="7">
-        <f t="shared" ref="AA32:AK32" si="132">AA17/AA16</f>
+      <c r="AA55" s="7">
+        <f t="shared" ref="AA55:AK55" si="132">AA40/AA39</f>
         <v>0.16616481474825659</v>
       </c>
-      <c r="AB32" s="7">
+      <c r="AB55" s="7">
         <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AC32" s="7">
+      <c r="AC55" s="7">
         <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AD32" s="7">
+      <c r="AD55" s="7">
         <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AE32" s="7">
+      <c r="AE55" s="7">
         <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AF32" s="7">
+      <c r="AF55" s="7">
         <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AG32" s="7">
+      <c r="AG55" s="7">
         <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AH32" s="7">
+      <c r="AH55" s="7">
         <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AI32" s="7">
+      <c r="AI55" s="7">
         <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AJ32" s="7">
+      <c r="AJ55" s="7">
         <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AK32" s="7">
+      <c r="AK55" s="7">
         <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
-      <c r="AN32" s="4" t="s">
+      <c r="AN55" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="AO32" s="12">
-        <f>AO30/AO31-1</f>
+      <c r="AO55" s="12">
+        <f>AO53/AO54-1</f>
         <v>-0.50596791605531888</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B33" s="1" t="s">
+    <row r="56" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B56" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="7">
-        <f t="shared" ref="C33:O33" si="133">C18/C16</f>
+      <c r="C56" s="7">
+        <f t="shared" ref="C56:O56" si="133">C41/C39</f>
         <v>1.8518518518518517E-2</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D56" s="7">
         <f t="shared" si="133"/>
         <v>2.2696929238985315E-2</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E56" s="7">
         <f t="shared" si="133"/>
         <v>4.7704233750745376E-3</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F56" s="7">
         <f t="shared" si="133"/>
         <v>2.7058823529411764E-2</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G56" s="7">
         <f t="shared" si="133"/>
         <v>3.0881527231892195E-2</v>
       </c>
-      <c r="H33" s="7">
+      <c r="H56" s="7">
         <f t="shared" si="133"/>
         <v>1.9912881144990666E-2</v>
       </c>
-      <c r="I33" s="7">
+      <c r="I56" s="7">
         <f t="shared" si="133"/>
         <v>-3.8577912254160365E-2</v>
       </c>
-      <c r="J33" s="7">
+      <c r="J56" s="7">
         <f t="shared" si="133"/>
         <v>2.655367231638418E-2</v>
       </c>
-      <c r="K33" s="7">
+      <c r="K56" s="7">
         <f t="shared" si="133"/>
         <v>1.8368449486763912E-2</v>
       </c>
-      <c r="L33" s="7">
+      <c r="L56" s="7">
         <f t="shared" si="133"/>
         <v>0.14953271028037382</v>
       </c>
-      <c r="M33" s="7">
+      <c r="M56" s="7">
         <f t="shared" si="133"/>
         <v>3.3053515215110178E-2</v>
       </c>
-      <c r="N33" s="7">
+      <c r="N56" s="7">
         <f t="shared" si="133"/>
         <v>3.8825286212045791E-2</v>
       </c>
-      <c r="O33" s="7">
+      <c r="O56" s="7">
         <f t="shared" si="133"/>
         <v>4.5965270684371805E-2</v>
       </c>
-      <c r="P33" s="7">
-        <f>P18/P16</f>
+      <c r="P56" s="7">
+        <f>P41/P39</f>
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="Q33" s="7">
-        <f t="shared" ref="Q33:R33" si="134">Q18/Q16</f>
+      <c r="Q56" s="7">
+        <f t="shared" ref="Q56:R56" si="134">Q41/Q39</f>
         <v>0.03</v>
       </c>
-      <c r="R33" s="7">
+      <c r="R56" s="7">
         <f t="shared" si="134"/>
         <v>0.03</v>
       </c>
-      <c r="U33" s="7">
-        <f t="shared" ref="U33:Y33" si="135">U18/U16</f>
+      <c r="U56" s="7">
+        <f t="shared" ref="U56:Y56" si="135">U41/U39</f>
         <v>5.3227360308285163E-2</v>
       </c>
-      <c r="V33" s="7">
+      <c r="V56" s="7">
         <f t="shared" si="135"/>
         <v>-7.6923076923076927E-2</v>
       </c>
-      <c r="W33" s="7">
+      <c r="W56" s="7">
         <f t="shared" si="135"/>
         <v>5.0294058000405595E-2</v>
       </c>
-      <c r="X33" s="7">
+      <c r="X56" s="7">
         <f t="shared" si="135"/>
         <v>1.8146150073565473E-2</v>
       </c>
-      <c r="Y33" s="7">
+      <c r="Y56" s="7">
         <f t="shared" si="135"/>
         <v>4.8227320125130341E-2</v>
       </c>
-      <c r="Z33" s="7">
-        <f>Z18/Z16</f>
+      <c r="Z56" s="7">
+        <f>Z41/Z39</f>
         <v>3.8585728123990956E-2</v>
       </c>
-      <c r="AA33" s="7">
-        <f t="shared" ref="AA33:AK33" si="136">AA18/AA16</f>
+      <c r="AA56" s="7">
+        <f t="shared" ref="AA56:AK56" si="136">AA41/AA39</f>
         <v>3.4610459591956327E-2</v>
       </c>
-      <c r="AB33" s="7">
+      <c r="AB56" s="7">
         <f t="shared" si="136"/>
         <v>3.0000000000000002E-2</v>
       </c>
-      <c r="AC33" s="7">
+      <c r="AC56" s="7">
         <f t="shared" si="136"/>
         <v>2.9999999999999995E-2</v>
       </c>
-      <c r="AD33" s="7">
+      <c r="AD56" s="7">
         <f t="shared" si="136"/>
         <v>0.03</v>
       </c>
-      <c r="AE33" s="7">
+      <c r="AE56" s="7">
         <f t="shared" si="136"/>
         <v>0.03</v>
       </c>
-      <c r="AF33" s="7">
+      <c r="AF56" s="7">
         <f t="shared" si="136"/>
         <v>3.0000000000000002E-2</v>
       </c>
-      <c r="AG33" s="7">
+      <c r="AG56" s="7">
         <f t="shared" si="136"/>
         <v>0.03</v>
       </c>
-      <c r="AH33" s="7">
+      <c r="AH56" s="7">
         <f t="shared" si="136"/>
         <v>0.03</v>
       </c>
-      <c r="AI33" s="7">
+      <c r="AI56" s="7">
         <f t="shared" si="136"/>
         <v>2.9999999999999995E-2</v>
       </c>
-      <c r="AJ33" s="7">
+      <c r="AJ56" s="7">
         <f t="shared" si="136"/>
         <v>0.03</v>
       </c>
-      <c r="AK33" s="7">
+      <c r="AK56" s="7">
         <f t="shared" si="136"/>
         <v>0.03</v>
       </c>
-      <c r="AN33" s="1" t="s">
+      <c r="AN56" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AO33" s="2" t="s">
+      <c r="AO56" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
+    <row r="57" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="7">
-        <f t="shared" ref="C34" si="137">C19/C5</f>
+      <c r="C57" s="7">
+        <f t="shared" ref="C57" si="137">C42/C28</f>
         <v>7.0183252736065155E-2</v>
       </c>
-      <c r="D34" s="7">
-        <f t="shared" ref="D34:N34" si="138">D19/D5</f>
+      <c r="D57" s="7">
+        <f t="shared" ref="D57:N57" si="138">D42/D28</f>
         <v>7.9931347309059708E-2</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E57" s="7">
         <f t="shared" si="138"/>
         <v>8.1824081175151914E-2</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F57" s="7">
         <f t="shared" si="138"/>
         <v>7.8593931354667551E-2</v>
       </c>
-      <c r="G34" s="7">
+      <c r="G57" s="7">
         <f t="shared" si="138"/>
         <v>8.2839549204136165E-2</v>
       </c>
-      <c r="H34" s="7">
+      <c r="H57" s="7">
         <f t="shared" si="138"/>
         <v>7.2454272454272453E-2</v>
       </c>
-      <c r="I34" s="7">
+      <c r="I57" s="7">
         <f t="shared" si="138"/>
         <v>-7.3083778966131913E-2</v>
       </c>
-      <c r="J34" s="7">
+      <c r="J57" s="7">
         <f t="shared" si="138"/>
         <v>7.1561198374065341E-2</v>
       </c>
-      <c r="K34" s="7">
+      <c r="K57" s="7">
         <f t="shared" si="138"/>
         <v>8.8526288526288521E-2</v>
       </c>
-      <c r="L34" s="7">
+      <c r="L57" s="7">
         <f t="shared" si="138"/>
         <v>5.6285178236397749E-3</v>
       </c>
-      <c r="M34" s="7">
+      <c r="M57" s="7">
         <f t="shared" si="138"/>
         <v>7.3273931007018761E-2</v>
       </c>
-      <c r="N34" s="7">
+      <c r="N57" s="7">
         <f t="shared" si="138"/>
         <v>6.8538130694168253E-2</v>
       </c>
-      <c r="O34" s="7">
-        <f t="shared" ref="O34" si="139">O19/O5</f>
+      <c r="O57" s="7">
+        <f t="shared" ref="O57" si="139">O42/O28</f>
         <v>7.5593420663843197E-2</v>
       </c>
-      <c r="P34" s="7">
-        <f t="shared" ref="P34" si="140">P19/P5</f>
+      <c r="P57" s="7">
+        <f t="shared" ref="P57" si="140">P42/P28</f>
         <v>7.6780501366943144E-2</v>
       </c>
-      <c r="Q34" s="7">
-        <f t="shared" ref="Q34:R34" si="141">Q19/Q5</f>
+      <c r="Q57" s="7">
+        <f t="shared" ref="Q57:R57" si="141">Q42/Q28</f>
         <v>7.5113023016734212E-2</v>
       </c>
-      <c r="R34" s="7">
+      <c r="R57" s="7">
         <f t="shared" si="141"/>
         <v>7.5192751878248712E-2</v>
       </c>
-      <c r="U34" s="7">
-        <f>U19/U5</f>
+      <c r="U57" s="7">
+        <f>U42/U28</f>
         <v>7.7399722154843545E-2</v>
       </c>
-      <c r="V34" s="7">
-        <f>V19/V5</f>
+      <c r="V57" s="7">
+        <f>V42/V28</f>
         <v>-5.4941947797197237E-2</v>
       </c>
-      <c r="W34" s="7">
-        <f t="shared" ref="W34:Z34" si="142">W19/W5</f>
+      <c r="W57" s="7">
+        <f t="shared" ref="W57:Z57" si="142">W42/W28</f>
         <v>6.0523700068335712E-2</v>
       </c>
-      <c r="X34" s="7">
+      <c r="X57" s="7">
         <f t="shared" si="142"/>
         <v>7.7764856725407755E-2</v>
       </c>
-      <c r="Y34" s="7">
+      <c r="Y57" s="7">
         <f t="shared" si="142"/>
         <v>4.6358096343586765E-2</v>
       </c>
-      <c r="Z34" s="7">
+      <c r="Z57" s="7">
         <f t="shared" si="142"/>
         <v>5.9129530084966186E-2</v>
       </c>
-      <c r="AA34" s="7">
-        <f t="shared" ref="AA34:AK34" si="143">AA19/AA5</f>
+      <c r="AA57" s="7">
+        <f t="shared" ref="AA57:AK57" si="143">AA42/AA28</f>
         <v>7.5658975369286591E-2</v>
       </c>
-      <c r="AB34" s="7">
+      <c r="AB57" s="7">
         <f t="shared" si="143"/>
         <v>8.1487340385963059E-2</v>
       </c>
-      <c r="AC34" s="7">
+      <c r="AC57" s="7">
         <f t="shared" si="143"/>
         <v>8.3778111570669833E-2</v>
       </c>
-      <c r="AD34" s="7">
+      <c r="AD57" s="7">
         <f t="shared" si="143"/>
         <v>8.4838593231775353E-2</v>
       </c>
-      <c r="AE34" s="7">
+      <c r="AE57" s="7">
         <f t="shared" si="143"/>
         <v>8.5565615998704644E-2</v>
       </c>
-      <c r="AF34" s="7">
+      <c r="AF57" s="7">
         <f t="shared" si="143"/>
         <v>8.6187866858918896E-2</v>
       </c>
-      <c r="AG34" s="7">
+      <c r="AG57" s="7">
         <f t="shared" si="143"/>
         <v>8.6806936703118842E-2</v>
       </c>
-      <c r="AH34" s="7">
+      <c r="AH57" s="7">
         <f t="shared" si="143"/>
         <v>8.7422857595766956E-2</v>
       </c>
-      <c r="AI34" s="7">
+      <c r="AI57" s="7">
         <f t="shared" si="143"/>
         <v>8.803566110408724E-2</v>
       </c>
-      <c r="AJ34" s="7">
+      <c r="AJ57" s="7">
         <f t="shared" si="143"/>
         <v>8.8645378302204439E-2</v>
       </c>
-      <c r="AK34" s="7">
+      <c r="AK57" s="7">
         <f t="shared" si="143"/>
         <v>8.9252039775281691E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:41" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="14" t="s">
+    <row r="60" spans="2:41" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="N37" s="14">
+      <c r="N60" s="14">
         <v>162861</v>
       </c>
-      <c r="P37" s="14">
+      <c r="P60" s="14">
         <v>167139</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
+    <row r="62" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="P39" s="15">
-        <f>Main!D9/Model!P37</f>
+      <c r="P62" s="15">
+        <f>Main!D9/Model!P60</f>
         <v>1.556568664405076</v>
       </c>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
+    <row r="63" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="P40" s="7">
-        <f>P37/Main!D9-1</f>
+      <c r="P63" s="7">
+        <f>P60/Main!D9-1</f>
         <v>-0.35756126737768923</v>
       </c>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="P41" s="7"/>
+    <row r="64" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="P64" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7807,4 +9238,16 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{292D4505-608F-421A-97B1-56F07D46F9CD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="8.88671875" style="13"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Financial Analysis/RTX.xlsx
+++ b/Financial Analysis/RTX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B2BACD7-3761-4F37-BA75-09A00F94E5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C256E6-1362-403C-89B4-DA773B7A150D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4DC2FBA0-6E3D-459B-9C6A-21AC42B1058B}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +37,7 @@
     <author>Anton Mniszek</author>
   </authors>
   <commentList>
-    <comment ref="V36" authorId="0" shapeId="0" xr:uid="{E96EA7C2-9517-4C2A-93C8-3EFDE14F9423}">
+    <comment ref="Z40" authorId="0" shapeId="0" xr:uid="{E96EA7C2-9517-4C2A-93C8-3EFDE14F9423}">
       <text>
         <r>
           <rPr>
@@ -61,7 +61,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W38" authorId="0" shapeId="0" xr:uid="{937DA12A-65A9-4053-ABBD-DC872F223AF8}">
+    <comment ref="AA42" authorId="0" shapeId="0" xr:uid="{937DA12A-65A9-4053-ABBD-DC872F223AF8}">
       <text>
         <r>
           <rPr>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="192">
   <si>
     <t>RTX</t>
   </si>
@@ -1046,7 +1046,22 @@
     <t>Raytheon y/y</t>
   </si>
   <si>
-    <t>Overvalued</t>
+    <t>Backlog</t>
+  </si>
+  <si>
+    <t>Collins Backlog %</t>
+  </si>
+  <si>
+    <t>P&amp;W Backlog %</t>
+  </si>
+  <si>
+    <t>Raytheon Backlog %</t>
+  </si>
+  <si>
+    <t>Q425 8K</t>
+  </si>
+  <si>
+    <t>Heavily overvalued</t>
   </si>
 </sst>
 </file>
@@ -1058,7 +1073,7 @@
     <numFmt numFmtId="165" formatCode="0.0\x"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1111,6 +1126,15 @@
     <font>
       <b/>
       <u/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -1213,7 +1237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1271,6 +1295,13 @@
     <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1415,7 +1446,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$50</c:f>
+              <c:f>Model!$B$54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1494,7 +1525,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$C$50:$P$50</c:f>
+              <c:f>Model!$C$54:$P$54</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="14"/>
@@ -1537,7 +1568,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$51</c:f>
+              <c:f>Model!$B$55</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1616,7 +1647,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$C$51:$P$51</c:f>
+              <c:f>Model!$C$55:$P$55</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="14"/>
@@ -1918,7 +1949,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$26</c:f>
+              <c:f>Model!$B$30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1991,7 +2022,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Model!$C$26:$P$26</c:f>
+              <c:f>Model!$C$30:$P$30</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="14"/>
@@ -2052,7 +2083,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$27</c:f>
+              <c:f>Model!$B$31</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2125,7 +2156,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Model!$C$27:$P$27</c:f>
+              <c:f>Model!$C$31:$P$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="14"/>
@@ -3494,15 +3525,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
+      <xdr:col>31</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>31</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3518,8 +3549,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16581120" y="7620"/>
-          <a:ext cx="0" cy="7780020"/>
+          <a:off x="19629120" y="7620"/>
+          <a:ext cx="0" cy="13449300"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3544,15 +3575,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>53340</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3568,8 +3599,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11117580" y="0"/>
-          <a:ext cx="0" cy="12176760"/>
+          <a:off x="11704320" y="0"/>
+          <a:ext cx="0" cy="12908280"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -19042,7 +19073,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A44D8AC4-127D-4D88-A9CD-05B4B0D26444}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A44D8AC4-127D-4D88-A9CD-05B4B0D26444}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B3:F59" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField axis="axisRow" showAll="0">
@@ -19709,7 +19740,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED3AC179-4CC4-4BFB-BB5F-20A759FB583E}">
   <dimension ref="B1:J52"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="8.88671875" style="1"/>
     <col min="5" max="7" width="12.6640625" style="8" customWidth="1"/>
@@ -19746,17 +19777,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="9">
-        <v>178.65</v>
+        <v>200.93</v>
       </c>
       <c r="E3" s="10">
-        <v>45955</v>
+        <v>46053</v>
       </c>
       <c r="F3" s="10">
         <f ca="1">TODAY()</f>
-        <v>45955</v>
+        <v>46053</v>
       </c>
       <c r="G3" s="10">
-        <v>46074</v>
+        <v>46140</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
@@ -19769,11 +19800,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="3">
-        <f>1343.1</f>
-        <v>1343.1</v>
+        <f>1344.9</f>
+        <v>1344.9</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="18"/>
@@ -19785,7 +19816,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>239944.815</v>
+        <v>270230.75700000004</v>
       </c>
       <c r="E5" s="11"/>
       <c r="I5" s="13" t="s">
@@ -19797,11 +19828,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="3">
-        <f>5966</f>
-        <v>5966</v>
+        <f>7435</f>
+        <v>7435</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H6" s="1"/>
       <c r="J6" s="1"/>
@@ -19811,11 +19842,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="3">
-        <f>215+584+38260</f>
-        <v>39059</v>
+        <f>204+3412+34288</f>
+        <v>37904</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H7" s="1"/>
       <c r="J7" s="1"/>
@@ -19826,7 +19857,7 @@
       </c>
       <c r="D8" s="3">
         <f>D6-D7</f>
-        <v>-33093</v>
+        <v>-30469</v>
       </c>
       <c r="E8" s="11"/>
       <c r="H8" s="1"/>
@@ -19838,7 +19869,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>273037.815</v>
+        <v>300699.75700000004</v>
       </c>
       <c r="E9" s="11"/>
     </row>
@@ -20034,18 +20065,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37BCCFEA-4609-4B74-A80E-9BDBF53DBD8A}">
-  <dimension ref="B2:EE68"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:EI72"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="19.109375" style="1" customWidth="1"/>
-    <col min="3" max="39" width="8.88671875" style="1"/>
-    <col min="40" max="40" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="17.109375" style="1" customWidth="1"/>
-    <col min="42" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="43" width="8.88671875" style="1"/>
+    <col min="44" max="44" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="17.109375" style="1" customWidth="1"/>
+    <col min="46" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
@@ -20094,59 +20125,63 @@
       <c r="R2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="U2" s="1">
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="Y2" s="1">
         <v>2019</v>
       </c>
-      <c r="V2" s="1">
+      <c r="Z2" s="1">
         <v>2020</v>
       </c>
-      <c r="W2" s="1">
+      <c r="AA2" s="1">
         <v>2021</v>
       </c>
-      <c r="X2" s="1">
+      <c r="AB2" s="1">
         <v>2022</v>
       </c>
-      <c r="Y2" s="1">
+      <c r="AC2" s="1">
         <v>2023</v>
       </c>
-      <c r="Z2" s="1">
+      <c r="AD2" s="1">
         <v>2024</v>
       </c>
-      <c r="AA2" s="1">
+      <c r="AE2" s="1">
         <v>2025</v>
       </c>
-      <c r="AB2" s="1">
+      <c r="AF2" s="1">
         <v>2026</v>
       </c>
-      <c r="AC2" s="1">
+      <c r="AG2" s="1">
         <v>2027</v>
       </c>
-      <c r="AD2" s="1">
+      <c r="AH2" s="1">
         <v>2028</v>
       </c>
-      <c r="AE2" s="1">
+      <c r="AI2" s="1">
         <v>2029</v>
       </c>
-      <c r="AF2" s="1">
+      <c r="AJ2" s="1">
         <v>2030</v>
       </c>
-      <c r="AG2" s="1">
+      <c r="AK2" s="1">
         <v>2031</v>
       </c>
-      <c r="AH2" s="1">
+      <c r="AL2" s="1">
         <v>2032</v>
       </c>
-      <c r="AI2" s="1">
+      <c r="AM2" s="1">
         <v>2033</v>
       </c>
-      <c r="AJ2" s="1">
+      <c r="AN2" s="1">
         <v>2034</v>
       </c>
-      <c r="AK2" s="1">
+      <c r="AO2" s="1">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>106</v>
       </c>
@@ -20166,17 +20201,21 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
-      <c r="X3" s="3">
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="AB3" s="3">
         <v>30317</v>
       </c>
-      <c r="Y3" s="3">
+      <c r="AC3" s="3">
         <v>31628</v>
       </c>
-      <c r="Z3" s="3">
+      <c r="AD3" s="3">
         <v>32246</v>
       </c>
     </row>
-    <row r="4" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>108</v>
       </c>
@@ -20196,20 +20235,24 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
-      <c r="X4" s="7">
-        <f>X3/X28</f>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="AB4" s="7">
+        <f>AB3/AB32</f>
         <v>0.45199332080985183</v>
       </c>
-      <c r="Y4" s="7">
-        <f>Y3/Y28</f>
+      <c r="AC4" s="7">
+        <f>AC3/AC32</f>
         <v>0.45890887986070805</v>
       </c>
-      <c r="Z4" s="7">
-        <f>Z3/Z28</f>
+      <c r="AD4" s="7">
+        <f>AD3/AD32</f>
         <v>0.39939062151651017</v>
       </c>
     </row>
-    <row r="5" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>107</v>
       </c>
@@ -20229,17 +20272,21 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
-      <c r="X5" s="3">
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="AB5" s="3">
         <v>25884</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="AC5" s="3">
         <v>29440</v>
       </c>
-      <c r="Z5" s="3">
+      <c r="AD5" s="3">
         <v>34651</v>
       </c>
     </row>
-    <row r="6" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>109</v>
       </c>
@@ -20259,20 +20306,24 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
-      <c r="X6" s="7">
-        <f>X5/X28</f>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="AB6" s="7">
+        <f>AB5/AB32</f>
         <v>0.38590213793720368</v>
       </c>
-      <c r="Y6" s="7">
-        <f>Y5/Y28</f>
+      <c r="AC6" s="7">
+        <f>AC5/AC32</f>
         <v>0.42716192687173532</v>
       </c>
-      <c r="Z6" s="7">
-        <f>Z5/Z28</f>
+      <c r="AD6" s="7">
+        <f>AD5/AD32</f>
         <v>0.42917832990661153</v>
       </c>
     </row>
-    <row r="7" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -20289,11 +20340,15 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="7"/>
-    </row>
-    <row r="8" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="AB7" s="7"/>
+      <c r="AC7" s="7"/>
+      <c r="AD7" s="7"/>
+    </row>
+    <row r="8" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>110</v>
       </c>
@@ -20313,13 +20368,17 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="3">
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="AB8" s="7"/>
+      <c r="AC8" s="7"/>
+      <c r="AD8" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="9" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -20336,8 +20395,12 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
-    </row>
-    <row r="10" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+    </row>
+    <row r="10" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>118</v>
       </c>
@@ -20352,21 +20415,35 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
+      <c r="N10" s="29">
+        <v>93000</v>
+      </c>
+      <c r="O10" s="29">
+        <v>92000</v>
+      </c>
+      <c r="P10" s="29">
+        <v>92000</v>
+      </c>
       <c r="Q10" s="29">
         <v>103000</v>
       </c>
       <c r="R10" s="2"/>
-      <c r="Y10" s="3">
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="AC10" s="3">
         <v>78000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AD10" s="3">
         <v>93000</v>
       </c>
-    </row>
-    <row r="11" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="AE10" s="31">
+        <f>Q10</f>
+        <v>103000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>119</v>
       </c>
@@ -20381,44 +20458,84 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
+      <c r="N11" s="29">
+        <v>125000</v>
+      </c>
+      <c r="O11" s="29">
+        <v>125000</v>
+      </c>
+      <c r="P11" s="29">
+        <v>144000</v>
+      </c>
       <c r="Q11" s="29">
         <v>148000</v>
       </c>
       <c r="R11" s="2"/>
-      <c r="Y11" s="3">
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="AC11" s="3">
         <v>118000</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="AD11" s="3">
         <v>125000</v>
       </c>
-    </row>
-    <row r="12" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-    </row>
-    <row r="13" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="AE11" s="31">
+        <f>Q11</f>
+        <v>148000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:41" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="30">
+        <f>SUM(N10:N11)</f>
+        <v>218000</v>
+      </c>
+      <c r="O12" s="30">
+        <f>SUM(O10:O11)</f>
+        <v>217000</v>
+      </c>
+      <c r="P12" s="30">
+        <f>SUM(P10:P11)</f>
+        <v>236000</v>
+      </c>
+      <c r="Q12" s="30">
+        <f>SUM(Q10:Q11)</f>
+        <v>251000</v>
+      </c>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
+      <c r="T12" s="22"/>
+      <c r="U12" s="22"/>
+      <c r="V12" s="22"/>
+      <c r="AC12" s="5">
+        <f>SUM(AC10:AC11)</f>
+        <v>196000</v>
+      </c>
+      <c r="AD12" s="5">
+        <f>SUM(AD10:AD11)</f>
+        <v>218000</v>
+      </c>
+      <c r="AE12" s="33">
+        <f>SUM(AE10:AE11)</f>
+        <v>251000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -20433,18 +20550,18 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
-      <c r="Q13" s="29"/>
+      <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
-      <c r="Y13" s="3">
-        <v>30000</v>
-      </c>
-      <c r="Z13" s="3">
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="14" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="AC13" s="3"/>
+      <c r="AD13" s="3"/>
+    </row>
+    <row r="14" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -20460,18 +20577,28 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
+      <c r="Q14" s="29"/>
       <c r="R14" s="2"/>
-      <c r="Y14" s="3">
-        <v>114000</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>119000</v>
-      </c>
-    </row>
-    <row r="15" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="AA14" s="7"/>
+      <c r="AB14" s="7"/>
+      <c r="AC14" s="3">
+        <v>30000</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>36000</v>
+      </c>
+      <c r="AE14" s="31">
+        <f>AE20*0.16</f>
+        <v>40160</v>
+      </c>
+    </row>
+    <row r="15" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -20489,50 +20616,63 @@
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
-      <c r="Y15" s="3">
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="7"/>
+      <c r="AC15" s="3">
+        <v>114000</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>119000</v>
+      </c>
+      <c r="AE15" s="31">
+        <f>AE20*0.56</f>
+        <v>140560</v>
+      </c>
+    </row>
+    <row r="16" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="7"/>
+      <c r="AC16" s="3">
         <v>52000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AD16" s="3">
         <v>63000</v>
       </c>
-    </row>
-    <row r="16" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="30">
-        <v>251000</v>
-      </c>
-      <c r="R16" s="22"/>
-      <c r="Y16" s="5">
-        <f>SUM(Y13:Y15)</f>
-        <v>196000</v>
-      </c>
-      <c r="Z16" s="5">
-        <f>SUM(Z13:Z15)</f>
-        <v>218000</v>
-      </c>
-      <c r="AA16" s="30">
-        <v>251000</v>
-      </c>
-    </row>
-    <row r="17" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="AE16" s="31">
+        <f>AE20*0.28</f>
+        <v>70280</v>
+      </c>
+    </row>
+    <row r="17" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -20550,14 +20690,28 @@
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
-      <c r="Z17" s="7"/>
-      <c r="AA17" s="7">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="18" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="7"/>
+      <c r="AC17" s="7">
+        <f>AC14/AC$20</f>
+        <v>0.15306122448979592</v>
+      </c>
+      <c r="AD17" s="7">
+        <f t="shared" ref="AD17:AE19" si="0">AD14/AD$20</f>
+        <v>0.16513761467889909</v>
+      </c>
+      <c r="AE17" s="32">
+        <f t="shared" si="0"/>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="18" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>105</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -20575,13 +20729,29 @@
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
-      <c r="Z18" s="7"/>
-      <c r="AA18" s="3">
-        <f>Z16*AA17</f>
-        <v>54500</v>
-      </c>
-    </row>
-    <row r="19" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="AA18" s="7"/>
+      <c r="AB18" s="7"/>
+      <c r="AC18" s="7">
+        <f t="shared" ref="AC18:AC19" si="1">AC15/AC$20</f>
+        <v>0.58163265306122447</v>
+      </c>
+      <c r="AD18" s="7">
+        <f t="shared" si="0"/>
+        <v>0.54587155963302747</v>
+      </c>
+      <c r="AE18" s="32">
+        <f t="shared" si="0"/>
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -20598,44 +20768,70 @@
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
-    </row>
-    <row r="20" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="29">
-        <v>7075</v>
-      </c>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29">
-        <v>7621</v>
-      </c>
-      <c r="R20" s="2"/>
-      <c r="X20" s="3">
-        <v>23052</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>26253</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>28284</v>
-      </c>
-    </row>
-    <row r="21" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="AA19" s="7"/>
+      <c r="AB19" s="7"/>
+      <c r="AC19" s="7">
+        <f t="shared" si="1"/>
+        <v>0.26530612244897961</v>
+      </c>
+      <c r="AD19" s="7">
+        <f t="shared" si="0"/>
+        <v>0.28899082568807338</v>
+      </c>
+      <c r="AE19" s="32">
+        <f t="shared" si="0"/>
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="2:41" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="30">
+        <v>217000</v>
+      </c>
+      <c r="P20" s="30">
+        <v>217000</v>
+      </c>
+      <c r="Q20" s="30">
+        <v>251000</v>
+      </c>
+      <c r="R20" s="22"/>
+      <c r="S20" s="22"/>
+      <c r="T20" s="22"/>
+      <c r="U20" s="22"/>
+      <c r="V20" s="22"/>
+      <c r="AC20" s="5">
+        <f>SUM(AC14:AC16)</f>
+        <v>196000</v>
+      </c>
+      <c r="AD20" s="5">
+        <f>SUM(AD14:AD16)</f>
+        <v>218000</v>
+      </c>
+      <c r="AE20" s="34">
+        <v>251000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -20647,29 +20843,24 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
-      <c r="M21" s="29">
-        <v>7239</v>
-      </c>
-      <c r="N21" s="29"/>
-      <c r="O21" s="29"/>
-      <c r="P21" s="29"/>
-      <c r="Q21" s="29">
-        <v>8423</v>
-      </c>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
-      <c r="X21" s="3">
-        <v>20530</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>18296</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>28066</v>
-      </c>
-    </row>
-    <row r="22" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="AD21" s="7"/>
+      <c r="AE21" s="32">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="22" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -20681,30 +20872,24 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
-      <c r="M22" s="29">
-        <v>6386</v>
-      </c>
-      <c r="N22" s="29"/>
-      <c r="O22" s="29"/>
-      <c r="P22" s="29"/>
-      <c r="Q22" s="29">
-        <v>7045</v>
-      </c>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
-      <c r="X22" s="3">
-        <v>25176</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>26350</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>26713</v>
-      </c>
-    </row>
-    <row r="23" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B23" s="1" t="s">
-        <v>112</v>
-      </c>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="31">
+        <f>AD20*AE21</f>
+        <v>54500</v>
+      </c>
+      <c r="AF22" s="3"/>
+    </row>
+    <row r="23" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -20715,66 +20900,63 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
-      <c r="M23" s="29">
-        <v>-611</v>
-      </c>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29">
-        <v>-611</v>
-      </c>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
-      <c r="X23" s="3">
-        <v>-1684</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-1979</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-2325</v>
-      </c>
-    </row>
-    <row r="24" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="30">
-        <f>SUM(M20:M23)</f>
-        <v>20089</v>
-      </c>
-      <c r="N24" s="22"/>
-      <c r="O24" s="22"/>
-      <c r="P24" s="22"/>
-      <c r="Q24" s="30">
-        <f>SUM(Q20:Q23)</f>
-        <v>22478</v>
-      </c>
-      <c r="R24" s="22"/>
-      <c r="X24" s="5">
-        <f>SUM(X20:X23)</f>
-        <v>67074</v>
-      </c>
-      <c r="Y24" s="5">
-        <f>SUM(Y20:Y23)</f>
-        <v>68920</v>
-      </c>
-      <c r="Z24" s="5">
-        <f>SUM(Z20:Z23)</f>
-        <v>80738</v>
-      </c>
-    </row>
-    <row r="25" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+    </row>
+    <row r="24" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="29">
+        <v>7075</v>
+      </c>
+      <c r="N24" s="29">
+        <v>7537</v>
+      </c>
+      <c r="O24" s="29"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="29">
+        <v>7621</v>
+      </c>
+      <c r="R24" s="29">
+        <v>7736</v>
+      </c>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="AB24" s="3">
+        <v>23052</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>26253</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>28284</v>
+      </c>
+    </row>
+    <row r="25" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -20785,4498 +20967,4789 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-    </row>
-    <row r="26" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="M25" s="29">
+        <v>7239</v>
+      </c>
+      <c r="N25" s="29">
+        <v>7569</v>
+      </c>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29">
+        <v>8423</v>
+      </c>
+      <c r="R25" s="29">
+        <v>9496</v>
+      </c>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="AB25" s="3">
+        <v>20530</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>18296</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>28066</v>
+      </c>
+    </row>
+    <row r="26" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="29">
+        <v>6386</v>
+      </c>
+      <c r="N26" s="29">
+        <v>7157</v>
+      </c>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29">
+        <v>7045</v>
+      </c>
+      <c r="R26" s="29">
+        <v>7657</v>
+      </c>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="AB26" s="3">
+        <v>25176</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>26350</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>26713</v>
+      </c>
+    </row>
+    <row r="27" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="29">
+        <v>-611</v>
+      </c>
+      <c r="N27" s="29">
+        <v>-640</v>
+      </c>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29">
+        <v>-611</v>
+      </c>
+      <c r="R27" s="29">
+        <v>-651</v>
+      </c>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="AB27" s="3">
+        <v>-1684</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>-1979</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>-2325</v>
+      </c>
+    </row>
+    <row r="28" spans="2:41" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="30">
+        <f>SUM(M24:M27)</f>
+        <v>20089</v>
+      </c>
+      <c r="N28" s="30">
+        <f>SUM(N24:N27)</f>
+        <v>21623</v>
+      </c>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="30">
+        <f>SUM(Q24:Q27)</f>
+        <v>22478</v>
+      </c>
+      <c r="R28" s="30">
+        <f>SUM(R24:R27)</f>
+        <v>24238</v>
+      </c>
+      <c r="S28" s="22"/>
+      <c r="T28" s="22"/>
+      <c r="U28" s="22"/>
+      <c r="V28" s="22"/>
+      <c r="AB28" s="5">
+        <f>SUM(AB24:AB27)</f>
+        <v>67074</v>
+      </c>
+      <c r="AC28" s="5">
+        <f>SUM(AC24:AC27)</f>
+        <v>68920</v>
+      </c>
+      <c r="AD28" s="5">
+        <f>SUM(AD24:AD27)</f>
+        <v>80738</v>
+      </c>
+    </row>
+    <row r="29" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+    </row>
+    <row r="30" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C30" s="3">
         <v>11862</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D30" s="3">
         <v>12258</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E30" s="3">
         <v>12756</v>
       </c>
-      <c r="F26" s="3">
-        <f>X26-E26-D26-C26</f>
+      <c r="F30" s="3">
+        <f>AB30-E30-D30-C30</f>
         <v>13897</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G30" s="3">
         <v>12787</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H30" s="3">
         <v>13411</v>
       </c>
-      <c r="I26" s="3">
+      <c r="I30" s="3">
         <v>8615</v>
       </c>
-      <c r="J26" s="3">
-        <f>Y26-I26-H26-G26</f>
+      <c r="J30" s="3">
+        <f>AC30-I30-H30-G30</f>
         <v>14758</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K30" s="3">
         <v>14303</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L30" s="3">
         <v>14562</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M30" s="3">
         <v>14708</v>
       </c>
-      <c r="N26" s="3">
-        <f>Z26-M26-L26-K26</f>
+      <c r="N30" s="3">
+        <f>AD30-M30-L30-K30</f>
         <v>16039</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O30" s="3">
         <v>14591</v>
       </c>
-      <c r="P26" s="3">
+      <c r="P30" s="3">
         <v>15551</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q30" s="3">
         <v>16264</v>
       </c>
-      <c r="R26" s="3">
-        <f>N26*1.1</f>
-        <v>17642.900000000001</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="Y30" s="3">
         <v>32998</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Z30" s="3">
         <v>43319</v>
       </c>
-      <c r="W26" s="3">
+      <c r="AA30" s="3">
         <v>49270</v>
       </c>
-      <c r="X26" s="3">
+      <c r="AB30" s="3">
         <v>50773</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AC30" s="3">
         <v>49571</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AD30" s="3">
         <v>59612</v>
       </c>
-      <c r="AA26" s="3">
-        <f>SUM(O26:R26)</f>
-        <v>64048.9</v>
-      </c>
-      <c r="AB26" s="3">
-        <f>AA26*1.08</f>
-        <v>69172.812000000005</v>
-      </c>
-      <c r="AC26" s="3">
-        <f>AB26*1.05</f>
-        <v>72631.452600000004</v>
-      </c>
-      <c r="AD26" s="3">
-        <f>AC26*1.04</f>
-        <v>75536.710704000012</v>
-      </c>
-      <c r="AE26" s="3">
-        <f>AD26*1.03</f>
-        <v>77802.812025120016</v>
-      </c>
-      <c r="AF26" s="3">
-        <f t="shared" ref="AF26:AK26" si="0">AE26*1.02</f>
-        <v>79358.868265622412</v>
-      </c>
-      <c r="AG26" s="3">
-        <f t="shared" si="0"/>
-        <v>80946.045630934866</v>
-      </c>
-      <c r="AH26" s="3">
-        <f t="shared" si="0"/>
-        <v>82564.966543553572</v>
-      </c>
-      <c r="AI26" s="3">
-        <f t="shared" si="0"/>
-        <v>84216.265874424644</v>
-      </c>
-      <c r="AJ26" s="3">
-        <f t="shared" si="0"/>
-        <v>85900.591191913132</v>
-      </c>
-      <c r="AK26" s="3">
-        <f t="shared" si="0"/>
-        <v>87618.603015751403</v>
-      </c>
-    </row>
-    <row r="27" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B27" s="1" t="s">
+      <c r="AE30" s="3"/>
+      <c r="AF30" s="3">
+        <f>AE30*1.08</f>
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <f>AF30*1.05</f>
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <f>AG30*1.04</f>
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <f>AH30*1.03</f>
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="3">
+        <f t="shared" ref="AJ30:AO30" si="2">AI30*1.02</f>
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AN30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C31" s="3">
         <v>3854</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D31" s="3">
         <v>4056</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E31" s="3">
         <v>4195</v>
       </c>
-      <c r="F27" s="3">
-        <f>X27-E27-D27-C27</f>
+      <c r="F31" s="3">
+        <f>AB31-E31-D31-C31</f>
         <v>4196</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G31" s="3">
         <v>4427</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H31" s="3">
         <v>4904</v>
       </c>
-      <c r="I27" s="3">
+      <c r="I31" s="3">
         <v>4849</v>
       </c>
-      <c r="J27" s="3">
-        <f>Y27-I27-H27-G27</f>
+      <c r="J31" s="3">
+        <f>AC31-I31-H31-G31</f>
         <v>5169</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K31" s="3">
         <v>5002</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L31" s="3">
         <v>5159</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M31" s="3">
         <v>5381</v>
       </c>
-      <c r="N27" s="3">
-        <f>Z27-M27-L27-K27</f>
+      <c r="N31" s="3">
+        <f>AD31-M31-L31-K31</f>
         <v>5584</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O31" s="3">
         <v>5715</v>
       </c>
-      <c r="P27" s="3">
+      <c r="P31" s="3">
         <v>6030</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q31" s="3">
         <v>6214</v>
       </c>
-      <c r="R27" s="3">
-        <f>N27*1.16</f>
-        <v>6477.44</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="Y31" s="3">
         <v>12351</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Z31" s="3">
         <v>13268</v>
       </c>
-      <c r="W27" s="3">
+      <c r="AA31" s="3">
         <v>15118</v>
       </c>
-      <c r="X27" s="3">
+      <c r="AB31" s="3">
         <v>16301</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AC31" s="3">
         <v>19349</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AD31" s="3">
         <v>21126</v>
       </c>
-      <c r="AA27" s="3">
-        <f>SUM(O27:R27)</f>
-        <v>24436.44</v>
-      </c>
-      <c r="AB27" s="3">
-        <f>AA27*1.13</f>
-        <v>27613.177199999995</v>
-      </c>
-      <c r="AC27" s="3">
-        <f>AB27*1.09</f>
-        <v>30098.363147999997</v>
-      </c>
-      <c r="AD27" s="3">
-        <f>AC27*1.05</f>
-        <v>31603.281305399996</v>
-      </c>
-      <c r="AE27" s="3">
-        <f>AD27*1.04</f>
-        <v>32867.412557616</v>
-      </c>
-      <c r="AF27" s="3">
-        <f>AE27*1.03</f>
-        <v>33853.434934344485</v>
-      </c>
-      <c r="AG27" s="3">
-        <f t="shared" ref="AG27:AK27" si="1">AF27*1.03</f>
-        <v>34869.037982374823</v>
-      </c>
-      <c r="AH27" s="3">
-        <f t="shared" si="1"/>
-        <v>35915.109121846072</v>
-      </c>
-      <c r="AI27" s="3">
-        <f t="shared" si="1"/>
-        <v>36992.562395501453</v>
-      </c>
-      <c r="AJ27" s="3">
-        <f t="shared" si="1"/>
-        <v>38102.3392673665</v>
-      </c>
-      <c r="AK27" s="3">
-        <f t="shared" si="1"/>
-        <v>39245.409445387493</v>
-      </c>
-    </row>
-    <row r="28" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="4" t="s">
+      <c r="AE31" s="3"/>
+      <c r="AF31" s="3">
+        <f>AE31*1.13</f>
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <f>AF31*1.09</f>
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <f>AG31*1.05</f>
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <f>AH31*1.04</f>
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="3">
+        <f>AI31*1.03</f>
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <f t="shared" ref="AK31:AO31" si="3">AJ31*1.03</f>
+        <v>0</v>
+      </c>
+      <c r="AL31" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM31" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN31" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:41" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="5">
-        <f t="shared" ref="C28:P28" si="2">C26+C27</f>
+      <c r="C32" s="5">
+        <f t="shared" ref="C32:P32" si="4">C30+C31</f>
         <v>15716</v>
       </c>
-      <c r="D28" s="5">
-        <f t="shared" si="2"/>
+      <c r="D32" s="5">
+        <f t="shared" si="4"/>
         <v>16314</v>
       </c>
-      <c r="E28" s="5">
-        <f t="shared" si="2"/>
+      <c r="E32" s="5">
+        <f t="shared" si="4"/>
         <v>16951</v>
       </c>
-      <c r="F28" s="5">
-        <f t="shared" si="2"/>
+      <c r="F32" s="5">
+        <f t="shared" si="4"/>
         <v>18093</v>
       </c>
-      <c r="G28" s="5">
-        <f t="shared" si="2"/>
+      <c r="G32" s="5">
+        <f t="shared" si="4"/>
         <v>17214</v>
       </c>
-      <c r="H28" s="5">
-        <f t="shared" si="2"/>
+      <c r="H32" s="5">
+        <f t="shared" si="4"/>
         <v>18315</v>
       </c>
-      <c r="I28" s="5">
-        <f t="shared" si="2"/>
+      <c r="I32" s="5">
+        <f t="shared" si="4"/>
         <v>13464</v>
       </c>
-      <c r="J28" s="5">
-        <f t="shared" si="2"/>
+      <c r="J32" s="5">
+        <f t="shared" si="4"/>
         <v>19927</v>
       </c>
-      <c r="K28" s="5">
-        <f t="shared" si="2"/>
+      <c r="K32" s="5">
+        <f t="shared" si="4"/>
         <v>19305</v>
       </c>
-      <c r="L28" s="5">
-        <f t="shared" si="2"/>
+      <c r="L32" s="5">
+        <f t="shared" si="4"/>
         <v>19721</v>
       </c>
-      <c r="M28" s="5">
-        <f t="shared" si="2"/>
+      <c r="M32" s="5">
+        <f t="shared" si="4"/>
         <v>20089</v>
       </c>
-      <c r="N28" s="5">
-        <f t="shared" si="2"/>
+      <c r="N32" s="5">
+        <f t="shared" si="4"/>
         <v>21623</v>
       </c>
-      <c r="O28" s="5">
-        <f t="shared" si="2"/>
+      <c r="O32" s="5">
+        <f t="shared" si="4"/>
         <v>20306</v>
       </c>
-      <c r="P28" s="5">
-        <f t="shared" si="2"/>
+      <c r="P32" s="5">
+        <f t="shared" si="4"/>
         <v>21581</v>
       </c>
-      <c r="Q28" s="5">
+      <c r="Q32" s="5">
         <v>22478</v>
       </c>
-      <c r="R28" s="5">
-        <f t="shared" ref="R28" si="3">R26+R27</f>
-        <v>24120.34</v>
-      </c>
-      <c r="U28" s="5">
-        <f t="shared" ref="U28:AK28" si="4">U26+U27</f>
+      <c r="R32" s="5">
+        <f>R28</f>
+        <v>24238</v>
+      </c>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
+      <c r="Y32" s="5">
+        <f t="shared" ref="Y32:AO32" si="5">Y30+Y31</f>
         <v>45349</v>
       </c>
-      <c r="V28" s="5">
-        <f t="shared" si="4"/>
+      <c r="Z32" s="5">
+        <f t="shared" si="5"/>
         <v>56587</v>
       </c>
-      <c r="W28" s="5">
-        <f t="shared" si="4"/>
+      <c r="AA32" s="5">
+        <f t="shared" si="5"/>
         <v>64388</v>
       </c>
-      <c r="X28" s="5">
-        <f t="shared" si="4"/>
+      <c r="AB32" s="5">
+        <f t="shared" si="5"/>
         <v>67074</v>
       </c>
-      <c r="Y28" s="5">
-        <f t="shared" si="4"/>
+      <c r="AC32" s="5">
+        <f t="shared" si="5"/>
         <v>68920</v>
       </c>
-      <c r="Z28" s="5">
-        <f t="shared" si="4"/>
+      <c r="AD32" s="5">
+        <f t="shared" si="5"/>
         <v>80738</v>
       </c>
-      <c r="AA28" s="5">
-        <f t="shared" si="4"/>
-        <v>88485.34</v>
-      </c>
-      <c r="AB28" s="5">
-        <f t="shared" si="4"/>
-        <v>96785.989199999996</v>
-      </c>
-      <c r="AC28" s="5">
-        <f t="shared" si="4"/>
-        <v>102729.81574799999</v>
-      </c>
-      <c r="AD28" s="5">
-        <f t="shared" si="4"/>
-        <v>107139.99200940001</v>
-      </c>
-      <c r="AE28" s="5">
-        <f t="shared" si="4"/>
-        <v>110670.22458273602</v>
-      </c>
-      <c r="AF28" s="5">
-        <f t="shared" si="4"/>
-        <v>113212.3031999669</v>
-      </c>
-      <c r="AG28" s="5">
-        <f t="shared" si="4"/>
-        <v>115815.08361330969</v>
-      </c>
-      <c r="AH28" s="5">
-        <f t="shared" si="4"/>
-        <v>118480.07566539964</v>
-      </c>
-      <c r="AI28" s="5">
-        <f t="shared" si="4"/>
-        <v>121208.8282699261</v>
-      </c>
-      <c r="AJ28" s="5">
-        <f t="shared" si="4"/>
-        <v>124002.93045927963</v>
-      </c>
-      <c r="AK28" s="5">
-        <f t="shared" si="4"/>
-        <v>126864.01246113889</v>
-      </c>
-    </row>
-    <row r="29" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B29" s="1" t="s">
+      <c r="AE32" s="5">
+        <f>SUM(O32:R32)</f>
+        <v>88603</v>
+      </c>
+      <c r="AF32" s="5">
+        <f>AE32*1.06</f>
+        <v>93919.180000000008</v>
+      </c>
+      <c r="AG32" s="5">
+        <f>AF32*1.05</f>
+        <v>98615.13900000001</v>
+      </c>
+      <c r="AH32" s="5">
+        <f>AG32*1.04</f>
+        <v>102559.74456000002</v>
+      </c>
+      <c r="AI32" s="5">
+        <f>AH32*1.04</f>
+        <v>106662.13434240002</v>
+      </c>
+      <c r="AJ32" s="5">
+        <f>AI32*1.03</f>
+        <v>109861.99837267202</v>
+      </c>
+      <c r="AK32" s="5">
+        <f>AJ32*1.03</f>
+        <v>113157.85832385218</v>
+      </c>
+      <c r="AL32" s="5">
+        <f t="shared" ref="AL32:AO32" si="6">AK32*1.02</f>
+        <v>115421.01549032923</v>
+      </c>
+      <c r="AM32" s="5">
+        <f t="shared" si="6"/>
+        <v>117729.43580013582</v>
+      </c>
+      <c r="AN32" s="5">
+        <f t="shared" si="6"/>
+        <v>120084.02451613854</v>
+      </c>
+      <c r="AO32" s="5">
+        <f t="shared" si="6"/>
+        <v>122485.70500646131</v>
+      </c>
+    </row>
+    <row r="33" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C33" s="3">
         <v>9820</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D33" s="3">
         <v>10040</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E33" s="3">
         <v>10493</v>
       </c>
-      <c r="F29" s="3">
-        <f t="shared" ref="F29:F30" si="5">X29-E29-D29-C29</f>
+      <c r="F33" s="3">
+        <f t="shared" ref="F33:F34" si="7">AB33-E33-D33-C33</f>
         <v>11574</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G33" s="3">
         <v>10700</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H33" s="3">
         <v>11089</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I33" s="3">
         <v>9289</v>
       </c>
-      <c r="J29" s="3">
-        <f t="shared" ref="J29:J30" si="6">Y29-I29-H29-G29</f>
+      <c r="J33" s="3">
+        <f t="shared" ref="J33:J34" si="8">AC33-I33-H33-G33</f>
         <v>12347</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K33" s="3">
         <v>12216</v>
       </c>
-      <c r="L29" s="3">
+      <c r="L33" s="3">
         <v>12625</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M33" s="3">
         <v>12336</v>
       </c>
-      <c r="N29" s="3">
-        <f t="shared" ref="N29:N30" si="7">Z29-M29-L29-K29</f>
+      <c r="N33" s="3">
+        <f t="shared" ref="N33:N34" si="9">AD33-M33-L33-K33</f>
         <v>13591</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O33" s="3">
         <v>12283</v>
       </c>
-      <c r="P29" s="3">
+      <c r="P33" s="3">
         <v>12989</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q33" s="3">
         <v>13593</v>
       </c>
-      <c r="R29" s="3">
-        <f>R26*0.84</f>
-        <v>14820.036</v>
-      </c>
-      <c r="U29" s="3">
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3"/>
+      <c r="Y33" s="3">
         <v>26910</v>
       </c>
-      <c r="V29" s="3">
+      <c r="Z33" s="3">
         <v>38137</v>
       </c>
-      <c r="W29" s="3">
+      <c r="AA33" s="3">
         <v>41095</v>
       </c>
-      <c r="X29" s="3">
+      <c r="AB33" s="3">
         <v>41927</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AC33" s="3">
         <v>43425</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AD33" s="3">
         <v>50768</v>
       </c>
-      <c r="AA29" s="3">
-        <f t="shared" ref="AA29:AA30" si="8">SUM(O29:R29)</f>
-        <v>53685.036</v>
-      </c>
-      <c r="AB29" s="3">
-        <f>AB26*0.84</f>
-        <v>58105.162080000002</v>
-      </c>
-      <c r="AC29" s="3">
-        <f t="shared" ref="AC29:AK29" si="9">AC26*0.84</f>
-        <v>61010.420184000002</v>
-      </c>
-      <c r="AD29" s="3">
+      <c r="AE33" s="3"/>
+      <c r="AF33" s="3">
+        <f>AF30*0.84</f>
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3">
+        <f t="shared" ref="AG33:AO33" si="10">AG30*0.84</f>
+        <v>0</v>
+      </c>
+      <c r="AH33" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AK33" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AL33" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AM33" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AN33" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AO33" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="3">
+        <v>2740</v>
+      </c>
+      <c r="D34" s="3">
+        <v>2816</v>
+      </c>
+      <c r="E34" s="3">
+        <v>2971</v>
+      </c>
+      <c r="F34" s="3">
+        <f t="shared" si="7"/>
+        <v>2952</v>
+      </c>
+      <c r="G34" s="3">
+        <v>2945</v>
+      </c>
+      <c r="H34" s="3">
+        <v>3429</v>
+      </c>
+      <c r="I34" s="3">
+        <v>3461</v>
+      </c>
+      <c r="J34" s="3">
+        <f t="shared" si="8"/>
+        <v>3571</v>
+      </c>
+      <c r="K34" s="3">
+        <v>3528</v>
+      </c>
+      <c r="L34" s="3">
+        <v>3516</v>
+      </c>
+      <c r="M34" s="3">
+        <v>3719</v>
+      </c>
+      <c r="N34" s="3">
         <f t="shared" si="9"/>
-        <v>63450.836991360011</v>
-      </c>
-      <c r="AE29" s="3">
-        <f t="shared" si="9"/>
-        <v>65354.362101100814</v>
-      </c>
-      <c r="AF29" s="3">
-        <f t="shared" si="9"/>
-        <v>66661.449343122818</v>
-      </c>
-      <c r="AG29" s="3">
-        <f t="shared" si="9"/>
-        <v>67994.678329985283</v>
-      </c>
-      <c r="AH29" s="3">
-        <f t="shared" si="9"/>
-        <v>69354.571896584996</v>
-      </c>
-      <c r="AI29" s="3">
-        <f t="shared" si="9"/>
-        <v>70741.663334516692</v>
-      </c>
-      <c r="AJ29" s="3">
-        <f t="shared" si="9"/>
-        <v>72156.496601207022</v>
-      </c>
-      <c r="AK29" s="3">
-        <f t="shared" si="9"/>
-        <v>73599.626533231174</v>
-      </c>
-    </row>
-    <row r="30" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="3">
-        <v>2740</v>
-      </c>
-      <c r="D30" s="3">
-        <v>2816</v>
-      </c>
-      <c r="E30" s="3">
-        <v>2971</v>
-      </c>
-      <c r="F30" s="3">
-        <f t="shared" si="5"/>
-        <v>2952</v>
-      </c>
-      <c r="G30" s="3">
-        <v>2945</v>
-      </c>
-      <c r="H30" s="3">
-        <v>3429</v>
-      </c>
-      <c r="I30" s="3">
-        <v>3461</v>
-      </c>
-      <c r="J30" s="3">
-        <f t="shared" si="6"/>
-        <v>3571</v>
-      </c>
-      <c r="K30" s="3">
-        <v>3528</v>
-      </c>
-      <c r="L30" s="3">
-        <v>3516</v>
-      </c>
-      <c r="M30" s="3">
-        <v>3719</v>
-      </c>
-      <c r="N30" s="3">
-        <f t="shared" si="7"/>
         <v>3797</v>
       </c>
-      <c r="O30" s="3">
+      <c r="O34" s="3">
         <v>3907</v>
       </c>
-      <c r="P30" s="3">
+      <c r="P34" s="3">
         <v>4216</v>
       </c>
-      <c r="Q30" s="3">
+      <c r="Q34" s="3">
         <v>4305</v>
       </c>
-      <c r="R30" s="3">
-        <f>R27*0.69</f>
-        <v>4469.4335999999994</v>
-      </c>
-      <c r="U30" s="3">
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3"/>
+      <c r="Y34" s="3">
         <v>7688</v>
       </c>
-      <c r="V30" s="3">
+      <c r="Z34" s="3">
         <v>9919</v>
       </c>
-      <c r="W30" s="3">
+      <c r="AA34" s="3">
         <v>10802</v>
       </c>
-      <c r="X30" s="3">
+      <c r="AB34" s="3">
         <v>11479</v>
       </c>
-      <c r="Y30" s="3">
+      <c r="AC34" s="3">
         <v>13406</v>
       </c>
-      <c r="Z30" s="3">
+      <c r="AD34" s="3">
         <v>14560</v>
       </c>
-      <c r="AA30" s="3">
-        <f t="shared" si="8"/>
-        <v>16897.4336</v>
-      </c>
-      <c r="AB30" s="3">
-        <f t="shared" ref="AB30:AK30" si="10">AB27*0.69</f>
-        <v>19053.092267999993</v>
-      </c>
-      <c r="AC30" s="3">
-        <f t="shared" si="10"/>
-        <v>20767.870572119995</v>
-      </c>
-      <c r="AD30" s="3">
-        <f t="shared" si="10"/>
-        <v>21806.264100725995</v>
-      </c>
-      <c r="AE30" s="3">
-        <f t="shared" si="10"/>
-        <v>22678.514664755039</v>
-      </c>
-      <c r="AF30" s="3">
-        <f t="shared" si="10"/>
-        <v>23358.870104697693</v>
-      </c>
-      <c r="AG30" s="3">
-        <f t="shared" si="10"/>
-        <v>24059.636207838626</v>
-      </c>
-      <c r="AH30" s="3">
-        <f t="shared" si="10"/>
-        <v>24781.425294073786</v>
-      </c>
-      <c r="AI30" s="3">
-        <f t="shared" si="10"/>
-        <v>25524.868052895999</v>
-      </c>
-      <c r="AJ30" s="3">
-        <f t="shared" si="10"/>
-        <v>26290.614094482884</v>
-      </c>
-      <c r="AK30" s="3">
-        <f t="shared" si="10"/>
-        <v>27079.332517317369</v>
-      </c>
-    </row>
-    <row r="31" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B31" s="1" t="s">
+      <c r="AE34" s="3"/>
+      <c r="AF34" s="3">
+        <f t="shared" ref="AF34:AO34" si="11">AF31*0.69</f>
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AL34" s="3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AM34" s="3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AN34" s="3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="3">
-        <f t="shared" ref="C31:P31" si="11">C29+C30</f>
+      <c r="C35" s="3">
+        <f t="shared" ref="C35:P35" si="12">C33+C34</f>
         <v>12560</v>
       </c>
-      <c r="D31" s="3">
-        <f t="shared" si="11"/>
+      <c r="D35" s="3">
+        <f t="shared" si="12"/>
         <v>12856</v>
       </c>
-      <c r="E31" s="3">
-        <f t="shared" si="11"/>
+      <c r="E35" s="3">
+        <f t="shared" si="12"/>
         <v>13464</v>
       </c>
-      <c r="F31" s="3">
-        <f t="shared" si="11"/>
+      <c r="F35" s="3">
+        <f t="shared" si="12"/>
         <v>14526</v>
       </c>
-      <c r="G31" s="3">
-        <f t="shared" si="11"/>
+      <c r="G35" s="3">
+        <f t="shared" si="12"/>
         <v>13645</v>
       </c>
-      <c r="H31" s="3">
-        <f t="shared" si="11"/>
+      <c r="H35" s="3">
+        <f t="shared" si="12"/>
         <v>14518</v>
       </c>
-      <c r="I31" s="3">
-        <f t="shared" si="11"/>
+      <c r="I35" s="3">
+        <f t="shared" si="12"/>
         <v>12750</v>
       </c>
-      <c r="J31" s="3">
-        <f t="shared" si="11"/>
+      <c r="J35" s="3">
+        <f t="shared" si="12"/>
         <v>15918</v>
       </c>
-      <c r="K31" s="3">
-        <f t="shared" si="11"/>
+      <c r="K35" s="3">
+        <f t="shared" si="12"/>
         <v>15744</v>
       </c>
-      <c r="L31" s="3">
-        <f t="shared" si="11"/>
+      <c r="L35" s="3">
+        <f t="shared" si="12"/>
         <v>16141</v>
       </c>
-      <c r="M31" s="3">
-        <f t="shared" si="11"/>
+      <c r="M35" s="3">
+        <f t="shared" si="12"/>
         <v>16055</v>
       </c>
-      <c r="N31" s="3">
-        <f t="shared" si="11"/>
+      <c r="N35" s="3">
+        <f t="shared" si="12"/>
         <v>17388</v>
       </c>
-      <c r="O31" s="3">
-        <f t="shared" si="11"/>
+      <c r="O35" s="3">
+        <f t="shared" si="12"/>
         <v>16190</v>
       </c>
-      <c r="P31" s="3">
-        <f t="shared" si="11"/>
+      <c r="P35" s="3">
+        <f t="shared" si="12"/>
         <v>17205</v>
       </c>
-      <c r="Q31" s="3">
+      <c r="Q35" s="3">
         <v>17898</v>
       </c>
-      <c r="R31" s="3">
-        <f t="shared" ref="R31" si="12">R29+R30</f>
-        <v>19289.4696</v>
-      </c>
-      <c r="U31" s="3">
-        <f t="shared" ref="U31:Z31" si="13">U29+U30</f>
+      <c r="R35" s="3">
+        <v>19521</v>
+      </c>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
+      <c r="V35" s="3"/>
+      <c r="Y35" s="3">
+        <f t="shared" ref="Y35:AD35" si="13">Y33+Y34</f>
         <v>34598</v>
       </c>
-      <c r="V31" s="3">
+      <c r="Z35" s="3">
         <f t="shared" si="13"/>
         <v>48056</v>
       </c>
-      <c r="W31" s="3">
+      <c r="AA35" s="3">
         <f t="shared" si="13"/>
         <v>51897</v>
       </c>
-      <c r="X31" s="3">
+      <c r="AB35" s="3">
         <f t="shared" si="13"/>
         <v>53406</v>
       </c>
-      <c r="Y31" s="3">
+      <c r="AC35" s="3">
         <f t="shared" si="13"/>
         <v>56831</v>
       </c>
-      <c r="Z31" s="3">
+      <c r="AD35" s="3">
         <f t="shared" si="13"/>
         <v>65328</v>
       </c>
-      <c r="AA31" s="3">
-        <f t="shared" ref="AA31:AK31" si="14">AA29+AA30</f>
-        <v>70582.469599999997</v>
-      </c>
-      <c r="AB31" s="3">
+      <c r="AE35" s="3">
+        <f>AE32*0.81</f>
+        <v>71768.430000000008</v>
+      </c>
+      <c r="AF35" s="3">
+        <f t="shared" ref="AF35:AO35" si="14">AF32*0.81</f>
+        <v>76074.535800000012</v>
+      </c>
+      <c r="AG35" s="3">
         <f t="shared" si="14"/>
-        <v>77158.254347999988</v>
-      </c>
-      <c r="AC31" s="3">
+        <v>79878.262590000013</v>
+      </c>
+      <c r="AH35" s="3">
         <f t="shared" si="14"/>
-        <v>81778.290756119997</v>
-      </c>
-      <c r="AD31" s="3">
+        <v>83073.393093600025</v>
+      </c>
+      <c r="AI35" s="3">
         <f t="shared" si="14"/>
-        <v>85257.101092085999</v>
-      </c>
-      <c r="AE31" s="3">
+        <v>86396.328817344023</v>
+      </c>
+      <c r="AJ35" s="3">
         <f t="shared" si="14"/>
-        <v>88032.87676585585</v>
-      </c>
-      <c r="AF31" s="3">
+        <v>88988.218681864339</v>
+      </c>
+      <c r="AK35" s="3">
         <f t="shared" si="14"/>
-        <v>90020.319447820511</v>
-      </c>
-      <c r="AG31" s="3">
+        <v>91657.865242320273</v>
+      </c>
+      <c r="AL35" s="3">
         <f t="shared" si="14"/>
-        <v>92054.314537823913</v>
-      </c>
-      <c r="AH31" s="3">
+        <v>93491.022547166678</v>
+      </c>
+      <c r="AM35" s="3">
         <f t="shared" si="14"/>
-        <v>94135.997190658789</v>
-      </c>
-      <c r="AI31" s="3">
+        <v>95360.84299811002</v>
+      </c>
+      <c r="AN35" s="3">
         <f t="shared" si="14"/>
-        <v>96266.531387412688</v>
-      </c>
-      <c r="AJ31" s="3">
+        <v>97268.059858072229</v>
+      </c>
+      <c r="AO35" s="3">
         <f t="shared" si="14"/>
-        <v>98447.110695689902</v>
-      </c>
-      <c r="AK31" s="3">
-        <f t="shared" si="14"/>
-        <v>100678.95905054854</v>
-      </c>
-    </row>
-    <row r="32" spans="2:37" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="4" t="s">
+        <v>99213.421055233674</v>
+      </c>
+    </row>
+    <row r="36" spans="2:139" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="5">
-        <f t="shared" ref="C32:P32" si="15">C28-C31</f>
+      <c r="C36" s="5">
+        <f t="shared" ref="C36:P36" si="15">C32-C35</f>
         <v>3156</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D36" s="5">
         <f t="shared" si="15"/>
         <v>3458</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E36" s="5">
         <f t="shared" si="15"/>
         <v>3487</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F36" s="5">
         <f t="shared" si="15"/>
         <v>3567</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G36" s="5">
         <f t="shared" si="15"/>
         <v>3569</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H36" s="5">
         <f t="shared" si="15"/>
         <v>3797</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I36" s="5">
         <f t="shared" si="15"/>
         <v>714</v>
       </c>
-      <c r="J32" s="5">
+      <c r="J36" s="5">
         <f t="shared" si="15"/>
         <v>4009</v>
       </c>
-      <c r="K32" s="5">
+      <c r="K36" s="5">
         <f t="shared" si="15"/>
         <v>3561</v>
       </c>
-      <c r="L32" s="5">
+      <c r="L36" s="5">
         <f t="shared" si="15"/>
         <v>3580</v>
       </c>
-      <c r="M32" s="5">
+      <c r="M36" s="5">
         <f t="shared" si="15"/>
         <v>4034</v>
       </c>
-      <c r="N32" s="5">
+      <c r="N36" s="5">
         <f t="shared" si="15"/>
         <v>4235</v>
       </c>
-      <c r="O32" s="5">
+      <c r="O36" s="5">
         <f t="shared" si="15"/>
         <v>4116</v>
       </c>
-      <c r="P32" s="5">
+      <c r="P36" s="5">
         <f t="shared" si="15"/>
         <v>4376</v>
       </c>
-      <c r="Q32" s="5">
-        <f t="shared" ref="Q32:R32" si="16">Q28-Q31</f>
+      <c r="Q36" s="5">
+        <f t="shared" ref="Q36:R36" si="16">Q32-Q35</f>
         <v>4580</v>
       </c>
-      <c r="R32" s="5">
+      <c r="R36" s="5">
         <f t="shared" si="16"/>
-        <v>4830.8703999999998</v>
-      </c>
-      <c r="U32" s="5">
-        <f t="shared" ref="U32:Z32" si="17">U28-U31</f>
+        <v>4717</v>
+      </c>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+      <c r="Y36" s="5">
+        <f t="shared" ref="Y36:AD36" si="17">Y32-Y35</f>
         <v>10751</v>
       </c>
-      <c r="V32" s="5">
+      <c r="Z36" s="5">
         <f t="shared" si="17"/>
         <v>8531</v>
       </c>
-      <c r="W32" s="5">
+      <c r="AA36" s="5">
         <f t="shared" si="17"/>
         <v>12491</v>
       </c>
-      <c r="X32" s="5">
+      <c r="AB36" s="5">
         <f t="shared" si="17"/>
         <v>13668</v>
       </c>
-      <c r="Y32" s="5">
+      <c r="AC36" s="5">
         <f t="shared" si="17"/>
         <v>12089</v>
       </c>
-      <c r="Z32" s="5">
+      <c r="AD36" s="5">
         <f t="shared" si="17"/>
         <v>15410</v>
       </c>
-      <c r="AA32" s="5">
-        <f t="shared" ref="AA32:AK32" si="18">AA28-AA31</f>
-        <v>17902.8704</v>
-      </c>
-      <c r="AB32" s="5">
+      <c r="AE36" s="5">
+        <f t="shared" ref="AE36:AO36" si="18">AE32-AE35</f>
+        <v>16834.569999999992</v>
+      </c>
+      <c r="AF36" s="5">
         <f t="shared" si="18"/>
-        <v>19627.734852000009</v>
-      </c>
-      <c r="AC32" s="5">
+        <v>17844.644199999995</v>
+      </c>
+      <c r="AG36" s="5">
         <f t="shared" si="18"/>
-        <v>20951.524991879996</v>
-      </c>
-      <c r="AD32" s="5">
+        <v>18736.876409999997</v>
+      </c>
+      <c r="AH36" s="5">
         <f t="shared" si="18"/>
-        <v>21882.890917314013</v>
-      </c>
-      <c r="AE32" s="5">
+        <v>19486.351466399996</v>
+      </c>
+      <c r="AI36" s="5">
         <f t="shared" si="18"/>
-        <v>22637.347816880167</v>
-      </c>
-      <c r="AF32" s="5">
+        <v>20265.805525055999</v>
+      </c>
+      <c r="AJ36" s="5">
         <f t="shared" si="18"/>
-        <v>23191.983752146392</v>
-      </c>
-      <c r="AG32" s="5">
+        <v>20873.779690807685</v>
+      </c>
+      <c r="AK36" s="5">
         <f t="shared" si="18"/>
-        <v>23760.769075485776</v>
-      </c>
-      <c r="AH32" s="5">
+        <v>21499.993081531909</v>
+      </c>
+      <c r="AL36" s="5">
         <f t="shared" si="18"/>
-        <v>24344.078474740847</v>
-      </c>
-      <c r="AI32" s="5">
+        <v>21929.99294316255</v>
+      </c>
+      <c r="AM36" s="5">
         <f t="shared" si="18"/>
-        <v>24942.296882513416</v>
-      </c>
-      <c r="AJ32" s="5">
+        <v>22368.5928020258</v>
+      </c>
+      <c r="AN36" s="5">
         <f t="shared" si="18"/>
-        <v>25555.819763589723</v>
-      </c>
-      <c r="AK32" s="5">
+        <v>22815.96465806631</v>
+      </c>
+      <c r="AO36" s="5">
         <f t="shared" si="18"/>
-        <v>26185.05341059035</v>
-      </c>
-    </row>
-    <row r="33" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B33" s="1" t="s">
+        <v>23272.283951227641</v>
+      </c>
+    </row>
+    <row r="37" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C37" s="3">
         <v>635</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D37" s="3">
         <v>698</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E37" s="3">
         <v>662</v>
       </c>
-      <c r="F33" s="3">
-        <f t="shared" ref="F33:F34" si="19">X33-E33-D33-C33</f>
+      <c r="F37" s="3">
+        <f t="shared" ref="F37:F38" si="19">AB37-E37-D37-C37</f>
         <v>716</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G37" s="3">
         <v>607</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H37" s="3">
         <v>729</v>
       </c>
-      <c r="I33" s="3">
+      <c r="I37" s="3">
         <v>712</v>
       </c>
-      <c r="J33" s="3">
-        <f t="shared" ref="J33:J34" si="20">Y33-I33-H33-G33</f>
+      <c r="J37" s="3">
+        <f t="shared" ref="J37:J38" si="20">AC37-I37-H37-G37</f>
         <v>757</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K37" s="3">
         <v>669</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L37" s="3">
         <v>706</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M37" s="3">
         <v>751</v>
       </c>
-      <c r="N33" s="3">
-        <f t="shared" ref="N33:N34" si="21">Z33-M33-L33-K33</f>
+      <c r="N37" s="3">
+        <f t="shared" ref="N37:N38" si="21">AD37-M37-L37-K37</f>
         <v>808</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O37" s="3">
         <v>637</v>
       </c>
-      <c r="P33" s="3">
+      <c r="P37" s="3">
         <v>697</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q37" s="3">
         <v>684</v>
       </c>
-      <c r="R33" s="3">
-        <f>N33*0.98</f>
-        <v>791.84</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="R37" s="3">
+        <v>789</v>
+      </c>
+      <c r="S37" s="3"/>
+      <c r="T37" s="3"/>
+      <c r="U37" s="3"/>
+      <c r="V37" s="3"/>
+      <c r="Y37" s="3">
         <v>2452</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Z37" s="3">
         <v>2582</v>
       </c>
-      <c r="W33" s="3">
+      <c r="AA37" s="3">
         <v>2732</v>
       </c>
-      <c r="X33" s="3">
+      <c r="AB37" s="3">
         <v>2711</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AC37" s="3">
         <v>2805</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AD37" s="3">
         <v>2934</v>
       </c>
-      <c r="AA33" s="3">
-        <f t="shared" ref="AA33:AA34" si="22">SUM(O33:R33)</f>
-        <v>2809.84</v>
-      </c>
-      <c r="AB33" s="3">
-        <f>AA33*1.01</f>
-        <v>2837.9384</v>
-      </c>
-      <c r="AC33" s="3">
-        <f t="shared" ref="AC33:AE33" si="23">AB33*1.02</f>
-        <v>2894.6971680000001</v>
-      </c>
-      <c r="AD33" s="3">
+      <c r="AE37" s="3">
+        <f t="shared" ref="AE37:AE38" si="22">SUM(O37:R37)</f>
+        <v>2807</v>
+      </c>
+      <c r="AF37" s="3">
+        <f>AE37*1.01</f>
+        <v>2835.07</v>
+      </c>
+      <c r="AG37" s="3">
+        <f t="shared" ref="AG37:AI37" si="23">AF37*1.02</f>
+        <v>2891.7714000000001</v>
+      </c>
+      <c r="AH37" s="3">
         <f t="shared" si="23"/>
-        <v>2952.59111136</v>
-      </c>
-      <c r="AE33" s="3">
+        <v>2949.606828</v>
+      </c>
+      <c r="AI37" s="3">
         <f t="shared" si="23"/>
-        <v>3011.6429335871999</v>
-      </c>
-      <c r="AF33" s="3">
-        <f>AE33*1.01</f>
-        <v>3041.7593629230719</v>
-      </c>
-      <c r="AG33" s="3">
-        <f t="shared" ref="AG33:AK33" si="24">AF33*1.01</f>
-        <v>3072.1769565523027</v>
-      </c>
-      <c r="AH33" s="3">
+        <v>3008.5989645599998</v>
+      </c>
+      <c r="AJ37" s="3">
+        <f>AI37*1.01</f>
+        <v>3038.6849542055998</v>
+      </c>
+      <c r="AK37" s="3">
+        <f t="shared" ref="AK37:AO37" si="24">AJ37*1.01</f>
+        <v>3069.0718037476558</v>
+      </c>
+      <c r="AL37" s="3">
         <f t="shared" si="24"/>
-        <v>3102.8987261178258</v>
-      </c>
-      <c r="AI33" s="3">
+        <v>3099.7625217851323</v>
+      </c>
+      <c r="AM37" s="3">
         <f t="shared" si="24"/>
-        <v>3133.9277133790042</v>
-      </c>
-      <c r="AJ33" s="3">
+        <v>3130.7601470029836</v>
+      </c>
+      <c r="AN37" s="3">
         <f t="shared" si="24"/>
-        <v>3165.2669905127941</v>
-      </c>
-      <c r="AK33" s="3">
+        <v>3162.0677484730136</v>
+      </c>
+      <c r="AO37" s="3">
         <f t="shared" si="24"/>
-        <v>3196.9196604179219</v>
-      </c>
-    </row>
-    <row r="34" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
+        <v>3193.6884259577437</v>
+      </c>
+    </row>
+    <row r="38" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C38" s="3">
         <v>1469</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D38" s="3">
         <v>1424</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E38" s="3">
         <v>1351</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F38" s="3">
         <f t="shared" si="19"/>
         <v>1329</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G38" s="3">
         <v>1398</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H38" s="3">
         <v>1600</v>
       </c>
-      <c r="I34" s="3">
+      <c r="I38" s="3">
         <v>1401</v>
       </c>
-      <c r="J34" s="3">
+      <c r="J38" s="3">
         <f t="shared" si="20"/>
         <v>1410</v>
       </c>
-      <c r="K34" s="3">
+      <c r="K38" s="3">
         <v>1394</v>
       </c>
-      <c r="L34" s="3">
+      <c r="L38" s="3">
         <v>1449</v>
       </c>
-      <c r="M34" s="3">
+      <c r="M38" s="3">
         <v>1389</v>
       </c>
-      <c r="N34" s="3">
+      <c r="N38" s="3">
         <f t="shared" si="21"/>
         <v>1574</v>
       </c>
-      <c r="O34" s="3">
+      <c r="O38" s="3">
         <v>1448</v>
       </c>
-      <c r="P34" s="3">
+      <c r="P38" s="3">
         <v>1573</v>
       </c>
-      <c r="Q34" s="3">
+      <c r="Q38" s="3">
         <v>1436</v>
       </c>
-      <c r="R34" s="3">
-        <f>R28*0.07</f>
-        <v>1688.4238000000003</v>
-      </c>
-      <c r="U34" s="3">
+      <c r="R38" s="3">
+        <v>1638</v>
+      </c>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="Y38" s="3">
         <v>3711</v>
       </c>
-      <c r="V34" s="3">
+      <c r="Z38" s="3">
         <v>5540</v>
       </c>
-      <c r="W34" s="3">
+      <c r="AA38" s="3">
         <v>5224</v>
       </c>
-      <c r="X34" s="3">
+      <c r="AB38" s="3">
         <v>5573</v>
       </c>
-      <c r="Y34" s="3">
+      <c r="AC38" s="3">
         <v>5809</v>
       </c>
-      <c r="Z34" s="3">
+      <c r="AD38" s="3">
         <v>5806</v>
       </c>
-      <c r="AA34" s="3">
+      <c r="AE38" s="3">
         <f t="shared" si="22"/>
-        <v>6145.4238000000005</v>
-      </c>
-      <c r="AB34" s="3">
-        <f t="shared" ref="AB34:AK34" si="25">AB28*0.07</f>
-        <v>6775.0192440000001</v>
-      </c>
-      <c r="AC34" s="3">
+        <v>6095</v>
+      </c>
+      <c r="AF38" s="3">
+        <f t="shared" ref="AF38:AO38" si="25">AF32*0.07</f>
+        <v>6574.3426000000009</v>
+      </c>
+      <c r="AG38" s="3">
         <f t="shared" si="25"/>
-        <v>7191.0871023600002</v>
-      </c>
-      <c r="AD34" s="3">
+        <v>6903.0597300000018</v>
+      </c>
+      <c r="AH38" s="3">
         <f t="shared" si="25"/>
-        <v>7499.7994406580019</v>
-      </c>
-      <c r="AE34" s="3">
+        <v>7179.1821192000025</v>
+      </c>
+      <c r="AI38" s="3">
         <f t="shared" si="25"/>
-        <v>7746.9157207915223</v>
-      </c>
-      <c r="AF34" s="3">
+        <v>7466.3494039680027</v>
+      </c>
+      <c r="AJ38" s="3">
         <f t="shared" si="25"/>
-        <v>7924.8612239976837</v>
-      </c>
-      <c r="AG34" s="3">
+        <v>7690.339886087042</v>
+      </c>
+      <c r="AK38" s="3">
         <f t="shared" si="25"/>
-        <v>8107.0558529316786</v>
-      </c>
-      <c r="AH34" s="3">
+        <v>7921.0500826696534</v>
+      </c>
+      <c r="AL38" s="3">
         <f t="shared" si="25"/>
-        <v>8293.6052965779745</v>
-      </c>
-      <c r="AI34" s="3">
+        <v>8079.4710843230469</v>
+      </c>
+      <c r="AM38" s="3">
         <f t="shared" si="25"/>
-        <v>8484.6179788948284</v>
-      </c>
-      <c r="AJ34" s="3">
+        <v>8241.0605060095077</v>
+      </c>
+      <c r="AN38" s="3">
         <f t="shared" si="25"/>
-        <v>8680.2051321495746</v>
-      </c>
-      <c r="AK34" s="3">
+        <v>8405.8817161296993</v>
+      </c>
+      <c r="AO38" s="3">
         <f t="shared" si="25"/>
-        <v>8880.4808722797225</v>
-      </c>
-    </row>
-    <row r="35" spans="2:135" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="4" t="s">
+        <v>8573.9993504522936</v>
+      </c>
+    </row>
+    <row r="39" spans="2:139" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="5">
-        <f t="shared" ref="C35:P35" si="26">C32-C33-C34</f>
+      <c r="C39" s="5">
+        <f t="shared" ref="C39:P39" si="26">C36-C37-C38</f>
         <v>1052</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D39" s="5">
         <f t="shared" si="26"/>
         <v>1336</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E39" s="5">
         <f t="shared" si="26"/>
         <v>1474</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F39" s="5">
         <f t="shared" si="26"/>
         <v>1522</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G39" s="5">
         <f t="shared" si="26"/>
         <v>1564</v>
       </c>
-      <c r="H35" s="5">
+      <c r="H39" s="5">
         <f t="shared" si="26"/>
         <v>1468</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I39" s="5">
         <f t="shared" si="26"/>
         <v>-1399</v>
       </c>
-      <c r="J35" s="5">
+      <c r="J39" s="5">
         <f t="shared" si="26"/>
         <v>1842</v>
       </c>
-      <c r="K35" s="5">
+      <c r="K39" s="5">
         <f t="shared" si="26"/>
         <v>1498</v>
       </c>
-      <c r="L35" s="5">
+      <c r="L39" s="5">
         <f t="shared" si="26"/>
         <v>1425</v>
       </c>
-      <c r="M35" s="5">
+      <c r="M39" s="5">
         <f t="shared" si="26"/>
         <v>1894</v>
       </c>
-      <c r="N35" s="5">
+      <c r="N39" s="5">
         <f t="shared" si="26"/>
         <v>1853</v>
       </c>
-      <c r="O35" s="5">
+      <c r="O39" s="5">
         <f t="shared" si="26"/>
         <v>2031</v>
       </c>
-      <c r="P35" s="5">
+      <c r="P39" s="5">
         <f t="shared" si="26"/>
         <v>2106</v>
       </c>
-      <c r="Q35" s="5">
-        <f t="shared" ref="Q35:R35" si="27">Q32-Q33-Q34</f>
+      <c r="Q39" s="5">
+        <f t="shared" ref="Q39:R39" si="27">Q36-Q37-Q38</f>
         <v>2460</v>
       </c>
-      <c r="R35" s="5">
+      <c r="R39" s="5">
         <f t="shared" si="27"/>
-        <v>2350.6065999999992</v>
-      </c>
-      <c r="U35" s="5">
-        <f t="shared" ref="U35:AA35" si="28">U32-U33-U34</f>
+        <v>2290</v>
+      </c>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
+      <c r="Y39" s="5">
+        <f t="shared" ref="Y39:AE39" si="28">Y36-Y37-Y38</f>
         <v>4588</v>
       </c>
-      <c r="V35" s="5">
+      <c r="Z39" s="5">
         <f t="shared" si="28"/>
         <v>409</v>
       </c>
-      <c r="W35" s="5">
+      <c r="AA39" s="5">
         <f t="shared" si="28"/>
         <v>4535</v>
       </c>
-      <c r="X35" s="5">
+      <c r="AB39" s="5">
         <f t="shared" si="28"/>
         <v>5384</v>
       </c>
-      <c r="Y35" s="5">
+      <c r="AC39" s="5">
         <f t="shared" si="28"/>
         <v>3475</v>
       </c>
-      <c r="Z35" s="5">
+      <c r="AD39" s="5">
         <f t="shared" si="28"/>
         <v>6670</v>
       </c>
-      <c r="AA35" s="5">
+      <c r="AE39" s="5">
         <f t="shared" si="28"/>
-        <v>8947.6065999999992</v>
-      </c>
-      <c r="AB35" s="5">
-        <f t="shared" ref="AB35:AK35" si="29">AB32-AB33-AB34</f>
-        <v>10014.77720800001</v>
-      </c>
-      <c r="AC35" s="5">
+        <v>7932.5699999999924</v>
+      </c>
+      <c r="AF39" s="5">
+        <f t="shared" ref="AF39:AO39" si="29">AF36-AF37-AF38</f>
+        <v>8435.2315999999955</v>
+      </c>
+      <c r="AG39" s="5">
         <f t="shared" si="29"/>
-        <v>10865.740721519996</v>
-      </c>
-      <c r="AD35" s="5">
+        <v>8942.0452799999948</v>
+      </c>
+      <c r="AH39" s="5">
         <f t="shared" si="29"/>
-        <v>11430.500365296009</v>
-      </c>
-      <c r="AE35" s="5">
+        <v>9357.5625191999934</v>
+      </c>
+      <c r="AI39" s="5">
         <f t="shared" si="29"/>
-        <v>11878.789162501442</v>
-      </c>
-      <c r="AF35" s="5">
+        <v>9790.8571565279981</v>
+      </c>
+      <c r="AJ39" s="5">
         <f t="shared" si="29"/>
-        <v>12225.363165225637</v>
-      </c>
-      <c r="AG35" s="5">
+        <v>10144.754850515043</v>
+      </c>
+      <c r="AK39" s="5">
         <f t="shared" si="29"/>
-        <v>12581.536266001795</v>
-      </c>
-      <c r="AH35" s="5">
+        <v>10509.871195114602</v>
+      </c>
+      <c r="AL39" s="5">
         <f t="shared" si="29"/>
-        <v>12947.574452045046</v>
-      </c>
-      <c r="AI35" s="5">
+        <v>10750.759337054373</v>
+      </c>
+      <c r="AM39" s="5">
         <f t="shared" si="29"/>
-        <v>13323.751190239582</v>
-      </c>
-      <c r="AJ35" s="5">
+        <v>10996.772149013308</v>
+      </c>
+      <c r="AN39" s="5">
         <f t="shared" si="29"/>
-        <v>13710.347640927353</v>
-      </c>
-      <c r="AK35" s="5">
+        <v>11248.015193463596</v>
+      </c>
+      <c r="AO39" s="5">
         <f t="shared" si="29"/>
-        <v>14107.652877892704</v>
-      </c>
-    </row>
-    <row r="36" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
+        <v>11504.596174817605</v>
+      </c>
+    </row>
+    <row r="40" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C40" s="3">
         <v>-28</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D40" s="3">
         <v>-17</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E40" s="3">
         <v>-46</v>
       </c>
-      <c r="F36" s="3">
-        <f t="shared" ref="F36:F38" si="30">X36-E36-D36-C36</f>
+      <c r="F40" s="3">
+        <f t="shared" ref="F40:F42" si="30">AB40-E40-D40-C40</f>
         <v>-29</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G40" s="3">
         <v>-88</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H40" s="3">
         <v>-25</v>
       </c>
-      <c r="I36" s="3">
+      <c r="I40" s="3">
         <v>-3</v>
       </c>
-      <c r="J36" s="3">
-        <f t="shared" ref="J36:J38" si="31">Y36-I36-H36-G36</f>
+      <c r="J40" s="3">
+        <f t="shared" ref="J40:J42" si="31">AC40-I40-H40-G40</f>
         <v>30</v>
       </c>
-      <c r="K36" s="3">
+      <c r="K40" s="3">
         <v>-372</v>
       </c>
-      <c r="L36" s="3">
+      <c r="L40" s="3">
         <v>896</v>
       </c>
-      <c r="M36" s="3">
+      <c r="M40" s="3">
         <v>-134</v>
       </c>
-      <c r="N36" s="3">
-        <f t="shared" ref="N36:N38" si="32">Z36-M36-L36-K36</f>
+      <c r="N40" s="3">
+        <f t="shared" ref="N40:N42" si="32">AD40-M40-L40-K40</f>
         <v>-258</v>
       </c>
-      <c r="O36" s="3">
+      <c r="O40" s="3">
         <v>-4</v>
       </c>
-      <c r="P36" s="3">
+      <c r="P40" s="3">
         <v>-40</v>
       </c>
-      <c r="Q36" s="3">
+      <c r="Q40" s="3">
         <v>-63</v>
       </c>
-      <c r="R36" s="3">
-        <v>0</v>
-      </c>
-      <c r="U36" s="3">
+      <c r="R40" s="3">
+        <v>-306</v>
+      </c>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="Y40" s="3">
         <v>-326</v>
       </c>
-      <c r="V36" s="3">
+      <c r="Z40" s="3">
         <f>3183-885</f>
         <v>2298</v>
       </c>
-      <c r="W36" s="3">
+      <c r="AA40" s="3">
         <v>-423</v>
       </c>
-      <c r="X36" s="3">
+      <c r="AB40" s="3">
         <v>-120</v>
       </c>
-      <c r="Y36" s="3">
+      <c r="AC40" s="3">
         <v>-86</v>
       </c>
-      <c r="Z36" s="3">
+      <c r="AD40" s="3">
         <v>132</v>
       </c>
-      <c r="AA36" s="3">
-        <f t="shared" ref="AA36:AA38" si="33">SUM(O36:R36)</f>
-        <v>-107</v>
-      </c>
-      <c r="AB36" s="3">
+      <c r="AE40" s="3">
+        <f t="shared" ref="AE40:AE42" si="33">SUM(O40:R40)</f>
+        <v>-413</v>
+      </c>
+      <c r="AF40" s="3">
         <v>0</v>
       </c>
-      <c r="AC36" s="3">
+      <c r="AG40" s="3">
         <v>0</v>
       </c>
-      <c r="AD36" s="3">
+      <c r="AH40" s="3">
         <v>0</v>
       </c>
-      <c r="AE36" s="3">
+      <c r="AI40" s="3">
         <v>0</v>
       </c>
-      <c r="AF36" s="3">
+      <c r="AJ40" s="3">
         <v>0</v>
       </c>
-      <c r="AG36" s="3">
+      <c r="AK40" s="3">
         <v>0</v>
       </c>
-      <c r="AH36" s="3">
+      <c r="AL40" s="3">
         <v>0</v>
       </c>
-      <c r="AI36" s="3">
+      <c r="AM40" s="3">
         <v>0</v>
       </c>
-      <c r="AJ36" s="3">
+      <c r="AN40" s="3">
         <v>0</v>
       </c>
-      <c r="AK36" s="3">
+      <c r="AO40" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
+    <row r="41" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C41" s="3">
         <v>-480</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D41" s="3">
         <v>-474</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E41" s="3">
         <v>-468</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F41" s="3">
         <f t="shared" si="30"/>
         <v>-467</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G41" s="3">
         <v>-444</v>
       </c>
-      <c r="H37" s="3">
+      <c r="H41" s="3">
         <v>-447</v>
       </c>
-      <c r="I37" s="3">
+      <c r="I41" s="3">
         <v>-443</v>
       </c>
-      <c r="J37" s="3">
+      <c r="J41" s="3">
         <f t="shared" si="31"/>
         <v>-446</v>
       </c>
-      <c r="K37" s="3">
+      <c r="K41" s="3">
         <v>-386</v>
       </c>
-      <c r="L37" s="3">
+      <c r="L41" s="3">
         <v>-374</v>
       </c>
-      <c r="M37" s="3">
+      <c r="M41" s="3">
         <v>-374</v>
       </c>
-      <c r="N37" s="3">
+      <c r="N41" s="3">
         <f t="shared" si="32"/>
         <v>-384</v>
       </c>
-      <c r="O37" s="3">
+      <c r="O41" s="3">
         <v>-366</v>
       </c>
-      <c r="P37" s="3">
+      <c r="P41" s="3">
         <v>-351</v>
       </c>
-      <c r="Q37" s="3">
+      <c r="Q41" s="3">
         <v>-364</v>
       </c>
-      <c r="R37" s="3">
-        <f>N37*1.01</f>
-        <v>-387.84000000000003</v>
-      </c>
-      <c r="U37" s="3">
+      <c r="R41" s="3">
+        <v>-101</v>
+      </c>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
+      <c r="Y41" s="3">
         <v>-829</v>
       </c>
-      <c r="V37" s="3">
+      <c r="Z41" s="3">
         <v>-902</v>
       </c>
-      <c r="W37" s="3">
+      <c r="AA41" s="3">
         <v>-1944</v>
       </c>
-      <c r="X37" s="3">
+      <c r="AB41" s="3">
         <v>-1889</v>
       </c>
-      <c r="Y37" s="3">
+      <c r="AC41" s="3">
         <v>-1780</v>
       </c>
-      <c r="Z37" s="3">
+      <c r="AD41" s="3">
         <v>-1518</v>
       </c>
-      <c r="AA37" s="3">
+      <c r="AE41" s="3">
         <f t="shared" si="33"/>
-        <v>-1468.8400000000001</v>
-      </c>
-      <c r="AB37" s="3">
-        <f t="shared" ref="AB37:AK37" si="34">AA37*1.01</f>
-        <v>-1483.5284000000001</v>
-      </c>
-      <c r="AC37" s="3">
+        <v>-1182</v>
+      </c>
+      <c r="AF41" s="3">
+        <f t="shared" ref="AF41:AO41" si="34">AE41*1.01</f>
+        <v>-1193.82</v>
+      </c>
+      <c r="AG41" s="3">
         <f t="shared" si="34"/>
-        <v>-1498.3636840000001</v>
-      </c>
-      <c r="AD37" s="3">
+        <v>-1205.7582</v>
+      </c>
+      <c r="AH41" s="3">
         <f t="shared" si="34"/>
-        <v>-1513.3473208400001</v>
-      </c>
-      <c r="AE37" s="3">
+        <v>-1217.8157819999999</v>
+      </c>
+      <c r="AI41" s="3">
         <f t="shared" si="34"/>
-        <v>-1528.4807940484002</v>
-      </c>
-      <c r="AF37" s="3">
+        <v>-1229.9939398199999</v>
+      </c>
+      <c r="AJ41" s="3">
         <f t="shared" si="34"/>
-        <v>-1543.7656019888841</v>
-      </c>
-      <c r="AG37" s="3">
+        <v>-1242.2938792181999</v>
+      </c>
+      <c r="AK41" s="3">
         <f t="shared" si="34"/>
-        <v>-1559.203258008773</v>
-      </c>
-      <c r="AH37" s="3">
+        <v>-1254.716818010382</v>
+      </c>
+      <c r="AL41" s="3">
         <f t="shared" si="34"/>
-        <v>-1574.7952905888608</v>
-      </c>
-      <c r="AI37" s="3">
+        <v>-1267.2639861904859</v>
+      </c>
+      <c r="AM41" s="3">
         <f t="shared" si="34"/>
-        <v>-1590.5432434947495</v>
-      </c>
-      <c r="AJ37" s="3">
+        <v>-1279.9366260523907</v>
+      </c>
+      <c r="AN41" s="3">
         <f t="shared" si="34"/>
-        <v>-1606.4486759296969</v>
-      </c>
-      <c r="AK37" s="3">
+        <v>-1292.7359923129145</v>
+      </c>
+      <c r="AO41" s="3">
         <f t="shared" si="34"/>
-        <v>-1622.513162688994</v>
-      </c>
-    </row>
-    <row r="38" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B38" s="1" t="s">
+        <v>-1305.6633522360437</v>
+      </c>
+    </row>
+    <row r="42" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C42" s="3">
         <v>318</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D42" s="3">
         <v>329</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E42" s="3">
         <v>311</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F42" s="3">
         <f t="shared" si="30"/>
         <v>318</v>
       </c>
-      <c r="G38" s="3">
+      <c r="G42" s="3">
         <v>315</v>
       </c>
-      <c r="H38" s="3">
+      <c r="H42" s="3">
         <v>333</v>
       </c>
-      <c r="I38" s="3">
+      <c r="I42" s="3">
         <v>369</v>
       </c>
-      <c r="J38" s="3">
+      <c r="J42" s="3">
         <f t="shared" si="31"/>
         <v>488</v>
       </c>
-      <c r="K38" s="3">
+      <c r="K42" s="3">
         <v>405</v>
       </c>
-      <c r="L38" s="3">
+      <c r="L42" s="3">
         <v>475</v>
       </c>
-      <c r="M38" s="3">
+      <c r="M42" s="3">
         <v>496</v>
       </c>
-      <c r="N38" s="3">
+      <c r="N42" s="3">
         <f t="shared" si="32"/>
         <v>486</v>
       </c>
-      <c r="O38" s="3">
+      <c r="O42" s="3">
         <v>443</v>
       </c>
-      <c r="P38" s="3">
+      <c r="P42" s="3">
         <v>457</v>
       </c>
-      <c r="Q38" s="3">
+      <c r="Q42" s="3">
         <v>449</v>
       </c>
-      <c r="R38" s="3">
-        <f t="shared" ref="R38" si="35">N38*1.01</f>
-        <v>490.86</v>
-      </c>
-      <c r="U38" s="3">
+      <c r="R42" s="3">
+        <v>400</v>
+      </c>
+      <c r="S42" s="3"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+      <c r="Y42" s="3">
         <v>1591</v>
       </c>
-      <c r="V38" s="3">
+      <c r="Z42" s="3">
         <v>1366</v>
       </c>
-      <c r="W38" s="3">
+      <c r="AA42" s="3">
         <f>1322+649</f>
         <v>1971</v>
       </c>
-      <c r="X38" s="3">
+      <c r="AB42" s="3">
         <v>1276</v>
       </c>
-      <c r="Y38" s="3">
+      <c r="AC42" s="3">
         <v>1505</v>
       </c>
-      <c r="Z38" s="3">
+      <c r="AD42" s="3">
         <v>1862</v>
       </c>
-      <c r="AA38" s="3">
+      <c r="AE42" s="3">
         <f t="shared" si="33"/>
-        <v>1839.8600000000001</v>
-      </c>
-      <c r="AB38" s="3">
-        <f t="shared" ref="AB38:AK38" si="36">AA38*1.01</f>
-        <v>1858.2586000000001</v>
-      </c>
-      <c r="AC38" s="3">
+        <v>1749</v>
+      </c>
+      <c r="AF42" s="3">
+        <f t="shared" ref="AF42:AO42" si="35">AE42*1.01</f>
+        <v>1766.49</v>
+      </c>
+      <c r="AG42" s="3">
+        <f t="shared" si="35"/>
+        <v>1784.1549</v>
+      </c>
+      <c r="AH42" s="3">
+        <f t="shared" si="35"/>
+        <v>1801.996449</v>
+      </c>
+      <c r="AI42" s="3">
+        <f t="shared" si="35"/>
+        <v>1820.0164134900001</v>
+      </c>
+      <c r="AJ42" s="3">
+        <f t="shared" si="35"/>
+        <v>1838.2165776249001</v>
+      </c>
+      <c r="AK42" s="3">
+        <f t="shared" si="35"/>
+        <v>1856.598743401149</v>
+      </c>
+      <c r="AL42" s="3">
+        <f t="shared" si="35"/>
+        <v>1875.1647308351605</v>
+      </c>
+      <c r="AM42" s="3">
+        <f t="shared" si="35"/>
+        <v>1893.9163781435122</v>
+      </c>
+      <c r="AN42" s="3">
+        <f t="shared" si="35"/>
+        <v>1912.8555419249474</v>
+      </c>
+      <c r="AO42" s="3">
+        <f t="shared" si="35"/>
+        <v>1931.9840973441969</v>
+      </c>
+    </row>
+    <row r="43" spans="2:139" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" s="5">
+        <f t="shared" ref="C43:P43" si="36">C39-C40-C41-C42</f>
+        <v>1242</v>
+      </c>
+      <c r="D43" s="5">
         <f t="shared" si="36"/>
-        <v>1876.8411860000001</v>
-      </c>
-      <c r="AD38" s="3">
+        <v>1498</v>
+      </c>
+      <c r="E43" s="5">
         <f t="shared" si="36"/>
-        <v>1895.6095978600001</v>
-      </c>
-      <c r="AE38" s="3">
+        <v>1677</v>
+      </c>
+      <c r="F43" s="5">
         <f t="shared" si="36"/>
-        <v>1914.5656938386001</v>
-      </c>
-      <c r="AF38" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G43" s="5">
         <f t="shared" si="36"/>
-        <v>1933.7113507769861</v>
-      </c>
-      <c r="AG38" s="3">
+        <v>1781</v>
+      </c>
+      <c r="H43" s="5">
         <f t="shared" si="36"/>
-        <v>1953.0484642847559</v>
-      </c>
-      <c r="AH38" s="3">
+        <v>1607</v>
+      </c>
+      <c r="I43" s="5">
         <f t="shared" si="36"/>
-        <v>1972.5789489276035</v>
-      </c>
-      <c r="AI38" s="3">
+        <v>-1322</v>
+      </c>
+      <c r="J43" s="5">
         <f t="shared" si="36"/>
-        <v>1992.3047384168794</v>
-      </c>
-      <c r="AJ38" s="3">
+        <v>1770</v>
+      </c>
+      <c r="K43" s="5">
         <f t="shared" si="36"/>
-        <v>2012.2277858010482</v>
-      </c>
-      <c r="AK38" s="3">
+        <v>1851</v>
+      </c>
+      <c r="L43" s="5">
         <f t="shared" si="36"/>
-        <v>2032.3500636590586</v>
-      </c>
-    </row>
-    <row r="39" spans="2:135" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C39" s="5">
-        <f t="shared" ref="C39:P39" si="37">C35-C36-C37-C38</f>
-        <v>1242</v>
-      </c>
-      <c r="D39" s="5">
+        <v>428</v>
+      </c>
+      <c r="M43" s="5">
+        <f t="shared" si="36"/>
+        <v>1906</v>
+      </c>
+      <c r="N43" s="5">
+        <f t="shared" si="36"/>
+        <v>2009</v>
+      </c>
+      <c r="O43" s="5">
+        <f t="shared" si="36"/>
+        <v>1958</v>
+      </c>
+      <c r="P43" s="5">
+        <f t="shared" si="36"/>
+        <v>2040</v>
+      </c>
+      <c r="Q43" s="5">
+        <f t="shared" ref="Q43:R43" si="37">Q39-Q40-Q41-Q42</f>
+        <v>2438</v>
+      </c>
+      <c r="R43" s="5">
         <f t="shared" si="37"/>
-        <v>1498</v>
-      </c>
-      <c r="E39" s="5">
-        <f t="shared" si="37"/>
-        <v>1677</v>
-      </c>
-      <c r="F39" s="5">
-        <f t="shared" si="37"/>
-        <v>1700</v>
-      </c>
-      <c r="G39" s="5">
-        <f t="shared" si="37"/>
-        <v>1781</v>
-      </c>
-      <c r="H39" s="5">
-        <f t="shared" si="37"/>
-        <v>1607</v>
-      </c>
-      <c r="I39" s="5">
-        <f t="shared" si="37"/>
-        <v>-1322</v>
-      </c>
-      <c r="J39" s="5">
-        <f t="shared" si="37"/>
-        <v>1770</v>
-      </c>
-      <c r="K39" s="5">
-        <f t="shared" si="37"/>
-        <v>1851</v>
-      </c>
-      <c r="L39" s="5">
-        <f t="shared" si="37"/>
-        <v>428</v>
-      </c>
-      <c r="M39" s="5">
-        <f t="shared" si="37"/>
-        <v>1906</v>
-      </c>
-      <c r="N39" s="5">
-        <f t="shared" si="37"/>
-        <v>2009</v>
-      </c>
-      <c r="O39" s="5">
-        <f t="shared" si="37"/>
-        <v>1958</v>
-      </c>
-      <c r="P39" s="5">
-        <f t="shared" si="37"/>
-        <v>2040</v>
-      </c>
-      <c r="Q39" s="5">
-        <f t="shared" ref="Q39:R39" si="38">Q35-Q36-Q37-Q38</f>
-        <v>2438</v>
-      </c>
-      <c r="R39" s="5">
+        <v>2297</v>
+      </c>
+      <c r="S43" s="5"/>
+      <c r="T43" s="5"/>
+      <c r="U43" s="5"/>
+      <c r="V43" s="5"/>
+      <c r="Y43" s="5">
+        <f t="shared" ref="Y43:AE43" si="38">Y39-Y40-Y41-Y42</f>
+        <v>4152</v>
+      </c>
+      <c r="Z43" s="5">
         <f t="shared" si="38"/>
-        <v>2247.5865999999992</v>
-      </c>
-      <c r="U39" s="5">
-        <f t="shared" ref="U39:AA39" si="39">U35-U36-U37-U38</f>
-        <v>4152</v>
-      </c>
-      <c r="V39" s="5">
+        <v>-2353</v>
+      </c>
+      <c r="AA43" s="5">
+        <f t="shared" si="38"/>
+        <v>4931</v>
+      </c>
+      <c r="AB43" s="5">
+        <f t="shared" si="38"/>
+        <v>6117</v>
+      </c>
+      <c r="AC43" s="5">
+        <f t="shared" si="38"/>
+        <v>3836</v>
+      </c>
+      <c r="AD43" s="5">
+        <f t="shared" si="38"/>
+        <v>6194</v>
+      </c>
+      <c r="AE43" s="5">
+        <f t="shared" si="38"/>
+        <v>7778.5699999999924</v>
+      </c>
+      <c r="AF43" s="5">
+        <f t="shared" ref="AF43:AO43" si="39">AF39-AF40-AF41-AF42</f>
+        <v>7862.5615999999955</v>
+      </c>
+      <c r="AG43" s="5">
         <f t="shared" si="39"/>
-        <v>-2353</v>
-      </c>
-      <c r="W39" s="5">
+        <v>8363.6485799999955</v>
+      </c>
+      <c r="AH43" s="5">
         <f t="shared" si="39"/>
-        <v>4931</v>
-      </c>
-      <c r="X39" s="5">
+        <v>8773.3818521999929</v>
+      </c>
+      <c r="AI43" s="5">
         <f t="shared" si="39"/>
-        <v>6117</v>
-      </c>
-      <c r="Y39" s="5">
+        <v>9200.8346828579979</v>
+      </c>
+      <c r="AJ43" s="5">
         <f t="shared" si="39"/>
-        <v>3836</v>
-      </c>
-      <c r="Z39" s="5">
+        <v>9548.8321521083417</v>
+      </c>
+      <c r="AK43" s="5">
         <f t="shared" si="39"/>
-        <v>6194</v>
-      </c>
-      <c r="AA39" s="5">
+        <v>9907.9892697238338</v>
+      </c>
+      <c r="AL43" s="5">
         <f t="shared" si="39"/>
-        <v>8683.5865999999987</v>
-      </c>
-      <c r="AB39" s="5">
-        <f t="shared" ref="AB39:AK39" si="40">AB35-AB36-AB37-AB38</f>
-        <v>9640.0470080000086</v>
-      </c>
-      <c r="AC39" s="5">
+        <v>10142.858592409699</v>
+      </c>
+      <c r="AM43" s="5">
+        <f t="shared" si="39"/>
+        <v>10382.792396922187</v>
+      </c>
+      <c r="AN43" s="5">
+        <f t="shared" si="39"/>
+        <v>10627.895643851563</v>
+      </c>
+      <c r="AO43" s="5">
+        <f t="shared" si="39"/>
+        <v>10878.275429709453</v>
+      </c>
+    </row>
+    <row r="44" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="3">
+        <v>116</v>
+      </c>
+      <c r="D44" s="3">
+        <v>160</v>
+      </c>
+      <c r="E44" s="3">
+        <v>282</v>
+      </c>
+      <c r="F44" s="3">
+        <f t="shared" ref="F44:F45" si="40">AB44-E44-D44-C44</f>
+        <v>232</v>
+      </c>
+      <c r="G44" s="3">
+        <v>300</v>
+      </c>
+      <c r="H44" s="3">
+        <v>248</v>
+      </c>
+      <c r="I44" s="3">
+        <v>-389</v>
+      </c>
+      <c r="J44" s="3">
+        <f t="shared" ref="J44:J45" si="41">AC44-I44-H44-G44</f>
+        <v>297</v>
+      </c>
+      <c r="K44" s="3">
+        <v>108</v>
+      </c>
+      <c r="L44" s="3">
+        <v>253</v>
+      </c>
+      <c r="M44" s="3">
+        <v>371</v>
+      </c>
+      <c r="N44" s="3">
+        <f t="shared" ref="N44:N45" si="42">AD44-M44-L44-K44</f>
+        <v>449</v>
+      </c>
+      <c r="O44" s="3">
+        <v>333</v>
+      </c>
+      <c r="P44" s="3">
+        <v>315</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>432</v>
+      </c>
+      <c r="R44" s="3">
+        <v>584</v>
+      </c>
+      <c r="S44" s="3"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="Y44" s="3">
+        <v>421</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>575</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>786</v>
+      </c>
+      <c r="AB44" s="3">
+        <v>790</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>456</v>
+      </c>
+      <c r="AD44" s="3">
+        <v>1181</v>
+      </c>
+      <c r="AE44" s="3">
+        <f t="shared" ref="AE44:AE45" si="43">SUM(O44:R44)</f>
+        <v>1664</v>
+      </c>
+      <c r="AF44" s="3">
+        <f t="shared" ref="AF44:AO44" si="44">AF43*0.15</f>
+        <v>1179.3842399999992</v>
+      </c>
+      <c r="AG44" s="3">
+        <f t="shared" si="44"/>
+        <v>1254.5472869999992</v>
+      </c>
+      <c r="AH44" s="3">
+        <f t="shared" si="44"/>
+        <v>1316.0072778299989</v>
+      </c>
+      <c r="AI44" s="3">
+        <f t="shared" si="44"/>
+        <v>1380.1252024286996</v>
+      </c>
+      <c r="AJ44" s="3">
+        <f t="shared" si="44"/>
+        <v>1432.3248228162513</v>
+      </c>
+      <c r="AK44" s="3">
+        <f t="shared" si="44"/>
+        <v>1486.198390458575</v>
+      </c>
+      <c r="AL44" s="3">
+        <f t="shared" si="44"/>
+        <v>1521.4287888614547</v>
+      </c>
+      <c r="AM44" s="3">
+        <f t="shared" si="44"/>
+        <v>1557.418859538328</v>
+      </c>
+      <c r="AN44" s="3">
+        <f t="shared" si="44"/>
+        <v>1594.1843465777345</v>
+      </c>
+      <c r="AO44" s="3">
+        <f t="shared" si="44"/>
+        <v>1631.7413144564177</v>
+      </c>
+    </row>
+    <row r="45" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="3">
+        <v>23</v>
+      </c>
+      <c r="D45" s="3">
+        <v>34</v>
+      </c>
+      <c r="E45" s="3">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <f t="shared" si="40"/>
-        <v>10487.263219519997</v>
-      </c>
-      <c r="AD39" s="5">
-        <f t="shared" si="40"/>
-        <v>11048.23808827601</v>
-      </c>
-      <c r="AE39" s="5">
-        <f t="shared" si="40"/>
-        <v>11492.704262711242</v>
-      </c>
-      <c r="AF39" s="5">
-        <f t="shared" si="40"/>
-        <v>11835.417416437534</v>
-      </c>
-      <c r="AG39" s="5">
-        <f t="shared" si="40"/>
-        <v>12187.69105972581</v>
-      </c>
-      <c r="AH39" s="5">
-        <f t="shared" si="40"/>
-        <v>12549.790793706305</v>
-      </c>
-      <c r="AI39" s="5">
-        <f t="shared" si="40"/>
-        <v>12921.98969531745</v>
-      </c>
-      <c r="AJ39" s="5">
-        <f t="shared" si="40"/>
-        <v>13304.568531056002</v>
-      </c>
-      <c r="AK39" s="5">
-        <f t="shared" si="40"/>
-        <v>13697.81597692264</v>
-      </c>
-    </row>
-    <row r="40" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C40" s="3">
-        <v>116</v>
-      </c>
-      <c r="D40" s="3">
-        <v>160</v>
-      </c>
-      <c r="E40" s="3">
-        <v>282</v>
-      </c>
-      <c r="F40" s="3">
-        <f t="shared" ref="F40:F41" si="41">X40-E40-D40-C40</f>
-        <v>232</v>
-      </c>
-      <c r="G40" s="3">
-        <v>300</v>
-      </c>
-      <c r="H40" s="3">
+        <v>46</v>
+      </c>
+      <c r="G45" s="3">
+        <v>55</v>
+      </c>
+      <c r="H45" s="3">
+        <v>32</v>
+      </c>
+      <c r="I45" s="3">
+        <v>51</v>
+      </c>
+      <c r="J45" s="3">
+        <f t="shared" si="41"/>
+        <v>47</v>
+      </c>
+      <c r="K45" s="3">
+        <v>34</v>
+      </c>
+      <c r="L45" s="3">
+        <v>64</v>
+      </c>
+      <c r="M45" s="3">
+        <v>63</v>
+      </c>
+      <c r="N45" s="3">
+        <f t="shared" si="42"/>
+        <v>78</v>
+      </c>
+      <c r="O45" s="3">
+        <v>90</v>
+      </c>
+      <c r="P45" s="3">
+        <v>68</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>88</v>
+      </c>
+      <c r="R45" s="3">
+        <v>91</v>
+      </c>
+      <c r="S45" s="3"/>
+      <c r="T45" s="3"/>
+      <c r="U45" s="3"/>
+      <c r="V45" s="3"/>
+      <c r="Y45" s="3">
+        <v>221</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>181</v>
+      </c>
+      <c r="AA45" s="3">
         <v>248</v>
       </c>
-      <c r="I40" s="3">
-        <v>-389</v>
-      </c>
-      <c r="J40" s="3">
-        <f t="shared" ref="J40:J41" si="42">Y40-I40-H40-G40</f>
-        <v>297</v>
-      </c>
-      <c r="K40" s="3">
-        <v>108</v>
-      </c>
-      <c r="L40" s="3">
-        <v>253</v>
-      </c>
-      <c r="M40" s="3">
-        <v>371</v>
-      </c>
-      <c r="N40" s="3">
-        <f t="shared" ref="N40:N41" si="43">Z40-M40-L40-K40</f>
-        <v>449</v>
-      </c>
-      <c r="O40" s="3">
-        <v>333</v>
-      </c>
-      <c r="P40" s="3">
-        <v>315</v>
-      </c>
-      <c r="Q40" s="3">
-        <v>432</v>
-      </c>
-      <c r="R40" s="3">
-        <f>R39*0.17</f>
-        <v>382.08972199999988</v>
-      </c>
-      <c r="U40" s="3">
-        <v>421</v>
-      </c>
-      <c r="V40" s="3">
-        <v>575</v>
-      </c>
-      <c r="W40" s="3">
-        <v>786</v>
-      </c>
-      <c r="X40" s="3">
-        <v>790</v>
-      </c>
-      <c r="Y40" s="3">
-        <v>456</v>
-      </c>
-      <c r="Z40" s="3">
-        <v>1181</v>
-      </c>
-      <c r="AA40" s="3">
-        <f t="shared" ref="AA40:AA41" si="44">SUM(O40:R40)</f>
-        <v>1462.0897219999999</v>
-      </c>
-      <c r="AB40" s="3">
-        <f t="shared" ref="AB40:AK40" si="45">AB39*0.15</f>
-        <v>1446.0070512000013</v>
-      </c>
-      <c r="AC40" s="3">
+      <c r="AB45" s="3">
+        <v>111</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>185</v>
+      </c>
+      <c r="AD45" s="3">
+        <v>239</v>
+      </c>
+      <c r="AE45" s="3">
+        <f t="shared" si="43"/>
+        <v>337</v>
+      </c>
+      <c r="AF45" s="3">
+        <f t="shared" ref="AF45:AO45" si="45">AF43*0.03</f>
+        <v>235.87684799999985</v>
+      </c>
+      <c r="AG45" s="3">
         <f t="shared" si="45"/>
-        <v>1573.0894829279994</v>
-      </c>
-      <c r="AD40" s="3">
+        <v>250.90945739999987</v>
+      </c>
+      <c r="AH45" s="3">
         <f t="shared" si="45"/>
-        <v>1657.2357132414015</v>
-      </c>
-      <c r="AE40" s="3">
+        <v>263.20145556599977</v>
+      </c>
+      <c r="AI45" s="3">
         <f t="shared" si="45"/>
-        <v>1723.9056394066863</v>
-      </c>
-      <c r="AF40" s="3">
+        <v>276.02504048573991</v>
+      </c>
+      <c r="AJ45" s="3">
         <f t="shared" si="45"/>
-        <v>1775.3126124656301</v>
-      </c>
-      <c r="AG40" s="3">
+        <v>286.46496456325025</v>
+      </c>
+      <c r="AK45" s="3">
         <f t="shared" si="45"/>
-        <v>1828.1536589588716</v>
-      </c>
-      <c r="AH40" s="3">
+        <v>297.23967809171501</v>
+      </c>
+      <c r="AL45" s="3">
         <f t="shared" si="45"/>
-        <v>1882.4686190559455</v>
-      </c>
-      <c r="AI40" s="3">
+        <v>304.28575777229094</v>
+      </c>
+      <c r="AM45" s="3">
         <f t="shared" si="45"/>
-        <v>1938.2984542976174</v>
-      </c>
-      <c r="AJ40" s="3">
+        <v>311.48377190766558</v>
+      </c>
+      <c r="AN45" s="3">
         <f t="shared" si="45"/>
-        <v>1995.6852796584003</v>
-      </c>
-      <c r="AK40" s="3">
+        <v>318.83686931554689</v>
+      </c>
+      <c r="AO45" s="3">
         <f t="shared" si="45"/>
-        <v>2054.6723965383958</v>
-      </c>
-    </row>
-    <row r="41" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C41" s="3">
-        <v>23</v>
-      </c>
-      <c r="D41" s="3">
-        <v>34</v>
-      </c>
-      <c r="E41" s="3">
-        <v>8</v>
-      </c>
-      <c r="F41" s="3">
-        <f t="shared" si="41"/>
-        <v>46</v>
-      </c>
-      <c r="G41" s="3">
-        <v>55</v>
-      </c>
-      <c r="H41" s="3">
-        <v>32</v>
-      </c>
-      <c r="I41" s="3">
-        <v>51</v>
-      </c>
-      <c r="J41" s="3">
-        <f t="shared" si="42"/>
-        <v>47</v>
-      </c>
-      <c r="K41" s="3">
-        <v>34</v>
-      </c>
-      <c r="L41" s="3">
-        <v>64</v>
-      </c>
-      <c r="M41" s="3">
-        <v>63</v>
-      </c>
-      <c r="N41" s="3">
-        <f t="shared" si="43"/>
-        <v>78</v>
-      </c>
-      <c r="O41" s="3">
-        <v>90</v>
-      </c>
-      <c r="P41" s="3">
-        <v>68</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>88</v>
-      </c>
-      <c r="R41" s="3">
-        <f>R39*0.03</f>
-        <v>67.427597999999975</v>
-      </c>
-      <c r="U41" s="3">
-        <v>221</v>
-      </c>
-      <c r="V41" s="3">
-        <v>181</v>
-      </c>
-      <c r="W41" s="3">
-        <v>248</v>
-      </c>
-      <c r="X41" s="3">
+        <v>326.34826289128358</v>
+      </c>
+    </row>
+    <row r="46" spans="2:139" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="5">
+        <f t="shared" ref="C46:P46" si="46">C43-C44-C45</f>
+        <v>1103</v>
+      </c>
+      <c r="D46" s="5">
+        <f t="shared" si="46"/>
+        <v>1304</v>
+      </c>
+      <c r="E46" s="5">
+        <f t="shared" si="46"/>
+        <v>1387</v>
+      </c>
+      <c r="F46" s="5">
+        <f t="shared" si="46"/>
+        <v>1422</v>
+      </c>
+      <c r="G46" s="5">
+        <f t="shared" si="46"/>
+        <v>1426</v>
+      </c>
+      <c r="H46" s="5">
+        <f t="shared" si="46"/>
+        <v>1327</v>
+      </c>
+      <c r="I46" s="5">
+        <f t="shared" si="46"/>
+        <v>-984</v>
+      </c>
+      <c r="J46" s="5">
+        <f t="shared" si="46"/>
+        <v>1426</v>
+      </c>
+      <c r="K46" s="5">
+        <f t="shared" si="46"/>
+        <v>1709</v>
+      </c>
+      <c r="L46" s="5">
+        <f t="shared" si="46"/>
         <v>111</v>
       </c>
-      <c r="Y41" s="3">
-        <v>185</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>239</v>
-      </c>
-      <c r="AA41" s="3">
-        <f t="shared" si="44"/>
-        <v>313.42759799999999</v>
-      </c>
-      <c r="AB41" s="3">
-        <f t="shared" ref="AB41:AK41" si="46">AB39*0.03</f>
-        <v>289.20141024000026</v>
-      </c>
-      <c r="AC41" s="3">
+      <c r="M46" s="5">
         <f t="shared" si="46"/>
-        <v>314.61789658559991</v>
-      </c>
-      <c r="AD41" s="3">
+        <v>1472</v>
+      </c>
+      <c r="N46" s="5">
         <f t="shared" si="46"/>
-        <v>331.44714264828031</v>
-      </c>
-      <c r="AE41" s="3">
+        <v>1482</v>
+      </c>
+      <c r="O46" s="5">
         <f t="shared" si="46"/>
-        <v>344.78112788133728</v>
-      </c>
-      <c r="AF41" s="3">
+        <v>1535</v>
+      </c>
+      <c r="P46" s="5">
         <f t="shared" si="46"/>
-        <v>355.06252249312604</v>
-      </c>
-      <c r="AG41" s="3">
-        <f t="shared" si="46"/>
-        <v>365.63073179177428</v>
-      </c>
-      <c r="AH41" s="3">
-        <f t="shared" si="46"/>
-        <v>376.49372381118911</v>
-      </c>
-      <c r="AI41" s="3">
-        <f t="shared" si="46"/>
-        <v>387.65969085952349</v>
-      </c>
-      <c r="AJ41" s="3">
-        <f t="shared" si="46"/>
-        <v>399.13705593168004</v>
-      </c>
-      <c r="AK41" s="3">
-        <f t="shared" si="46"/>
-        <v>410.93447930767917</v>
-      </c>
-    </row>
-    <row r="42" spans="2:135" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C42" s="5">
-        <f t="shared" ref="C42:P42" si="47">C39-C40-C41</f>
-        <v>1103</v>
-      </c>
-      <c r="D42" s="5">
+        <v>1657</v>
+      </c>
+      <c r="Q46" s="5">
+        <f t="shared" ref="Q46:R46" si="47">Q43-Q44-Q45</f>
+        <v>1918</v>
+      </c>
+      <c r="R46" s="5">
         <f t="shared" si="47"/>
-        <v>1304</v>
-      </c>
-      <c r="E42" s="5">
-        <f t="shared" si="47"/>
-        <v>1387</v>
-      </c>
-      <c r="F42" s="5">
-        <f t="shared" si="47"/>
-        <v>1422</v>
-      </c>
-      <c r="G42" s="5">
-        <f t="shared" si="47"/>
-        <v>1426</v>
-      </c>
-      <c r="H42" s="5">
-        <f t="shared" si="47"/>
-        <v>1327</v>
-      </c>
-      <c r="I42" s="5">
-        <f t="shared" si="47"/>
-        <v>-984</v>
-      </c>
-      <c r="J42" s="5">
-        <f t="shared" si="47"/>
-        <v>1426</v>
-      </c>
-      <c r="K42" s="5">
-        <f t="shared" si="47"/>
-        <v>1709</v>
-      </c>
-      <c r="L42" s="5">
-        <f t="shared" si="47"/>
-        <v>111</v>
-      </c>
-      <c r="M42" s="5">
-        <f t="shared" si="47"/>
-        <v>1472</v>
-      </c>
-      <c r="N42" s="5">
-        <f t="shared" si="47"/>
-        <v>1482</v>
-      </c>
-      <c r="O42" s="5">
-        <f t="shared" si="47"/>
-        <v>1535</v>
-      </c>
-      <c r="P42" s="5">
-        <f t="shared" si="47"/>
-        <v>1657</v>
-      </c>
-      <c r="Q42" s="5">
-        <f t="shared" ref="Q42:R42" si="48">Q39-Q40-Q41</f>
-        <v>1918</v>
-      </c>
-      <c r="R42" s="5">
+        <v>1622</v>
+      </c>
+      <c r="S46" s="5"/>
+      <c r="T46" s="5"/>
+      <c r="U46" s="5"/>
+      <c r="V46" s="5"/>
+      <c r="Y46" s="5">
+        <f t="shared" ref="Y46:AD46" si="48">Y43-Y44-Y45</f>
+        <v>3510</v>
+      </c>
+      <c r="Z46" s="5">
         <f t="shared" si="48"/>
-        <v>1798.0692799999993</v>
-      </c>
-      <c r="U42" s="5">
-        <f t="shared" ref="U42:Z42" si="49">U39-U40-U41</f>
-        <v>3510</v>
-      </c>
-      <c r="V42" s="5">
+        <v>-3109</v>
+      </c>
+      <c r="AA46" s="5">
+        <f t="shared" si="48"/>
+        <v>3897</v>
+      </c>
+      <c r="AB46" s="5">
+        <f t="shared" si="48"/>
+        <v>5216</v>
+      </c>
+      <c r="AC46" s="5">
+        <f t="shared" si="48"/>
+        <v>3195</v>
+      </c>
+      <c r="AD46" s="5">
+        <f t="shared" si="48"/>
+        <v>4774</v>
+      </c>
+      <c r="AE46" s="5">
+        <f t="shared" ref="AE46:AO46" si="49">AE43-AE44-AE45</f>
+        <v>5777.5699999999924</v>
+      </c>
+      <c r="AF46" s="5">
         <f t="shared" si="49"/>
-        <v>-3109</v>
-      </c>
-      <c r="W42" s="5">
+        <v>6447.3005119999962</v>
+      </c>
+      <c r="AG46" s="5">
         <f t="shared" si="49"/>
-        <v>3897</v>
-      </c>
-      <c r="X42" s="5">
+        <v>6858.191835599996</v>
+      </c>
+      <c r="AH46" s="5">
         <f t="shared" si="49"/>
-        <v>5216</v>
-      </c>
-      <c r="Y42" s="5">
+        <v>7194.1731188039939</v>
+      </c>
+      <c r="AI46" s="5">
         <f t="shared" si="49"/>
-        <v>3195</v>
-      </c>
-      <c r="Z42" s="5">
+        <v>7544.6844399435586</v>
+      </c>
+      <c r="AJ46" s="5">
         <f t="shared" si="49"/>
-        <v>4774</v>
-      </c>
-      <c r="AA42" s="5">
-        <f t="shared" ref="AA42:AK42" si="50">AA39-AA40-AA41</f>
-        <v>6908.0692799999988</v>
-      </c>
-      <c r="AB42" s="5">
+        <v>7830.0423647288408</v>
+      </c>
+      <c r="AK46" s="5">
+        <f t="shared" si="49"/>
+        <v>8124.5512011735445</v>
+      </c>
+      <c r="AL46" s="5">
+        <f t="shared" si="49"/>
+        <v>8317.1440457759527</v>
+      </c>
+      <c r="AM46" s="5">
+        <f t="shared" si="49"/>
+        <v>8513.8897654761931</v>
+      </c>
+      <c r="AN46" s="5">
+        <f t="shared" si="49"/>
+        <v>8714.8744279582825</v>
+      </c>
+      <c r="AO46" s="5">
+        <f t="shared" si="49"/>
+        <v>8920.1858523617502</v>
+      </c>
+      <c r="AP46" s="4">
+        <f>AO46*(1+$AS$56)</f>
+        <v>8830.9839938381319</v>
+      </c>
+      <c r="AQ46" s="4">
+        <f t="shared" ref="AQ46:DB46" si="50">AP46*(1+$AS$56)</f>
+        <v>8742.6741538997503</v>
+      </c>
+      <c r="AR46" s="4">
         <f t="shared" si="50"/>
-        <v>7904.8385465600068</v>
-      </c>
-      <c r="AC42" s="5">
+        <v>8655.2474123607535</v>
+      </c>
+      <c r="AS46" s="4">
         <f t="shared" si="50"/>
-        <v>8599.5558400063983</v>
-      </c>
-      <c r="AD42" s="5">
+        <v>8568.6949382371458</v>
+      </c>
+      <c r="AT46" s="4">
         <f t="shared" si="50"/>
-        <v>9059.5552323863285</v>
-      </c>
-      <c r="AE42" s="5">
+        <v>8483.0079888547734</v>
+      </c>
+      <c r="AU46" s="4">
         <f t="shared" si="50"/>
-        <v>9424.0174954232189</v>
-      </c>
-      <c r="AF42" s="5">
+        <v>8398.177908966225</v>
+      </c>
+      <c r="AV46" s="4">
         <f t="shared" si="50"/>
-        <v>9705.042281478778</v>
-      </c>
-      <c r="AG42" s="5">
+        <v>8314.1961298765618</v>
+      </c>
+      <c r="AW46" s="4">
         <f t="shared" si="50"/>
-        <v>9993.9066689751635</v>
-      </c>
-      <c r="AH42" s="5">
+        <v>8231.0541685777953</v>
+      </c>
+      <c r="AX46" s="4">
         <f t="shared" si="50"/>
-        <v>10290.82845083917</v>
-      </c>
-      <c r="AI42" s="5">
+        <v>8148.7436268920173</v>
+      </c>
+      <c r="AY46" s="4">
         <f t="shared" si="50"/>
-        <v>10596.031550160309</v>
-      </c>
-      <c r="AJ42" s="5">
+        <v>8067.2561906230967</v>
+      </c>
+      <c r="AZ46" s="4">
         <f t="shared" si="50"/>
-        <v>10909.746195465921</v>
-      </c>
-      <c r="AK42" s="5">
+        <v>7986.5836287168659</v>
+      </c>
+      <c r="BA46" s="4">
         <f t="shared" si="50"/>
-        <v>11232.209101076565</v>
-      </c>
-      <c r="AL42" s="4">
-        <f>AK42*(1+$AO$52)</f>
-        <v>11119.887010065799</v>
-      </c>
-      <c r="AM42" s="4">
-        <f t="shared" ref="AM42:CX42" si="51">AL42*(1+$AO$52)</f>
-        <v>11008.688139965141</v>
-      </c>
-      <c r="AN42" s="4">
+        <v>7906.7177924296975</v>
+      </c>
+      <c r="BB46" s="4">
+        <f t="shared" si="50"/>
+        <v>7827.6506145054009</v>
+      </c>
+      <c r="BC46" s="4">
+        <f t="shared" si="50"/>
+        <v>7749.3741083603472</v>
+      </c>
+      <c r="BD46" s="4">
+        <f t="shared" si="50"/>
+        <v>7671.8803672767435</v>
+      </c>
+      <c r="BE46" s="4">
+        <f t="shared" si="50"/>
+        <v>7595.161563603976</v>
+      </c>
+      <c r="BF46" s="4">
+        <f t="shared" si="50"/>
+        <v>7519.2099479679364</v>
+      </c>
+      <c r="BG46" s="4">
+        <f t="shared" si="50"/>
+        <v>7444.0178484882572</v>
+      </c>
+      <c r="BH46" s="4">
+        <f t="shared" si="50"/>
+        <v>7369.5776700033748</v>
+      </c>
+      <c r="BI46" s="4">
+        <f t="shared" si="50"/>
+        <v>7295.8818933033408</v>
+      </c>
+      <c r="BJ46" s="4">
+        <f t="shared" si="50"/>
+        <v>7222.9230743703074</v>
+      </c>
+      <c r="BK46" s="4">
+        <f t="shared" si="50"/>
+        <v>7150.6938436266046</v>
+      </c>
+      <c r="BL46" s="4">
+        <f t="shared" si="50"/>
+        <v>7079.1869051903386</v>
+      </c>
+      <c r="BM46" s="4">
+        <f t="shared" si="50"/>
+        <v>7008.395036138435</v>
+      </c>
+      <c r="BN46" s="4">
+        <f t="shared" si="50"/>
+        <v>6938.3110857770507</v>
+      </c>
+      <c r="BO46" s="4">
+        <f t="shared" si="50"/>
+        <v>6868.9279749192801</v>
+      </c>
+      <c r="BP46" s="4">
+        <f t="shared" si="50"/>
+        <v>6800.2386951700873</v>
+      </c>
+      <c r="BQ46" s="4">
+        <f t="shared" si="50"/>
+        <v>6732.2363082183865</v>
+      </c>
+      <c r="BR46" s="4">
+        <f t="shared" si="50"/>
+        <v>6664.9139451362025</v>
+      </c>
+      <c r="BS46" s="4">
+        <f t="shared" si="50"/>
+        <v>6598.2648056848402</v>
+      </c>
+      <c r="BT46" s="4">
+        <f t="shared" si="50"/>
+        <v>6532.2821576279921</v>
+      </c>
+      <c r="BU46" s="4">
+        <f t="shared" si="50"/>
+        <v>6466.9593360517119</v>
+      </c>
+      <c r="BV46" s="4">
+        <f t="shared" si="50"/>
+        <v>6402.289742691195</v>
+      </c>
+      <c r="BW46" s="4">
+        <f t="shared" si="50"/>
+        <v>6338.2668452642829</v>
+      </c>
+      <c r="BX46" s="4">
+        <f t="shared" si="50"/>
+        <v>6274.8841768116399</v>
+      </c>
+      <c r="BY46" s="4">
+        <f t="shared" si="50"/>
+        <v>6212.1353350435238</v>
+      </c>
+      <c r="BZ46" s="4">
+        <f t="shared" si="50"/>
+        <v>6150.0139816930887</v>
+      </c>
+      <c r="CA46" s="4">
+        <f t="shared" si="50"/>
+        <v>6088.513841876158</v>
+      </c>
+      <c r="CB46" s="4">
+        <f t="shared" si="50"/>
+        <v>6027.6287034573961</v>
+      </c>
+      <c r="CC46" s="4">
+        <f t="shared" si="50"/>
+        <v>5967.352416422822</v>
+      </c>
+      <c r="CD46" s="4">
+        <f t="shared" si="50"/>
+        <v>5907.6788922585938</v>
+      </c>
+      <c r="CE46" s="4">
+        <f t="shared" si="50"/>
+        <v>5848.6021033360075</v>
+      </c>
+      <c r="CF46" s="4">
+        <f t="shared" si="50"/>
+        <v>5790.1160823026476</v>
+      </c>
+      <c r="CG46" s="4">
+        <f t="shared" si="50"/>
+        <v>5732.2149214796209</v>
+      </c>
+      <c r="CH46" s="4">
+        <f t="shared" si="50"/>
+        <v>5674.892772264825</v>
+      </c>
+      <c r="CI46" s="4">
+        <f t="shared" si="50"/>
+        <v>5618.1438445421763</v>
+      </c>
+      <c r="CJ46" s="4">
+        <f t="shared" si="50"/>
+        <v>5561.9624060967544</v>
+      </c>
+      <c r="CK46" s="4">
+        <f t="shared" si="50"/>
+        <v>5506.3427820357865</v>
+      </c>
+      <c r="CL46" s="4">
+        <f t="shared" si="50"/>
+        <v>5451.2793542154286</v>
+      </c>
+      <c r="CM46" s="4">
+        <f t="shared" si="50"/>
+        <v>5396.7665606732744</v>
+      </c>
+      <c r="CN46" s="4">
+        <f t="shared" si="50"/>
+        <v>5342.7988950665413</v>
+      </c>
+      <c r="CO46" s="4">
+        <f t="shared" si="50"/>
+        <v>5289.3709061158761</v>
+      </c>
+      <c r="CP46" s="4">
+        <f t="shared" si="50"/>
+        <v>5236.4771970547172</v>
+      </c>
+      <c r="CQ46" s="4">
+        <f t="shared" si="50"/>
+        <v>5184.1124250841704</v>
+      </c>
+      <c r="CR46" s="4">
+        <f t="shared" si="50"/>
+        <v>5132.2713008333285</v>
+      </c>
+      <c r="CS46" s="4">
+        <f t="shared" si="50"/>
+        <v>5080.9485878249952</v>
+      </c>
+      <c r="CT46" s="4">
+        <f t="shared" si="50"/>
+        <v>5030.1391019467455</v>
+      </c>
+      <c r="CU46" s="4">
+        <f t="shared" si="50"/>
+        <v>4979.8377109272778</v>
+      </c>
+      <c r="CV46" s="4">
+        <f t="shared" si="50"/>
+        <v>4930.0393338180047</v>
+      </c>
+      <c r="CW46" s="4">
+        <f t="shared" si="50"/>
+        <v>4880.738940479825</v>
+      </c>
+      <c r="CX46" s="4">
+        <f t="shared" si="50"/>
+        <v>4831.9315510750266</v>
+      </c>
+      <c r="CY46" s="4">
+        <f t="shared" si="50"/>
+        <v>4783.6122355642765</v>
+      </c>
+      <c r="CZ46" s="4">
+        <f t="shared" si="50"/>
+        <v>4735.7761132086334</v>
+      </c>
+      <c r="DA46" s="4">
+        <f t="shared" si="50"/>
+        <v>4688.4183520765473</v>
+      </c>
+      <c r="DB46" s="4">
+        <f t="shared" si="50"/>
+        <v>4641.5341685557814</v>
+      </c>
+      <c r="DC46" s="4">
+        <f t="shared" ref="DC46:EI46" si="51">DB46*(1+$AS$56)</f>
+        <v>4595.1188268702235</v>
+      </c>
+      <c r="DD46" s="4">
         <f t="shared" si="51"/>
-        <v>10898.60125856549</v>
-      </c>
-      <c r="AO42" s="4">
+        <v>4549.1676386015215</v>
+      </c>
+      <c r="DE46" s="4">
         <f t="shared" si="51"/>
-        <v>10789.615245979834</v>
-      </c>
-      <c r="AP42" s="4">
+        <v>4503.6759622155059</v>
+      </c>
+      <c r="DF46" s="4">
         <f t="shared" si="51"/>
-        <v>10681.719093520036</v>
-      </c>
-      <c r="AQ42" s="4">
+        <v>4458.639202593351</v>
+      </c>
+      <c r="DG46" s="4">
         <f t="shared" si="51"/>
-        <v>10574.901902584836</v>
-      </c>
-      <c r="AR42" s="4">
+        <v>4414.0528105674175</v>
+      </c>
+      <c r="DH46" s="4">
         <f t="shared" si="51"/>
-        <v>10469.152883558987</v>
-      </c>
-      <c r="AS42" s="4">
+        <v>4369.9122824617434</v>
+      </c>
+      <c r="DI46" s="4">
         <f t="shared" si="51"/>
-        <v>10364.461354723397</v>
-      </c>
-      <c r="AT42" s="4">
+        <v>4326.2131596371255</v>
+      </c>
+      <c r="DJ46" s="4">
         <f t="shared" si="51"/>
-        <v>10260.816741176162</v>
-      </c>
-      <c r="AU42" s="4">
+        <v>4282.951028040754</v>
+      </c>
+      <c r="DK46" s="4">
         <f t="shared" si="51"/>
-        <v>10158.208573764401</v>
-      </c>
-      <c r="AV42" s="4">
+        <v>4240.1215177603463</v>
+      </c>
+      <c r="DL46" s="4">
         <f t="shared" si="51"/>
-        <v>10056.626488026757</v>
-      </c>
-      <c r="AW42" s="4">
+        <v>4197.720302582743</v>
+      </c>
+      <c r="DM46" s="4">
         <f t="shared" si="51"/>
-        <v>9956.0602231464891</v>
-      </c>
-      <c r="AX42" s="4">
+        <v>4155.7430995569157</v>
+      </c>
+      <c r="DN46" s="4">
         <f t="shared" si="51"/>
-        <v>9856.4996209150249</v>
-      </c>
-      <c r="AY42" s="4">
+        <v>4114.1856685613466</v>
+      </c>
+      <c r="DO46" s="4">
         <f t="shared" si="51"/>
-        <v>9757.9346247058747</v>
-      </c>
-      <c r="AZ42" s="4">
+        <v>4073.0438118757329</v>
+      </c>
+      <c r="DP46" s="4">
         <f t="shared" si="51"/>
-        <v>9660.3552784588155</v>
-      </c>
-      <c r="BA42" s="4">
+        <v>4032.3133737569756</v>
+      </c>
+      <c r="DQ46" s="4">
         <f t="shared" si="51"/>
-        <v>9563.7517256742267</v>
-      </c>
-      <c r="BB42" s="4">
+        <v>3991.990240019406</v>
+      </c>
+      <c r="DR46" s="4">
         <f t="shared" si="51"/>
-        <v>9468.1142084174844</v>
-      </c>
-      <c r="BC42" s="4">
+        <v>3952.0703376192118</v>
+      </c>
+      <c r="DS46" s="4">
         <f t="shared" si="51"/>
-        <v>9373.4330663333094</v>
-      </c>
-      <c r="BD42" s="4">
+        <v>3912.5496342430197</v>
+      </c>
+      <c r="DT46" s="4">
         <f t="shared" si="51"/>
-        <v>9279.6987356699756</v>
-      </c>
-      <c r="BE42" s="4">
+        <v>3873.4241379005894</v>
+      </c>
+      <c r="DU46" s="4">
         <f t="shared" si="51"/>
-        <v>9186.9017483132757</v>
-      </c>
-      <c r="BF42" s="4">
+        <v>3834.6898965215833</v>
+      </c>
+      <c r="DV46" s="4">
         <f t="shared" si="51"/>
-        <v>9095.0327308301421</v>
-      </c>
-      <c r="BG42" s="4">
+        <v>3796.3429975563672</v>
+      </c>
+      <c r="DW46" s="4">
         <f t="shared" si="51"/>
-        <v>9004.0824035218411</v>
-      </c>
-      <c r="BH42" s="4">
+        <v>3758.3795675808037</v>
+      </c>
+      <c r="DX46" s="4">
         <f t="shared" si="51"/>
-        <v>8914.0415794866221</v>
-      </c>
-      <c r="BI42" s="4">
+        <v>3720.7957719049955</v>
+      </c>
+      <c r="DY46" s="4">
         <f t="shared" si="51"/>
-        <v>8824.9011636917567</v>
-      </c>
-      <c r="BJ42" s="4">
+        <v>3683.5878141859457</v>
+      </c>
+      <c r="DZ46" s="4">
         <f t="shared" si="51"/>
-        <v>8736.6521520548395</v>
-      </c>
-      <c r="BK42" s="4">
+        <v>3646.7519360440861</v>
+      </c>
+      <c r="EA46" s="4">
         <f t="shared" si="51"/>
-        <v>8649.2856305342902</v>
-      </c>
-      <c r="BL42" s="4">
+        <v>3610.2844166836453</v>
+      </c>
+      <c r="EB46" s="4">
         <f t="shared" si="51"/>
-        <v>8562.7927742289467</v>
-      </c>
-      <c r="BM42" s="4">
+        <v>3574.181572516809</v>
+      </c>
+      <c r="EC46" s="4">
         <f t="shared" si="51"/>
-        <v>8477.1648464866576</v>
-      </c>
-      <c r="BN42" s="4">
+        <v>3538.4397567916408</v>
+      </c>
+      <c r="ED46" s="4">
         <f t="shared" si="51"/>
-        <v>8392.3931980217912</v>
-      </c>
-      <c r="BO42" s="4">
+        <v>3503.0553592237243</v>
+      </c>
+      <c r="EE46" s="4">
         <f t="shared" si="51"/>
-        <v>8308.4692660415731</v>
-      </c>
-      <c r="BP42" s="4">
+        <v>3468.0248056314872</v>
+      </c>
+      <c r="EF46" s="4">
         <f t="shared" si="51"/>
-        <v>8225.3845733811577</v>
-      </c>
-      <c r="BQ42" s="4">
+        <v>3433.3445575751721</v>
+      </c>
+      <c r="EG46" s="4">
         <f t="shared" si="51"/>
-        <v>8143.1307276473462</v>
-      </c>
-      <c r="BR42" s="4">
+        <v>3399.0111119994203</v>
+      </c>
+      <c r="EH46" s="4">
         <f t="shared" si="51"/>
-        <v>8061.6994203708728</v>
-      </c>
-      <c r="BS42" s="4">
+        <v>3365.0210008794261</v>
+      </c>
+      <c r="EI46" s="4">
         <f t="shared" si="51"/>
-        <v>7981.0824261671642</v>
-      </c>
-      <c r="BT42" s="4">
-        <f t="shared" si="51"/>
-        <v>7901.2716019054924</v>
-      </c>
-      <c r="BU42" s="4">
-        <f t="shared" si="51"/>
-        <v>7822.2588858864374</v>
-      </c>
-      <c r="BV42" s="4">
-        <f t="shared" si="51"/>
-        <v>7744.0362970275728</v>
-      </c>
-      <c r="BW42" s="4">
-        <f t="shared" si="51"/>
-        <v>7666.5959340572972</v>
-      </c>
-      <c r="BX42" s="4">
-        <f t="shared" si="51"/>
-        <v>7589.9299747167242</v>
-      </c>
-      <c r="BY42" s="4">
-        <f t="shared" si="51"/>
-        <v>7514.0306749695574</v>
-      </c>
-      <c r="BZ42" s="4">
-        <f t="shared" si="51"/>
-        <v>7438.8903682198616</v>
-      </c>
-      <c r="CA42" s="4">
-        <f t="shared" si="51"/>
-        <v>7364.5014645376632</v>
-      </c>
-      <c r="CB42" s="4">
-        <f t="shared" si="51"/>
-        <v>7290.8564498922869</v>
-      </c>
-      <c r="CC42" s="4">
-        <f t="shared" si="51"/>
-        <v>7217.9478853933642</v>
-      </c>
-      <c r="CD42" s="4">
-        <f t="shared" si="51"/>
-        <v>7145.7684065394305</v>
-      </c>
-      <c r="CE42" s="4">
-        <f t="shared" si="51"/>
-        <v>7074.3107224740361</v>
-      </c>
-      <c r="CF42" s="4">
-        <f t="shared" si="51"/>
-        <v>7003.5676152492961</v>
-      </c>
-      <c r="CG42" s="4">
-        <f t="shared" si="51"/>
-        <v>6933.5319390968034</v>
-      </c>
-      <c r="CH42" s="4">
-        <f t="shared" si="51"/>
-        <v>6864.1966197058355</v>
-      </c>
-      <c r="CI42" s="4">
-        <f t="shared" si="51"/>
-        <v>6795.5546535087769</v>
-      </c>
-      <c r="CJ42" s="4">
-        <f t="shared" si="51"/>
-        <v>6727.5991069736892</v>
-      </c>
-      <c r="CK42" s="4">
-        <f t="shared" si="51"/>
-        <v>6660.3231159039524</v>
-      </c>
-      <c r="CL42" s="4">
-        <f t="shared" si="51"/>
-        <v>6593.7198847449126</v>
-      </c>
-      <c r="CM42" s="4">
-        <f t="shared" si="51"/>
-        <v>6527.7826858974631</v>
-      </c>
-      <c r="CN42" s="4">
-        <f t="shared" si="51"/>
-        <v>6462.5048590384886</v>
-      </c>
-      <c r="CO42" s="4">
-        <f t="shared" si="51"/>
-        <v>6397.8798104481039</v>
-      </c>
-      <c r="CP42" s="4">
-        <f t="shared" si="51"/>
-        <v>6333.9010123436228</v>
-      </c>
-      <c r="CQ42" s="4">
-        <f t="shared" si="51"/>
-        <v>6270.5620022201865</v>
-      </c>
-      <c r="CR42" s="4">
-        <f t="shared" si="51"/>
-        <v>6207.8563821979842</v>
-      </c>
-      <c r="CS42" s="4">
-        <f t="shared" si="51"/>
-        <v>6145.7778183760047</v>
-      </c>
-      <c r="CT42" s="4">
-        <f t="shared" si="51"/>
-        <v>6084.320040192245</v>
-      </c>
-      <c r="CU42" s="4">
-        <f t="shared" si="51"/>
-        <v>6023.4768397903226</v>
-      </c>
-      <c r="CV42" s="4">
-        <f t="shared" si="51"/>
-        <v>5963.2420713924193</v>
-      </c>
-      <c r="CW42" s="4">
-        <f t="shared" si="51"/>
-        <v>5903.6096506784952</v>
-      </c>
-      <c r="CX42" s="4">
-        <f t="shared" si="51"/>
-        <v>5844.5735541717104</v>
-      </c>
-      <c r="CY42" s="4">
-        <f t="shared" ref="CY42:EE42" si="52">CX42*(1+$AO$52)</f>
-        <v>5786.1278186299933</v>
-      </c>
-      <c r="CZ42" s="4">
-        <f t="shared" si="52"/>
-        <v>5728.266540443693</v>
-      </c>
-      <c r="DA42" s="4">
-        <f t="shared" si="52"/>
-        <v>5670.9838750392564</v>
-      </c>
-      <c r="DB42" s="4">
-        <f t="shared" si="52"/>
-        <v>5614.2740362888635</v>
-      </c>
-      <c r="DC42" s="4">
-        <f t="shared" si="52"/>
-        <v>5558.1312959259749</v>
-      </c>
-      <c r="DD42" s="4">
-        <f t="shared" si="52"/>
-        <v>5502.5499829667151</v>
-      </c>
-      <c r="DE42" s="4">
-        <f t="shared" si="52"/>
-        <v>5447.5244831370483</v>
-      </c>
-      <c r="DF42" s="4">
-        <f t="shared" si="52"/>
-        <v>5393.049238305678</v>
-      </c>
-      <c r="DG42" s="4">
-        <f t="shared" si="52"/>
-        <v>5339.1187459226212</v>
-      </c>
-      <c r="DH42" s="4">
-        <f t="shared" si="52"/>
-        <v>5285.7275584633953</v>
-      </c>
-      <c r="DI42" s="4">
-        <f t="shared" si="52"/>
-        <v>5232.8702828787609</v>
-      </c>
-      <c r="DJ42" s="4">
-        <f t="shared" si="52"/>
-        <v>5180.5415800499732</v>
-      </c>
-      <c r="DK42" s="4">
-        <f t="shared" si="52"/>
-        <v>5128.7361642494734</v>
-      </c>
-      <c r="DL42" s="4">
-        <f t="shared" si="52"/>
-        <v>5077.4488026069785</v>
-      </c>
-      <c r="DM42" s="4">
-        <f t="shared" si="52"/>
-        <v>5026.6743145809087</v>
-      </c>
-      <c r="DN42" s="4">
-        <f t="shared" si="52"/>
-        <v>4976.4075714350993</v>
-      </c>
-      <c r="DO42" s="4">
-        <f t="shared" si="52"/>
-        <v>4926.6434957207484</v>
-      </c>
-      <c r="DP42" s="4">
-        <f t="shared" si="52"/>
-        <v>4877.3770607635406</v>
-      </c>
-      <c r="DQ42" s="4">
-        <f t="shared" si="52"/>
-        <v>4828.6032901559056</v>
-      </c>
-      <c r="DR42" s="4">
-        <f t="shared" si="52"/>
-        <v>4780.3172572543463</v>
-      </c>
-      <c r="DS42" s="4">
-        <f t="shared" si="52"/>
-        <v>4732.5140846818031</v>
-      </c>
-      <c r="DT42" s="4">
-        <f t="shared" si="52"/>
-        <v>4685.1889438349854</v>
-      </c>
-      <c r="DU42" s="4">
-        <f t="shared" si="52"/>
-        <v>4638.3370543966357</v>
-      </c>
-      <c r="DV42" s="4">
-        <f t="shared" si="52"/>
-        <v>4591.9536838526692</v>
-      </c>
-      <c r="DW42" s="4">
-        <f t="shared" si="52"/>
-        <v>4546.034147014142</v>
-      </c>
-      <c r="DX42" s="4">
-        <f t="shared" si="52"/>
-        <v>4500.5738055440006</v>
-      </c>
-      <c r="DY42" s="4">
-        <f t="shared" si="52"/>
-        <v>4455.5680674885607</v>
-      </c>
-      <c r="DZ42" s="4">
-        <f t="shared" si="52"/>
-        <v>4411.0123868136752</v>
-      </c>
-      <c r="EA42" s="4">
-        <f t="shared" si="52"/>
-        <v>4366.9022629455385</v>
-      </c>
-      <c r="EB42" s="4">
-        <f t="shared" si="52"/>
-        <v>4323.2332403160826</v>
-      </c>
-      <c r="EC42" s="4">
-        <f t="shared" si="52"/>
-        <v>4280.0009079129213</v>
-      </c>
-      <c r="ED42" s="4">
-        <f t="shared" si="52"/>
-        <v>4237.2008988337921</v>
-      </c>
-      <c r="EE42" s="4">
-        <f t="shared" si="52"/>
-        <v>4194.8288898454539</v>
-      </c>
-    </row>
-    <row r="43" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B43" s="1" t="s">
+        <v>3331.3707908706319</v>
+      </c>
+    </row>
+    <row r="47" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C47" s="3">
         <v>1330</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D47" s="3">
         <v>1330</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E47" s="3">
         <v>1330</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F47" s="3">
         <v>1330</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G47" s="3">
         <v>1330</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H47" s="3">
         <v>1330</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I47" s="3">
         <v>1330</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J47" s="3">
         <v>1330</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K47" s="3">
         <v>1330</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L47" s="3">
         <v>1330</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M47" s="3">
         <v>1330</v>
       </c>
-      <c r="N43" s="3">
+      <c r="N47" s="3">
         <v>1330</v>
       </c>
-      <c r="O43" s="3">
+      <c r="O47" s="3">
         <v>1330</v>
       </c>
-      <c r="P43" s="3">
+      <c r="P47" s="3">
         <f>1338.5</f>
         <v>1338.5</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="Q47" s="3">
         <f>1343.1</f>
         <v>1343.1</v>
       </c>
-      <c r="R43" s="3">
-        <f>1343.1</f>
-        <v>1343.1</v>
-      </c>
-      <c r="U43" s="3">
-        <f t="shared" ref="U43:Z43" si="53">1332.1</f>
+      <c r="R47" s="3">
+        <f>1344.9</f>
+        <v>1344.9</v>
+      </c>
+      <c r="S47" s="3"/>
+      <c r="T47" s="3"/>
+      <c r="U47" s="3"/>
+      <c r="V47" s="3"/>
+      <c r="Y47" s="3">
+        <f t="shared" ref="Y47:AD47" si="52">1332.1</f>
         <v>1332.1</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Z47" s="3">
+        <f t="shared" si="52"/>
+        <v>1332.1</v>
+      </c>
+      <c r="AA47" s="3">
+        <f t="shared" si="52"/>
+        <v>1332.1</v>
+      </c>
+      <c r="AB47" s="3">
+        <f t="shared" si="52"/>
+        <v>1332.1</v>
+      </c>
+      <c r="AC47" s="3">
+        <f t="shared" si="52"/>
+        <v>1332.1</v>
+      </c>
+      <c r="AD47" s="3">
+        <f t="shared" si="52"/>
+        <v>1332.1</v>
+      </c>
+      <c r="AE47" s="3">
+        <f>1344.9</f>
+        <v>1344.9</v>
+      </c>
+      <c r="AF47" s="3">
+        <f>1344.9</f>
+        <v>1344.9</v>
+      </c>
+      <c r="AG47" s="3">
+        <f>1344.9</f>
+        <v>1344.9</v>
+      </c>
+      <c r="AH47" s="3">
+        <f>1344.9</f>
+        <v>1344.9</v>
+      </c>
+      <c r="AI47" s="3">
+        <f>1344.9</f>
+        <v>1344.9</v>
+      </c>
+      <c r="AJ47" s="3">
+        <f>1344.9</f>
+        <v>1344.9</v>
+      </c>
+      <c r="AK47" s="3">
+        <f>1344.9</f>
+        <v>1344.9</v>
+      </c>
+      <c r="AL47" s="3">
+        <f>1344.9</f>
+        <v>1344.9</v>
+      </c>
+      <c r="AM47" s="3">
+        <f>1344.9</f>
+        <v>1344.9</v>
+      </c>
+      <c r="AN47" s="3">
+        <f>1344.9</f>
+        <v>1344.9</v>
+      </c>
+      <c r="AO47" s="3">
+        <f>1344.9</f>
+        <v>1344.9</v>
+      </c>
+    </row>
+    <row r="48" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C48" s="6">
+        <f t="shared" ref="C48:P48" si="53">C46/C47</f>
+        <v>0.82932330827067668</v>
+      </c>
+      <c r="D48" s="6">
         <f t="shared" si="53"/>
-        <v>1332.1</v>
-      </c>
-      <c r="W43" s="3">
+        <v>0.98045112781954891</v>
+      </c>
+      <c r="E48" s="6">
         <f t="shared" si="53"/>
-        <v>1332.1</v>
-      </c>
-      <c r="X43" s="3">
+        <v>1.0428571428571429</v>
+      </c>
+      <c r="F48" s="6">
         <f t="shared" si="53"/>
-        <v>1332.1</v>
-      </c>
-      <c r="Y43" s="3">
+        <v>1.069172932330827</v>
+      </c>
+      <c r="G48" s="6">
         <f t="shared" si="53"/>
-        <v>1332.1</v>
-      </c>
-      <c r="Z43" s="3">
+        <v>1.0721804511278195</v>
+      </c>
+      <c r="H48" s="6">
         <f t="shared" si="53"/>
-        <v>1332.1</v>
-      </c>
-      <c r="AA43" s="3">
-        <f t="shared" ref="AA43:AK43" si="54">1343.1</f>
-        <v>1343.1</v>
-      </c>
-      <c r="AB43" s="3">
+        <v>0.9977443609022556</v>
+      </c>
+      <c r="I48" s="6">
+        <f t="shared" si="53"/>
+        <v>-0.73984962406015042</v>
+      </c>
+      <c r="J48" s="6">
+        <f t="shared" si="53"/>
+        <v>1.0721804511278195</v>
+      </c>
+      <c r="K48" s="6">
+        <f t="shared" si="53"/>
+        <v>1.2849624060150375</v>
+      </c>
+      <c r="L48" s="6">
+        <f t="shared" si="53"/>
+        <v>8.3458646616541357E-2</v>
+      </c>
+      <c r="M48" s="6">
+        <f t="shared" si="53"/>
+        <v>1.1067669172932331</v>
+      </c>
+      <c r="N48" s="6">
+        <f t="shared" si="53"/>
+        <v>1.1142857142857143</v>
+      </c>
+      <c r="O48" s="6">
+        <f t="shared" si="53"/>
+        <v>1.1541353383458646</v>
+      </c>
+      <c r="P48" s="6">
+        <f t="shared" si="53"/>
+        <v>1.2379529323870004</v>
+      </c>
+      <c r="Q48" s="6">
+        <f t="shared" ref="Q48:R48" si="54">Q46/Q47</f>
+        <v>1.4280396098577919</v>
+      </c>
+      <c r="R48" s="6">
         <f t="shared" si="54"/>
-        <v>1343.1</v>
-      </c>
-      <c r="AC43" s="3">
-        <f t="shared" si="54"/>
-        <v>1343.1</v>
-      </c>
-      <c r="AD43" s="3">
-        <f t="shared" si="54"/>
-        <v>1343.1</v>
-      </c>
-      <c r="AE43" s="3">
-        <f t="shared" si="54"/>
-        <v>1343.1</v>
-      </c>
-      <c r="AF43" s="3">
-        <f t="shared" si="54"/>
-        <v>1343.1</v>
-      </c>
-      <c r="AG43" s="3">
-        <f t="shared" si="54"/>
-        <v>1343.1</v>
-      </c>
-      <c r="AH43" s="3">
-        <f t="shared" si="54"/>
-        <v>1343.1</v>
-      </c>
-      <c r="AI43" s="3">
-        <f t="shared" si="54"/>
-        <v>1343.1</v>
-      </c>
-      <c r="AJ43" s="3">
-        <f t="shared" si="54"/>
-        <v>1343.1</v>
-      </c>
-      <c r="AK43" s="3">
-        <f t="shared" si="54"/>
-        <v>1343.1</v>
-      </c>
-    </row>
-    <row r="44" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B44" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C44" s="6">
-        <f t="shared" ref="C44:P44" si="55">C42/C43</f>
-        <v>0.82932330827067668</v>
-      </c>
-      <c r="D44" s="6">
+        <v>1.2060376236151387</v>
+      </c>
+      <c r="S48" s="6"/>
+      <c r="T48" s="6"/>
+      <c r="U48" s="6"/>
+      <c r="V48" s="6"/>
+      <c r="Y48" s="6">
+        <f t="shared" ref="Y48:AD48" si="55">Y46/Y47</f>
+        <v>2.6349373170182422</v>
+      </c>
+      <c r="Z48" s="6">
         <f t="shared" si="55"/>
-        <v>0.98045112781954891</v>
-      </c>
-      <c r="E44" s="6">
+        <v>-2.3339088657007734</v>
+      </c>
+      <c r="AA48" s="6">
         <f t="shared" si="55"/>
-        <v>1.0428571428571429</v>
-      </c>
-      <c r="F44" s="6">
+        <v>2.9254560468433302</v>
+      </c>
+      <c r="AB48" s="6">
         <f t="shared" si="55"/>
-        <v>1.069172932330827</v>
-      </c>
-      <c r="G44" s="6">
+        <v>3.9156219503040317</v>
+      </c>
+      <c r="AC48" s="6">
         <f t="shared" si="55"/>
-        <v>1.0721804511278195</v>
-      </c>
-      <c r="H44" s="6">
+        <v>2.3984685834396817</v>
+      </c>
+      <c r="AD48" s="6">
         <f t="shared" si="55"/>
-        <v>0.9977443609022556</v>
-      </c>
-      <c r="I44" s="6">
-        <f t="shared" si="55"/>
-        <v>-0.73984962406015042</v>
-      </c>
-      <c r="J44" s="6">
-        <f t="shared" si="55"/>
-        <v>1.0721804511278195</v>
-      </c>
-      <c r="K44" s="6">
-        <f t="shared" si="55"/>
-        <v>1.2849624060150375</v>
-      </c>
-      <c r="L44" s="6">
-        <f t="shared" si="55"/>
-        <v>8.3458646616541357E-2</v>
-      </c>
-      <c r="M44" s="6">
-        <f t="shared" si="55"/>
-        <v>1.1067669172932331</v>
-      </c>
-      <c r="N44" s="6">
-        <f t="shared" si="55"/>
-        <v>1.1142857142857143</v>
-      </c>
-      <c r="O44" s="6">
-        <f t="shared" si="55"/>
-        <v>1.1541353383458646</v>
-      </c>
-      <c r="P44" s="6">
-        <f t="shared" si="55"/>
-        <v>1.2379529323870004</v>
-      </c>
-      <c r="Q44" s="6">
-        <f t="shared" ref="Q44:R44" si="56">Q42/Q43</f>
-        <v>1.4280396098577919</v>
-      </c>
-      <c r="R44" s="6">
+        <v>3.5838150289017343</v>
+      </c>
+      <c r="AE48" s="6">
+        <f t="shared" ref="AE48:AO48" si="56">AE46/AE47</f>
+        <v>4.2959104766153562</v>
+      </c>
+      <c r="AF48" s="6">
         <f t="shared" si="56"/>
-        <v>1.3387456481274658</v>
-      </c>
-      <c r="U44" s="6">
-        <f t="shared" ref="U44:Z44" si="57">U42/U43</f>
-        <v>2.6349373170182422</v>
-      </c>
-      <c r="V44" s="6">
+        <v>4.7938884021116781</v>
+      </c>
+      <c r="AG48" s="6">
+        <f t="shared" si="56"/>
+        <v>5.0994065250947989</v>
+      </c>
+      <c r="AH48" s="6">
+        <f t="shared" si="56"/>
+        <v>5.349225309542712</v>
+      </c>
+      <c r="AI48" s="6">
+        <f t="shared" si="56"/>
+        <v>5.609847899430112</v>
+      </c>
+      <c r="AJ48" s="6">
+        <f t="shared" si="56"/>
+        <v>5.8220257005939775</v>
+      </c>
+      <c r="AK48" s="6">
+        <f t="shared" si="56"/>
+        <v>6.0410076594345634</v>
+      </c>
+      <c r="AL48" s="6">
+        <f t="shared" si="56"/>
+        <v>6.1842100124737547</v>
+      </c>
+      <c r="AM48" s="6">
+        <f t="shared" si="56"/>
+        <v>6.3305002345722299</v>
+      </c>
+      <c r="AN48" s="6">
+        <f t="shared" si="56"/>
+        <v>6.4799423213311638</v>
+      </c>
+      <c r="AO48" s="6">
+        <f t="shared" si="56"/>
+        <v>6.6326015706459582</v>
+      </c>
+    </row>
+    <row r="50" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q50" s="7">
+        <f>Q24/M24-1</f>
+        <v>7.7173144876325095E-2</v>
+      </c>
+      <c r="R50" s="7">
+        <f>R24/N24-1</f>
+        <v>2.6403078147804182E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q51" s="7">
+        <f t="shared" ref="Q51:R52" si="57">Q25/M25-1</f>
+        <v>0.16355850255560167</v>
+      </c>
+      <c r="R51" s="7">
         <f t="shared" si="57"/>
-        <v>-2.3339088657007734</v>
-      </c>
-      <c r="W44" s="6">
+        <v>0.25459109525696921</v>
+      </c>
+    </row>
+    <row r="52" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q52" s="7">
         <f t="shared" si="57"/>
-        <v>2.9254560468433302</v>
-      </c>
-      <c r="X44" s="6">
+        <v>0.10319448794237385</v>
+      </c>
+      <c r="R52" s="7">
         <f t="shared" si="57"/>
-        <v>3.9156219503040317</v>
-      </c>
-      <c r="Y44" s="6">
-        <f t="shared" si="57"/>
-        <v>2.3984685834396817</v>
-      </c>
-      <c r="Z44" s="6">
-        <f t="shared" si="57"/>
-        <v>3.5838150289017343</v>
-      </c>
-      <c r="AA44" s="6">
-        <f t="shared" ref="AA44:AK44" si="58">AA42/AA43</f>
-        <v>5.1433767254858163</v>
-      </c>
-      <c r="AB44" s="6">
+        <v>6.9861673885706299E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7">
+        <f t="shared" ref="G54:P56" si="58">G30/C30-1</f>
+        <v>7.7980104535491535E-2</v>
+      </c>
+      <c r="H54" s="7">
         <f t="shared" si="58"/>
-        <v>5.8855174942744455</v>
-      </c>
-      <c r="AC44" s="6">
+        <v>9.4061021373796683E-2</v>
+      </c>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7">
         <f t="shared" si="58"/>
-        <v>6.4027666145531974</v>
-      </c>
-      <c r="AD44" s="6">
+        <v>6.1955817802403335E-2</v>
+      </c>
+      <c r="K54" s="7">
         <f t="shared" si="58"/>
-        <v>6.7452574137341443</v>
-      </c>
-      <c r="AE44" s="6">
+        <v>0.11855791037772745</v>
+      </c>
+      <c r="L54" s="7">
         <f t="shared" si="58"/>
-        <v>7.0166164063906038</v>
-      </c>
-      <c r="AF44" s="6">
+        <v>8.5825068973230945E-2</v>
+      </c>
+      <c r="M54" s="7"/>
+      <c r="N54" s="7">
         <f t="shared" si="58"/>
-        <v>7.2258523426988148</v>
-      </c>
-      <c r="AG44" s="6">
+        <v>8.6800379455210797E-2</v>
+      </c>
+      <c r="O54" s="7">
         <f t="shared" si="58"/>
-        <v>7.4409252244621875</v>
-      </c>
-      <c r="AH44" s="6">
+        <v>2.0135635880584424E-2</v>
+      </c>
+      <c r="P54" s="7">
         <f t="shared" si="58"/>
-        <v>7.6619972085765546</v>
-      </c>
-      <c r="AI44" s="6">
+        <v>6.7916494986952403E-2</v>
+      </c>
+      <c r="Q54" s="7">
+        <f t="shared" ref="Q54:Q56" si="59">Q30/M30-1</f>
+        <v>0.10579276584171882</v>
+      </c>
+      <c r="R54" s="7">
+        <f t="shared" ref="R54:R56" si="60">R30/N30-1</f>
+        <v>-1</v>
+      </c>
+      <c r="S54" s="7"/>
+      <c r="T54" s="7"/>
+      <c r="U54" s="7"/>
+      <c r="V54" s="7"/>
+      <c r="Y54" s="7"/>
+      <c r="Z54" s="7">
+        <f>Z30/Y30-1</f>
+        <v>0.31277653191102495</v>
+      </c>
+      <c r="AA54" s="7">
+        <f t="shared" ref="AA54:AD54" si="61">AA30/Z30-1</f>
+        <v>0.13737620905376402</v>
+      </c>
+      <c r="AB54" s="7">
+        <f t="shared" si="61"/>
+        <v>3.0505378526486604E-2</v>
+      </c>
+      <c r="AC54" s="7">
+        <f t="shared" si="61"/>
+        <v>-2.3673999960609038E-2</v>
+      </c>
+      <c r="AD54" s="7">
+        <f t="shared" si="61"/>
+        <v>0.20255794718686326</v>
+      </c>
+      <c r="AE54" s="7">
+        <f t="shared" ref="AE54:AE56" si="62">AE30/AD30-1</f>
+        <v>-1</v>
+      </c>
+      <c r="AF54" s="7" t="e">
+        <f t="shared" ref="AF54:AF56" si="63">AF30/AE30-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG54" s="7" t="e">
+        <f t="shared" ref="AG54:AG56" si="64">AG30/AF30-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH54" s="7" t="e">
+        <f t="shared" ref="AH54:AH56" si="65">AH30/AG30-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AI54" s="7" t="e">
+        <f t="shared" ref="AI54:AI56" si="66">AI30/AH30-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AJ54" s="7" t="e">
+        <f t="shared" ref="AJ54:AJ56" si="67">AJ30/AI30-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AK54" s="7" t="e">
+        <f t="shared" ref="AK54:AK56" si="68">AK30/AJ30-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL54" s="7" t="e">
+        <f t="shared" ref="AL54:AL56" si="69">AL30/AK30-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AM54" s="7" t="e">
+        <f t="shared" ref="AM54:AM56" si="70">AM30/AL30-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AN54" s="7" t="e">
+        <f t="shared" ref="AN54:AN56" si="71">AN30/AM30-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AO54" s="7" t="e">
+        <f t="shared" ref="AO54:AO56" si="72">AO30/AN30-1</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="55" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7">
         <f t="shared" si="58"/>
-        <v>7.8892350161271017</v>
-      </c>
-      <c r="AJ44" s="6">
+        <v>0.14867669953295271</v>
+      </c>
+      <c r="H55" s="7">
         <f t="shared" si="58"/>
-        <v>8.1228100628887816</v>
-      </c>
-      <c r="AK44" s="6">
+        <v>0.20907297830374749</v>
+      </c>
+      <c r="I55" s="7">
         <f t="shared" si="58"/>
-        <v>8.3628985936092377</v>
-      </c>
-    </row>
-    <row r="46" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B46" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q46" s="7">
-        <f>Q20/M20-1</f>
-        <v>7.7173144876325095E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B47" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q47" s="7">
-        <f t="shared" ref="Q47:Q48" si="59">Q21/M21-1</f>
-        <v>0.16355850255560167</v>
-      </c>
-    </row>
-    <row r="48" spans="2:135" x14ac:dyDescent="0.3">
-      <c r="B48" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q48" s="7">
+        <v>0.15589988081048878</v>
+      </c>
+      <c r="J55" s="7">
+        <f t="shared" si="58"/>
+        <v>0.23188751191611057</v>
+      </c>
+      <c r="K55" s="7">
+        <f t="shared" si="58"/>
+        <v>0.12988479783148854</v>
+      </c>
+      <c r="L55" s="7">
+        <f t="shared" si="58"/>
+        <v>5.1998368678629614E-2</v>
+      </c>
+      <c r="M55" s="7">
+        <f t="shared" si="58"/>
+        <v>0.10971334295731072</v>
+      </c>
+      <c r="N55" s="7">
+        <f t="shared" si="58"/>
+        <v>8.0286322306055258E-2</v>
+      </c>
+      <c r="O55" s="7">
+        <f t="shared" si="58"/>
+        <v>0.14254298280687716</v>
+      </c>
+      <c r="P55" s="7">
+        <f t="shared" si="58"/>
+        <v>0.16883116883116878</v>
+      </c>
+      <c r="Q55" s="7">
         <f t="shared" si="59"/>
-        <v>0.10319448794237385</v>
-      </c>
-    </row>
-    <row r="50" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B50" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7">
-        <f t="shared" ref="G50:P52" si="60">G26/C26-1</f>
-        <v>7.7980104535491535E-2</v>
-      </c>
-      <c r="H50" s="7">
+        <v>0.15480393978814355</v>
+      </c>
+      <c r="R55" s="7">
         <f t="shared" si="60"/>
-        <v>9.4061021373796683E-2</v>
-      </c>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7">
-        <f t="shared" si="60"/>
-        <v>6.1955817802403335E-2</v>
-      </c>
-      <c r="K50" s="7">
-        <f t="shared" si="60"/>
-        <v>0.11855791037772745</v>
-      </c>
-      <c r="L50" s="7">
-        <f t="shared" si="60"/>
-        <v>8.5825068973230945E-2</v>
-      </c>
-      <c r="M50" s="7"/>
-      <c r="N50" s="7">
-        <f t="shared" si="60"/>
-        <v>8.6800379455210797E-2</v>
-      </c>
-      <c r="O50" s="7">
-        <f t="shared" si="60"/>
-        <v>2.0135635880584424E-2</v>
-      </c>
-      <c r="P50" s="7">
-        <f t="shared" si="60"/>
-        <v>6.7916494986952403E-2</v>
-      </c>
-      <c r="Q50" s="7">
-        <f t="shared" ref="Q50:Q52" si="61">Q26/M26-1</f>
-        <v>0.10579276584171882</v>
-      </c>
-      <c r="R50" s="7">
-        <f t="shared" ref="R50:R52" si="62">R26/N26-1</f>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="U50" s="7"/>
-      <c r="V50" s="7">
-        <f>V26/U26-1</f>
-        <v>0.31277653191102495</v>
-      </c>
-      <c r="W50" s="7">
-        <f t="shared" ref="W50:Z50" si="63">W26/V26-1</f>
-        <v>0.13737620905376402</v>
-      </c>
-      <c r="X50" s="7">
+        <v>-1</v>
+      </c>
+      <c r="S55" s="7"/>
+      <c r="T55" s="7"/>
+      <c r="U55" s="7"/>
+      <c r="V55" s="7"/>
+      <c r="Y55" s="7"/>
+      <c r="Z55" s="7">
+        <f t="shared" ref="Z55:AD56" si="73">Z31/Y31-1</f>
+        <v>7.4245000404825623E-2</v>
+      </c>
+      <c r="AA55" s="7">
+        <f t="shared" si="73"/>
+        <v>0.13943322279167925</v>
+      </c>
+      <c r="AB55" s="7">
+        <f t="shared" si="73"/>
+        <v>7.8251091414208274E-2</v>
+      </c>
+      <c r="AC55" s="7">
+        <f t="shared" si="73"/>
+        <v>0.18698239371817671</v>
+      </c>
+      <c r="AD55" s="7">
+        <f t="shared" si="73"/>
+        <v>9.1839371543749104E-2</v>
+      </c>
+      <c r="AE55" s="7">
+        <f t="shared" si="62"/>
+        <v>-1</v>
+      </c>
+      <c r="AF55" s="7" t="e">
         <f t="shared" si="63"/>
-        <v>3.0505378526486604E-2</v>
-      </c>
-      <c r="Y50" s="7">
-        <f t="shared" si="63"/>
-        <v>-2.3673999960609038E-2</v>
-      </c>
-      <c r="Z50" s="7">
-        <f t="shared" si="63"/>
-        <v>0.20255794718686326</v>
-      </c>
-      <c r="AA50" s="7">
-        <f t="shared" ref="AA50:AA52" si="64">AA26/Z26-1</f>
-        <v>7.4429645037911829E-2</v>
-      </c>
-      <c r="AB50" s="7">
-        <f t="shared" ref="AB50:AB52" si="65">AB26/AA26-1</f>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="AC50" s="7">
-        <f t="shared" ref="AC50:AC52" si="66">AC26/AB26-1</f>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AD50" s="7">
-        <f t="shared" ref="AD50:AD52" si="67">AD26/AC26-1</f>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AE50" s="7">
-        <f t="shared" ref="AE50:AE52" si="68">AE26/AD26-1</f>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AF50" s="7">
-        <f t="shared" ref="AF50:AF52" si="69">AF26/AE26-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AG50" s="7">
-        <f t="shared" ref="AG50:AG52" si="70">AG26/AF26-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AH50" s="7">
-        <f t="shared" ref="AH50:AH52" si="71">AH26/AG26-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AI50" s="7">
-        <f t="shared" ref="AI50:AI52" si="72">AI26/AH26-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AJ50" s="7">
-        <f t="shared" ref="AJ50:AJ52" si="73">AJ26/AI26-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AK50" s="7">
-        <f t="shared" ref="AK50:AK52" si="74">AK26/AJ26-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B51" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7">
-        <f t="shared" si="60"/>
-        <v>0.14867669953295271</v>
-      </c>
-      <c r="H51" s="7">
-        <f t="shared" si="60"/>
-        <v>0.20907297830374749</v>
-      </c>
-      <c r="I51" s="7">
-        <f t="shared" si="60"/>
-        <v>0.15589988081048878</v>
-      </c>
-      <c r="J51" s="7">
-        <f t="shared" si="60"/>
-        <v>0.23188751191611057</v>
-      </c>
-      <c r="K51" s="7">
-        <f t="shared" si="60"/>
-        <v>0.12988479783148854</v>
-      </c>
-      <c r="L51" s="7">
-        <f t="shared" si="60"/>
-        <v>5.1998368678629614E-2</v>
-      </c>
-      <c r="M51" s="7">
-        <f t="shared" si="60"/>
-        <v>0.10971334295731072</v>
-      </c>
-      <c r="N51" s="7">
-        <f t="shared" si="60"/>
-        <v>8.0286322306055258E-2</v>
-      </c>
-      <c r="O51" s="7">
-        <f t="shared" si="60"/>
-        <v>0.14254298280687716</v>
-      </c>
-      <c r="P51" s="7">
-        <f t="shared" si="60"/>
-        <v>0.16883116883116878</v>
-      </c>
-      <c r="Q51" s="7">
-        <f t="shared" si="61"/>
-        <v>0.15480393978814355</v>
-      </c>
-      <c r="R51" s="7">
-        <f t="shared" si="62"/>
-        <v>0.15999999999999992</v>
-      </c>
-      <c r="U51" s="7"/>
-      <c r="V51" s="7">
-        <f t="shared" ref="V51:Z52" si="75">V27/U27-1</f>
-        <v>7.4245000404825623E-2</v>
-      </c>
-      <c r="W51" s="7">
-        <f t="shared" si="75"/>
-        <v>0.13943322279167925</v>
-      </c>
-      <c r="X51" s="7">
-        <f t="shared" si="75"/>
-        <v>7.8251091414208274E-2</v>
-      </c>
-      <c r="Y51" s="7">
-        <f t="shared" si="75"/>
-        <v>0.18698239371817671</v>
-      </c>
-      <c r="Z51" s="7">
-        <f t="shared" si="75"/>
-        <v>9.1839371543749104E-2</v>
-      </c>
-      <c r="AA51" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG55" s="7" t="e">
         <f t="shared" si="64"/>
-        <v>0.15669980119284288</v>
-      </c>
-      <c r="AB51" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH55" s="7" t="e">
         <f t="shared" si="65"/>
-        <v>0.12999999999999989</v>
-      </c>
-      <c r="AC51" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AI55" s="7" t="e">
         <f t="shared" si="66"/>
-        <v>9.000000000000008E-2</v>
-      </c>
-      <c r="AD51" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AJ55" s="7" t="e">
         <f t="shared" si="67"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AE51" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AK55" s="7" t="e">
         <f t="shared" si="68"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AF51" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL55" s="7" t="e">
         <f t="shared" si="69"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AG51" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AM55" s="7" t="e">
         <f t="shared" si="70"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AH51" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AN55" s="7" t="e">
         <f t="shared" si="71"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AI51" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AO55" s="7" t="e">
         <f t="shared" si="72"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AJ51" s="7">
-        <f t="shared" si="73"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AK51" s="7">
-        <f t="shared" si="74"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="2:41" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="4" t="s">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="56" spans="2:45" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7">
-        <f t="shared" si="60"/>
-        <v>9.531687452277926E-2</v>
-      </c>
-      <c r="H52" s="7">
-        <f t="shared" si="60"/>
-        <v>0.12265538801029785</v>
-      </c>
-      <c r="I52" s="7">
-        <f t="shared" si="60"/>
-        <v>-0.20571057754704736</v>
-      </c>
-      <c r="J52" s="7">
-        <f t="shared" si="60"/>
-        <v>0.10136516884983138</v>
-      </c>
-      <c r="K52" s="7">
-        <f t="shared" si="60"/>
-        <v>0.12147089578250259</v>
-      </c>
-      <c r="L52" s="7">
-        <f t="shared" si="60"/>
-        <v>7.6767676767676818E-2</v>
-      </c>
-      <c r="M52" s="7">
-        <f t="shared" si="60"/>
-        <v>0.49205288175876416</v>
-      </c>
-      <c r="N52" s="7">
-        <f t="shared" si="60"/>
-        <v>8.5110653886686372E-2</v>
-      </c>
-      <c r="O52" s="7">
-        <f t="shared" si="60"/>
-        <v>5.1851851851851816E-2</v>
-      </c>
-      <c r="P52" s="7">
-        <f t="shared" si="60"/>
-        <v>9.4315704071801676E-2</v>
-      </c>
-      <c r="Q52" s="7">
-        <f t="shared" si="61"/>
-        <v>0.11892080242919012</v>
-      </c>
-      <c r="R52" s="7">
-        <f t="shared" si="62"/>
-        <v>0.11549461221847102</v>
-      </c>
-      <c r="U52" s="7"/>
-      <c r="V52" s="7">
-        <f t="shared" si="75"/>
-        <v>0.24781141811285812</v>
-      </c>
-      <c r="W52" s="7">
-        <f t="shared" si="75"/>
-        <v>0.1378585187410537</v>
-      </c>
-      <c r="X52" s="7">
-        <f t="shared" si="75"/>
-        <v>4.1715847673479578E-2</v>
-      </c>
-      <c r="Y52" s="7">
-        <f t="shared" si="75"/>
-        <v>2.7521841548140857E-2</v>
-      </c>
-      <c r="Z52" s="7">
-        <f t="shared" si="75"/>
-        <v>0.17147417295414979</v>
-      </c>
-      <c r="AA52" s="7">
-        <f t="shared" si="64"/>
-        <v>9.5956550818697472E-2</v>
-      </c>
-      <c r="AB52" s="7">
-        <f t="shared" si="65"/>
-        <v>9.3808185627133334E-2</v>
-      </c>
-      <c r="AC52" s="7">
-        <f t="shared" si="66"/>
-        <v>6.1412055578804692E-2</v>
-      </c>
-      <c r="AD52" s="7">
-        <f t="shared" si="67"/>
-        <v>4.2929856627197172E-2</v>
-      </c>
-      <c r="AE52" s="7">
-        <f t="shared" si="68"/>
-        <v>3.2949718467649936E-2</v>
-      </c>
-      <c r="AF52" s="7">
-        <f t="shared" si="69"/>
-        <v>2.2969851437596445E-2</v>
-      </c>
-      <c r="AG52" s="7">
-        <f t="shared" si="70"/>
-        <v>2.2990261126880407E-2</v>
-      </c>
-      <c r="AH52" s="7">
-        <f t="shared" si="71"/>
-        <v>2.3010751008806229E-2</v>
-      </c>
-      <c r="AI52" s="7">
-        <f t="shared" si="72"/>
-        <v>2.3031320576066827E-2</v>
-      </c>
-      <c r="AJ52" s="7">
-        <f t="shared" si="73"/>
-        <v>2.3051969309786591E-2</v>
-      </c>
-      <c r="AK52" s="7">
-        <f t="shared" si="74"/>
-        <v>2.3072696679525606E-2</v>
-      </c>
-      <c r="AN52" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AO52" s="7">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="53" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B53" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C53" s="7">
-        <f t="shared" ref="C53" si="76">(C26-C29)/C26</f>
-        <v>0.17214634968807957</v>
-      </c>
-      <c r="D53" s="7">
-        <f t="shared" ref="D53:N53" si="77">(D26-D29)/D26</f>
-        <v>0.18094305759503998</v>
-      </c>
-      <c r="E53" s="7">
-        <f t="shared" si="77"/>
-        <v>0.17740671056757604</v>
-      </c>
-      <c r="F53" s="7">
-        <f t="shared" si="77"/>
-        <v>0.16715837950636828</v>
-      </c>
-      <c r="G53" s="7">
-        <f t="shared" si="77"/>
-        <v>0.16321263783530149</v>
-      </c>
-      <c r="H53" s="7">
-        <f t="shared" si="77"/>
-        <v>0.17314145104764744</v>
-      </c>
-      <c r="I53" s="7">
-        <f t="shared" si="77"/>
-        <v>-7.8235635519442834E-2</v>
-      </c>
-      <c r="J53" s="7">
-        <f t="shared" si="77"/>
-        <v>0.16336902019243799</v>
-      </c>
-      <c r="K53" s="7">
-        <f t="shared" si="77"/>
-        <v>0.14591344473187443</v>
-      </c>
-      <c r="L53" s="7">
-        <f t="shared" si="77"/>
-        <v>0.13301744265897542</v>
-      </c>
-      <c r="M53" s="7">
-        <f t="shared" si="77"/>
-        <v>0.16127277672015231</v>
-      </c>
-      <c r="N53" s="7">
-        <f t="shared" si="77"/>
-        <v>0.15262796932477088</v>
-      </c>
-      <c r="O53" s="7">
-        <f t="shared" ref="O53" si="78">(O26-O29)/O26</f>
-        <v>0.15817969981495442</v>
-      </c>
-      <c r="P53" s="7">
-        <f t="shared" ref="P53" si="79">(P26-P29)/P26</f>
-        <v>0.16474824770111246</v>
-      </c>
-      <c r="Q53" s="7">
-        <f t="shared" ref="Q53:R53" si="80">(Q26-Q29)/Q26</f>
-        <v>0.16422774225282832</v>
-      </c>
-      <c r="R53" s="7">
-        <f t="shared" si="80"/>
-        <v>0.16000000000000006</v>
-      </c>
-      <c r="U53" s="7">
-        <f>(U26-U29)/U26</f>
-        <v>0.18449603006242801</v>
-      </c>
-      <c r="V53" s="7">
-        <f>(V26-V29)/V26</f>
-        <v>0.11962418338373462</v>
-      </c>
-      <c r="W53" s="7">
-        <f t="shared" ref="W53:Z53" si="81">(W26-W29)/W26</f>
-        <v>0.16592246803328597</v>
-      </c>
-      <c r="X53" s="7">
-        <f t="shared" si="81"/>
-        <v>0.17422645894471472</v>
-      </c>
-      <c r="Y53" s="7">
-        <f t="shared" si="81"/>
-        <v>0.1239837808396038</v>
-      </c>
-      <c r="Z53" s="7">
-        <f t="shared" si="81"/>
-        <v>0.14835939072669932</v>
-      </c>
-      <c r="AA53" s="7">
-        <f t="shared" ref="AA53:AK53" si="82">(AA26-AA29)/AA26</f>
-        <v>0.16181174071685855</v>
-      </c>
-      <c r="AB53" s="7">
-        <f t="shared" si="82"/>
-        <v>0.16000000000000003</v>
-      </c>
-      <c r="AC53" s="7">
-        <f t="shared" si="82"/>
-        <v>0.16</v>
-      </c>
-      <c r="AD53" s="7">
-        <f t="shared" si="82"/>
-        <v>0.15999999999999998</v>
-      </c>
-      <c r="AE53" s="7">
-        <f t="shared" si="82"/>
-        <v>0.15999999999999998</v>
-      </c>
-      <c r="AF53" s="7">
-        <f t="shared" si="82"/>
-        <v>0.16000000000000009</v>
-      </c>
-      <c r="AG53" s="7">
-        <f t="shared" si="82"/>
-        <v>0.16000000000000006</v>
-      </c>
-      <c r="AH53" s="7">
-        <f t="shared" si="82"/>
-        <v>0.16000000000000006</v>
-      </c>
-      <c r="AI53" s="7">
-        <f t="shared" si="82"/>
-        <v>0.16000000000000011</v>
-      </c>
-      <c r="AJ53" s="7">
-        <f t="shared" si="82"/>
-        <v>0.16000000000000011</v>
-      </c>
-      <c r="AK53" s="7">
-        <f t="shared" si="82"/>
-        <v>0.16000000000000006</v>
-      </c>
-      <c r="AN53" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AO53" s="7">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="54" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B54" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C54" s="7">
-        <f t="shared" ref="C54" si="83">(C27-C30)/C27</f>
-        <v>0.28905033731188373</v>
-      </c>
-      <c r="D54" s="7">
-        <f t="shared" ref="D54:N54" si="84">(D27-D30)/D27</f>
-        <v>0.3057199211045365</v>
-      </c>
-      <c r="E54" s="7">
-        <f t="shared" si="84"/>
-        <v>0.29177592371871275</v>
-      </c>
-      <c r="F54" s="7">
-        <f t="shared" si="84"/>
-        <v>0.29647283126787416</v>
-      </c>
-      <c r="G54" s="7">
-        <f t="shared" si="84"/>
-        <v>0.33476394849785407</v>
-      </c>
-      <c r="H54" s="7">
-        <f t="shared" si="84"/>
-        <v>0.30077487765089722</v>
-      </c>
-      <c r="I54" s="7">
-        <f t="shared" si="84"/>
-        <v>0.28624458651268303</v>
-      </c>
-      <c r="J54" s="7">
-        <f t="shared" si="84"/>
-        <v>0.30915070613271428</v>
-      </c>
-      <c r="K54" s="7">
-        <f t="shared" si="84"/>
-        <v>0.29468212714914033</v>
-      </c>
-      <c r="L54" s="7">
-        <f t="shared" si="84"/>
-        <v>0.3184725722039155</v>
-      </c>
-      <c r="M54" s="7">
-        <f t="shared" si="84"/>
-        <v>0.30886452332280245</v>
-      </c>
-      <c r="N54" s="7">
-        <f t="shared" si="84"/>
-        <v>0.32002148997134672</v>
-      </c>
-      <c r="O54" s="7">
-        <f t="shared" ref="O54" si="85">(O27-O30)/O27</f>
-        <v>0.31636045494313209</v>
-      </c>
-      <c r="P54" s="7">
-        <f t="shared" ref="P54" si="86">(P27-P30)/P27</f>
-        <v>0.30082918739635156</v>
-      </c>
-      <c r="Q54" s="7">
-        <f t="shared" ref="Q54:R54" si="87">(Q27-Q30)/Q27</f>
-        <v>0.30720952687479886</v>
-      </c>
-      <c r="R54" s="7">
-        <f t="shared" si="87"/>
-        <v>0.31000000000000005</v>
-      </c>
-      <c r="U54" s="7">
-        <f>(U27-U30)/U27</f>
-        <v>0.37754028013926</v>
-      </c>
-      <c r="V54" s="7">
-        <f>(V27-V30)/V27</f>
-        <v>0.25241181790774797</v>
-      </c>
-      <c r="W54" s="7">
-        <f t="shared" ref="W54:Z54" si="88">(W27-W30)/W27</f>
-        <v>0.28548749834634213</v>
-      </c>
-      <c r="X54" s="7">
-        <f t="shared" si="88"/>
-        <v>0.29581007300165635</v>
-      </c>
-      <c r="Y54" s="7">
-        <f t="shared" si="88"/>
-        <v>0.30714765620962325</v>
-      </c>
-      <c r="Z54" s="7">
-        <f t="shared" si="88"/>
-        <v>0.3108018555334659</v>
-      </c>
-      <c r="AA54" s="7">
-        <f t="shared" ref="AA54:AK54" si="89">(AA27-AA30)/AA27</f>
-        <v>0.30851492279562814</v>
-      </c>
-      <c r="AB54" s="7">
-        <f t="shared" si="89"/>
-        <v>0.31000000000000011</v>
-      </c>
-      <c r="AC54" s="7">
-        <f t="shared" si="89"/>
-        <v>0.31000000000000011</v>
-      </c>
-      <c r="AD54" s="7">
-        <f t="shared" si="89"/>
-        <v>0.31000000000000005</v>
-      </c>
-      <c r="AE54" s="7">
-        <f t="shared" si="89"/>
-        <v>0.31000000000000005</v>
-      </c>
-      <c r="AF54" s="7">
-        <f t="shared" si="89"/>
-        <v>0.31000000000000005</v>
-      </c>
-      <c r="AG54" s="7">
-        <f t="shared" si="89"/>
-        <v>0.31000000000000005</v>
-      </c>
-      <c r="AH54" s="7">
-        <f t="shared" si="89"/>
-        <v>0.31000000000000011</v>
-      </c>
-      <c r="AI54" s="7">
-        <f t="shared" si="89"/>
-        <v>0.31000000000000005</v>
-      </c>
-      <c r="AJ54" s="7">
-        <f t="shared" si="89"/>
-        <v>0.31000000000000005</v>
-      </c>
-      <c r="AK54" s="7">
-        <f t="shared" si="89"/>
-        <v>0.31000000000000005</v>
-      </c>
-      <c r="AN54" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AO54" s="3">
-        <f>NPV(AO53,AA42:EE42)</f>
-        <v>156795.97693203905</v>
-      </c>
-    </row>
-    <row r="55" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B55" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C55" s="7">
-        <f t="shared" ref="C55" si="90">C32/C28</f>
-        <v>0.20081445660473402</v>
-      </c>
-      <c r="D55" s="7">
-        <f t="shared" ref="D55:N55" si="91">D32/D28</f>
-        <v>0.21196518327816599</v>
-      </c>
-      <c r="E55" s="7">
-        <f t="shared" si="91"/>
-        <v>0.20571057754704739</v>
-      </c>
-      <c r="F55" s="7">
-        <f t="shared" si="91"/>
-        <v>0.19714806831371248</v>
-      </c>
-      <c r="G55" s="7">
-        <f t="shared" si="91"/>
-        <v>0.20733124201231556</v>
-      </c>
-      <c r="H55" s="7">
-        <f t="shared" si="91"/>
-        <v>0.20731640731640733</v>
-      </c>
-      <c r="I55" s="7">
-        <f t="shared" si="91"/>
-        <v>5.3030303030303032E-2</v>
-      </c>
-      <c r="J55" s="7">
-        <f t="shared" si="91"/>
-        <v>0.20118432277814022</v>
-      </c>
-      <c r="K55" s="7">
-        <f t="shared" si="91"/>
-        <v>0.18445998445998446</v>
-      </c>
-      <c r="L55" s="7">
-        <f t="shared" si="91"/>
-        <v>0.18153237665432786</v>
-      </c>
-      <c r="M55" s="7">
-        <f t="shared" si="91"/>
-        <v>0.20080641146896311</v>
-      </c>
-      <c r="N55" s="7">
-        <f t="shared" si="91"/>
-        <v>0.1958562641631596</v>
-      </c>
-      <c r="O55" s="7">
-        <f t="shared" ref="O55" si="92">O32/O28</f>
-        <v>0.20269870974096327</v>
-      </c>
-      <c r="P55" s="7">
-        <f t="shared" ref="P55" si="93">P32/P28</f>
-        <v>0.20277095593345998</v>
-      </c>
-      <c r="Q55" s="7">
-        <f t="shared" ref="Q55:R55" si="94">Q32/Q28</f>
-        <v>0.20375478245395498</v>
-      </c>
-      <c r="R55" s="7">
-        <f t="shared" si="94"/>
-        <v>0.20028201924185146</v>
-      </c>
-      <c r="U55" s="7">
-        <f>U32/U28</f>
-        <v>0.23707248230390968</v>
-      </c>
-      <c r="V55" s="7">
-        <f>V32/V28</f>
-        <v>0.15075900825277891</v>
-      </c>
-      <c r="W55" s="7">
-        <f t="shared" ref="W55:Z55" si="95">W32/W28</f>
-        <v>0.19399577561036219</v>
-      </c>
-      <c r="X55" s="7">
-        <f t="shared" si="95"/>
-        <v>0.20377493514625639</v>
-      </c>
-      <c r="Y55" s="7">
-        <f t="shared" si="95"/>
-        <v>0.17540626813697041</v>
-      </c>
-      <c r="Z55" s="7">
-        <f t="shared" si="95"/>
-        <v>0.19086427704426664</v>
-      </c>
-      <c r="AA55" s="7">
-        <f t="shared" ref="AA55:AK55" si="96">AA32/AA28</f>
-        <v>0.20232583612155416</v>
-      </c>
-      <c r="AB55" s="7">
-        <f t="shared" si="96"/>
-        <v>0.20279520842051804</v>
-      </c>
-      <c r="AC55" s="7">
-        <f t="shared" si="96"/>
-        <v>0.20394784940795432</v>
-      </c>
-      <c r="AD55" s="7">
-        <f t="shared" si="96"/>
-        <v>0.20424577701475002</v>
-      </c>
-      <c r="AE55" s="7">
-        <f t="shared" si="96"/>
-        <v>0.20454777156394671</v>
-      </c>
-      <c r="AF55" s="7">
-        <f t="shared" si="96"/>
-        <v>0.20485391690320431</v>
-      </c>
-      <c r="AG55" s="7">
-        <f t="shared" si="96"/>
-        <v>0.20516126513209323</v>
-      </c>
-      <c r="AH55" s="7">
-        <f t="shared" si="96"/>
-        <v>0.20546980864099987</v>
-      </c>
-      <c r="AI55" s="7">
-        <f t="shared" si="96"/>
-        <v>0.20577953964679987</v>
-      </c>
-      <c r="AJ55" s="7">
-        <f t="shared" si="96"/>
-        <v>0.20609045019288316</v>
-      </c>
-      <c r="AK55" s="7">
-        <f t="shared" si="96"/>
-        <v>0.20640253214922855</v>
-      </c>
-      <c r="AN55" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AO55" s="3">
-        <f>Main!D8</f>
-        <v>-33093</v>
-      </c>
-    </row>
-    <row r="56" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B56" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="7">
-        <f t="shared" ref="G56:P56" si="97">G33/C33-1</f>
+        <f t="shared" si="58"/>
+        <v>9.531687452277926E-2</v>
+      </c>
+      <c r="H56" s="7">
+        <f t="shared" si="58"/>
+        <v>0.12265538801029785</v>
+      </c>
+      <c r="I56" s="7">
+        <f t="shared" si="58"/>
+        <v>-0.20571057754704736</v>
+      </c>
+      <c r="J56" s="7">
+        <f t="shared" si="58"/>
+        <v>0.10136516884983138</v>
+      </c>
+      <c r="K56" s="7">
+        <f t="shared" si="58"/>
+        <v>0.12147089578250259</v>
+      </c>
+      <c r="L56" s="7">
+        <f t="shared" si="58"/>
+        <v>7.6767676767676818E-2</v>
+      </c>
+      <c r="M56" s="7">
+        <f t="shared" si="58"/>
+        <v>0.49205288175876416</v>
+      </c>
+      <c r="N56" s="7">
+        <f t="shared" si="58"/>
+        <v>8.5110653886686372E-2</v>
+      </c>
+      <c r="O56" s="7">
+        <f t="shared" si="58"/>
+        <v>5.1851851851851816E-2</v>
+      </c>
+      <c r="P56" s="7">
+        <f t="shared" si="58"/>
+        <v>9.4315704071801676E-2</v>
+      </c>
+      <c r="Q56" s="7">
+        <f t="shared" si="59"/>
+        <v>0.11892080242919012</v>
+      </c>
+      <c r="R56" s="7">
+        <f t="shared" si="60"/>
+        <v>0.12093604032742911</v>
+      </c>
+      <c r="S56" s="7"/>
+      <c r="T56" s="7"/>
+      <c r="U56" s="7"/>
+      <c r="V56" s="7"/>
+      <c r="Y56" s="7"/>
+      <c r="Z56" s="7">
+        <f t="shared" si="73"/>
+        <v>0.24781141811285812</v>
+      </c>
+      <c r="AA56" s="7">
+        <f t="shared" si="73"/>
+        <v>0.1378585187410537</v>
+      </c>
+      <c r="AB56" s="7">
+        <f t="shared" si="73"/>
+        <v>4.1715847673479578E-2</v>
+      </c>
+      <c r="AC56" s="7">
+        <f t="shared" si="73"/>
+        <v>2.7521841548140857E-2</v>
+      </c>
+      <c r="AD56" s="7">
+        <f t="shared" si="73"/>
+        <v>0.17147417295414979</v>
+      </c>
+      <c r="AE56" s="7">
+        <f t="shared" si="62"/>
+        <v>9.7413857167628626E-2</v>
+      </c>
+      <c r="AF56" s="7">
+        <f t="shared" si="63"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="AG56" s="7">
+        <f t="shared" si="64"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AH56" s="7">
+        <f t="shared" si="65"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AI56" s="7">
+        <f t="shared" si="66"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AJ56" s="7">
+        <f t="shared" si="67"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AK56" s="7">
+        <f t="shared" si="68"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AL56" s="7">
+        <f t="shared" si="69"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AM56" s="7">
+        <f t="shared" si="70"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AN56" s="7">
+        <f t="shared" si="71"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AO56" s="7">
+        <f t="shared" si="72"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AR56" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AS56" s="7">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="57" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C57" s="7">
+        <f t="shared" ref="C57" si="74">(C30-C33)/C30</f>
+        <v>0.17214634968807957</v>
+      </c>
+      <c r="D57" s="7">
+        <f t="shared" ref="D57:N57" si="75">(D30-D33)/D30</f>
+        <v>0.18094305759503998</v>
+      </c>
+      <c r="E57" s="7">
+        <f t="shared" si="75"/>
+        <v>0.17740671056757604</v>
+      </c>
+      <c r="F57" s="7">
+        <f t="shared" si="75"/>
+        <v>0.16715837950636828</v>
+      </c>
+      <c r="G57" s="7">
+        <f t="shared" si="75"/>
+        <v>0.16321263783530149</v>
+      </c>
+      <c r="H57" s="7">
+        <f t="shared" si="75"/>
+        <v>0.17314145104764744</v>
+      </c>
+      <c r="I57" s="7">
+        <f t="shared" si="75"/>
+        <v>-7.8235635519442834E-2</v>
+      </c>
+      <c r="J57" s="7">
+        <f t="shared" si="75"/>
+        <v>0.16336902019243799</v>
+      </c>
+      <c r="K57" s="7">
+        <f t="shared" si="75"/>
+        <v>0.14591344473187443</v>
+      </c>
+      <c r="L57" s="7">
+        <f t="shared" si="75"/>
+        <v>0.13301744265897542</v>
+      </c>
+      <c r="M57" s="7">
+        <f t="shared" si="75"/>
+        <v>0.16127277672015231</v>
+      </c>
+      <c r="N57" s="7">
+        <f t="shared" si="75"/>
+        <v>0.15262796932477088</v>
+      </c>
+      <c r="O57" s="7">
+        <f t="shared" ref="O57" si="76">(O30-O33)/O30</f>
+        <v>0.15817969981495442</v>
+      </c>
+      <c r="P57" s="7">
+        <f t="shared" ref="P57" si="77">(P30-P33)/P30</f>
+        <v>0.16474824770111246</v>
+      </c>
+      <c r="Q57" s="7">
+        <f t="shared" ref="Q57:R57" si="78">(Q30-Q33)/Q30</f>
+        <v>0.16422774225282832</v>
+      </c>
+      <c r="R57" s="7" t="e">
+        <f t="shared" si="78"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S57" s="7"/>
+      <c r="T57" s="7"/>
+      <c r="U57" s="7"/>
+      <c r="V57" s="7"/>
+      <c r="Y57" s="7">
+        <f>(Y30-Y33)/Y30</f>
+        <v>0.18449603006242801</v>
+      </c>
+      <c r="Z57" s="7">
+        <f>(Z30-Z33)/Z30</f>
+        <v>0.11962418338373462</v>
+      </c>
+      <c r="AA57" s="7">
+        <f t="shared" ref="AA57:AD57" si="79">(AA30-AA33)/AA30</f>
+        <v>0.16592246803328597</v>
+      </c>
+      <c r="AB57" s="7">
+        <f t="shared" si="79"/>
+        <v>0.17422645894471472</v>
+      </c>
+      <c r="AC57" s="7">
+        <f t="shared" si="79"/>
+        <v>0.1239837808396038</v>
+      </c>
+      <c r="AD57" s="7">
+        <f t="shared" si="79"/>
+        <v>0.14835939072669932</v>
+      </c>
+      <c r="AE57" s="7" t="e">
+        <f t="shared" ref="AE57:AO57" si="80">(AE30-AE33)/AE30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF57" s="7" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG57" s="7" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH57" s="7" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AI57" s="7" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AJ57" s="7" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AK57" s="7" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL57" s="7" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AM57" s="7" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AN57" s="7" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AO57" s="7" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AR57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AS57" s="7">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="58" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B58" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C58" s="7">
+        <f t="shared" ref="C58" si="81">(C31-C34)/C31</f>
+        <v>0.28905033731188373</v>
+      </c>
+      <c r="D58" s="7">
+        <f t="shared" ref="D58:N58" si="82">(D31-D34)/D31</f>
+        <v>0.3057199211045365</v>
+      </c>
+      <c r="E58" s="7">
+        <f t="shared" si="82"/>
+        <v>0.29177592371871275</v>
+      </c>
+      <c r="F58" s="7">
+        <f t="shared" si="82"/>
+        <v>0.29647283126787416</v>
+      </c>
+      <c r="G58" s="7">
+        <f t="shared" si="82"/>
+        <v>0.33476394849785407</v>
+      </c>
+      <c r="H58" s="7">
+        <f t="shared" si="82"/>
+        <v>0.30077487765089722</v>
+      </c>
+      <c r="I58" s="7">
+        <f t="shared" si="82"/>
+        <v>0.28624458651268303</v>
+      </c>
+      <c r="J58" s="7">
+        <f t="shared" si="82"/>
+        <v>0.30915070613271428</v>
+      </c>
+      <c r="K58" s="7">
+        <f t="shared" si="82"/>
+        <v>0.29468212714914033</v>
+      </c>
+      <c r="L58" s="7">
+        <f t="shared" si="82"/>
+        <v>0.3184725722039155</v>
+      </c>
+      <c r="M58" s="7">
+        <f t="shared" si="82"/>
+        <v>0.30886452332280245</v>
+      </c>
+      <c r="N58" s="7">
+        <f t="shared" si="82"/>
+        <v>0.32002148997134672</v>
+      </c>
+      <c r="O58" s="7">
+        <f t="shared" ref="O58" si="83">(O31-O34)/O31</f>
+        <v>0.31636045494313209</v>
+      </c>
+      <c r="P58" s="7">
+        <f t="shared" ref="P58" si="84">(P31-P34)/P31</f>
+        <v>0.30082918739635156</v>
+      </c>
+      <c r="Q58" s="7">
+        <f t="shared" ref="Q58:R58" si="85">(Q31-Q34)/Q31</f>
+        <v>0.30720952687479886</v>
+      </c>
+      <c r="R58" s="7" t="e">
+        <f t="shared" si="85"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S58" s="7"/>
+      <c r="T58" s="7"/>
+      <c r="U58" s="7"/>
+      <c r="V58" s="7"/>
+      <c r="Y58" s="7">
+        <f>(Y31-Y34)/Y31</f>
+        <v>0.37754028013926</v>
+      </c>
+      <c r="Z58" s="7">
+        <f>(Z31-Z34)/Z31</f>
+        <v>0.25241181790774797</v>
+      </c>
+      <c r="AA58" s="7">
+        <f t="shared" ref="AA58:AD58" si="86">(AA31-AA34)/AA31</f>
+        <v>0.28548749834634213</v>
+      </c>
+      <c r="AB58" s="7">
+        <f t="shared" si="86"/>
+        <v>0.29581007300165635</v>
+      </c>
+      <c r="AC58" s="7">
+        <f t="shared" si="86"/>
+        <v>0.30714765620962325</v>
+      </c>
+      <c r="AD58" s="7">
+        <f t="shared" si="86"/>
+        <v>0.3108018555334659</v>
+      </c>
+      <c r="AE58" s="7" t="e">
+        <f t="shared" ref="AE58:AO58" si="87">(AE31-AE34)/AE31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF58" s="7" t="e">
+        <f t="shared" si="87"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG58" s="7" t="e">
+        <f t="shared" si="87"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH58" s="7" t="e">
+        <f t="shared" si="87"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AI58" s="7" t="e">
+        <f t="shared" si="87"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AJ58" s="7" t="e">
+        <f t="shared" si="87"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AK58" s="7" t="e">
+        <f t="shared" si="87"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL58" s="7" t="e">
+        <f t="shared" si="87"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AM58" s="7" t="e">
+        <f t="shared" si="87"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AN58" s="7" t="e">
+        <f t="shared" si="87"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AO58" s="7" t="e">
+        <f t="shared" si="87"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AR58" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS58" s="3">
+        <f>NPV(AS57,AE46:EI46)</f>
+        <v>125405.04849548574</v>
+      </c>
+    </row>
+    <row r="59" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C59" s="7">
+        <f t="shared" ref="C59" si="88">C36/C32</f>
+        <v>0.20081445660473402</v>
+      </c>
+      <c r="D59" s="7">
+        <f t="shared" ref="D59:N59" si="89">D36/D32</f>
+        <v>0.21196518327816599</v>
+      </c>
+      <c r="E59" s="7">
+        <f t="shared" si="89"/>
+        <v>0.20571057754704739</v>
+      </c>
+      <c r="F59" s="7">
+        <f t="shared" si="89"/>
+        <v>0.19714806831371248</v>
+      </c>
+      <c r="G59" s="7">
+        <f t="shared" si="89"/>
+        <v>0.20733124201231556</v>
+      </c>
+      <c r="H59" s="7">
+        <f t="shared" si="89"/>
+        <v>0.20731640731640733</v>
+      </c>
+      <c r="I59" s="7">
+        <f t="shared" si="89"/>
+        <v>5.3030303030303032E-2</v>
+      </c>
+      <c r="J59" s="7">
+        <f t="shared" si="89"/>
+        <v>0.20118432277814022</v>
+      </c>
+      <c r="K59" s="7">
+        <f t="shared" si="89"/>
+        <v>0.18445998445998446</v>
+      </c>
+      <c r="L59" s="7">
+        <f t="shared" si="89"/>
+        <v>0.18153237665432786</v>
+      </c>
+      <c r="M59" s="7">
+        <f t="shared" si="89"/>
+        <v>0.20080641146896311</v>
+      </c>
+      <c r="N59" s="7">
+        <f t="shared" si="89"/>
+        <v>0.1958562641631596</v>
+      </c>
+      <c r="O59" s="7">
+        <f t="shared" ref="O59" si="90">O36/O32</f>
+        <v>0.20269870974096327</v>
+      </c>
+      <c r="P59" s="7">
+        <f t="shared" ref="P59" si="91">P36/P32</f>
+        <v>0.20277095593345998</v>
+      </c>
+      <c r="Q59" s="7">
+        <f t="shared" ref="Q59:R59" si="92">Q36/Q32</f>
+        <v>0.20375478245395498</v>
+      </c>
+      <c r="R59" s="7">
+        <f t="shared" si="92"/>
+        <v>0.19461176664741314</v>
+      </c>
+      <c r="S59" s="7"/>
+      <c r="T59" s="7"/>
+      <c r="U59" s="7"/>
+      <c r="V59" s="7"/>
+      <c r="Y59" s="7">
+        <f>Y36/Y32</f>
+        <v>0.23707248230390968</v>
+      </c>
+      <c r="Z59" s="7">
+        <f>Z36/Z32</f>
+        <v>0.15075900825277891</v>
+      </c>
+      <c r="AA59" s="7">
+        <f t="shared" ref="AA59:AD59" si="93">AA36/AA32</f>
+        <v>0.19399577561036219</v>
+      </c>
+      <c r="AB59" s="7">
+        <f t="shared" si="93"/>
+        <v>0.20377493514625639</v>
+      </c>
+      <c r="AC59" s="7">
+        <f t="shared" si="93"/>
+        <v>0.17540626813697041</v>
+      </c>
+      <c r="AD59" s="7">
+        <f t="shared" si="93"/>
+        <v>0.19086427704426664</v>
+      </c>
+      <c r="AE59" s="7">
+        <f t="shared" ref="AE59:AO59" si="94">AE36/AE32</f>
+        <v>0.18999999999999992</v>
+      </c>
+      <c r="AF59" s="7">
+        <f t="shared" si="94"/>
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AG59" s="7">
+        <f t="shared" si="94"/>
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AH59" s="7">
+        <f t="shared" si="94"/>
+        <v>0.18999999999999992</v>
+      </c>
+      <c r="AI59" s="7">
+        <f t="shared" si="94"/>
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AJ59" s="7">
+        <f t="shared" si="94"/>
+        <v>0.19</v>
+      </c>
+      <c r="AK59" s="7">
+        <f t="shared" si="94"/>
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AL59" s="7">
+        <f t="shared" si="94"/>
+        <v>0.18999999999999997</v>
+      </c>
+      <c r="AM59" s="7">
+        <f t="shared" si="94"/>
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AN59" s="7">
+        <f t="shared" si="94"/>
+        <v>0.18999999999999989</v>
+      </c>
+      <c r="AO59" s="7">
+        <f t="shared" si="94"/>
+        <v>0.18999999999999992</v>
+      </c>
+      <c r="AR59" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AS59" s="3">
+        <f>Main!D8</f>
+        <v>-30469</v>
+      </c>
+    </row>
+    <row r="60" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B60" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7">
+        <f t="shared" ref="G60:P60" si="95">G37/C37-1</f>
         <v>-4.4094488188976433E-2</v>
       </c>
-      <c r="H56" s="7">
-        <f t="shared" si="97"/>
+      <c r="H60" s="7">
+        <f t="shared" si="95"/>
         <v>4.4412607449856756E-2</v>
       </c>
-      <c r="I56" s="7">
-        <f t="shared" si="97"/>
+      <c r="I60" s="7">
+        <f t="shared" si="95"/>
         <v>7.5528700906344337E-2</v>
       </c>
-      <c r="J56" s="7">
-        <f t="shared" si="97"/>
+      <c r="J60" s="7">
+        <f t="shared" si="95"/>
         <v>5.7262569832402299E-2</v>
       </c>
-      <c r="K56" s="7">
-        <f t="shared" si="97"/>
+      <c r="K60" s="7">
+        <f t="shared" si="95"/>
         <v>0.10214168039538718</v>
       </c>
-      <c r="L56" s="7">
-        <f t="shared" si="97"/>
+      <c r="L60" s="7">
+        <f t="shared" si="95"/>
         <v>-3.1550068587105629E-2</v>
       </c>
-      <c r="M56" s="7">
-        <f t="shared" si="97"/>
+      <c r="M60" s="7">
+        <f t="shared" si="95"/>
         <v>5.47752808988764E-2</v>
       </c>
-      <c r="N56" s="7">
-        <f t="shared" si="97"/>
+      <c r="N60" s="7">
+        <f t="shared" si="95"/>
         <v>6.7371202113606365E-2</v>
       </c>
-      <c r="O56" s="7">
-        <f t="shared" si="97"/>
+      <c r="O60" s="7">
+        <f t="shared" si="95"/>
         <v>-4.783258594917783E-2</v>
       </c>
-      <c r="P56" s="7">
-        <f t="shared" si="97"/>
+      <c r="P60" s="7">
+        <f t="shared" si="95"/>
         <v>-1.2747875354107596E-2</v>
       </c>
-      <c r="Q56" s="7">
-        <f t="shared" ref="Q56" si="98">Q33/M33-1</f>
+      <c r="Q60" s="7">
+        <f t="shared" ref="Q60" si="96">Q37/M37-1</f>
         <v>-8.9214380825565875E-2</v>
       </c>
-      <c r="R56" s="7">
-        <f t="shared" ref="R56" si="99">R33/N33-1</f>
-        <v>-1.9999999999999907E-2</v>
-      </c>
-      <c r="U56" s="7"/>
-      <c r="V56" s="7">
-        <f>V33/U33-1</f>
+      <c r="R60" s="7">
+        <f t="shared" ref="R60" si="97">R37/N37-1</f>
+        <v>-2.3514851485148536E-2</v>
+      </c>
+      <c r="S60" s="7"/>
+      <c r="T60" s="7"/>
+      <c r="U60" s="7"/>
+      <c r="V60" s="7"/>
+      <c r="Y60" s="7"/>
+      <c r="Z60" s="7">
+        <f>Z37/Y37-1</f>
         <v>5.3017944535073358E-2</v>
       </c>
-      <c r="W56" s="7">
-        <f t="shared" ref="W56:Z56" si="100">W33/V33-1</f>
+      <c r="AA60" s="7">
+        <f t="shared" ref="AA60:AD60" si="98">AA37/Z37-1</f>
         <v>5.8094500387296577E-2</v>
       </c>
-      <c r="X56" s="7">
-        <f t="shared" si="100"/>
+      <c r="AB60" s="7">
+        <f t="shared" si="98"/>
         <v>-7.6866764275256294E-3</v>
       </c>
-      <c r="Y56" s="7">
-        <f t="shared" si="100"/>
+      <c r="AC60" s="7">
+        <f t="shared" si="98"/>
         <v>3.4673552194762092E-2</v>
       </c>
-      <c r="Z56" s="7">
-        <f t="shared" si="100"/>
+      <c r="AD60" s="7">
+        <f t="shared" si="98"/>
         <v>4.5989304812834142E-2</v>
       </c>
-      <c r="AA56" s="7">
-        <f t="shared" ref="AA56" si="101">AA33/Z33-1</f>
-        <v>-4.2317655078391248E-2</v>
-      </c>
-      <c r="AB56" s="7">
-        <f t="shared" ref="AB56" si="102">AB33/AA33-1</f>
+      <c r="AE60" s="7">
+        <f t="shared" ref="AE60" si="99">AE37/AD37-1</f>
+        <v>-4.3285616905248792E-2</v>
+      </c>
+      <c r="AF60" s="7">
+        <f t="shared" ref="AF60" si="100">AF37/AE37-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AC56" s="7">
-        <f t="shared" ref="AC56" si="103">AC33/AB33-1</f>
+      <c r="AG60" s="7">
+        <f t="shared" ref="AG60" si="101">AG37/AF37-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AD56" s="7">
-        <f t="shared" ref="AD56" si="104">AD33/AC33-1</f>
+      <c r="AH60" s="7">
+        <f t="shared" ref="AH60" si="102">AH37/AG37-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE56" s="7">
-        <f t="shared" ref="AE56" si="105">AE33/AD33-1</f>
+      <c r="AI60" s="7">
+        <f t="shared" ref="AI60" si="103">AI37/AH37-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AF56" s="7">
-        <f t="shared" ref="AF56" si="106">AF33/AE33-1</f>
+      <c r="AJ60" s="7">
+        <f t="shared" ref="AJ60" si="104">AJ37/AI37-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AG56" s="7">
-        <f t="shared" ref="AG56" si="107">AG33/AF33-1</f>
+      <c r="AK60" s="7">
+        <f t="shared" ref="AK60" si="105">AK37/AJ37-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH56" s="7">
-        <f t="shared" ref="AH56" si="108">AH33/AG33-1</f>
+      <c r="AL60" s="7">
+        <f t="shared" ref="AL60" si="106">AL37/AK37-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AI56" s="7">
-        <f t="shared" ref="AI56" si="109">AI33/AH33-1</f>
+      <c r="AM60" s="7">
+        <f t="shared" ref="AM60" si="107">AM37/AL37-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AJ56" s="7">
-        <f t="shared" ref="AJ56" si="110">AJ33/AI33-1</f>
+      <c r="AN60" s="7">
+        <f t="shared" ref="AN60" si="108">AN37/AM37-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AK56" s="7">
-        <f t="shared" ref="AK56" si="111">AK33/AJ33-1</f>
+      <c r="AO60" s="7">
+        <f t="shared" ref="AO60" si="109">AO37/AN37-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AN56" s="1" t="s">
+      <c r="AR60" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AO56" s="3">
-        <f>AO54+AO55</f>
-        <v>123702.97693203905</v>
-      </c>
-    </row>
-    <row r="57" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B57" s="1" t="s">
+      <c r="AS60" s="3">
+        <f>AS58+AS59</f>
+        <v>94936.048495485738</v>
+      </c>
+    </row>
+    <row r="61" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B61" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C57" s="7">
-        <f t="shared" ref="C57" si="112">C34/C28</f>
+      <c r="C61" s="7">
+        <f t="shared" ref="C61" si="110">C38/C32</f>
         <v>9.3471621277678801E-2</v>
       </c>
-      <c r="D57" s="7">
-        <f t="shared" ref="D57:N57" si="113">D34/D28</f>
+      <c r="D61" s="7">
+        <f t="shared" ref="D61:N61" si="111">D38/D32</f>
         <v>8.7286992766948637E-2</v>
       </c>
-      <c r="E57" s="7">
-        <f t="shared" si="113"/>
+      <c r="E61" s="7">
+        <f t="shared" si="111"/>
         <v>7.9700312665919412E-2</v>
       </c>
-      <c r="F57" s="7">
-        <f t="shared" si="113"/>
+      <c r="F61" s="7">
+        <f t="shared" si="111"/>
         <v>7.3453821920079584E-2</v>
       </c>
-      <c r="G57" s="7">
-        <f t="shared" si="113"/>
+      <c r="G61" s="7">
+        <f t="shared" si="111"/>
         <v>8.121296619031021E-2</v>
       </c>
-      <c r="H57" s="7">
-        <f t="shared" si="113"/>
+      <c r="H61" s="7">
+        <f t="shared" si="111"/>
         <v>8.7360087360087366E-2</v>
       </c>
-      <c r="I57" s="7">
-        <f t="shared" si="113"/>
+      <c r="I61" s="7">
+        <f t="shared" si="111"/>
         <v>0.10405525846702317</v>
       </c>
-      <c r="J57" s="7">
-        <f t="shared" si="113"/>
+      <c r="J61" s="7">
+        <f t="shared" si="111"/>
         <v>7.0758267677021133E-2</v>
       </c>
-      <c r="K57" s="7">
-        <f t="shared" si="113"/>
+      <c r="K61" s="7">
+        <f t="shared" si="111"/>
         <v>7.2209272209272216E-2</v>
       </c>
-      <c r="L57" s="7">
-        <f t="shared" si="113"/>
+      <c r="L61" s="7">
+        <f t="shared" si="111"/>
         <v>7.3474975914000304E-2</v>
       </c>
-      <c r="M57" s="7">
-        <f t="shared" si="113"/>
+      <c r="M61" s="7">
+        <f t="shared" si="111"/>
         <v>6.9142316690726263E-2</v>
       </c>
-      <c r="N57" s="7">
-        <f t="shared" si="113"/>
+      <c r="N61" s="7">
+        <f t="shared" si="111"/>
         <v>7.2792859455209732E-2</v>
       </c>
-      <c r="O57" s="7">
-        <f t="shared" ref="O57" si="114">O34/O28</f>
+      <c r="O61" s="7">
+        <f t="shared" ref="O61" si="112">O38/O32</f>
         <v>7.1308972717423424E-2</v>
       </c>
-      <c r="P57" s="7">
-        <f t="shared" ref="P57" si="115">P34/P28</f>
+      <c r="P61" s="7">
+        <f t="shared" ref="P61" si="113">P38/P32</f>
         <v>7.2888188684490984E-2</v>
       </c>
-      <c r="Q57" s="7">
-        <f t="shared" ref="Q57:R57" si="116">Q34/Q28</f>
+      <c r="Q61" s="7">
+        <f t="shared" ref="Q61:R61" si="114">Q38/Q32</f>
         <v>6.3884687249755323E-2</v>
       </c>
-      <c r="R57" s="7">
+      <c r="R61" s="7">
+        <f t="shared" si="114"/>
+        <v>6.7579833319580826E-2</v>
+      </c>
+      <c r="S61" s="7"/>
+      <c r="T61" s="7"/>
+      <c r="U61" s="7"/>
+      <c r="V61" s="7"/>
+      <c r="Y61" s="7">
+        <f>Y38/Y32</f>
+        <v>8.1832013936360234E-2</v>
+      </c>
+      <c r="Z61" s="7">
+        <f>Z38/Z32</f>
+        <v>9.7902345061586585E-2</v>
+      </c>
+      <c r="AA61" s="7">
+        <f t="shared" ref="AA61:AD61" si="115">AA38/AA32</f>
+        <v>8.1133130396968373E-2</v>
+      </c>
+      <c r="AB61" s="7">
+        <f t="shared" si="115"/>
+        <v>8.308733637475027E-2</v>
+      </c>
+      <c r="AC61" s="7">
+        <f t="shared" si="115"/>
+        <v>8.4286128845037722E-2</v>
+      </c>
+      <c r="AD61" s="7">
+        <f t="shared" si="115"/>
+        <v>7.1911615348410909E-2</v>
+      </c>
+      <c r="AE61" s="7">
+        <f t="shared" ref="AE61:AO61" si="116">AE38/AE32</f>
+        <v>6.8789995824069167E-2</v>
+      </c>
+      <c r="AF61" s="7">
         <f t="shared" si="116"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="U57" s="7">
-        <f>U34/U28</f>
-        <v>8.1832013936360234E-2</v>
-      </c>
-      <c r="V57" s="7">
-        <f>V34/V28</f>
-        <v>9.7902345061586585E-2</v>
-      </c>
-      <c r="W57" s="7">
-        <f t="shared" ref="W57:Z57" si="117">W34/W28</f>
-        <v>8.1133130396968373E-2</v>
-      </c>
-      <c r="X57" s="7">
-        <f t="shared" si="117"/>
-        <v>8.308733637475027E-2</v>
-      </c>
-      <c r="Y57" s="7">
-        <f t="shared" si="117"/>
-        <v>8.4286128845037722E-2</v>
-      </c>
-      <c r="Z57" s="7">
-        <f t="shared" si="117"/>
-        <v>7.1911615348410909E-2</v>
-      </c>
-      <c r="AA57" s="7">
-        <f t="shared" ref="AA57:AK57" si="118">AA34/AA28</f>
-        <v>6.9451321540946798E-2</v>
-      </c>
-      <c r="AB57" s="7">
+      <c r="AG61" s="7">
+        <f t="shared" si="116"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AH61" s="7">
+        <f t="shared" si="116"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AI61" s="7">
+        <f t="shared" si="116"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AJ61" s="7">
+        <f t="shared" si="116"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AK61" s="7">
+        <f t="shared" si="116"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AL61" s="7">
+        <f t="shared" si="116"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AM61" s="7">
+        <f t="shared" si="116"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AN61" s="7">
+        <f t="shared" si="116"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AO61" s="7">
+        <f t="shared" si="116"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AR61" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AS61" s="9">
+        <f>AS60/AO47</f>
+        <v>70.589670975898386</v>
+      </c>
+    </row>
+    <row r="62" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C62" s="7">
+        <f t="shared" ref="C62" si="117">C39/C32</f>
+        <v>6.6938152201578005E-2</v>
+      </c>
+      <c r="D62" s="7">
+        <f t="shared" ref="D62:N62" si="118">D39/D32</f>
+        <v>8.1892852764496746E-2</v>
+      </c>
+      <c r="E62" s="7">
         <f t="shared" si="118"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AC57" s="7">
+        <v>8.6956521739130432E-2</v>
+      </c>
+      <c r="F62" s="7">
         <f t="shared" si="118"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AD57" s="7">
+        <v>8.4120930746697617E-2</v>
+      </c>
+      <c r="G62" s="7">
         <f t="shared" si="118"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AE57" s="7">
+        <v>9.0856279772278378E-2</v>
+      </c>
+      <c r="H62" s="7">
         <f t="shared" si="118"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AF57" s="7">
+        <v>8.0152880152880149E-2</v>
+      </c>
+      <c r="I62" s="7">
         <f t="shared" si="118"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AG57" s="7">
+        <v>-0.10390671420083185</v>
+      </c>
+      <c r="J62" s="7">
         <f t="shared" si="118"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AH57" s="7">
+        <v>9.243739649721483E-2</v>
+      </c>
+      <c r="K62" s="7">
         <f t="shared" si="118"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AI57" s="7">
+        <v>7.75964775964776E-2</v>
+      </c>
+      <c r="L62" s="7">
         <f t="shared" si="118"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AJ57" s="7">
+        <v>7.2257999087267377E-2</v>
+      </c>
+      <c r="M62" s="7">
         <f t="shared" si="118"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AK57" s="7">
+        <v>9.428045198865051E-2</v>
+      </c>
+      <c r="N62" s="7">
         <f t="shared" si="118"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AN57" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AO57" s="9">
-        <f>AO56/AK43</f>
-        <v>92.102581291072184</v>
-      </c>
-    </row>
-    <row r="58" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B58" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C58" s="7">
-        <f t="shared" ref="C58" si="119">C35/C28</f>
-        <v>6.6938152201578005E-2</v>
-      </c>
-      <c r="D58" s="7">
-        <f t="shared" ref="D58:N58" si="120">D35/D28</f>
-        <v>8.1892852764496746E-2</v>
-      </c>
-      <c r="E58" s="7">
-        <f t="shared" si="120"/>
-        <v>8.6956521739130432E-2</v>
-      </c>
-      <c r="F58" s="7">
-        <f t="shared" si="120"/>
-        <v>8.4120930746697617E-2</v>
-      </c>
-      <c r="G58" s="7">
-        <f t="shared" si="120"/>
-        <v>9.0856279772278378E-2</v>
-      </c>
-      <c r="H58" s="7">
-        <f t="shared" si="120"/>
-        <v>8.0152880152880149E-2</v>
-      </c>
-      <c r="I58" s="7">
-        <f t="shared" si="120"/>
-        <v>-0.10390671420083185</v>
-      </c>
-      <c r="J58" s="7">
-        <f t="shared" si="120"/>
-        <v>9.243739649721483E-2</v>
-      </c>
-      <c r="K58" s="7">
-        <f t="shared" si="120"/>
-        <v>7.75964775964776E-2</v>
-      </c>
-      <c r="L58" s="7">
-        <f t="shared" si="120"/>
-        <v>7.2257999087267377E-2</v>
-      </c>
-      <c r="M58" s="7">
-        <f t="shared" si="120"/>
-        <v>9.428045198865051E-2</v>
-      </c>
-      <c r="N58" s="7">
-        <f t="shared" si="120"/>
         <v>8.5695786893585535E-2</v>
       </c>
-      <c r="O58" s="7">
-        <f t="shared" ref="O58" si="121">O35/O28</f>
+      <c r="O62" s="7">
+        <f t="shared" ref="O62" si="119">O39/O32</f>
         <v>0.1000196986112479</v>
       </c>
-      <c r="P58" s="7">
-        <f t="shared" ref="P58" si="122">P35/P28</f>
+      <c r="P62" s="7">
+        <f t="shared" ref="P62" si="120">P39/P32</f>
         <v>9.758583939576479E-2</v>
       </c>
-      <c r="Q58" s="7">
-        <f t="shared" ref="Q58:R58" si="123">Q35/Q28</f>
+      <c r="Q62" s="7">
+        <f t="shared" ref="Q62:R62" si="121">Q39/Q32</f>
         <v>0.10944034166740814</v>
       </c>
-      <c r="R58" s="7">
+      <c r="R62" s="7">
+        <f t="shared" si="121"/>
+        <v>9.447974255301593E-2</v>
+      </c>
+      <c r="S62" s="7"/>
+      <c r="T62" s="7"/>
+      <c r="U62" s="7"/>
+      <c r="V62" s="7"/>
+      <c r="Y62" s="7">
+        <f>Y39/Y32</f>
+        <v>0.10117091887362456</v>
+      </c>
+      <c r="Z62" s="7">
+        <f>Z39/Z32</f>
+        <v>7.2278085072543163E-3</v>
+      </c>
+      <c r="AA62" s="7">
+        <f t="shared" ref="AA62:AD62" si="122">AA39/AA32</f>
+        <v>7.043237870410636E-2</v>
+      </c>
+      <c r="AB62" s="7">
+        <f t="shared" si="122"/>
+        <v>8.0269553030980711E-2</v>
+      </c>
+      <c r="AC62" s="7">
+        <f t="shared" si="122"/>
+        <v>5.0420777713290774E-2</v>
+      </c>
+      <c r="AD62" s="7">
+        <f t="shared" si="122"/>
+        <v>8.2612896034085559E-2</v>
+      </c>
+      <c r="AE62" s="7">
+        <f t="shared" ref="AE62:AO62" si="123">AE39/AE32</f>
+        <v>8.9529361308307756E-2</v>
+      </c>
+      <c r="AF62" s="7">
         <f t="shared" si="123"/>
-        <v>9.7453294605299889E-2</v>
-      </c>
-      <c r="U58" s="7">
-        <f>U35/U28</f>
-        <v>0.10117091887362456</v>
-      </c>
-      <c r="V58" s="7">
-        <f>V35/V28</f>
-        <v>7.2278085072543163E-3</v>
-      </c>
-      <c r="W58" s="7">
-        <f t="shared" ref="W58:Z58" si="124">W35/W28</f>
-        <v>7.043237870410636E-2</v>
-      </c>
-      <c r="X58" s="7">
-        <f t="shared" si="124"/>
-        <v>8.0269553030980711E-2</v>
-      </c>
-      <c r="Y58" s="7">
-        <f t="shared" si="124"/>
-        <v>5.0420777713290774E-2</v>
-      </c>
-      <c r="Z58" s="7">
-        <f t="shared" si="124"/>
-        <v>8.2612896034085559E-2</v>
-      </c>
-      <c r="AA58" s="7">
-        <f t="shared" ref="AA58:AK58" si="125">AA35/AA28</f>
-        <v>0.10111964987646541</v>
-      </c>
-      <c r="AB58" s="7">
+        <v>8.9813727078962943E-2</v>
+      </c>
+      <c r="AG62" s="7">
+        <f t="shared" si="123"/>
+        <v>9.0676192019563992E-2</v>
+      </c>
+      <c r="AH62" s="7">
+        <f t="shared" si="123"/>
+        <v>9.1240111403803129E-2</v>
+      </c>
+      <c r="AI62" s="7">
+        <f t="shared" si="123"/>
+        <v>9.1793186184499262E-2</v>
+      </c>
+      <c r="AJ62" s="7">
+        <f t="shared" si="123"/>
+        <v>9.2340891307130385E-2</v>
+      </c>
+      <c r="AK62" s="7">
+        <f t="shared" si="123"/>
+        <v>9.2877961378836554E-2</v>
+      </c>
+      <c r="AL62" s="7">
+        <f t="shared" si="123"/>
+        <v>9.3143863718259751E-2</v>
+      </c>
+      <c r="AM62" s="7">
+        <f t="shared" si="123"/>
+        <v>9.3407159172002263E-2</v>
+      </c>
+      <c r="AN62" s="7">
+        <f t="shared" si="123"/>
+        <v>9.3667873297766879E-2</v>
+      </c>
+      <c r="AO62" s="7">
+        <f t="shared" si="123"/>
+        <v>9.3926031402690777E-2</v>
+      </c>
+      <c r="AR62" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS62" s="9">
+        <f>Main!D3</f>
+        <v>200.93</v>
+      </c>
+    </row>
+    <row r="63" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C63" s="7">
+        <f t="shared" ref="C63" si="124">C44/C43</f>
+        <v>9.3397745571658614E-2</v>
+      </c>
+      <c r="D63" s="7">
+        <f t="shared" ref="D63:N63" si="125">D44/D43</f>
+        <v>0.1068090787716956</v>
+      </c>
+      <c r="E63" s="7">
         <f t="shared" si="125"/>
-        <v>0.10347341893985634</v>
-      </c>
-      <c r="AC58" s="7">
+        <v>0.16815742397137745</v>
+      </c>
+      <c r="F63" s="7">
         <f t="shared" si="125"/>
-        <v>0.10577007894352752</v>
-      </c>
-      <c r="AD58" s="7">
+        <v>0.13647058823529412</v>
+      </c>
+      <c r="G63" s="7">
         <f t="shared" si="125"/>
-        <v>0.10668752303335197</v>
-      </c>
-      <c r="AE58" s="7">
+        <v>0.16844469399213924</v>
+      </c>
+      <c r="H63" s="7">
         <f t="shared" si="125"/>
-        <v>0.10733500548398156</v>
-      </c>
-      <c r="AF58" s="7">
+        <v>0.15432482887367766</v>
+      </c>
+      <c r="I63" s="7">
         <f t="shared" si="125"/>
-        <v>0.10798617128769103</v>
-      </c>
-      <c r="AG58" s="7">
+        <v>0.29425113464447805</v>
+      </c>
+      <c r="J63" s="7">
         <f t="shared" si="125"/>
-        <v>0.10863469483828012</v>
-      </c>
-      <c r="AH58" s="7">
+        <v>0.16779661016949152</v>
+      </c>
+      <c r="K63" s="7">
         <f t="shared" si="125"/>
-        <v>0.10928060586836875</v>
-      </c>
-      <c r="AI58" s="7">
+        <v>5.834683954619125E-2</v>
+      </c>
+      <c r="L63" s="7">
         <f t="shared" si="125"/>
-        <v>0.10992393359803992</v>
-      </c>
-      <c r="AJ58" s="7">
+        <v>0.59112149532710279</v>
+      </c>
+      <c r="M63" s="7">
         <f t="shared" si="125"/>
-        <v>0.11056470673835882</v>
-      </c>
-      <c r="AK58" s="7">
+        <v>0.19464847848898217</v>
+      </c>
+      <c r="N63" s="7">
         <f t="shared" si="125"/>
-        <v>0.11120295349490207</v>
-      </c>
-      <c r="AN58" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AO58" s="9">
-        <f>Main!D3</f>
-        <v>178.65</v>
-      </c>
-    </row>
-    <row r="59" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B59" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C59" s="7">
-        <f t="shared" ref="C59" si="126">C40/C39</f>
-        <v>9.3397745571658614E-2</v>
-      </c>
-      <c r="D59" s="7">
-        <f t="shared" ref="D59:N59" si="127">D40/D39</f>
-        <v>0.1068090787716956</v>
-      </c>
-      <c r="E59" s="7">
-        <f t="shared" si="127"/>
-        <v>0.16815742397137745</v>
-      </c>
-      <c r="F59" s="7">
-        <f t="shared" si="127"/>
-        <v>0.13647058823529412</v>
-      </c>
-      <c r="G59" s="7">
-        <f t="shared" si="127"/>
-        <v>0.16844469399213924</v>
-      </c>
-      <c r="H59" s="7">
-        <f t="shared" si="127"/>
-        <v>0.15432482887367766</v>
-      </c>
-      <c r="I59" s="7">
-        <f t="shared" si="127"/>
-        <v>0.29425113464447805</v>
-      </c>
-      <c r="J59" s="7">
-        <f t="shared" si="127"/>
-        <v>0.16779661016949152</v>
-      </c>
-      <c r="K59" s="7">
-        <f t="shared" si="127"/>
-        <v>5.834683954619125E-2</v>
-      </c>
-      <c r="L59" s="7">
-        <f t="shared" si="127"/>
-        <v>0.59112149532710279</v>
-      </c>
-      <c r="M59" s="7">
-        <f t="shared" si="127"/>
-        <v>0.19464847848898217</v>
-      </c>
-      <c r="N59" s="7">
-        <f t="shared" si="127"/>
         <v>0.22349427575908412</v>
       </c>
-      <c r="O59" s="7">
-        <f t="shared" ref="O59" si="128">O40/O39</f>
+      <c r="O63" s="7">
+        <f t="shared" ref="O63" si="126">O44/O43</f>
         <v>0.17007150153217568</v>
       </c>
-      <c r="P59" s="7">
-        <f t="shared" ref="P59" si="129">P40/P39</f>
+      <c r="P63" s="7">
+        <f t="shared" ref="P63" si="127">P44/P43</f>
         <v>0.15441176470588236</v>
       </c>
-      <c r="Q59" s="7">
-        <f t="shared" ref="Q59:R59" si="130">Q40/Q39</f>
+      <c r="Q63" s="7">
+        <f t="shared" ref="Q63:R63" si="128">Q44/Q43</f>
         <v>0.17719442165709598</v>
       </c>
-      <c r="R59" s="7">
+      <c r="R63" s="7">
+        <f t="shared" si="128"/>
+        <v>0.25424466695690029</v>
+      </c>
+      <c r="S63" s="7"/>
+      <c r="T63" s="7"/>
+      <c r="U63" s="7"/>
+      <c r="V63" s="7"/>
+      <c r="Y63" s="7">
+        <f>Y44/Y43</f>
+        <v>0.10139691714836223</v>
+      </c>
+      <c r="Z63" s="7">
+        <f>Z44/Z43</f>
+        <v>-0.24436889077773055</v>
+      </c>
+      <c r="AA63" s="7">
+        <f t="shared" ref="AA63:AD63" si="129">AA44/AA43</f>
+        <v>0.15939971608193065</v>
+      </c>
+      <c r="AB63" s="7">
+        <f t="shared" si="129"/>
+        <v>0.12914827529834885</v>
+      </c>
+      <c r="AC63" s="7">
+        <f t="shared" si="129"/>
+        <v>0.11887382690302398</v>
+      </c>
+      <c r="AD63" s="7">
+        <f t="shared" si="129"/>
+        <v>0.19066838876331935</v>
+      </c>
+      <c r="AE63" s="7">
+        <f t="shared" ref="AE63:AO63" si="130">AE44/AE43</f>
+        <v>0.21392106775409897</v>
+      </c>
+      <c r="AF63" s="7">
         <f t="shared" si="130"/>
-        <v>0.17</v>
-      </c>
-      <c r="U59" s="7">
-        <f>U40/U39</f>
-        <v>0.10139691714836223</v>
-      </c>
-      <c r="V59" s="7">
-        <f>V40/V39</f>
-        <v>-0.24436889077773055</v>
-      </c>
-      <c r="W59" s="7">
-        <f t="shared" ref="W59:Z59" si="131">W40/W39</f>
-        <v>0.15939971608193065</v>
-      </c>
-      <c r="X59" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="AG63" s="7">
+        <f t="shared" si="130"/>
+        <v>0.15</v>
+      </c>
+      <c r="AH63" s="7">
+        <f t="shared" si="130"/>
+        <v>0.15</v>
+      </c>
+      <c r="AI63" s="7">
+        <f t="shared" si="130"/>
+        <v>0.15</v>
+      </c>
+      <c r="AJ63" s="7">
+        <f t="shared" si="130"/>
+        <v>0.15</v>
+      </c>
+      <c r="AK63" s="7">
+        <f t="shared" si="130"/>
+        <v>0.15</v>
+      </c>
+      <c r="AL63" s="7">
+        <f t="shared" si="130"/>
+        <v>0.15</v>
+      </c>
+      <c r="AM63" s="7">
+        <f t="shared" si="130"/>
+        <v>0.15</v>
+      </c>
+      <c r="AN63" s="7">
+        <f t="shared" si="130"/>
+        <v>0.15</v>
+      </c>
+      <c r="AO63" s="7">
+        <f t="shared" si="130"/>
+        <v>0.15</v>
+      </c>
+      <c r="AR63" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AS63" s="12">
+        <f>AS61/AS62-1</f>
+        <v>-0.64868525866770321</v>
+      </c>
+    </row>
+    <row r="64" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64" s="7">
+        <f t="shared" ref="C64:O64" si="131">C45/C43</f>
+        <v>1.8518518518518517E-2</v>
+      </c>
+      <c r="D64" s="7">
         <f t="shared" si="131"/>
-        <v>0.12914827529834885</v>
-      </c>
-      <c r="Y59" s="7">
+        <v>2.2696929238985315E-2</v>
+      </c>
+      <c r="E64" s="7">
         <f t="shared" si="131"/>
-        <v>0.11887382690302398</v>
-      </c>
-      <c r="Z59" s="7">
+        <v>4.7704233750745376E-3</v>
+      </c>
+      <c r="F64" s="7">
         <f t="shared" si="131"/>
-        <v>0.19066838876331935</v>
-      </c>
-      <c r="AA59" s="7">
-        <f t="shared" ref="AA59:AK59" si="132">AA40/AA39</f>
-        <v>0.16837394378032691</v>
-      </c>
-      <c r="AB59" s="7">
+        <v>2.7058823529411764E-2</v>
+      </c>
+      <c r="G64" s="7">
+        <f t="shared" si="131"/>
+        <v>3.0881527231892195E-2</v>
+      </c>
+      <c r="H64" s="7">
+        <f t="shared" si="131"/>
+        <v>1.9912881144990666E-2</v>
+      </c>
+      <c r="I64" s="7">
+        <f t="shared" si="131"/>
+        <v>-3.8577912254160365E-2</v>
+      </c>
+      <c r="J64" s="7">
+        <f t="shared" si="131"/>
+        <v>2.655367231638418E-2</v>
+      </c>
+      <c r="K64" s="7">
+        <f t="shared" si="131"/>
+        <v>1.8368449486763912E-2</v>
+      </c>
+      <c r="L64" s="7">
+        <f t="shared" si="131"/>
+        <v>0.14953271028037382</v>
+      </c>
+      <c r="M64" s="7">
+        <f t="shared" si="131"/>
+        <v>3.3053515215110178E-2</v>
+      </c>
+      <c r="N64" s="7">
+        <f t="shared" si="131"/>
+        <v>3.8825286212045791E-2</v>
+      </c>
+      <c r="O64" s="7">
+        <f t="shared" si="131"/>
+        <v>4.5965270684371805E-2</v>
+      </c>
+      <c r="P64" s="7">
+        <f>P45/P43</f>
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="Q64" s="7">
+        <f t="shared" ref="Q64:R64" si="132">Q45/Q43</f>
+        <v>3.6095159967186222E-2</v>
+      </c>
+      <c r="R64" s="7">
         <f t="shared" si="132"/>
-        <v>0.15</v>
-      </c>
-      <c r="AC59" s="7">
-        <f t="shared" si="132"/>
-        <v>0.15</v>
-      </c>
-      <c r="AD59" s="7">
-        <f t="shared" si="132"/>
-        <v>0.15</v>
-      </c>
-      <c r="AE59" s="7">
-        <f t="shared" si="132"/>
-        <v>0.15</v>
-      </c>
-      <c r="AF59" s="7">
-        <f t="shared" si="132"/>
-        <v>0.15</v>
-      </c>
-      <c r="AG59" s="7">
-        <f t="shared" si="132"/>
-        <v>0.15</v>
-      </c>
-      <c r="AH59" s="7">
-        <f t="shared" si="132"/>
-        <v>0.15</v>
-      </c>
-      <c r="AI59" s="7">
-        <f t="shared" si="132"/>
-        <v>0.15</v>
-      </c>
-      <c r="AJ59" s="7">
-        <f t="shared" si="132"/>
-        <v>0.15</v>
-      </c>
-      <c r="AK59" s="7">
-        <f t="shared" si="132"/>
-        <v>0.14999999999999997</v>
-      </c>
-      <c r="AN59" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="AO59" s="12">
-        <f>AO57/AO58-1</f>
-        <v>-0.48445238572027882</v>
-      </c>
-    </row>
-    <row r="60" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B60" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C60" s="7">
-        <f t="shared" ref="C60:O60" si="133">C41/C39</f>
-        <v>1.8518518518518517E-2</v>
-      </c>
-      <c r="D60" s="7">
+        <v>3.9616891597736174E-2</v>
+      </c>
+      <c r="S64" s="7"/>
+      <c r="T64" s="7"/>
+      <c r="U64" s="7"/>
+      <c r="V64" s="7"/>
+      <c r="Y64" s="7">
+        <f t="shared" ref="Y64:AC64" si="133">Y45/Y43</f>
+        <v>5.3227360308285163E-2</v>
+      </c>
+      <c r="Z64" s="7">
         <f t="shared" si="133"/>
-        <v>2.2696929238985315E-2</v>
-      </c>
-      <c r="E60" s="7">
+        <v>-7.6923076923076927E-2</v>
+      </c>
+      <c r="AA64" s="7">
         <f t="shared" si="133"/>
-        <v>4.7704233750745376E-3</v>
-      </c>
-      <c r="F60" s="7">
+        <v>5.0294058000405595E-2</v>
+      </c>
+      <c r="AB64" s="7">
         <f t="shared" si="133"/>
-        <v>2.7058823529411764E-2</v>
-      </c>
-      <c r="G60" s="7">
+        <v>1.8146150073565473E-2</v>
+      </c>
+      <c r="AC64" s="7">
         <f t="shared" si="133"/>
-        <v>3.0881527231892195E-2</v>
-      </c>
-      <c r="H60" s="7">
-        <f t="shared" si="133"/>
-        <v>1.9912881144990666E-2</v>
-      </c>
-      <c r="I60" s="7">
-        <f t="shared" si="133"/>
-        <v>-3.8577912254160365E-2</v>
-      </c>
-      <c r="J60" s="7">
-        <f t="shared" si="133"/>
-        <v>2.655367231638418E-2</v>
-      </c>
-      <c r="K60" s="7">
-        <f t="shared" si="133"/>
-        <v>1.8368449486763912E-2</v>
-      </c>
-      <c r="L60" s="7">
-        <f t="shared" si="133"/>
-        <v>0.14953271028037382</v>
-      </c>
-      <c r="M60" s="7">
-        <f t="shared" si="133"/>
-        <v>3.3053515215110178E-2</v>
-      </c>
-      <c r="N60" s="7">
-        <f t="shared" si="133"/>
-        <v>3.8825286212045791E-2</v>
-      </c>
-      <c r="O60" s="7">
-        <f t="shared" si="133"/>
-        <v>4.5965270684371805E-2</v>
-      </c>
-      <c r="P60" s="7">
-        <f>P41/P39</f>
-        <v>3.3333333333333333E-2</v>
-      </c>
-      <c r="Q60" s="7">
-        <f t="shared" ref="Q60:R60" si="134">Q41/Q39</f>
-        <v>3.6095159967186222E-2</v>
-      </c>
-      <c r="R60" s="7">
+        <v>4.8227320125130341E-2</v>
+      </c>
+      <c r="AD64" s="7">
+        <f>AD45/AD43</f>
+        <v>3.8585728123990956E-2</v>
+      </c>
+      <c r="AE64" s="7">
+        <f t="shared" ref="AE64:AO64" si="134">AE45/AE43</f>
+        <v>4.3324158553564515E-2</v>
+      </c>
+      <c r="AF64" s="7">
         <f t="shared" si="134"/>
         <v>0.03</v>
       </c>
-      <c r="U60" s="7">
-        <f t="shared" ref="U60:Y60" si="135">U41/U39</f>
-        <v>5.3227360308285163E-2</v>
-      </c>
-      <c r="V60" s="7">
-        <f t="shared" si="135"/>
-        <v>-7.6923076923076927E-2</v>
-      </c>
-      <c r="W60" s="7">
-        <f t="shared" si="135"/>
-        <v>5.0294058000405595E-2</v>
-      </c>
-      <c r="X60" s="7">
-        <f t="shared" si="135"/>
-        <v>1.8146150073565473E-2</v>
-      </c>
-      <c r="Y60" s="7">
-        <f t="shared" si="135"/>
-        <v>4.8227320125130341E-2</v>
-      </c>
-      <c r="Z60" s="7">
-        <f>Z41/Z39</f>
-        <v>3.8585728123990956E-2</v>
-      </c>
-      <c r="AA60" s="7">
-        <f t="shared" ref="AA60:AK60" si="136">AA41/AA39</f>
-        <v>3.6094256030106277E-2</v>
-      </c>
-      <c r="AB60" s="7">
+      <c r="AG64" s="7">
+        <f t="shared" si="134"/>
+        <v>0.03</v>
+      </c>
+      <c r="AH64" s="7">
+        <f t="shared" si="134"/>
+        <v>0.03</v>
+      </c>
+      <c r="AI64" s="7">
+        <f t="shared" si="134"/>
+        <v>2.9999999999999995E-2</v>
+      </c>
+      <c r="AJ64" s="7">
+        <f t="shared" si="134"/>
+        <v>0.03</v>
+      </c>
+      <c r="AK64" s="7">
+        <f t="shared" si="134"/>
+        <v>0.03</v>
+      </c>
+      <c r="AL64" s="7">
+        <f t="shared" si="134"/>
+        <v>0.03</v>
+      </c>
+      <c r="AM64" s="7">
+        <f t="shared" si="134"/>
+        <v>0.03</v>
+      </c>
+      <c r="AN64" s="7">
+        <f t="shared" si="134"/>
+        <v>0.03</v>
+      </c>
+      <c r="AO64" s="7">
+        <f t="shared" si="134"/>
+        <v>3.0000000000000002E-2</v>
+      </c>
+      <c r="AR64" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AS64" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="65" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C65" s="7">
+        <f t="shared" ref="C65" si="135">C46/C32</f>
+        <v>7.0183252736065155E-2</v>
+      </c>
+      <c r="D65" s="7">
+        <f t="shared" ref="D65:N65" si="136">D46/D32</f>
+        <v>7.9931347309059708E-2</v>
+      </c>
+      <c r="E65" s="7">
         <f t="shared" si="136"/>
-        <v>0.03</v>
-      </c>
-      <c r="AC60" s="7">
+        <v>8.1824081175151914E-2</v>
+      </c>
+      <c r="F65" s="7">
         <f t="shared" si="136"/>
-        <v>3.0000000000000002E-2</v>
-      </c>
-      <c r="AD60" s="7">
+        <v>7.8593931354667551E-2</v>
+      </c>
+      <c r="G65" s="7">
         <f t="shared" si="136"/>
-        <v>3.0000000000000002E-2</v>
-      </c>
-      <c r="AE60" s="7">
+        <v>8.2839549204136165E-2</v>
+      </c>
+      <c r="H65" s="7">
         <f t="shared" si="136"/>
-        <v>3.0000000000000002E-2</v>
-      </c>
-      <c r="AF60" s="7">
+        <v>7.2454272454272453E-2</v>
+      </c>
+      <c r="I65" s="7">
         <f t="shared" si="136"/>
-        <v>0.03</v>
-      </c>
-      <c r="AG60" s="7">
+        <v>-7.3083778966131913E-2</v>
+      </c>
+      <c r="J65" s="7">
         <f t="shared" si="136"/>
-        <v>0.03</v>
-      </c>
-      <c r="AH60" s="7">
+        <v>7.1561198374065341E-2</v>
+      </c>
+      <c r="K65" s="7">
         <f t="shared" si="136"/>
-        <v>0.03</v>
-      </c>
-      <c r="AI60" s="7">
+        <v>8.8526288526288521E-2</v>
+      </c>
+      <c r="L65" s="7">
         <f t="shared" si="136"/>
-        <v>0.03</v>
-      </c>
-      <c r="AJ60" s="7">
+        <v>5.6285178236397749E-3</v>
+      </c>
+      <c r="M65" s="7">
         <f t="shared" si="136"/>
-        <v>0.03</v>
-      </c>
-      <c r="AK60" s="7">
+        <v>7.3273931007018761E-2</v>
+      </c>
+      <c r="N65" s="7">
         <f t="shared" si="136"/>
-        <v>2.9999999999999995E-2</v>
-      </c>
-      <c r="AN60" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AO60" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="61" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B61" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C61" s="7">
-        <f t="shared" ref="C61" si="137">C42/C28</f>
-        <v>7.0183252736065155E-2</v>
-      </c>
-      <c r="D61" s="7">
-        <f t="shared" ref="D61:N61" si="138">D42/D28</f>
-        <v>7.9931347309059708E-2</v>
-      </c>
-      <c r="E61" s="7">
-        <f t="shared" si="138"/>
-        <v>8.1824081175151914E-2</v>
-      </c>
-      <c r="F61" s="7">
-        <f t="shared" si="138"/>
-        <v>7.8593931354667551E-2</v>
-      </c>
-      <c r="G61" s="7">
-        <f t="shared" si="138"/>
-        <v>8.2839549204136165E-2</v>
-      </c>
-      <c r="H61" s="7">
-        <f t="shared" si="138"/>
-        <v>7.2454272454272453E-2</v>
-      </c>
-      <c r="I61" s="7">
-        <f t="shared" si="138"/>
-        <v>-7.3083778966131913E-2</v>
-      </c>
-      <c r="J61" s="7">
-        <f t="shared" si="138"/>
-        <v>7.1561198374065341E-2</v>
-      </c>
-      <c r="K61" s="7">
-        <f t="shared" si="138"/>
-        <v>8.8526288526288521E-2</v>
-      </c>
-      <c r="L61" s="7">
-        <f t="shared" si="138"/>
-        <v>5.6285178236397749E-3</v>
-      </c>
-      <c r="M61" s="7">
-        <f t="shared" si="138"/>
-        <v>7.3273931007018761E-2</v>
-      </c>
-      <c r="N61" s="7">
-        <f t="shared" si="138"/>
         <v>6.8538130694168253E-2</v>
       </c>
-      <c r="O61" s="7">
-        <f t="shared" ref="O61" si="139">O42/O28</f>
+      <c r="O65" s="7">
+        <f t="shared" ref="O65" si="137">O46/O32</f>
         <v>7.5593420663843197E-2</v>
       </c>
-      <c r="P61" s="7">
-        <f t="shared" ref="P61" si="140">P42/P28</f>
+      <c r="P65" s="7">
+        <f t="shared" ref="P65" si="138">P46/P32</f>
         <v>7.6780501366943144E-2</v>
       </c>
-      <c r="Q61" s="7">
-        <f t="shared" ref="Q61:R61" si="141">Q42/Q28</f>
+      <c r="Q65" s="7">
+        <f t="shared" ref="Q65:R65" si="139">Q46/Q32</f>
         <v>8.5327876145564557E-2</v>
       </c>
-      <c r="R61" s="7">
+      <c r="R65" s="7">
+        <f t="shared" si="139"/>
+        <v>6.6919712847594681E-2</v>
+      </c>
+      <c r="S65" s="7"/>
+      <c r="T65" s="7"/>
+      <c r="U65" s="7"/>
+      <c r="V65" s="7"/>
+      <c r="Y65" s="7">
+        <f>Y46/Y32</f>
+        <v>7.7399722154843545E-2</v>
+      </c>
+      <c r="Z65" s="7">
+        <f>Z46/Z32</f>
+        <v>-5.4941947797197237E-2</v>
+      </c>
+      <c r="AA65" s="7">
+        <f t="shared" ref="AA65:AD65" si="140">AA46/AA32</f>
+        <v>6.0523700068335712E-2</v>
+      </c>
+      <c r="AB65" s="7">
+        <f t="shared" si="140"/>
+        <v>7.7764856725407755E-2</v>
+      </c>
+      <c r="AC65" s="7">
+        <f t="shared" si="140"/>
+        <v>4.6358096343586765E-2</v>
+      </c>
+      <c r="AD65" s="7">
+        <f t="shared" si="140"/>
+        <v>5.9129530084966186E-2</v>
+      </c>
+      <c r="AE65" s="7">
+        <f t="shared" ref="AE65:AO65" si="141">AE46/AE32</f>
+        <v>6.5207385754432606E-2</v>
+      </c>
+      <c r="AF65" s="7">
         <f t="shared" si="141"/>
-        <v>7.454576842614985E-2</v>
-      </c>
-      <c r="U61" s="7">
-        <f>U42/U28</f>
-        <v>7.7399722154843545E-2</v>
-      </c>
-      <c r="V61" s="7">
-        <f>V42/V28</f>
-        <v>-5.4941947797197237E-2</v>
-      </c>
-      <c r="W61" s="7">
-        <f t="shared" ref="W61:Z61" si="142">W42/W28</f>
-        <v>6.0523700068335712E-2</v>
-      </c>
-      <c r="X61" s="7">
-        <f t="shared" si="142"/>
-        <v>7.7764856725407755E-2</v>
-      </c>
-      <c r="Y61" s="7">
-        <f t="shared" si="142"/>
-        <v>4.6358096343586765E-2</v>
-      </c>
-      <c r="Z61" s="7">
-        <f t="shared" si="142"/>
-        <v>5.9129530084966186E-2</v>
-      </c>
-      <c r="AA61" s="7">
-        <f t="shared" ref="AA61:AK61" si="143">AA42/AA28</f>
-        <v>7.8070212308615175E-2</v>
-      </c>
-      <c r="AB61" s="7">
-        <f t="shared" si="143"/>
-        <v>8.1673376610589071E-2</v>
-      </c>
-      <c r="AC61" s="7">
-        <f t="shared" si="143"/>
-        <v>8.3710418220757102E-2</v>
-      </c>
-      <c r="AD61" s="7">
-        <f t="shared" si="143"/>
-        <v>8.4558110024793368E-2</v>
-      </c>
-      <c r="AE61" s="7">
-        <f t="shared" si="143"/>
-        <v>8.515404690787369E-2</v>
-      </c>
-      <c r="AF61" s="7">
-        <f t="shared" si="143"/>
-        <v>8.5724272072592325E-2</v>
-      </c>
-      <c r="AG61" s="7">
-        <f t="shared" si="143"/>
-        <v>8.6291926381052542E-2</v>
-      </c>
-      <c r="AH61" s="7">
-        <f t="shared" si="143"/>
-        <v>8.6857038139489098E-2</v>
-      </c>
-      <c r="AI61" s="7">
-        <f t="shared" si="143"/>
-        <v>8.7419635198217313E-2</v>
-      </c>
-      <c r="AJ61" s="7">
-        <f t="shared" si="143"/>
-        <v>8.797974495488628E-2</v>
-      </c>
-      <c r="AK61" s="7">
-        <f t="shared" si="143"/>
-        <v>8.8537394357735819E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="2:41" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="14" t="s">
+        <v>6.864732541319031E-2</v>
+      </c>
+      <c r="AG65" s="7">
+        <f t="shared" si="141"/>
+        <v>6.9545020218447343E-2</v>
+      </c>
+      <c r="AH65" s="7">
+        <f t="shared" si="141"/>
+        <v>7.0146168456915597E-2</v>
+      </c>
+      <c r="AI65" s="7">
+        <f t="shared" si="141"/>
+        <v>7.0734422168265365E-2</v>
+      </c>
+      <c r="AJ65" s="7">
+        <f t="shared" si="141"/>
+        <v>7.12716178543185E-2</v>
+      </c>
+      <c r="AK65" s="7">
+        <f t="shared" si="141"/>
+        <v>7.1798382556176363E-2</v>
+      </c>
+      <c r="AL65" s="7">
+        <f t="shared" si="141"/>
+        <v>7.2059182727194263E-2</v>
+      </c>
+      <c r="AM65" s="7">
+        <f t="shared" si="141"/>
+        <v>7.2317426033790363E-2</v>
+      </c>
+      <c r="AN65" s="7">
+        <f t="shared" si="141"/>
+        <v>7.2573137543262944E-2</v>
+      </c>
+      <c r="AO65" s="7">
+        <f t="shared" si="141"/>
+        <v>7.2826342077152564E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="2:41" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="N64" s="14">
+      <c r="N68" s="14">
         <v>162861</v>
       </c>
-      <c r="P64" s="14">
+      <c r="P68" s="35">
         <v>167139</v>
       </c>
-      <c r="Q64" s="14">
+      <c r="Q68" s="35">
         <v>168672</v>
       </c>
-      <c r="AA64" s="14">
-        <v>168672</v>
-      </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B66" s="1" t="s">
+      <c r="R68" s="35">
+        <f>171079</f>
+        <v>171079</v>
+      </c>
+      <c r="AE68" s="35">
+        <f>171079</f>
+        <v>171079</v>
+      </c>
+      <c r="AF68" s="35"/>
+    </row>
+    <row r="70" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B70" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="P66" s="15"/>
-      <c r="Q66" s="15">
-        <f>Main!$D$9/Model!Q64</f>
-        <v>1.6187500889299944</v>
-      </c>
-      <c r="AA66" s="15">
-        <f>Main!$D$9/Model!AA64</f>
-        <v>1.6187500889299944</v>
-      </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B67" s="1" t="s">
+      <c r="P70" s="15"/>
+      <c r="Q70" s="15"/>
+      <c r="R70" s="15">
+        <f>Main!$D$9/Model!R68</f>
+        <v>1.7576660899350596</v>
+      </c>
+      <c r="AE70" s="15">
+        <f>Main!$D$9/Model!AE68</f>
+        <v>1.7576660899350596</v>
+      </c>
+      <c r="AF70" s="15"/>
+    </row>
+    <row r="71" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B71" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="P67" s="7"/>
-      <c r="Q67" s="7">
-        <f>Q64/Main!$D$9-1</f>
-        <v>-0.38223941617757229</v>
-      </c>
-      <c r="AA67" s="7">
-        <f>AA64/Main!$D$9-1</f>
-        <v>-0.38223941617757229</v>
-      </c>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="P68" s="7"/>
+      <c r="P71" s="7"/>
+      <c r="Q71" s="7"/>
+      <c r="R71" s="7">
+        <f>R68/Main!$D$9-1</f>
+        <v>-0.43106372380606883</v>
+      </c>
+      <c r="AE71" s="7">
+        <f>AE68/Main!$D$9-1</f>
+        <v>-0.43106372380606883</v>
+      </c>
+      <c r="AF71" s="7"/>
+    </row>
+    <row r="72" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="P72" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -25289,7 +25762,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF47B37D-5C25-469B-9D0C-C2E6A30B3F3A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="8.88671875" style="13"/>
   </cols>
@@ -25302,7 +25775,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{292D4505-608F-421A-97B1-56F07D46F9CD}">
   <dimension ref="B2:L9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="13"/>
     <col min="2" max="2" width="10.77734375" style="23" bestFit="1" customWidth="1"/>
@@ -25391,7 +25864,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{015A9873-A383-4395-9D61-A91E52DD2221}">
   <dimension ref="B3:F198"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="13"/>
     <col min="2" max="2" width="23.77734375" style="13" bestFit="1" customWidth="1"/>
